--- a/patchnote_TC.xlsx
+++ b/patchnote_TC.xlsx
@@ -502,7 +502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F141"/>
+  <dimension ref="A1:F150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -548,21 +548,318 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>TC-11.1a-001</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>[실험체] 레니 - 곰돌이! 공격(P) 피해량 수치 확인</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>· 11.1a 패치 적용 완료
+· 레니 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 레니 선택
+3. 곰돌이! 공격(P) 스킬 레벨 최대화 후 스킬 정보창 확인
+4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>곰돌이! 공격(P) 피해량: 15/25/35(+레니 레벨 *4)
+(변경 전: 20/30/40(+레니 레벨 *5))</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr"/>
+    </row>
+    <row r="3" ht="60" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>TC-11.1a-002</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>[실험체] 코렐라인 - 인과의 이면(P) 피해량 수치 확인</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>· 11.1a 패치 적용 완료
+· 코렐라인 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 코렐라인 선택
+3. 인과의 이면(P) 스킬 레벨 최대화 후 스킬 정보창 확인
+4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>인과의 이면(P) 피해량: 20/40/60/80/100(+스킬 증폭의 12%)
+(변경 전: 20/40/60/80/100(+스킬 증폭의 15%))</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>TC-11.1-001</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>[실험체] 레니 - 뿅! 망치(W) 이동 속도 증가 수치 확인</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>· 11.1 패치 적용 완료
+· 레니 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 레니 선택
+3. 뿅! 망치(W) 스킬 레벨 최대화 후 스킬 정보창 확인
+4. 이동 속도 증가 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>뿅! 망치(W) 이동 속도 증가: 11/12/13/14/15(+레벨*1)%
+(변경 전: 16/17/18/19/20(+레벨*1)%)</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr"/>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>TC-11.1-002</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>[실험체] 미르카 - 백스탭 러시(E) 받는 피해 감소 수치 확인</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>· 11.1 패치 적용 완료
+· 미르카 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 미르카 선택
+3. 백스탭 러시(E) 스킬 레벨 최대화 후 스킬 정보창 확인
+4. 받는 피해 감소 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>백스탭 러시(E) 받는 피해 감소: 60%
+(변경 전: 80%)</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>TC-11.1-003</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>[실험체] 아드리아나 - 방화(Q) 피해량 수치 확인</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>· 11.1 패치 적용 완료
+· 아드리아나 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 아드리아나 선택
+3. 방화(Q) 스킬 레벨 최대화 후 스킬 정보창 확인
+4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>방화(Q) 피해량: 35/45/55/65/75(+스킬 증폭의 25/27/29/31/33%)
+(변경 전: 30/40/50/60/70(+스킬 증폭의 25/27/29/31/33%))</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr"/>
+    </row>
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>TC-11.1-004</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>[실험체] 자히르 - 간디바(W) 피해량 수치 확인</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>· 11.1 패치 적용 완료
+· 자히르 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 자히르 선택
+3. 간디바(W) 스킬 레벨 최대화 후 스킬 정보창 확인
+4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>간디바(W) 피해량: 70/95/120/145/170(+스킬 증폭의 50%)
+(변경 전: 60/85/110/135/160(+스킬 증폭의 50%))</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>TC-11.1-005</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>[실험체] 레온 - 톤파 무기 숙련도 레벨 당 스킬 증폭 수치 확인</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>· 11.1 패치 적용 완료
+· 레온 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 레온 선택
+3. 캐릭터 정보창(스탯창)에서 톤파 무기 숙련도 레벨 당 스킬 증폭 확인
+4. 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>톤파 무기 숙련도 레벨 당 스킬 증폭: 4.8%
+(변경 전: 5%)</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>TC-11.1-006</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>[실험체] 로지 - 기본 공격력 수치 확인</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>· 11.1 패치 적용 완료
+· 로지 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 로지 선택
+3. 캐릭터 정보창(스탯창)에서 기본 공격력 확인
+4. 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>기본 공격력: 32
+(변경 전: 35)</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>TC-11.1-007</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>[실험체] 현우 - 글러브 무기 숙련도 레벨 당 기본 공격 증폭 수치 확인</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>· 11.1 패치 적용 완료
+· 현우 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 현우 선택
+3. 캐릭터 정보창(스탯창)에서 글러브 무기 숙련도 레벨 당 기본 공격 증폭 확인
+4. 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>글러브 무기 숙련도 레벨 당 기본 공격 증폭: 2.2%
+(변경 전: 2.3%)</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
           <t>TC-11.0-001</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>[실험체] 블레어 - 블레이드 시프트(P) 체력 회복량 입힌 피해의 수치 확인</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>· 11.0 패치 적용 완료
 · 블레어 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 블레어 선택
@@ -570,32 +867,32 @@
 4. 체력 회복량 입힌 피해의 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>블레이드 시프트(P) 체력 회복량 입힌 피해의: 8(+추가 공격력의 5%)%
 (변경 전: 8(+추가 공격력의 4%)%)</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr"/>
-    </row>
-    <row r="3" ht="60" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>TC-11.0-002</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>[실험체] 블레어 - 기본 체력 수치 확인</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>· 11.0 패치 적용 완료
 · 블레어 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 블레어 선택
@@ -603,32 +900,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>기본 체력: 970
 (변경 전: 940)</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr"/>
-    </row>
-    <row r="4" ht="60" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>TC-11.0-003</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>[실험체] 히스이 - 기본 체력 수치 확인</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>· 11.0 패치 적용 완료
 · 히스이 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 히스이 선택
@@ -636,32 +933,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>기본 체력: 980
 (변경 전: 940)</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr"/>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>TC-11.0-004</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>[실험체] 히스이 - 기본 방어력 수치 확인</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>· 11.0 패치 적용 완료
 · 히스이 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 히스이 선택
@@ -669,32 +966,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>기본 방어력: 54
 (변경 전: 52)</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr"/>
-    </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-001</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>[실험체] 가넷 - 억누른 고통(W) 받는 피해 감소 수치 확인</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 가넷 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 가넷 선택
@@ -702,32 +999,32 @@
 4. 받는 피해 감소 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>억누른 고통(W) 받는 피해 감소: 50%
 (변경 전: 55%)</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr"/>
-    </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-002</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>[실험체] 라우라 - 날카로운 꽃(Q) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 라우라 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 라우라 선택
@@ -735,32 +1032,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>날카로운 꽃(Q) 피해량: 50/75/100/125/150(+스킬 증폭의 55%)
 (변경 전: 50/75/100/125/150(+스킬 증폭의 60%))</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr"/>
-    </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-003</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>[실험체] 레니 - 스프링! 트랩(R) 쿨다운 수치 확인</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 레니 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 레니 선택
@@ -768,32 +1065,32 @@
 4. 쿨다운 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
         <is>
           <t>스프링! 트랩(R) 쿨다운: 20/17/14초
 (변경 전: 20/16/12초)</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr"/>
-    </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="F17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-004</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>[실험체] 마이 - 오뜨꾸뛰르(P) 기본 공격 추가 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 마이 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 마이 선택
@@ -801,32 +1098,32 @@
 4. 기본 공격 추가 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t>오뜨꾸뛰르(P) 기본 공격 추가 피해량: 30(+추가 체력의 5/8/11%)
 (변경 전: 30(+추가 체력의 4/7/10%))</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr"/>
-    </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="F18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-005</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>[실험체] 마커스 - 파괴(W) 쿨다운 수치 확인</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 마커스 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 마커스 선택
@@ -834,32 +1131,32 @@
 4. 쿨다운 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>파괴(W) 쿨다운: 13/12/11/10/9초
 (변경 전: 12/11/10/9/8초)</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr"/>
-    </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="F19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-006</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>[실험체] 매그너스 - 17대 1(W) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 매그너스 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 매그너스 선택
@@ -867,32 +1164,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>17대 1(W) 피해량: 16/22/28/34/40(+추가 공격력의 45%)(+스킬 증폭의 18%)(+적 최대 체력의 2.5%)
 (변경 전: 16/22/28/34/40(+추가 공격력의 50%)(+스킬 증폭의 18%)(+적 최대 체력의 2.5%))</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr"/>
-    </row>
-    <row r="12" ht="60" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="F20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-007</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>[실험체] 쇼우 - 식사 시간(W) 방어력 증가 지속 시간 수치 확인</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 쇼우 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 쇼우 선택
@@ -900,32 +1197,32 @@
 4. 방어력 증가 지속 시간 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t>식사 시간(W) 방어력 증가 지속 시간: 2.5초
 (변경 전: 2초)</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr"/>
-    </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="F21" s="3" t="inlineStr"/>
+    </row>
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-008</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>[실험체] 실비아 - 기동전(R) 방어력 증가 수치 확인</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 실비아 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 실비아 선택
@@ -933,32 +1230,32 @@
 4. 방어력 증가 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>기동전(R) 방어력 증가: 14/18/22
 (변경 전: 15/20/25)</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr"/>
-    </row>
-    <row r="14" ht="60" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="F22" s="3" t="inlineStr"/>
+    </row>
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-009</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>[실험체] 아비게일 - 워프 슬래시(E) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 아비게일 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 아비게일 선택
@@ -966,32 +1263,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E23" s="3" t="inlineStr">
         <is>
           <t>워프 슬래시(E) 피해량: 70/85/100/115/130(+스킬 증폭의 40%)
 (변경 전: 80/100/120/140/160(+스킬 증폭의 40%))</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr"/>
-    </row>
-    <row r="15" ht="60" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="F23" s="3" t="inlineStr"/>
+    </row>
+    <row r="24" ht="60" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-010</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>[실험체] 아비게일 - 티어링 블레이드(P) 방어력 감소 수치 확인</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 아비게일 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 아비게일 선택
@@ -999,32 +1296,32 @@
 4. 방어력 감소 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E24" s="3" t="inlineStr">
         <is>
           <t>티어링 블레이드(P) 방어력 감소: 4/7/10
 (변경 전: 4/8/12)</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr"/>
-    </row>
-    <row r="16" ht="60" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="F24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-011</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>[실험체] 아야 - 2연발(Q) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 아야 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 아야 선택
@@ -1032,32 +1329,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E25" s="3" t="inlineStr">
         <is>
           <t>2연발(Q) 피해량: 40/70/100/130/160(+공격력의 30%)(+스킬 증폭의 65%)
 (변경 전: 40/70/100/130/160(+공격력의 30%)(+스킬 증폭의 70%))</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr"/>
-    </row>
-    <row r="17" ht="60" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="F25" s="3" t="inlineStr"/>
+    </row>
+    <row r="26" ht="60" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-012</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>[실험체] 알론소 - 마그네틱 펀치(Q) 기절 지속 시간 수치 확인</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 알론소 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 알론소 선택
@@ -1065,32 +1362,32 @@
 4. 기절 지속 시간 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr">
         <is>
           <t>마그네틱 펀치(Q) 기절 지속 시간: 0.9초
 (변경 전: 0.85초)</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr"/>
-    </row>
-    <row r="18" ht="60" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="F26" s="3" t="inlineStr"/>
+    </row>
+    <row r="27" ht="60" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-013</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>[실험체] 에이든 - 뇌격(Q) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 에이든 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 에이든 선택
@@ -1098,32 +1395,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E27" s="3" t="inlineStr">
         <is>
           <t>뇌격(Q) 피해량: 70/100/130/160/190(+공격력의 75%) * (기본 공격 증폭)
 (변경 전: 60/90/120/150/180(+공격력의 75%) * (기본 공격 증폭))</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr"/>
-    </row>
-    <row r="19" ht="60" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="F27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28" ht="60" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-014</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>[실험체] 에이든 - 전자포(과전하 Q) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 에이든 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 에이든 선택
@@ -1131,32 +1428,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="E28" s="3" t="inlineStr">
         <is>
           <t>전자포(과전하 Q) 피해량: 70/100/130/160/190(+공격력의 75%) * (기본 공격 증폭)
 (변경 전: 60/90/120/150/180(+공격력의 75%) * (기본 공격 증폭))</t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr"/>
-    </row>
-    <row r="20" ht="60" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="F28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-015</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>[실험체] 일레븐 - 힘내자고!(P) 일레븐 버거 체력 회복량 수치 확인</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 일레븐 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 일레븐 선택
@@ -1164,32 +1461,32 @@
 4. 일레븐 버거 체력 회복량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t>힘내자고!(P) 일레븐 버거 체력 회복량: 2/4/6%
 (변경 전: 최대 체력의 3/5/7%)</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr"/>
-    </row>
-    <row r="21" ht="60" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="F29" s="3" t="inlineStr"/>
+    </row>
+    <row r="30" ht="60" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-016</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>[실험체] 칼라 - 작살 장전(P) 완전 충전시 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 칼라 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 칼라 선택
@@ -1197,32 +1494,32 @@
 4. 완전 충전시 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="E30" s="3" t="inlineStr">
         <is>
           <t>작살 장전(P) 완전 충전시 피해량: 10/25/40(+공격력의 100%)(+스킬 증폭의 25%)(+대상 최대 체력의 4/8/12%)
 (변경 전: 10/25/40(+공격력의 100%)(+스킬 증폭의 25%)(+대상 최대 체력의 4/7/10%))</t>
         </is>
       </c>
-      <c r="F21" s="3" t="inlineStr"/>
-    </row>
-    <row r="22" ht="60" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="F30" s="3" t="inlineStr"/>
+    </row>
+    <row r="31" ht="60" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-017</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>[실험체] 케네스 - 분노의 일격(Q) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 케네스 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 케네스 선택
@@ -1230,32 +1527,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="E31" s="3" t="inlineStr">
         <is>
           <t>분노의 일격(Q) 피해량: 30/40/50/60/70(+공격력의 165/170/175/180/185%)
 (변경 전: 30/40/50/60/70(+공격력의 150/155/160/165/170%))</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr"/>
-    </row>
-    <row r="23" ht="60" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="F31" s="3" t="inlineStr"/>
+    </row>
+    <row r="32" ht="60" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-018</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>[실험체] 코렐라인 - 죄의 굴레(E) 거울 강화 시 투사체 속도 수치 확인</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 코렐라인 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="D32" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 코렐라인 선택
@@ -1263,32 +1560,32 @@
 4. 거울 강화 시 투사체 속도 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E23" s="3" t="inlineStr">
+      <c r="E32" s="3" t="inlineStr">
         <is>
           <t>죄의 굴레(E) 거울 강화 시 투사체 속도: 13/ms
 (변경 전: 15m/s)</t>
         </is>
       </c>
-      <c r="F23" s="3" t="inlineStr"/>
-    </row>
-    <row r="24" ht="60" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="F32" s="3" t="inlineStr"/>
+    </row>
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-019</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>[실험체] 코렐라인 - 진실의 거울/거짓의 거울(W) 스킬 증폭 증가 수치 확인</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 코렐라인 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 코렐라인 선택
@@ -1296,32 +1593,32 @@
 4. 스킬 증폭 증가 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="E33" s="3" t="inlineStr">
         <is>
           <t>진실의 거울/거짓의 거울(W) 스킬 증폭 증가: 3/5/7%
 (변경 전: 4/6/8%)</t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr"/>
-    </row>
-    <row r="25" ht="60" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="F33" s="3" t="inlineStr"/>
+    </row>
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-020</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>[실험체] 키아라 - 부정의 손길(Q) 체력 회복량 수치 확인</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 키아라 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="D34" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 키아라 선택
@@ -1329,32 +1626,32 @@
 4. 체력 회복량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E25" s="3" t="inlineStr">
+      <c r="E34" s="3" t="inlineStr">
         <is>
           <t>부정의 손길(Q) 체력 회복량: 13/16/19/22/25(+스킬 증폭의 4%)
 (변경 전: 10/13/16/19/22(+스킬 증폭의 3%))</t>
         </is>
       </c>
-      <c r="F25" s="3" t="inlineStr"/>
-    </row>
-    <row r="26" ht="60" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="F34" s="3" t="inlineStr"/>
+    </row>
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-021</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>[실험체] 타지아 - 스틸레토(Q) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C35" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 타지아 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D35" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 타지아 선택
@@ -1362,32 +1659,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="E35" s="3" t="inlineStr">
         <is>
           <t>스틸레토(Q) 피해량: 30/60/90/120/150(+스킬 증폭의 40%)
 (변경 전: 30/55/80/105/130(+스킬 증폭의 40%))</t>
         </is>
       </c>
-      <c r="F26" s="3" t="inlineStr"/>
-    </row>
-    <row r="27" ht="60" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="F35" s="3" t="inlineStr"/>
+    </row>
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-022</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>[실험체] 타지아 - 스틸레토(Q) 스파다(강화 Q) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 타지아 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="D36" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 타지아 선택
@@ -1395,32 +1692,32 @@
 4. 스파다(강화 Q) 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E27" s="3" t="inlineStr">
+      <c r="E36" s="3" t="inlineStr">
         <is>
           <t>스틸레토(Q) 스파다(강화 Q) 피해량: 30/60/90/120/150(+스킬 증폭의 50%)
 (변경 전: 30/55/80/105/130(+스킬 증폭의 50%))</t>
         </is>
       </c>
-      <c r="F27" s="3" t="inlineStr"/>
-    </row>
-    <row r="28" ht="60" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="F36" s="3" t="inlineStr"/>
+    </row>
+    <row r="37" ht="60" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-023</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>[실험체] 테오도르 - 에너지 필드(R) 이동 속도 증가 수치 확인</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 테오도르 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="D37" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 테오도르 선택
@@ -1428,32 +1725,32 @@
 4. 이동 속도 증가 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="E37" s="3" t="inlineStr">
         <is>
           <t>에너지 필드(R) 이동 속도 증가: 50/70/90%(+스킬 증폭의 2%)
 (변경 전: 60/80/100%(+스킬 증폭의 2%))</t>
         </is>
       </c>
-      <c r="F28" s="3" t="inlineStr"/>
-    </row>
-    <row r="29" ht="60" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="F37" s="3" t="inlineStr"/>
+    </row>
+    <row r="38" ht="60" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-024</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B38" s="3" t="inlineStr">
         <is>
           <t>[실험체] 프리야 - 개화의 선율(Q) 만개 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="C38" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 프리야 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="D38" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 프리야 선택
@@ -1461,32 +1758,32 @@
 4. 만개 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E29" s="3" t="inlineStr">
+      <c r="E38" s="3" t="inlineStr">
         <is>
           <t>개화의 선율(Q) 만개 피해량: 60/80/100/120/140(+스킬 증폭의 60%)
 (변경 전: 60/80/100/120/140(+스킬 증폭의 55%))</t>
         </is>
       </c>
-      <c r="F29" s="3" t="inlineStr"/>
-    </row>
-    <row r="30" ht="60" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="F38" s="3" t="inlineStr"/>
+    </row>
+    <row r="39" ht="60" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-025</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>[실험체] 프리야 - 포르타멘토(W) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="C39" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 프리야 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="D39" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 프리야 선택
@@ -1494,32 +1791,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E30" s="3" t="inlineStr">
+      <c r="E39" s="3" t="inlineStr">
         <is>
           <t>포르타멘토(W) 피해량: 60/100/140/180/220(+스킬 증폭의 65%)
 (변경 전: 60/100/140/180/220(+스킬 증폭의 60%))</t>
         </is>
       </c>
-      <c r="F30" s="3" t="inlineStr"/>
-    </row>
-    <row r="31" ht="60" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="F39" s="3" t="inlineStr"/>
+    </row>
+    <row r="40" ht="60" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-026</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>[실험체] 헤이즈 - 산탄 포화(W) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="C40" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 헤이즈 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="D40" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 헤이즈 선택
@@ -1527,32 +1824,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E31" s="3" t="inlineStr">
+      <c r="E40" s="3" t="inlineStr">
         <is>
           <t>산탄 포화(W) 피해량: 80/120/160/200/240(+스킬 증폭의 75%)
 (변경 전: 80/120/160/200/240(+스킬 증폭의 70%))</t>
         </is>
       </c>
-      <c r="F31" s="3" t="inlineStr"/>
-    </row>
-    <row r="32" ht="60" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="F40" s="3" t="inlineStr"/>
+    </row>
+    <row r="41" ht="60" customHeight="1">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-027</t>
         </is>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>[실험체] 헨리 - 시간 제어 장치(W) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 헨리 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
+      <c r="D41" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 헨리 선택
@@ -1560,32 +1857,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E32" s="3" t="inlineStr">
+      <c r="E41" s="3" t="inlineStr">
         <is>
           <t>시간 제어 장치(W) 피해량: 8/16/24/32/40(+스킬 증폭의 22%)(+대상 최대 체력의 1/1/2/2/3%)
 (변경 전: 8/16/24/32/40(+스킬 증폭의 20%)(+대상 최대 체력의 1/1/2/2/3%))</t>
         </is>
       </c>
-      <c r="F32" s="3" t="inlineStr"/>
-    </row>
-    <row r="33" ht="60" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="F41" s="3" t="inlineStr"/>
+    </row>
+    <row r="42" ht="60" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-028</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B42" s="3" t="inlineStr">
         <is>
           <t>[실험체] 현우 - 핵펀치(R) 방어력 감소 수치 확인</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="C42" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 현우 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
+      <c r="D42" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 현우 선택
@@ -1593,32 +1890,32 @@
 4. 방어력 감소 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E33" s="3" t="inlineStr">
+      <c r="E42" s="3" t="inlineStr">
         <is>
           <t>핵펀치(R) 방어력 감소: 10/15/20%
 (변경 전: 15/20/25%)</t>
         </is>
       </c>
-      <c r="F33" s="3" t="inlineStr"/>
-    </row>
-    <row r="34" ht="60" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="F42" s="3" t="inlineStr"/>
+    </row>
+    <row r="43" ht="60" customHeight="1">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-029</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>[실험체] 혜진 - 오대존명왕진(R) 부적 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 혜진 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D34" s="3" t="inlineStr">
+      <c r="D43" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 혜진 선택
@@ -1626,32 +1923,32 @@
 4. 부적 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E34" s="3" t="inlineStr">
+      <c r="E43" s="3" t="inlineStr">
         <is>
           <t>오대존명왕진(R) 부적 피해량: 80/105/130(+스킬 증폭의 50%)
 (변경 전: 80/115/150(+스킬 증폭의 50%))</t>
         </is>
       </c>
-      <c r="F34" s="3" t="inlineStr"/>
-    </row>
-    <row r="35" ht="60" customHeight="1">
-      <c r="A35" s="4" t="inlineStr">
+      <c r="F43" s="3" t="inlineStr"/>
+    </row>
+    <row r="44" ht="60" customHeight="1">
+      <c r="A44" s="4" t="inlineStr">
         <is>
           <t>TC-10.7-030</t>
         </is>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B44" s="5" t="inlineStr">
         <is>
           <t>[실험체] 나딘 - 기본 공격력 수치 확인</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="C44" s="5" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 나딘 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="D44" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 나딘 선택
@@ -1659,32 +1956,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr">
+      <c r="E44" s="5" t="inlineStr">
         <is>
           <t>기본 공격력: 33
 (변경 전: 35)</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr"/>
-    </row>
-    <row r="36" ht="60" customHeight="1">
-      <c r="A36" s="4" t="inlineStr">
+      <c r="F44" s="5" t="inlineStr"/>
+    </row>
+    <row r="45" ht="60" customHeight="1">
+      <c r="A45" s="4" t="inlineStr">
         <is>
           <t>TC-10.7-031</t>
         </is>
       </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="B45" s="5" t="inlineStr">
         <is>
           <t>[실험체] 나타폰 - 카메라 무기 숙련도 레벨 당 스킬 증폭 수치 확인</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
+      <c r="C45" s="5" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 나타폰 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="D45" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 나타폰 선택
@@ -1692,32 +1989,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E36" s="5" t="inlineStr">
+      <c r="E45" s="5" t="inlineStr">
         <is>
           <t>카메라 무기 숙련도 레벨 당 스킬 증폭: 4.4%
 (변경 전: 4.3%)</t>
         </is>
       </c>
-      <c r="F36" s="5" t="inlineStr"/>
-    </row>
-    <row r="37" ht="60" customHeight="1">
-      <c r="A37" s="4" t="inlineStr">
+      <c r="F45" s="5" t="inlineStr"/>
+    </row>
+    <row r="46" ht="60" customHeight="1">
+      <c r="A46" s="4" t="inlineStr">
         <is>
           <t>TC-10.7-032</t>
         </is>
       </c>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="B46" s="5" t="inlineStr">
         <is>
           <t>[실험체] 르노어 - 받는 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
+      <c r="C46" s="5" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 르노어 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D46" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 르노어 선택
@@ -1725,32 +2022,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E37" s="5" t="inlineStr">
+      <c r="E46" s="5" t="inlineStr">
         <is>
           <t>받는 피해량: 100%
 (변경 전: 102%)</t>
         </is>
       </c>
-      <c r="F37" s="5" t="inlineStr"/>
-    </row>
-    <row r="38" ht="60" customHeight="1">
-      <c r="A38" s="4" t="inlineStr">
+      <c r="F46" s="5" t="inlineStr"/>
+    </row>
+    <row r="47" ht="60" customHeight="1">
+      <c r="A47" s="4" t="inlineStr">
         <is>
           <t>TC-10.7-033</t>
         </is>
       </c>
-      <c r="B38" s="5" t="inlineStr">
+      <c r="B47" s="5" t="inlineStr">
         <is>
           <t>[실험체] 리 다이린 - 글러브 무기 숙련도 레벨 당 기본 공격 증폭 수치 확인</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr">
+      <c r="C47" s="5" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 리 다이린 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="D47" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 리 다이린 선택
@@ -1758,32 +2055,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E38" s="5" t="inlineStr">
+      <c r="E47" s="5" t="inlineStr">
         <is>
           <t>글러브 무기 숙련도 레벨 당 기본 공격 증폭: 1.9%
 (변경 전: 1.8%)</t>
         </is>
       </c>
-      <c r="F38" s="5" t="inlineStr"/>
-    </row>
-    <row r="39" ht="60" customHeight="1">
-      <c r="A39" s="4" t="inlineStr">
+      <c r="F47" s="5" t="inlineStr"/>
+    </row>
+    <row r="48" ht="60" customHeight="1">
+      <c r="A48" s="4" t="inlineStr">
         <is>
           <t>TC-10.7-034</t>
         </is>
       </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="B48" s="5" t="inlineStr">
         <is>
           <t>[실험체] 마커스 - 레벨 당 체력 수치 확인</t>
         </is>
       </c>
-      <c r="C39" s="5" t="inlineStr">
+      <c r="C48" s="5" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 마커스 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="D48" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 마커스 선택
@@ -1791,32 +2088,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E39" s="5" t="inlineStr">
+      <c r="E48" s="5" t="inlineStr">
         <is>
           <t>레벨 당 체력: 94
 (변경 전: 97)</t>
         </is>
       </c>
-      <c r="F39" s="5" t="inlineStr"/>
-    </row>
-    <row r="40" ht="60" customHeight="1">
-      <c r="A40" s="4" t="inlineStr">
+      <c r="F48" s="5" t="inlineStr"/>
+    </row>
+    <row r="49" ht="60" customHeight="1">
+      <c r="A49" s="4" t="inlineStr">
         <is>
           <t>TC-10.7-035</t>
         </is>
       </c>
-      <c r="B40" s="5" t="inlineStr">
+      <c r="B49" s="5" t="inlineStr">
         <is>
           <t>[실험체] 미르카 - 기본 체력 수치 확인</t>
         </is>
       </c>
-      <c r="C40" s="5" t="inlineStr">
+      <c r="C49" s="5" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 미르카 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D40" s="5" t="inlineStr">
+      <c r="D49" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 미르카 선택
@@ -1824,32 +2121,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E40" s="5" t="inlineStr">
+      <c r="E49" s="5" t="inlineStr">
         <is>
           <t>기본 체력: 960
 (변경 전: 930)</t>
         </is>
       </c>
-      <c r="F40" s="5" t="inlineStr"/>
-    </row>
-    <row r="41" ht="60" customHeight="1">
-      <c r="A41" s="4" t="inlineStr">
+      <c r="F49" s="5" t="inlineStr"/>
+    </row>
+    <row r="50" ht="60" customHeight="1">
+      <c r="A50" s="4" t="inlineStr">
         <is>
           <t>TC-10.7-036</t>
         </is>
       </c>
-      <c r="B41" s="5" t="inlineStr">
+      <c r="B50" s="5" t="inlineStr">
         <is>
           <t>[실험체] 클로에 - 기본 공격력 수치 확인</t>
         </is>
       </c>
-      <c r="C41" s="5" t="inlineStr">
+      <c r="C50" s="5" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 클로에 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="D50" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 클로에 선택
@@ -1857,32 +2154,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E41" s="5" t="inlineStr">
+      <c r="E50" s="5" t="inlineStr">
         <is>
           <t>기본 공격력: 32
 (변경 전: 35)</t>
         </is>
       </c>
-      <c r="F41" s="5" t="inlineStr"/>
-    </row>
-    <row r="42" ht="60" customHeight="1">
-      <c r="A42" s="4" t="inlineStr">
+      <c r="F50" s="5" t="inlineStr"/>
+    </row>
+    <row r="51" ht="60" customHeight="1">
+      <c r="A51" s="4" t="inlineStr">
         <is>
           <t>TC-10.7-037</t>
         </is>
       </c>
-      <c r="B42" s="5" t="inlineStr">
+      <c r="B51" s="5" t="inlineStr">
         <is>
           <t>[실험체] 펜리르 - 레벨 당 공격력 수치 확인</t>
         </is>
       </c>
-      <c r="C42" s="5" t="inlineStr">
+      <c r="C51" s="5" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 펜리르 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="D51" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 펜리르 선택
@@ -1890,32 +2187,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E42" s="5" t="inlineStr">
+      <c r="E51" s="5" t="inlineStr">
         <is>
           <t>레벨 당 공격력: 4.8
 (변경 전: 4.6)</t>
         </is>
       </c>
-      <c r="F42" s="5" t="inlineStr"/>
-    </row>
-    <row r="43" ht="60" customHeight="1">
-      <c r="A43" s="4" t="inlineStr">
+      <c r="F51" s="5" t="inlineStr"/>
+    </row>
+    <row r="52" ht="60" customHeight="1">
+      <c r="A52" s="4" t="inlineStr">
         <is>
           <t>TC-10.7-038</t>
         </is>
       </c>
-      <c r="B43" s="5" t="inlineStr">
+      <c r="B52" s="5" t="inlineStr">
         <is>
           <t>[실험체] 하트 - 기본 방어력 수치 확인</t>
         </is>
       </c>
-      <c r="C43" s="5" t="inlineStr">
+      <c r="C52" s="5" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 하트 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="D52" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 하트 선택
@@ -1923,32 +2220,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E43" s="5" t="inlineStr">
+      <c r="E52" s="5" t="inlineStr">
         <is>
           <t>기본 방어력: 51
 (변경 전: 49)</t>
         </is>
       </c>
-      <c r="F43" s="5" t="inlineStr"/>
-    </row>
-    <row r="44" ht="60" customHeight="1">
-      <c r="A44" s="4" t="inlineStr">
+      <c r="F52" s="5" t="inlineStr"/>
+    </row>
+    <row r="53" ht="60" customHeight="1">
+      <c r="A53" s="4" t="inlineStr">
         <is>
           <t>TC-10.6c-001</t>
         </is>
       </c>
-      <c r="B44" s="5" t="inlineStr">
+      <c r="B53" s="5" t="inlineStr">
         <is>
           <t>[실험체] 코렐라인 - 아르카나 무기 숙련도 레벨 당 스킬 증폭 수치 확인</t>
         </is>
       </c>
-      <c r="C44" s="5" t="inlineStr">
+      <c r="C53" s="5" t="inlineStr">
         <is>
           <t>· 10.6c 패치 적용 완료
 · 코렐라인 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D44" s="5" t="inlineStr">
+      <c r="D53" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 코렐라인 선택
@@ -1956,32 +2253,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E44" s="5" t="inlineStr">
+      <c r="E53" s="5" t="inlineStr">
         <is>
           <t>아르카나 무기 숙련도 레벨 당 스킬 증폭: 4%
 (변경 전: 4.2%)</t>
         </is>
       </c>
-      <c r="F44" s="5" t="inlineStr"/>
-    </row>
-    <row r="45" ht="60" customHeight="1">
-      <c r="A45" s="2" t="inlineStr">
+      <c r="F53" s="5" t="inlineStr"/>
+    </row>
+    <row r="54" ht="60" customHeight="1">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-001</t>
         </is>
       </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="B54" s="3" t="inlineStr">
         <is>
           <t>[실험체] 가넷 - 억누른 고통(W) 쿨다운 수치 확인</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
+      <c r="C54" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 가넷 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D45" s="3" t="inlineStr">
+      <c r="D54" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 가넷 선택
@@ -1989,32 +2286,32 @@
 4. 쿨다운 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E45" s="3" t="inlineStr">
+      <c r="E54" s="3" t="inlineStr">
         <is>
           <t>억누른 고통(W) 쿨다운: 14/13/12/11/10초
 (변경 전: 15/14/13/12/11초)</t>
         </is>
       </c>
-      <c r="F45" s="3" t="inlineStr"/>
-    </row>
-    <row r="46" ht="60" customHeight="1">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="F54" s="3" t="inlineStr"/>
+    </row>
+    <row r="55" ht="60" customHeight="1">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-002</t>
         </is>
       </c>
-      <c r="B46" s="3" t="inlineStr">
+      <c r="B55" s="3" t="inlineStr">
         <is>
           <t>[실험체] 가넷 - 짓뭉개기&amp;꿰뚫기(Q) 이동 속도 감소 수치 확인</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr">
+      <c r="C55" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 가넷 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D46" s="3" t="inlineStr">
+      <c r="D55" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 가넷 선택
@@ -2022,32 +2319,32 @@
 4. 이동 속도 감소 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E46" s="3" t="inlineStr">
+      <c r="E55" s="3" t="inlineStr">
         <is>
           <t>짓뭉개기&amp;꿰뚫기(Q) 이동 속도 감소: 40%
 (변경 전: 35%)</t>
         </is>
       </c>
-      <c r="F46" s="3" t="inlineStr"/>
-    </row>
-    <row r="47" ht="60" customHeight="1">
-      <c r="A47" s="2" t="inlineStr">
+      <c r="F55" s="3" t="inlineStr"/>
+    </row>
+    <row r="56" ht="60" customHeight="1">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-003</t>
         </is>
       </c>
-      <c r="B47" s="3" t="inlineStr">
+      <c r="B56" s="3" t="inlineStr">
         <is>
           <t>[실험체] 라우라 - 황혼의 도둑(R) 폭발 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C47" s="3" t="inlineStr">
+      <c r="C56" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 라우라 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D47" s="3" t="inlineStr">
+      <c r="D56" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 라우라 선택
@@ -2055,32 +2352,32 @@
 4. 폭발 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E47" s="3" t="inlineStr">
+      <c r="E56" s="3" t="inlineStr">
         <is>
           <t>황혼의 도둑(R) 폭발 피해량: 180/260/340(+스킬 증폭의 90%)
 (변경 전: 180/260/340(+스킬 증폭의 85%))</t>
         </is>
       </c>
-      <c r="F47" s="3" t="inlineStr"/>
-    </row>
-    <row r="48" ht="60" customHeight="1">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="F56" s="3" t="inlineStr"/>
+    </row>
+    <row r="57" ht="60" customHeight="1">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-004</t>
         </is>
       </c>
-      <c r="B48" s="3" t="inlineStr">
+      <c r="B57" s="3" t="inlineStr">
         <is>
           <t>[실험체] 라우라 - 황혼의 도둑(R) 보호막량 수치 확인</t>
         </is>
       </c>
-      <c r="C48" s="3" t="inlineStr">
+      <c r="C57" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 라우라 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D48" s="3" t="inlineStr">
+      <c r="D57" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 라우라 선택
@@ -2088,32 +2385,32 @@
 4. 보호막량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E48" s="3" t="inlineStr">
+      <c r="E57" s="3" t="inlineStr">
         <is>
           <t>황혼의 도둑(R) 보호막량: 90/120/150(+스킬 증폭의 20%)
 (변경 전: 90/120/150(+스킬 증폭의 15%))</t>
         </is>
       </c>
-      <c r="F48" s="3" t="inlineStr"/>
-    </row>
-    <row r="49" ht="60" customHeight="1">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="F57" s="3" t="inlineStr"/>
+    </row>
+    <row r="58" ht="60" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-005</t>
         </is>
       </c>
-      <c r="B49" s="3" t="inlineStr">
+      <c r="B58" s="3" t="inlineStr">
         <is>
           <t>[실험체] 레니 - 당근! 바주카(Q) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C49" s="3" t="inlineStr">
+      <c r="C58" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 레니 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D49" s="3" t="inlineStr">
+      <c r="D58" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 레니 선택
@@ -2121,32 +2418,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E49" s="3" t="inlineStr">
+      <c r="E58" s="3" t="inlineStr">
         <is>
           <t>당근! 바주카(Q) 피해량: 40/55/70/85/100(+레니 레벨*18)(+스킬 증폭의 35%)
 (변경 전: 40/55/70/85/100(+레니 레벨*18)(+스킬 증폭의 30%))</t>
         </is>
       </c>
-      <c r="F49" s="3" t="inlineStr"/>
-    </row>
-    <row r="50" ht="60" customHeight="1">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="F58" s="3" t="inlineStr"/>
+    </row>
+    <row r="59" ht="60" customHeight="1">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-006</t>
         </is>
       </c>
-      <c r="B50" s="3" t="inlineStr">
+      <c r="B59" s="3" t="inlineStr">
         <is>
           <t>[실험체] 레니 - 당근! 바주카(Q) 회복량 수치 확인</t>
         </is>
       </c>
-      <c r="C50" s="3" t="inlineStr">
+      <c r="C59" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 레니 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D50" s="3" t="inlineStr">
+      <c r="D59" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 레니 선택
@@ -2154,32 +2451,32 @@
 4. 회복량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E50" s="3" t="inlineStr">
+      <c r="E59" s="3" t="inlineStr">
         <is>
           <t>당근! 바주카(Q) 회복량: 10/20/30/40/50(+레니 레벨*2)(+스킬 증폭의 20%)
 (변경 전: 10/20/30/40/50(+레니 레벨*2)(+스킬 증폭의 18%))</t>
         </is>
       </c>
-      <c r="F50" s="3" t="inlineStr"/>
-    </row>
-    <row r="51" ht="60" customHeight="1">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="F59" s="3" t="inlineStr"/>
+    </row>
+    <row r="60" ht="60" customHeight="1">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-007</t>
         </is>
       </c>
-      <c r="B51" s="3" t="inlineStr">
+      <c r="B60" s="3" t="inlineStr">
         <is>
           <t>[실험체] 레온 - 물보라(W) 레온 보호막 흡수량 수치 확인</t>
         </is>
       </c>
-      <c r="C51" s="3" t="inlineStr">
+      <c r="C60" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 레온 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D51" s="3" t="inlineStr">
+      <c r="D60" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 레온 선택
@@ -2187,32 +2484,32 @@
 4. 레온 보호막 흡수량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E51" s="3" t="inlineStr">
+      <c r="E60" s="3" t="inlineStr">
         <is>
           <t>물보라(W) 레온 보호막 흡수량: 80/110/140/170/200(+스킬 증폭의 40%)
 (변경 전: 80/110/140/170/200(+스킬 증폭의 35%))</t>
         </is>
       </c>
-      <c r="F51" s="3" t="inlineStr"/>
-    </row>
-    <row r="52" ht="60" customHeight="1">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="F60" s="3" t="inlineStr"/>
+    </row>
+    <row r="61" ht="60" customHeight="1">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-008</t>
         </is>
       </c>
-      <c r="B52" s="3" t="inlineStr">
+      <c r="B61" s="3" t="inlineStr">
         <is>
           <t>[실험체] 르노어 - 고통의 선율(P) 아첼레란도 중첩 당 쿨다운 감소 수치 확인</t>
         </is>
       </c>
-      <c r="C52" s="3" t="inlineStr">
+      <c r="C61" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 르노어 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D52" s="3" t="inlineStr">
+      <c r="D61" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 르노어 선택
@@ -2220,32 +2517,32 @@
 4. 아첼레란도 중첩 당 쿨다운 감소 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E52" s="3" t="inlineStr">
+      <c r="E61" s="3" t="inlineStr">
         <is>
           <t>고통의 선율(P) 아첼레란도 중첩 당 쿨다운 감소: 3
 (변경 전: 2)</t>
         </is>
       </c>
-      <c r="F52" s="3" t="inlineStr"/>
-    </row>
-    <row r="53" ht="60" customHeight="1">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="F61" s="3" t="inlineStr"/>
+    </row>
+    <row r="62" ht="60" customHeight="1">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-009</t>
         </is>
       </c>
-      <c r="B53" s="3" t="inlineStr">
+      <c r="B62" s="3" t="inlineStr">
         <is>
           <t>[실험체] 르노어 - 고통의 선율(P) 쿨다운 감소 수치 확인</t>
         </is>
       </c>
-      <c r="C53" s="3" t="inlineStr">
+      <c r="C62" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 르노어 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D53" s="3" t="inlineStr">
+      <c r="D62" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 르노어 선택
@@ -2253,32 +2550,32 @@
 4. 쿨다운 감소 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E53" s="3" t="inlineStr">
+      <c r="E62" s="3" t="inlineStr">
         <is>
           <t>고통의 선율(P) 쿨다운 감소: 2
 (변경 전: 40 이후 아첼레란도 중첩 당 궁극기 쿨다운 감소 3)</t>
         </is>
       </c>
-      <c r="F53" s="3" t="inlineStr"/>
-    </row>
-    <row r="54" ht="60" customHeight="1">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="F62" s="3" t="inlineStr"/>
+    </row>
+    <row r="63" ht="60" customHeight="1">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-010</t>
         </is>
       </c>
-      <c r="B54" s="3" t="inlineStr">
+      <c r="B63" s="3" t="inlineStr">
         <is>
           <t>[실험체] 마르티나 - 일시정지 - 방송 중(W) 속박 지속 시간 수치 확인</t>
         </is>
       </c>
-      <c r="C54" s="3" t="inlineStr">
+      <c r="C63" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 마르티나 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D54" s="3" t="inlineStr">
+      <c r="D63" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 마르티나 선택
@@ -2286,32 +2583,32 @@
 4. 속박 지속 시간 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E54" s="3" t="inlineStr">
+      <c r="E63" s="3" t="inlineStr">
         <is>
           <t>일시정지 - 방송 중(W) 속박 지속 시간: 1.2초
 (변경 전: 1초)</t>
         </is>
       </c>
-      <c r="F54" s="3" t="inlineStr"/>
-    </row>
-    <row r="55" ht="60" customHeight="1">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="F63" s="3" t="inlineStr"/>
+    </row>
+    <row r="64" ht="60" customHeight="1">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-011</t>
         </is>
       </c>
-      <c r="B55" s="3" t="inlineStr">
+      <c r="B64" s="3" t="inlineStr">
         <is>
           <t>[실험체] 마이 - 숄 장막(W) 이동 속도 증가 수치 확인</t>
         </is>
       </c>
-      <c r="C55" s="3" t="inlineStr">
+      <c r="C64" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 마이 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D55" s="3" t="inlineStr">
+      <c r="D64" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 마이 선택
@@ -2319,32 +2616,32 @@
 4. 이동 속도 증가 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E55" s="3" t="inlineStr">
+      <c r="E64" s="3" t="inlineStr">
         <is>
           <t>숄 장막(W) 이동 속도 증가: 10/14/18/22/26%
 (변경 전: 8/11/14/17/20%)</t>
         </is>
       </c>
-      <c r="F55" s="3" t="inlineStr"/>
-    </row>
-    <row r="56" ht="60" customHeight="1">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="F64" s="3" t="inlineStr"/>
+    </row>
+    <row r="65" ht="60" customHeight="1">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-012</t>
         </is>
       </c>
-      <c r="B56" s="3" t="inlineStr">
+      <c r="B65" s="3" t="inlineStr">
         <is>
           <t>[실험체] 바바라 - BT-Mk2 센트리건(Q) 센트리건 기본 공격 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C56" s="3" t="inlineStr">
+      <c r="C65" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 바바라 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D56" s="3" t="inlineStr">
+      <c r="D65" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 바바라 선택
@@ -2352,32 +2649,32 @@
 4. 센트리건 기본 공격 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E56" s="3" t="inlineStr">
+      <c r="E65" s="3" t="inlineStr">
         <is>
           <t>BT-Mk2 센트리건(Q) 센트리건 기본 공격 피해량: 30/40/50/60/70(+스킬 증폭의 18%)
 (변경 전: 30/40/50/60/70(+스킬 증폭의 20%))</t>
         </is>
       </c>
-      <c r="F56" s="3" t="inlineStr"/>
-    </row>
-    <row r="57" ht="60" customHeight="1">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="F65" s="3" t="inlineStr"/>
+    </row>
+    <row r="66" ht="60" customHeight="1">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-013</t>
         </is>
       </c>
-      <c r="B57" s="3" t="inlineStr">
+      <c r="B66" s="3" t="inlineStr">
         <is>
           <t>[실험체] 셀린 - 자력 융합(R) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C57" s="3" t="inlineStr">
+      <c r="C66" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 셀린 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D57" s="3" t="inlineStr">
+      <c r="D66" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 셀린 선택
@@ -2385,32 +2682,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E57" s="3" t="inlineStr">
+      <c r="E66" s="3" t="inlineStr">
         <is>
           <t>자력 융합(R) 피해량: 60/80/100/120/140(+스킬 증폭의 37%)
 (변경 전: 60/80/100/120/140(+스킬 증폭의 36%))</t>
         </is>
       </c>
-      <c r="F57" s="3" t="inlineStr"/>
-    </row>
-    <row r="58" ht="60" customHeight="1">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="F66" s="3" t="inlineStr"/>
+    </row>
+    <row r="67" ht="60" customHeight="1">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-014</t>
         </is>
       </c>
-      <c r="B58" s="3" t="inlineStr">
+      <c r="B67" s="3" t="inlineStr">
         <is>
           <t>[실험체] 쇼이치 - 비약(W) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C58" s="3" t="inlineStr">
+      <c r="C67" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 쇼이치 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D58" s="3" t="inlineStr">
+      <c r="D67" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 쇼이치 선택
@@ -2418,32 +2715,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E58" s="3" t="inlineStr">
+      <c r="E67" s="3" t="inlineStr">
         <is>
           <t>비약(W) 피해량: 30/50/70/90/110(+스킬 증폭의 60%)
 (변경 전: 40/60/80/100/120(+스킬 증폭의 60%))</t>
         </is>
       </c>
-      <c r="F58" s="3" t="inlineStr"/>
-    </row>
-    <row r="59" ht="60" customHeight="1">
-      <c r="A59" s="2" t="inlineStr">
+      <c r="F67" s="3" t="inlineStr"/>
+    </row>
+    <row r="68" ht="60" customHeight="1">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-015</t>
         </is>
       </c>
-      <c r="B59" s="3" t="inlineStr">
+      <c r="B68" s="3" t="inlineStr">
         <is>
           <t>[실험체] 수아 - 기억력(R) 쿨다운 수치 확인</t>
         </is>
       </c>
-      <c r="C59" s="3" t="inlineStr">
+      <c r="C68" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 수아 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D59" s="3" t="inlineStr">
+      <c r="D68" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 수아 선택
@@ -2451,32 +2748,32 @@
 4. 쿨다운 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E59" s="3" t="inlineStr">
+      <c r="E68" s="3" t="inlineStr">
         <is>
           <t>기억력(R) 쿨다운: 26/22/18초
 (변경 전: 30/24/18초)</t>
         </is>
       </c>
-      <c r="F59" s="3" t="inlineStr"/>
-    </row>
-    <row r="60" ht="60" customHeight="1">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="F68" s="3" t="inlineStr"/>
+    </row>
+    <row r="69" ht="60" customHeight="1">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-016</t>
         </is>
       </c>
-      <c r="B60" s="3" t="inlineStr">
+      <c r="B69" s="3" t="inlineStr">
         <is>
           <t>[실험체] 시셀라 - 삶은 고통이에요.(P) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C60" s="3" t="inlineStr">
+      <c r="C69" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 시셀라 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D60" s="3" t="inlineStr">
+      <c r="D69" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 시셀라 선택
@@ -2484,32 +2781,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E60" s="3" t="inlineStr">
+      <c r="E69" s="3" t="inlineStr">
         <is>
           <t>삶은 고통이에요.(P) 피해량: 30(+스킬 증폭의 45%)(+캐릭터 레벨*9)
 (변경 전: 30(+스킬 증폭의 40%)(+캐릭터 레벨*9))</t>
         </is>
       </c>
-      <c r="F60" s="3" t="inlineStr"/>
-    </row>
-    <row r="61" ht="60" customHeight="1">
-      <c r="A61" s="2" t="inlineStr">
+      <c r="F69" s="3" t="inlineStr"/>
+    </row>
+    <row r="70" ht="60" customHeight="1">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-017</t>
         </is>
       </c>
-      <c r="B61" s="3" t="inlineStr">
+      <c r="B70" s="3" t="inlineStr">
         <is>
           <t>[실험체] 아디나 - 폴 디그니티(E) 별 컨정션 효과 체력 회복량 수치 확인</t>
         </is>
       </c>
-      <c r="C61" s="3" t="inlineStr">
+      <c r="C70" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 아디나 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D61" s="3" t="inlineStr">
+      <c r="D70" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 아디나 선택
@@ -2517,32 +2814,32 @@
 4. 별 컨정션 효과 체력 회복량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E61" s="3" t="inlineStr">
+      <c r="E70" s="3" t="inlineStr">
         <is>
           <t>폴 디그니티(E) 별 컨정션 효과 체력 회복량: 20/30/40/50(+스킬 증폭의 6%)
 (변경 전: 20/30/40/50(+스킬 증폭의 4%))</t>
         </is>
       </c>
-      <c r="F61" s="3" t="inlineStr"/>
-    </row>
-    <row r="62" ht="60" customHeight="1">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="F70" s="3" t="inlineStr"/>
+    </row>
+    <row r="71" ht="60" customHeight="1">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-018</t>
         </is>
       </c>
-      <c r="B62" s="3" t="inlineStr">
+      <c r="B71" s="3" t="inlineStr">
         <is>
           <t>[실험체] 아이작 - 현장 급습(Q) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C62" s="3" t="inlineStr">
+      <c r="C71" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 아이작 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D62" s="3" t="inlineStr">
+      <c r="D71" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 아이작 선택
@@ -2550,32 +2847,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E62" s="3" t="inlineStr">
+      <c r="E71" s="3" t="inlineStr">
         <is>
           <t>현장 급습(Q) 피해량: 20/60/100/140/180(+공격력의 70%)
 (변경 전: 30/70/110/150/190(+공격력의 70%))</t>
         </is>
       </c>
-      <c r="F62" s="3" t="inlineStr"/>
-    </row>
-    <row r="63" ht="60" customHeight="1">
-      <c r="A63" s="2" t="inlineStr">
+      <c r="F71" s="3" t="inlineStr"/>
+    </row>
+    <row r="72" ht="60" customHeight="1">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-019</t>
         </is>
       </c>
-      <c r="B63" s="3" t="inlineStr">
+      <c r="B72" s="3" t="inlineStr">
         <is>
           <t>[실험체] 알렉스 - 플라즈마 마인(W) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C63" s="3" t="inlineStr">
+      <c r="C72" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 알렉스 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D63" s="3" t="inlineStr">
+      <c r="D72" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 알렉스 선택
@@ -2583,32 +2880,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E63" s="3" t="inlineStr">
+      <c r="E72" s="3" t="inlineStr">
         <is>
           <t>플라즈마 마인(W) 피해량: 40/75/110/145/180(+공격력의 80%)
 (변경 전: 40/80/120/160/200(+공격력의 80%))</t>
         </is>
       </c>
-      <c r="F63" s="3" t="inlineStr"/>
-    </row>
-    <row r="64" ht="60" customHeight="1">
-      <c r="A64" s="2" t="inlineStr">
+      <c r="F72" s="3" t="inlineStr"/>
+    </row>
+    <row r="73" ht="60" customHeight="1">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-020</t>
         </is>
       </c>
-      <c r="B64" s="3" t="inlineStr">
+      <c r="B73" s="3" t="inlineStr">
         <is>
           <t>[실험체] 에스텔 - 헬기호출(R) 보호막 흡수량 수치 확인</t>
         </is>
       </c>
-      <c r="C64" s="3" t="inlineStr">
+      <c r="C73" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 에스텔 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D64" s="3" t="inlineStr">
+      <c r="D73" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 에스텔 선택
@@ -2616,32 +2913,32 @@
 4. 보호막 흡수량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E64" s="3" t="inlineStr">
+      <c r="E73" s="3" t="inlineStr">
         <is>
           <t>헬기호출(R) 보호막 흡수량: 100/150/200(+스킬 증폭의 55%)(+잃은 체력의 20%)
 (변경 전: 100/150/200(+스킬 증폭의 50%)(+잃은 체력의 20%))</t>
         </is>
       </c>
-      <c r="F64" s="3" t="inlineStr"/>
-    </row>
-    <row r="65" ht="60" customHeight="1">
-      <c r="A65" s="2" t="inlineStr">
+      <c r="F73" s="3" t="inlineStr"/>
+    </row>
+    <row r="74" ht="60" customHeight="1">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-021</t>
         </is>
       </c>
-      <c r="B65" s="3" t="inlineStr">
+      <c r="B74" s="3" t="inlineStr">
         <is>
           <t>[실험체] 에스텔 - 헬기호출(R) 아군 보호막 흡수량 수치 확인</t>
         </is>
       </c>
-      <c r="C65" s="3" t="inlineStr">
+      <c r="C74" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 에스텔 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D65" s="3" t="inlineStr">
+      <c r="D74" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 에스텔 선택
@@ -2649,32 +2946,32 @@
 4. 아군 보호막 흡수량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E65" s="3" t="inlineStr">
+      <c r="E74" s="3" t="inlineStr">
         <is>
           <t>헬기호출(R) 아군 보호막 흡수량: 100/200/300(+스킬 증폭의 55%)(+대상의 잃은 체력의 15%)
 (변경 전: 100/200/300(+스킬 증폭의 50%)(+대상의 잃은 체력의 15%))</t>
         </is>
       </c>
-      <c r="F65" s="3" t="inlineStr"/>
-    </row>
-    <row r="66" ht="60" customHeight="1">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="F74" s="3" t="inlineStr"/>
+    </row>
+    <row r="75" ht="60" customHeight="1">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-022</t>
         </is>
       </c>
-      <c r="B66" s="3" t="inlineStr">
+      <c r="B75" s="3" t="inlineStr">
         <is>
           <t>[실험체] 에키온 - VF 폭주(R) 독사의 진노[블랙맘바] 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C66" s="3" t="inlineStr">
+      <c r="C75" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 에키온 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D66" s="3" t="inlineStr">
+      <c r="D75" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 에키온 선택
@@ -2682,32 +2979,32 @@
 4. 독사의 진노[블랙맘바] 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E66" s="3" t="inlineStr">
+      <c r="E75" s="3" t="inlineStr">
         <is>
           <t>VF 폭주(R) 독사의 진노[블랙맘바] 피해량: 50/120/175/220(+공격력의 80%)(+추가 체력의 12%)
 (변경 전: 50/120/175/220(+공격력의 80%)(+추가 체력의 10%))</t>
         </is>
       </c>
-      <c r="F66" s="3" t="inlineStr"/>
-    </row>
-    <row r="67" ht="60" customHeight="1">
-      <c r="A67" s="2" t="inlineStr">
+      <c r="F75" s="3" t="inlineStr"/>
+    </row>
+    <row r="76" ht="60" customHeight="1">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-023</t>
         </is>
       </c>
-      <c r="B67" s="3" t="inlineStr">
+      <c r="B76" s="3" t="inlineStr">
         <is>
           <t>[실험체] 엠마 - 마술 토끼(E) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C67" s="3" t="inlineStr">
+      <c r="C76" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 엠마 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D67" s="3" t="inlineStr">
+      <c r="D76" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 엠마 선택
@@ -2715,32 +3012,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E67" s="3" t="inlineStr">
+      <c r="E76" s="3" t="inlineStr">
         <is>
           <t>마술 토끼(E) 피해량: 30/55/80/105/130(+스킬 증폭의 30%)
 (변경 전: 20/40/60/80/100(+스킬 증폭의 30%))</t>
         </is>
       </c>
-      <c r="F67" s="3" t="inlineStr"/>
-    </row>
-    <row r="68" ht="60" customHeight="1">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="F76" s="3" t="inlineStr"/>
+    </row>
+    <row r="77" ht="60" customHeight="1">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-024</t>
         </is>
       </c>
-      <c r="B68" s="3" t="inlineStr">
+      <c r="B77" s="3" t="inlineStr">
         <is>
           <t>[실험체] 엠마 - 마술 토끼(E) 변이 지속 시간 수치 확인</t>
         </is>
       </c>
-      <c r="C68" s="3" t="inlineStr">
+      <c r="C77" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 엠마 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D68" s="3" t="inlineStr">
+      <c r="D77" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 엠마 선택
@@ -2748,32 +3045,32 @@
 4. 변이 지속 시간 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E68" s="3" t="inlineStr">
+      <c r="E77" s="3" t="inlineStr">
         <is>
           <t>마술 토끼(E) 변이 지속 시간: 0.8/0.85/0.9/0.95/1초
 (변경 전: 0.6/0.7/0.8/0.9/1초)</t>
         </is>
       </c>
-      <c r="F68" s="3" t="inlineStr"/>
-    </row>
-    <row r="69" ht="60" customHeight="1">
-      <c r="A69" s="2" t="inlineStr">
+      <c r="F77" s="3" t="inlineStr"/>
+    </row>
+    <row r="78" ht="60" customHeight="1">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-025</t>
         </is>
       </c>
-      <c r="B69" s="3" t="inlineStr">
+      <c r="B78" s="3" t="inlineStr">
         <is>
           <t>[실험체] 유키 - 머리치기!(Q) 쿨다운 수치 확인</t>
         </is>
       </c>
-      <c r="C69" s="3" t="inlineStr">
+      <c r="C78" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 유키 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D69" s="3" t="inlineStr">
+      <c r="D78" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 유키 선택
@@ -2781,32 +3078,32 @@
 4. 쿨다운 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E69" s="3" t="inlineStr">
+      <c r="E78" s="3" t="inlineStr">
         <is>
           <t>머리치기!(Q) 쿨다운: 5초
 (변경 전: 6초)</t>
         </is>
       </c>
-      <c r="F69" s="3" t="inlineStr"/>
-    </row>
-    <row r="70" ht="60" customHeight="1">
-      <c r="A70" s="2" t="inlineStr">
+      <c r="F78" s="3" t="inlineStr"/>
+    </row>
+    <row r="79" ht="60" customHeight="1">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-026</t>
         </is>
       </c>
-      <c r="B70" s="3" t="inlineStr">
+      <c r="B79" s="3" t="inlineStr">
         <is>
           <t>[실험체] 이슈트반 - 관측(Q) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C70" s="3" t="inlineStr">
+      <c r="C79" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 이슈트반 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D70" s="3" t="inlineStr">
+      <c r="D79" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 이슈트반 선택
@@ -2814,32 +3111,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E70" s="3" t="inlineStr">
+      <c r="E79" s="3" t="inlineStr">
         <is>
           <t>관측(Q) 피해량: 40/80/120/160/200(+공격력의 100%)
 (변경 전: 40/80/120/160/200(+공격력의 110%))</t>
         </is>
       </c>
-      <c r="F70" s="3" t="inlineStr"/>
-    </row>
-    <row r="71" ht="60" customHeight="1">
-      <c r="A71" s="2" t="inlineStr">
+      <c r="F79" s="3" t="inlineStr"/>
+    </row>
+    <row r="80" ht="60" customHeight="1">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-027</t>
         </is>
       </c>
-      <c r="B71" s="3" t="inlineStr">
+      <c r="B80" s="3" t="inlineStr">
         <is>
           <t>[실험체] 이슈트반 - 관측(Q) 다른 가능성 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C71" s="3" t="inlineStr">
+      <c r="C80" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 이슈트반 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D71" s="3" t="inlineStr">
+      <c r="D80" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 이슈트반 선택
@@ -2847,32 +3144,32 @@
 4. 다른 가능성 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E71" s="3" t="inlineStr">
+      <c r="E80" s="3" t="inlineStr">
         <is>
           <t>관측(Q) 다른 가능성 피해량: 40/80/120/160/200(+공격력의 100%)
 (변경 전: 40/80/120/160/200(+공격력의 110%))</t>
         </is>
       </c>
-      <c r="F71" s="3" t="inlineStr"/>
-    </row>
-    <row r="72" ht="60" customHeight="1">
-      <c r="A72" s="2" t="inlineStr">
+      <c r="F80" s="3" t="inlineStr"/>
+    </row>
+    <row r="81" ht="60" customHeight="1">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-028</t>
         </is>
       </c>
-      <c r="B72" s="3" t="inlineStr">
+      <c r="B81" s="3" t="inlineStr">
         <is>
           <t>[실험체] 츠바메 - 오의 - 생사 각인(P) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C72" s="3" t="inlineStr">
+      <c r="C81" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 츠바메 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D72" s="3" t="inlineStr">
+      <c r="D81" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 츠바메 선택
@@ -2880,32 +3177,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E72" s="3" t="inlineStr">
+      <c r="E81" s="3" t="inlineStr">
         <is>
           <t>오의 - 생사 각인(P) 피해량: 30(+추가 공격력의 25%)(+대상 최대 체력의 4/7/10(+추가 공격력의 4%)%)
 (변경 전: 30(+추가 공격력의 45%)(+대상 최대 체력의 4/7/10(+추가 공격력의 4%)%))</t>
         </is>
       </c>
-      <c r="F72" s="3" t="inlineStr"/>
-    </row>
-    <row r="73" ht="60" customHeight="1">
-      <c r="A73" s="2" t="inlineStr">
+      <c r="F81" s="3" t="inlineStr"/>
+    </row>
+    <row r="82" ht="60" customHeight="1">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-029</t>
         </is>
       </c>
-      <c r="B73" s="3" t="inlineStr">
+      <c r="B82" s="3" t="inlineStr">
         <is>
           <t>[실험체] 코렐라인 - 단죄의 섬광(Q) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C73" s="3" t="inlineStr">
+      <c r="C82" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 코렐라인 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D73" s="3" t="inlineStr">
+      <c r="D82" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 코렐라인 선택
@@ -2913,32 +3210,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E73" s="3" t="inlineStr">
+      <c r="E82" s="3" t="inlineStr">
         <is>
           <t>단죄의 섬광(Q) 피해량: 50/90/130/170/210(+스킬 증폭의 80%)
 (변경 전: 50/90/130/170/210(+스킬 증폭의 75%))</t>
         </is>
       </c>
-      <c r="F73" s="3" t="inlineStr"/>
-    </row>
-    <row r="74" ht="60" customHeight="1">
-      <c r="A74" s="2" t="inlineStr">
+      <c r="F82" s="3" t="inlineStr"/>
+    </row>
+    <row r="83" ht="60" customHeight="1">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-030</t>
         </is>
       </c>
-      <c r="B74" s="3" t="inlineStr">
+      <c r="B83" s="3" t="inlineStr">
         <is>
           <t>[실험체] 코렐라인 - 죄의 굴레(E) 백경 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C74" s="3" t="inlineStr">
+      <c r="C83" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 코렐라인 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D74" s="3" t="inlineStr">
+      <c r="D83" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 코렐라인 선택
@@ -2946,32 +3243,32 @@
 4. 백경 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E74" s="3" t="inlineStr">
+      <c r="E83" s="3" t="inlineStr">
         <is>
           <t>죄의 굴레(E) 백경 피해량: 80/110/140/170/200(+스킬 증폭의 65%)
 (변경 전: 80/110/140/170/200(+스킬 증폭의 70%))</t>
         </is>
       </c>
-      <c r="F74" s="3" t="inlineStr"/>
-    </row>
-    <row r="75" ht="60" customHeight="1">
-      <c r="A75" s="2" t="inlineStr">
+      <c r="F83" s="3" t="inlineStr"/>
+    </row>
+    <row r="84" ht="60" customHeight="1">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-031</t>
         </is>
       </c>
-      <c r="B75" s="3" t="inlineStr">
+      <c r="B84" s="3" t="inlineStr">
         <is>
           <t>[실험체] 코렐라인 - 죄의 굴레(E) 흑경 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C75" s="3" t="inlineStr">
+      <c r="C84" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 코렐라인 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D75" s="3" t="inlineStr">
+      <c r="D84" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 코렐라인 선택
@@ -2979,32 +3276,32 @@
 4. 흑경 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E75" s="3" t="inlineStr">
+      <c r="E84" s="3" t="inlineStr">
         <is>
           <t>죄의 굴레(E) 흑경 피해량: 80/110/140/170/200(+스킬 증폭의 65%)
 (변경 전: 80/110/140/170/200(+스킬 증폭의 70%))</t>
         </is>
       </c>
-      <c r="F75" s="3" t="inlineStr"/>
-    </row>
-    <row r="76" ht="60" customHeight="1">
-      <c r="A76" s="2" t="inlineStr">
+      <c r="F84" s="3" t="inlineStr"/>
+    </row>
+    <row r="85" ht="60" customHeight="1">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-032</t>
         </is>
       </c>
-      <c r="B76" s="3" t="inlineStr">
+      <c r="B85" s="3" t="inlineStr">
         <is>
           <t>[실험체] 코렐라인 - 죄의 굴레(E) 흑경 방어력 감소량 수치 확인</t>
         </is>
       </c>
-      <c r="C76" s="3" t="inlineStr">
+      <c r="C85" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 코렐라인 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D76" s="3" t="inlineStr">
+      <c r="D85" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 코렐라인 선택
@@ -3012,32 +3309,32 @@
 4. 흑경 방어력 감소량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E76" s="3" t="inlineStr">
+      <c r="E85" s="3" t="inlineStr">
         <is>
           <t>죄의 굴레(E) 흑경 방어력 감소량: 10/11/12/13/14%
 (변경 전: 12/13/14/15/16%)</t>
         </is>
       </c>
-      <c r="F76" s="3" t="inlineStr"/>
-    </row>
-    <row r="77" ht="60" customHeight="1">
-      <c r="A77" s="2" t="inlineStr">
+      <c r="F85" s="3" t="inlineStr"/>
+    </row>
+    <row r="86" ht="60" customHeight="1">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-033</t>
         </is>
       </c>
-      <c r="B77" s="3" t="inlineStr">
+      <c r="B86" s="3" t="inlineStr">
         <is>
           <t>[실험체] 클로에 - 살아 있는 마리오네트(P) 니나 부활 시 클로에 체력 소모량 현재 체력의 수치 확인</t>
         </is>
       </c>
-      <c r="C77" s="3" t="inlineStr">
+      <c r="C86" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 클로에 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D77" s="3" t="inlineStr">
+      <c r="D86" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 클로에 선택
@@ -3045,32 +3342,32 @@
 4. 니나 부활 시 클로에 체력 소모량 현재 체력의 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E77" s="3" t="inlineStr">
+      <c r="E86" s="3" t="inlineStr">
         <is>
           <t>살아 있는 마리오네트(P) 니나 부활 시 클로에 체력 소모량 현재 체력의: 20%
 (변경 전: 30%)</t>
         </is>
       </c>
-      <c r="F77" s="3" t="inlineStr"/>
-    </row>
-    <row r="78" ht="60" customHeight="1">
-      <c r="A78" s="2" t="inlineStr">
+      <c r="F86" s="3" t="inlineStr"/>
+    </row>
+    <row r="87" ht="60" customHeight="1">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-034</t>
         </is>
       </c>
-      <c r="B78" s="3" t="inlineStr">
+      <c r="B87" s="3" t="inlineStr">
         <is>
           <t>[실험체] 키아라 - 뒤틀린 기도(W) 최소 보호막량 수치 확인</t>
         </is>
       </c>
-      <c r="C78" s="3" t="inlineStr">
+      <c r="C87" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 키아라 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D78" s="3" t="inlineStr">
+      <c r="D87" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 키아라 선택
@@ -3078,32 +3375,32 @@
 4. 최소 보호막량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E78" s="3" t="inlineStr">
+      <c r="E87" s="3" t="inlineStr">
         <is>
           <t>뒤틀린 기도(W) 최소 보호막량: 110/130/150/170/190(+스킬 증폭의 50%)
 (변경 전: 90/110/130/150/170(+스킬 증폭의 50%))</t>
         </is>
       </c>
-      <c r="F78" s="3" t="inlineStr"/>
-    </row>
-    <row r="79" ht="60" customHeight="1">
-      <c r="A79" s="2" t="inlineStr">
+      <c r="F87" s="3" t="inlineStr"/>
+    </row>
+    <row r="88" ht="60" customHeight="1">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-035</t>
         </is>
       </c>
-      <c r="B79" s="3" t="inlineStr">
+      <c r="B88" s="3" t="inlineStr">
         <is>
           <t>[실험체] 키아라 - 뒤틀린 기도(W) 최대 보호막량 수치 확인</t>
         </is>
       </c>
-      <c r="C79" s="3" t="inlineStr">
+      <c r="C88" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 키아라 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D79" s="3" t="inlineStr">
+      <c r="D88" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 키아라 선택
@@ -3111,32 +3408,32 @@
 4. 최대 보호막량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E79" s="3" t="inlineStr">
+      <c r="E88" s="3" t="inlineStr">
         <is>
           <t>뒤틀린 기도(W) 최대 보호막량: 165/195/225/255/285(+스킬 증폭의 75%)
 (변경 전: 135/165/195/225/255(+스킬 증폭의 75%))</t>
         </is>
       </c>
-      <c r="F79" s="3" t="inlineStr"/>
-    </row>
-    <row r="80" ht="60" customHeight="1">
-      <c r="A80" s="2" t="inlineStr">
+      <c r="F88" s="3" t="inlineStr"/>
+    </row>
+    <row r="89" ht="60" customHeight="1">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-036</t>
         </is>
       </c>
-      <c r="B80" s="3" t="inlineStr">
+      <c r="B89" s="3" t="inlineStr">
         <is>
           <t>[실험체] 펜리르 - 먹잇감 추적(W) 본능적 후퇴(W2) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C80" s="3" t="inlineStr">
+      <c r="C89" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 펜리르 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D80" s="3" t="inlineStr">
+      <c r="D89" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 펜리르 선택
@@ -3144,32 +3441,32 @@
 4. 본능적 후퇴(W2) 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E80" s="3" t="inlineStr">
+      <c r="E89" s="3" t="inlineStr">
         <is>
           <t>먹잇감 추적(W) 본능적 후퇴(W2) 피해량: 30/55/80/105/130(+공격력의 60%)
 (변경 전: 20/40/60/80/100(+공격력의 60%))</t>
         </is>
       </c>
-      <c r="F80" s="3" t="inlineStr"/>
-    </row>
-    <row r="81" ht="60" customHeight="1">
-      <c r="A81" s="2" t="inlineStr">
+      <c r="F89" s="3" t="inlineStr"/>
+    </row>
+    <row r="90" ht="60" customHeight="1">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-037</t>
         </is>
       </c>
-      <c r="B81" s="3" t="inlineStr">
+      <c r="B90" s="3" t="inlineStr">
         <is>
           <t>[실험체] 프리야 - 대지의 메아리(R) 받는 피해 감소 수치 확인</t>
         </is>
       </c>
-      <c r="C81" s="3" t="inlineStr">
+      <c r="C90" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 프리야 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D81" s="3" t="inlineStr">
+      <c r="D90" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 프리야 선택
@@ -3177,32 +3474,32 @@
 4. 받는 피해 감소 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E81" s="3" t="inlineStr">
+      <c r="E90" s="3" t="inlineStr">
         <is>
           <t>대지의 메아리(R) 받는 피해 감소: 40%
 (변경 전: 50%)</t>
         </is>
       </c>
-      <c r="F81" s="3" t="inlineStr"/>
-    </row>
-    <row r="82" ht="60" customHeight="1">
-      <c r="A82" s="2" t="inlineStr">
+      <c r="F90" s="3" t="inlineStr"/>
+    </row>
+    <row r="91" ht="60" customHeight="1">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-038</t>
         </is>
       </c>
-      <c r="B82" s="3" t="inlineStr">
+      <c r="B91" s="3" t="inlineStr">
         <is>
           <t>[실험체] 프리야 - 포르타멘토(W) 아군 이동 속도 증가 수치 확인</t>
         </is>
       </c>
-      <c r="C82" s="3" t="inlineStr">
+      <c r="C91" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 프리야 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D82" s="3" t="inlineStr">
+      <c r="D91" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 프리야 선택
@@ -3210,32 +3507,32 @@
 4. 아군 이동 속도 증가 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E82" s="3" t="inlineStr">
+      <c r="E91" s="3" t="inlineStr">
         <is>
           <t>포르타멘토(W) 아군 이동 속도 증가: 8/9/10/11/12%
 (변경 전: 10/11/12/13/14%)</t>
         </is>
       </c>
-      <c r="F82" s="3" t="inlineStr"/>
-    </row>
-    <row r="83" ht="60" customHeight="1">
-      <c r="A83" s="2" t="inlineStr">
+      <c r="F91" s="3" t="inlineStr"/>
+    </row>
+    <row r="92" ht="60" customHeight="1">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-039</t>
         </is>
       </c>
-      <c r="B83" s="3" t="inlineStr">
+      <c r="B92" s="3" t="inlineStr">
         <is>
           <t>[실험체] 현우 - 허세(W) 방어력 증가 수치 확인</t>
         </is>
       </c>
-      <c r="C83" s="3" t="inlineStr">
+      <c r="C92" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 현우 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D83" s="3" t="inlineStr">
+      <c r="D92" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 현우 선택
@@ -3243,32 +3540,32 @@
 4. 방어력 증가 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E83" s="3" t="inlineStr">
+      <c r="E92" s="3" t="inlineStr">
         <is>
           <t>허세(W) 방어력 증가: 14/21/28/35/42(+방어력 10당 1)
 (변경 전: 14/23/32/41/50(+방어력 10당 1))</t>
         </is>
       </c>
-      <c r="F83" s="3" t="inlineStr"/>
-    </row>
-    <row r="84" ht="60" customHeight="1">
-      <c r="A84" s="4" t="inlineStr">
+      <c r="F92" s="3" t="inlineStr"/>
+    </row>
+    <row r="93" ht="60" customHeight="1">
+      <c r="A93" s="4" t="inlineStr">
         <is>
           <t>TC-10.6-040</t>
         </is>
       </c>
-      <c r="B84" s="5" t="inlineStr">
+      <c r="B93" s="5" t="inlineStr">
         <is>
           <t>[실험체] 라우라 - 채찍 무기 숙련도 레벨 당 공격 속도 수치 확인</t>
         </is>
       </c>
-      <c r="C84" s="5" t="inlineStr">
+      <c r="C93" s="5" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 라우라 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D84" s="5" t="inlineStr">
+      <c r="D93" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 라우라 선택
@@ -3276,32 +3573,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E84" s="5" t="inlineStr">
+      <c r="E93" s="5" t="inlineStr">
         <is>
           <t>채찍 무기 숙련도 레벨 당 공격 속도: 3.3%
 (변경 전: 2.8%)</t>
         </is>
       </c>
-      <c r="F84" s="5" t="inlineStr"/>
-    </row>
-    <row r="85" ht="60" customHeight="1">
-      <c r="A85" s="4" t="inlineStr">
+      <c r="F93" s="5" t="inlineStr"/>
+    </row>
+    <row r="94" ht="60" customHeight="1">
+      <c r="A94" s="4" t="inlineStr">
         <is>
           <t>TC-10.6-041</t>
         </is>
       </c>
-      <c r="B85" s="5" t="inlineStr">
+      <c r="B94" s="5" t="inlineStr">
         <is>
           <t>[실험체] 레니 - 주는 보호막 효과 수치 확인</t>
         </is>
       </c>
-      <c r="C85" s="5" t="inlineStr">
+      <c r="C94" s="5" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 레니 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D85" s="5" t="inlineStr">
+      <c r="D94" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 레니 선택
@@ -3309,32 +3606,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E85" s="5" t="inlineStr">
+      <c r="E94" s="5" t="inlineStr">
         <is>
           <t>주는 보호막 효과: 70%
 (변경 전: 65%)</t>
         </is>
       </c>
-      <c r="F85" s="5" t="inlineStr"/>
-    </row>
-    <row r="86" ht="60" customHeight="1">
-      <c r="A86" s="4" t="inlineStr">
+      <c r="F94" s="5" t="inlineStr"/>
+    </row>
+    <row r="95" ht="60" customHeight="1">
+      <c r="A95" s="4" t="inlineStr">
         <is>
           <t>TC-10.6-042</t>
         </is>
       </c>
-      <c r="B86" s="5" t="inlineStr">
+      <c r="B95" s="5" t="inlineStr">
         <is>
           <t>[실험체] 리 다이린 - 레벨 당 공격력 수치 확인</t>
         </is>
       </c>
-      <c r="C86" s="5" t="inlineStr">
+      <c r="C95" s="5" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 리 다이린 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D86" s="5" t="inlineStr">
+      <c r="D95" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 리 다이린 선택
@@ -3342,32 +3639,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E86" s="5" t="inlineStr">
+      <c r="E95" s="5" t="inlineStr">
         <is>
           <t>레벨 당 공격력: 5
 (변경 전: 4.8)</t>
         </is>
       </c>
-      <c r="F86" s="5" t="inlineStr"/>
-    </row>
-    <row r="87" ht="60" customHeight="1">
-      <c r="A87" s="4" t="inlineStr">
+      <c r="F95" s="5" t="inlineStr"/>
+    </row>
+    <row r="96" ht="60" customHeight="1">
+      <c r="A96" s="4" t="inlineStr">
         <is>
           <t>TC-10.6-043</t>
         </is>
       </c>
-      <c r="B87" s="5" t="inlineStr">
+      <c r="B96" s="5" t="inlineStr">
         <is>
           <t>[실험체] 버니스 - 기본 공격력 수치 확인</t>
         </is>
       </c>
-      <c r="C87" s="5" t="inlineStr">
+      <c r="C96" s="5" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 버니스 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D87" s="5" t="inlineStr">
+      <c r="D96" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 버니스 선택
@@ -3375,32 +3672,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E87" s="5" t="inlineStr">
+      <c r="E96" s="5" t="inlineStr">
         <is>
           <t>기본 공격력: 37
 (변경 전: 35)</t>
         </is>
       </c>
-      <c r="F87" s="5" t="inlineStr"/>
-    </row>
-    <row r="88" ht="60" customHeight="1">
-      <c r="A88" s="4" t="inlineStr">
+      <c r="F96" s="5" t="inlineStr"/>
+    </row>
+    <row r="97" ht="60" customHeight="1">
+      <c r="A97" s="4" t="inlineStr">
         <is>
           <t>TC-10.6-044</t>
         </is>
       </c>
-      <c r="B88" s="5" t="inlineStr">
+      <c r="B97" s="5" t="inlineStr">
         <is>
           <t>[실험체] 샬럿 - 주는 보호막 효과 수치 확인</t>
         </is>
       </c>
-      <c r="C88" s="5" t="inlineStr">
+      <c r="C97" s="5" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 샬럿 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D88" s="5" t="inlineStr">
+      <c r="D97" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 샬럿 선택
@@ -3408,32 +3705,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E88" s="5" t="inlineStr">
+      <c r="E97" s="5" t="inlineStr">
         <is>
           <t>주는 보호막 효과: 70%
 (변경 전: 65%)</t>
         </is>
       </c>
-      <c r="F88" s="5" t="inlineStr"/>
-    </row>
-    <row r="89" ht="60" customHeight="1">
-      <c r="A89" s="4" t="inlineStr">
+      <c r="F97" s="5" t="inlineStr"/>
+    </row>
+    <row r="98" ht="60" customHeight="1">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t>TC-10.6-045</t>
         </is>
       </c>
-      <c r="B89" s="5" t="inlineStr">
+      <c r="B98" s="5" t="inlineStr">
         <is>
           <t>[실험체] 슈린 - 레벨 당 공격력 수치 확인</t>
         </is>
       </c>
-      <c r="C89" s="5" t="inlineStr">
+      <c r="C98" s="5" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 슈린 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D89" s="5" t="inlineStr">
+      <c r="D98" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 슈린 선택
@@ -3441,32 +3738,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E89" s="5" t="inlineStr">
+      <c r="E98" s="5" t="inlineStr">
         <is>
           <t>레벨 당 공격력: 4.6
 (변경 전: 4.3)</t>
         </is>
       </c>
-      <c r="F89" s="5" t="inlineStr"/>
-    </row>
-    <row r="90" ht="60" customHeight="1">
-      <c r="A90" s="4" t="inlineStr">
+      <c r="F98" s="5" t="inlineStr"/>
+    </row>
+    <row r="99" ht="60" customHeight="1">
+      <c r="A99" s="4" t="inlineStr">
         <is>
           <t>TC-10.6-046</t>
         </is>
       </c>
-      <c r="B90" s="5" t="inlineStr">
+      <c r="B99" s="5" t="inlineStr">
         <is>
           <t>[실험체] 실비아 - 주는 회복 효과 수치 확인</t>
         </is>
       </c>
-      <c r="C90" s="5" t="inlineStr">
+      <c r="C99" s="5" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 실비아 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D90" s="5" t="inlineStr">
+      <c r="D99" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 실비아 선택
@@ -3474,32 +3771,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E90" s="5" t="inlineStr">
+      <c r="E99" s="5" t="inlineStr">
         <is>
           <t>주는 회복 효과: 70%
 (변경 전: 65%)</t>
         </is>
       </c>
-      <c r="F90" s="5" t="inlineStr"/>
-    </row>
-    <row r="91" ht="60" customHeight="1">
-      <c r="A91" s="4" t="inlineStr">
+      <c r="F99" s="5" t="inlineStr"/>
+    </row>
+    <row r="100" ht="60" customHeight="1">
+      <c r="A100" s="4" t="inlineStr">
         <is>
           <t>TC-10.6-047</t>
         </is>
       </c>
-      <c r="B91" s="5" t="inlineStr">
+      <c r="B100" s="5" t="inlineStr">
         <is>
           <t>[실험체] 아르다 - 주는 회복 효과 수치 확인</t>
         </is>
       </c>
-      <c r="C91" s="5" t="inlineStr">
+      <c r="C100" s="5" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 아르다 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D91" s="5" t="inlineStr">
+      <c r="D100" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 아르다 선택
@@ -3507,32 +3804,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E91" s="5" t="inlineStr">
+      <c r="E100" s="5" t="inlineStr">
         <is>
           <t>주는 회복 효과: 70%
 (변경 전: 65%)</t>
         </is>
       </c>
-      <c r="F91" s="5" t="inlineStr"/>
-    </row>
-    <row r="92" ht="60" customHeight="1">
-      <c r="A92" s="4" t="inlineStr">
+      <c r="F100" s="5" t="inlineStr"/>
+    </row>
+    <row r="101" ht="60" customHeight="1">
+      <c r="A101" s="4" t="inlineStr">
         <is>
           <t>TC-10.6-048</t>
         </is>
       </c>
-      <c r="B92" s="5" t="inlineStr">
+      <c r="B101" s="5" t="inlineStr">
         <is>
           <t>[실험체] 아이솔 - 권총 무기 숙련도 레벨 당 스킬 증폭 수치 확인</t>
         </is>
       </c>
-      <c r="C92" s="5" t="inlineStr">
+      <c r="C101" s="5" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 아이솔 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D92" s="5" t="inlineStr">
+      <c r="D101" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 아이솔 선택
@@ -3540,32 +3837,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E92" s="5" t="inlineStr">
+      <c r="E101" s="5" t="inlineStr">
         <is>
           <t>권총 무기 숙련도 레벨 당 스킬 증폭: 4.5%
 (변경 전: 4.4%)</t>
         </is>
       </c>
-      <c r="F92" s="5" t="inlineStr"/>
-    </row>
-    <row r="93" ht="60" customHeight="1">
-      <c r="A93" s="4" t="inlineStr">
+      <c r="F101" s="5" t="inlineStr"/>
+    </row>
+    <row r="102" ht="60" customHeight="1">
+      <c r="A102" s="4" t="inlineStr">
         <is>
           <t>TC-10.6-049</t>
         </is>
       </c>
-      <c r="B93" s="5" t="inlineStr">
+      <c r="B102" s="5" t="inlineStr">
         <is>
           <t>[실험체] 에키온 - 기본 공격력 수치 확인</t>
         </is>
       </c>
-      <c r="C93" s="5" t="inlineStr">
+      <c r="C102" s="5" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 에키온 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D93" s="5" t="inlineStr">
+      <c r="D102" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 에키온 선택
@@ -3573,32 +3870,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E93" s="5" t="inlineStr">
+      <c r="E102" s="5" t="inlineStr">
         <is>
           <t>기본 공격력: 35
 (변경 전: 39)</t>
         </is>
       </c>
-      <c r="F93" s="5" t="inlineStr"/>
-    </row>
-    <row r="94" ht="60" customHeight="1">
-      <c r="A94" s="4" t="inlineStr">
+      <c r="F102" s="5" t="inlineStr"/>
+    </row>
+    <row r="103" ht="60" customHeight="1">
+      <c r="A103" s="4" t="inlineStr">
         <is>
           <t>TC-10.6-050</t>
         </is>
       </c>
-      <c r="B94" s="5" t="inlineStr">
+      <c r="B103" s="5" t="inlineStr">
         <is>
           <t>[실험체] 이렘 - 투척 무기 숙련도 레벨 당 공격 속도 수치 확인</t>
         </is>
       </c>
-      <c r="C94" s="5" t="inlineStr">
+      <c r="C103" s="5" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 이렘 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D94" s="5" t="inlineStr">
+      <c r="D103" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 이렘 선택
@@ -3606,32 +3903,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E94" s="5" t="inlineStr">
+      <c r="E103" s="5" t="inlineStr">
         <is>
           <t>투척 무기 숙련도 레벨 당 공격 속도: 2.2%
 (변경 전: 1.6%)</t>
         </is>
       </c>
-      <c r="F94" s="5" t="inlineStr"/>
-    </row>
-    <row r="95" ht="60" customHeight="1">
-      <c r="A95" s="4" t="inlineStr">
+      <c r="F103" s="5" t="inlineStr"/>
+    </row>
+    <row r="104" ht="60" customHeight="1">
+      <c r="A104" s="4" t="inlineStr">
         <is>
           <t>TC-10.6-051</t>
         </is>
       </c>
-      <c r="B95" s="5" t="inlineStr">
+      <c r="B104" s="5" t="inlineStr">
         <is>
           <t>[실험체] 카밀로 - 레이피어 무기 숙련도 레벨 당 기본 공격 증폭 수치 확인</t>
         </is>
       </c>
-      <c r="C95" s="5" t="inlineStr">
+      <c r="C104" s="5" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 카밀로 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D95" s="5" t="inlineStr">
+      <c r="D104" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 카밀로 선택
@@ -3639,32 +3936,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E95" s="5" t="inlineStr">
+      <c r="E104" s="5" t="inlineStr">
         <is>
           <t>레이피어 무기 숙련도 레벨 당 기본 공격 증폭: 1.4%
 (변경 전: 1.5%)</t>
         </is>
       </c>
-      <c r="F95" s="5" t="inlineStr"/>
-    </row>
-    <row r="96" ht="60" customHeight="1">
-      <c r="A96" s="4" t="inlineStr">
+      <c r="F104" s="5" t="inlineStr"/>
+    </row>
+    <row r="105" ht="60" customHeight="1">
+      <c r="A105" s="4" t="inlineStr">
         <is>
           <t>TC-10.6-052</t>
         </is>
       </c>
-      <c r="B96" s="5" t="inlineStr">
+      <c r="B105" s="5" t="inlineStr">
         <is>
           <t>[실험체] 캐시 - 기본 체력 수치 확인</t>
         </is>
       </c>
-      <c r="C96" s="5" t="inlineStr">
+      <c r="C105" s="5" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 캐시 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D96" s="5" t="inlineStr">
+      <c r="D105" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 캐시 선택
@@ -3672,32 +3969,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E96" s="5" t="inlineStr">
+      <c r="E105" s="5" t="inlineStr">
         <is>
           <t>기본 체력: 970
 (변경 전: 940)</t>
         </is>
       </c>
-      <c r="F96" s="5" t="inlineStr"/>
-    </row>
-    <row r="97" ht="60" customHeight="1">
-      <c r="A97" s="4" t="inlineStr">
+      <c r="F105" s="5" t="inlineStr"/>
+    </row>
+    <row r="106" ht="60" customHeight="1">
+      <c r="A106" s="4" t="inlineStr">
         <is>
           <t>TC-10.6-053</t>
         </is>
       </c>
-      <c r="B97" s="5" t="inlineStr">
+      <c r="B106" s="5" t="inlineStr">
         <is>
           <t>[실험체] 펜리르 - 레벨 당 체력 수치 확인</t>
         </is>
       </c>
-      <c r="C97" s="5" t="inlineStr">
+      <c r="C106" s="5" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 펜리르 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D97" s="5" t="inlineStr">
+      <c r="D106" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 펜리르 선택
@@ -3705,32 +4002,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E97" s="5" t="inlineStr">
+      <c r="E106" s="5" t="inlineStr">
         <is>
           <t>레벨 당 체력: 94
 (변경 전: 92)</t>
         </is>
       </c>
-      <c r="F97" s="5" t="inlineStr"/>
-    </row>
-    <row r="98" ht="60" customHeight="1">
-      <c r="A98" s="4" t="inlineStr">
+      <c r="F106" s="5" t="inlineStr"/>
+    </row>
+    <row r="107" ht="60" customHeight="1">
+      <c r="A107" s="4" t="inlineStr">
         <is>
           <t>TC-10.6-054</t>
         </is>
       </c>
-      <c r="B98" s="5" t="inlineStr">
+      <c r="B107" s="5" t="inlineStr">
         <is>
           <t>[실험체] 피오라 - 레이피어 무기 숙련도 레벨 당 스킬 증폭 수치 확인</t>
         </is>
       </c>
-      <c r="C98" s="5" t="inlineStr">
+      <c r="C107" s="5" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 피오라 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D98" s="5" t="inlineStr">
+      <c r="D107" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 피오라 선택
@@ -3738,32 +4035,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E98" s="5" t="inlineStr">
+      <c r="E107" s="5" t="inlineStr">
         <is>
           <t>레이피어 무기 숙련도 레벨 당 스킬 증폭: 4.2%
 (변경 전: 4.3%)</t>
         </is>
       </c>
-      <c r="F98" s="5" t="inlineStr"/>
-    </row>
-    <row r="99" ht="60" customHeight="1">
-      <c r="A99" s="4" t="inlineStr">
+      <c r="F107" s="5" t="inlineStr"/>
+    </row>
+    <row r="108" ht="60" customHeight="1">
+      <c r="A108" s="4" t="inlineStr">
         <is>
           <t>TC-10.6-055</t>
         </is>
       </c>
-      <c r="B99" s="5" t="inlineStr">
+      <c r="B108" s="5" t="inlineStr">
         <is>
           <t>[실험체] 현우 - 톤파 무기 숙련도 레벨 당 스킬 증폭 수치 확인</t>
         </is>
       </c>
-      <c r="C99" s="5" t="inlineStr">
+      <c r="C108" s="5" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 현우 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D99" s="5" t="inlineStr">
+      <c r="D108" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 현우 선택
@@ -3771,32 +4068,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E99" s="5" t="inlineStr">
+      <c r="E108" s="5" t="inlineStr">
         <is>
           <t>톤파 무기 숙련도 레벨 당 스킬 증폭: 4.5%
 (변경 전: 4.3%)</t>
         </is>
       </c>
-      <c r="F99" s="5" t="inlineStr"/>
-    </row>
-    <row r="100" ht="60" customHeight="1">
-      <c r="A100" s="2" t="inlineStr">
+      <c r="F108" s="5" t="inlineStr"/>
+    </row>
+    <row r="109" ht="60" customHeight="1">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>TC-10.5a-001</t>
         </is>
       </c>
-      <c r="B100" s="3" t="inlineStr">
+      <c r="B109" s="3" t="inlineStr">
         <is>
           <t>[실험체] 코렐라인 - 단죄의 섬광(Q) 백경 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C100" s="3" t="inlineStr">
+      <c r="C109" s="3" t="inlineStr">
         <is>
           <t>· 10.5a 패치 적용 완료
 · 코렐라인 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D100" s="3" t="inlineStr">
+      <c r="D109" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 코렐라인 선택
@@ -3804,32 +4101,32 @@
 4. 백경 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E100" s="3" t="inlineStr">
+      <c r="E109" s="3" t="inlineStr">
         <is>
           <t>단죄의 섬광(Q) 백경 피해량: 60/105/150/195/240(+스킬 증폭의 80%)(+현재 체력의 4/6/8/10/12%)
 (변경 전: 60/105/150/195/240(+스킬 증폭의 85%)(+현재 체력의 4/6/8/10/12%))</t>
         </is>
       </c>
-      <c r="F100" s="3" t="inlineStr"/>
-    </row>
-    <row r="101" ht="60" customHeight="1">
-      <c r="A101" s="2" t="inlineStr">
+      <c r="F109" s="3" t="inlineStr"/>
+    </row>
+    <row r="110" ht="60" customHeight="1">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>TC-10.5a-002</t>
         </is>
       </c>
-      <c r="B101" s="3" t="inlineStr">
+      <c r="B110" s="3" t="inlineStr">
         <is>
           <t>[실험체] 코렐라인 - 단죄의 섬광(Q) 흑경 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C101" s="3" t="inlineStr">
+      <c r="C110" s="3" t="inlineStr">
         <is>
           <t>· 10.5a 패치 적용 완료
 · 코렐라인 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D101" s="3" t="inlineStr">
+      <c r="D110" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 코렐라인 선택
@@ -3837,32 +4134,32 @@
 4. 흑경 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E101" s="3" t="inlineStr">
+      <c r="E110" s="3" t="inlineStr">
         <is>
           <t>단죄의 섬광(Q) 흑경 피해량: 60/105/150/195/240(+스킬 증폭의 80%)(+잃은 체력의 3/6/9/12/15%)
 (변경 전: 60/105/150/195/240(+스킬 증폭의 85%)(+잃은 체력의 3/6/9/12/15%))</t>
         </is>
       </c>
-      <c r="F101" s="3" t="inlineStr"/>
-    </row>
-    <row r="102" ht="60" customHeight="1">
-      <c r="A102" s="4" t="inlineStr">
+      <c r="F110" s="3" t="inlineStr"/>
+    </row>
+    <row r="111" ht="60" customHeight="1">
+      <c r="A111" s="4" t="inlineStr">
         <is>
           <t>TC-10.5a-003</t>
         </is>
       </c>
-      <c r="B102" s="5" t="inlineStr">
+      <c r="B111" s="5" t="inlineStr">
         <is>
           <t>[실험체] 현우 - 최대 체력 수치 확인</t>
         </is>
       </c>
-      <c r="C102" s="5" t="inlineStr">
+      <c r="C111" s="5" t="inlineStr">
         <is>
           <t>· 10.5a 패치 적용 완료
 · 현우 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D102" s="5" t="inlineStr">
+      <c r="D111" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 현우 선택
@@ -3870,32 +4167,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E102" s="5" t="inlineStr">
+      <c r="E111" s="5" t="inlineStr">
         <is>
           <t>최대 체력: 960
 (변경 전: 1000)</t>
         </is>
       </c>
-      <c r="F102" s="5" t="inlineStr"/>
-    </row>
-    <row r="103" ht="60" customHeight="1">
-      <c r="A103" s="2" t="inlineStr">
+      <c r="F111" s="5" t="inlineStr"/>
+    </row>
+    <row r="112" ht="60" customHeight="1">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-001</t>
         </is>
       </c>
-      <c r="B103" s="3" t="inlineStr">
+      <c r="B112" s="3" t="inlineStr">
         <is>
           <t>[실험체] 나타폰 - 슬로우 셔터(P) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C103" s="3" t="inlineStr">
+      <c r="C112" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 나타폰 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D103" s="3" t="inlineStr">
+      <c r="D112" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 나타폰 선택
@@ -3903,32 +4200,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E103" s="3" t="inlineStr">
+      <c r="E112" s="3" t="inlineStr">
         <is>
           <t>슬로우 셔터(P) 피해량: 30/60/90(+공격 속도의 20%)(+스킬 증폭의 65%)
 (변경 전: 40/70/100(+공격 속도의 20%)(+스킬 증폭의 65%))</t>
         </is>
       </c>
-      <c r="F103" s="3" t="inlineStr"/>
-    </row>
-    <row r="104" ht="60" customHeight="1">
-      <c r="A104" s="2" t="inlineStr">
+      <c r="F112" s="3" t="inlineStr"/>
+    </row>
+    <row r="113" ht="60" customHeight="1">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-002</t>
         </is>
       </c>
-      <c r="B104" s="3" t="inlineStr">
+      <c r="B113" s="3" t="inlineStr">
         <is>
           <t>[실험체] 다르코 - 고리대금(Q) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C104" s="3" t="inlineStr">
+      <c r="C113" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 다르코 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D104" s="3" t="inlineStr">
+      <c r="D113" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 다르코 선택
@@ -3936,32 +4233,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E104" s="3" t="inlineStr">
+      <c r="E113" s="3" t="inlineStr">
         <is>
           <t>고리대금(Q) 피해량: 20/40/60/80/100(+공격력의 40%)(+대상 최대 체력의 2/3/4/5/6%)
 (변경 전: 20/40/60/80/100(+공격력의 40%)(+대상 최대 체력의 1/2/3/4/5%))</t>
         </is>
       </c>
-      <c r="F104" s="3" t="inlineStr"/>
-    </row>
-    <row r="105" ht="60" customHeight="1">
-      <c r="A105" s="2" t="inlineStr">
+      <c r="F113" s="3" t="inlineStr"/>
+    </row>
+    <row r="114" ht="60" customHeight="1">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-003</t>
         </is>
       </c>
-      <c r="B105" s="3" t="inlineStr">
+      <c r="B114" s="3" t="inlineStr">
         <is>
           <t>[실험체] 띠아 - 색칠놀이(E) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C105" s="3" t="inlineStr">
+      <c r="C114" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 띠아 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D105" s="3" t="inlineStr">
+      <c r="D114" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 띠아 선택
@@ -3969,32 +4266,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E105" s="3" t="inlineStr">
+      <c r="E114" s="3" t="inlineStr">
         <is>
           <t>색칠놀이(E) 피해량: 40/90/140/190/240(+스킬 증폭의 90%)
 (변경 전: 40/90/140/190/240(+스킬 증폭의 80%))</t>
         </is>
       </c>
-      <c r="F105" s="3" t="inlineStr"/>
-    </row>
-    <row r="106" ht="60" customHeight="1">
-      <c r="A106" s="2" t="inlineStr">
+      <c r="F114" s="3" t="inlineStr"/>
+    </row>
+    <row r="115" ht="60" customHeight="1">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-004</t>
         </is>
       </c>
-      <c r="B106" s="3" t="inlineStr">
+      <c r="B115" s="3" t="inlineStr">
         <is>
           <t>[실험체] 라우라 - 날카로운 꽃(Q) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C106" s="3" t="inlineStr">
+      <c r="C115" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 라우라 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D106" s="3" t="inlineStr">
+      <c r="D115" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 라우라 선택
@@ -4002,32 +4299,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E106" s="3" t="inlineStr">
+      <c r="E115" s="3" t="inlineStr">
         <is>
           <t>날카로운 꽃(Q) 피해량: 50/75/100/125/150(+스킬 증폭의 60%)
 (변경 전: 50/75/100/125/150(+스킬 증폭의 55%))</t>
         </is>
       </c>
-      <c r="F106" s="3" t="inlineStr"/>
-    </row>
-    <row r="107" ht="60" customHeight="1">
-      <c r="A107" s="2" t="inlineStr">
+      <c r="F115" s="3" t="inlineStr"/>
+    </row>
+    <row r="116" ht="60" customHeight="1">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-005</t>
         </is>
       </c>
-      <c r="B107" s="3" t="inlineStr">
+      <c r="B116" s="3" t="inlineStr">
         <is>
           <t>[실험체] 레녹스 - 위풍당당(P) 쿨다운 수치 확인</t>
         </is>
       </c>
-      <c r="C107" s="3" t="inlineStr">
+      <c r="C116" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 레녹스 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D107" s="3" t="inlineStr">
+      <c r="D116" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 레녹스 선택
@@ -4035,32 +4332,32 @@
 4. 쿨다운 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E107" s="3" t="inlineStr">
+      <c r="E116" s="3" t="inlineStr">
         <is>
           <t>위풍당당(P) 쿨다운: 15/13/11초
 (변경 전: 14/12/10초)</t>
         </is>
       </c>
-      <c r="F107" s="3" t="inlineStr"/>
-    </row>
-    <row r="108" ht="60" customHeight="1">
-      <c r="A108" s="2" t="inlineStr">
+      <c r="F116" s="3" t="inlineStr"/>
+    </row>
+    <row r="117" ht="60" customHeight="1">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-006</t>
         </is>
       </c>
-      <c r="B108" s="3" t="inlineStr">
+      <c r="B117" s="3" t="inlineStr">
         <is>
           <t>[실험체] 마르티나 - 되감기 - 방송 중(E) 체력 회복량 받은 피해의 수치 확인</t>
         </is>
       </c>
-      <c r="C108" s="3" t="inlineStr">
+      <c r="C117" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 마르티나 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D108" s="3" t="inlineStr">
+      <c r="D117" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 마르티나 선택
@@ -4068,32 +4365,32 @@
 4. 체력 회복량 받은 피해의 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E108" s="3" t="inlineStr">
+      <c r="E117" s="3" t="inlineStr">
         <is>
           <t>되감기 - 방송 중(E) 체력 회복량 받은 피해의: 40/45/50/55/60%
 (변경 전: 37/41/45/49/53%)</t>
         </is>
       </c>
-      <c r="F108" s="3" t="inlineStr"/>
-    </row>
-    <row r="109" ht="60" customHeight="1">
-      <c r="A109" s="2" t="inlineStr">
+      <c r="F117" s="3" t="inlineStr"/>
+    </row>
+    <row r="118" ht="60" customHeight="1">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-007</t>
         </is>
       </c>
-      <c r="B109" s="3" t="inlineStr">
+      <c r="B118" s="3" t="inlineStr">
         <is>
           <t>[실험체] 마이 - 캣 워크(E) 보호막 흡수량 수치 확인</t>
         </is>
       </c>
-      <c r="C109" s="3" t="inlineStr">
+      <c r="C118" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 마이 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D109" s="3" t="inlineStr">
+      <c r="D118" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 마이 선택
@@ -4101,32 +4398,32 @@
 4. 보호막 흡수량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E109" s="3" t="inlineStr">
+      <c r="E118" s="3" t="inlineStr">
         <is>
           <t>캣 워크(E) 보호막 흡수량: 60/90/120/150/180(+스킬 증폭의 40%)(+최대 체력의 7%)
 (변경 전: 60/90/120/150/180(+스킬 증폭의 40%)(+최대 체력의 6%))</t>
         </is>
       </c>
-      <c r="F109" s="3" t="inlineStr"/>
-    </row>
-    <row r="110" ht="60" customHeight="1">
-      <c r="A110" s="2" t="inlineStr">
+      <c r="F118" s="3" t="inlineStr"/>
+    </row>
+    <row r="119" ht="60" customHeight="1">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-008</t>
         </is>
       </c>
-      <c r="B110" s="3" t="inlineStr">
+      <c r="B119" s="3" t="inlineStr">
         <is>
           <t>[실험체] 비앙카 - 진조의 군림(R)  수치 확인</t>
         </is>
       </c>
-      <c r="C110" s="3" t="inlineStr">
+      <c r="C119" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 비앙카 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D110" s="3" t="inlineStr">
+      <c r="D119" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 비앙카 선택
@@ -4134,32 +4431,32 @@
 4.  수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E110" s="3" t="inlineStr">
+      <c r="E119" s="3" t="inlineStr">
         <is>
           <t>진조의 군림(R) : 50/100/150(+스킬 증폭의 40%)(+대상 최대 체력의 11%)
 (변경 전: 1타 피해량 50/100/150(+스킬 증폭의 50%)(+대상 최대 체력의 11%))</t>
         </is>
       </c>
-      <c r="F110" s="3" t="inlineStr"/>
-    </row>
-    <row r="111" ht="60" customHeight="1">
-      <c r="A111" s="2" t="inlineStr">
+      <c r="F119" s="3" t="inlineStr"/>
+    </row>
+    <row r="120" ht="60" customHeight="1">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-009</t>
         </is>
       </c>
-      <c r="B111" s="3" t="inlineStr">
+      <c r="B120" s="3" t="inlineStr">
         <is>
           <t>[실험체] 시셀라 - 모두 해방이에요.(R) 패시브 효과 증가 지속 시간 수치 확인</t>
         </is>
       </c>
-      <c r="C111" s="3" t="inlineStr">
+      <c r="C120" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 시셀라 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D111" s="3" t="inlineStr">
+      <c r="D120" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 시셀라 선택
@@ -4167,32 +4464,32 @@
 4. 패시브 효과 증가 지속 시간 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E111" s="3" t="inlineStr">
+      <c r="E120" s="3" t="inlineStr">
         <is>
           <t>모두 해방이에요.(R) 패시브 효과 증가 지속 시간: 7/8/9초
 (변경 전: 6/7/8초)</t>
         </is>
       </c>
-      <c r="F111" s="3" t="inlineStr"/>
-    </row>
-    <row r="112" ht="60" customHeight="1">
-      <c r="A112" s="2" t="inlineStr">
+      <c r="F120" s="3" t="inlineStr"/>
+    </row>
+    <row r="121" ht="60" customHeight="1">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-010</t>
         </is>
       </c>
-      <c r="B112" s="3" t="inlineStr">
+      <c r="B121" s="3" t="inlineStr">
         <is>
           <t>[실험체] 시셀라 - 어딨어 윌슨?(W) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C112" s="3" t="inlineStr">
+      <c r="C121" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 시셀라 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D112" s="3" t="inlineStr">
+      <c r="D121" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 시셀라 선택
@@ -4200,32 +4497,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E112" s="3" t="inlineStr">
+      <c r="E121" s="3" t="inlineStr">
         <is>
           <t>어딨어 윌슨?(W) 피해량: 100/135/170/205/240(+스킬 증폭의 80%)
 (변경 전: 100/135/170/205/240(+스킬 증폭의 70%))</t>
         </is>
       </c>
-      <c r="F112" s="3" t="inlineStr"/>
-    </row>
-    <row r="113" ht="60" customHeight="1">
-      <c r="A113" s="2" t="inlineStr">
+      <c r="F121" s="3" t="inlineStr"/>
+    </row>
+    <row r="122" ht="60" customHeight="1">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-011</t>
         </is>
       </c>
-      <c r="B113" s="3" t="inlineStr">
+      <c r="B122" s="3" t="inlineStr">
         <is>
           <t>[실험체] 아야 - 고정 사격(W) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C113" s="3" t="inlineStr">
+      <c r="C122" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 아야 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D113" s="3" t="inlineStr">
+      <c r="D122" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 아야 선택
@@ -4233,32 +4530,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E113" s="3" t="inlineStr">
+      <c r="E122" s="3" t="inlineStr">
         <is>
           <t>고정 사격(W) 피해량: 30/40/50/60/70(+공격력의 50%)(+스킬 증폭의 30/35/40/45/50%)
 (변경 전: 20/30/40/50/60(+공격력의 50%)(+스킬 증폭의 30/35/40/45/50%))</t>
         </is>
       </c>
-      <c r="F113" s="3" t="inlineStr"/>
-    </row>
-    <row r="114" ht="60" customHeight="1">
-      <c r="A114" s="2" t="inlineStr">
+      <c r="F122" s="3" t="inlineStr"/>
+    </row>
+    <row r="123" ht="60" customHeight="1">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-012</t>
         </is>
       </c>
-      <c r="B114" s="3" t="inlineStr">
+      <c r="B123" s="3" t="inlineStr">
         <is>
           <t>[실험체] 알론소 - 어트랙션 슬램!(E) 속박 지속 시간 수치 확인</t>
         </is>
       </c>
-      <c r="C114" s="3" t="inlineStr">
+      <c r="C123" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 알론소 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D114" s="3" t="inlineStr">
+      <c r="D123" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 알론소 선택
@@ -4266,32 +4563,32 @@
 4. 속박 지속 시간 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E114" s="3" t="inlineStr">
+      <c r="E123" s="3" t="inlineStr">
         <is>
           <t>어트랙션 슬램!(E) 속박 지속 시간: 0.8/0.9/1/1.1/1.2초
 (변경 전: 0.7/0.8/0.9/1/1.1초)</t>
         </is>
       </c>
-      <c r="F114" s="3" t="inlineStr"/>
-    </row>
-    <row r="115" ht="60" customHeight="1">
-      <c r="A115" s="2" t="inlineStr">
+      <c r="F123" s="3" t="inlineStr"/>
+    </row>
+    <row r="124" ht="60" customHeight="1">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-013</t>
         </is>
       </c>
-      <c r="B115" s="3" t="inlineStr">
+      <c r="B124" s="3" t="inlineStr">
         <is>
           <t>[실험체] 얀 - 니 스트라이크(Q) 리핑 니 스트라이크(Q2) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C115" s="3" t="inlineStr">
+      <c r="C124" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 얀 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D115" s="3" t="inlineStr">
+      <c r="D124" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 얀 선택
@@ -4299,32 +4596,32 @@
 4. 리핑 니 스트라이크(Q2) 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E115" s="3" t="inlineStr">
+      <c r="E124" s="3" t="inlineStr">
         <is>
           <t>니 스트라이크(Q) 리핑 니 스트라이크(Q2) 피해량: 65/90/115/140/165(+추가 공격력의 90%)(+스킬 증폭의 70%)(+적 최대 체력의 6%)
 (변경 전: 65/90/115/140/165(+추가 공격력의 90%)(+스킬 증폭의 60%)(+적 최대 체력의 6%))</t>
         </is>
       </c>
-      <c r="F115" s="3" t="inlineStr"/>
-    </row>
-    <row r="116" ht="60" customHeight="1">
-      <c r="A116" s="2" t="inlineStr">
+      <c r="F124" s="3" t="inlineStr"/>
+    </row>
+    <row r="125" ht="60" customHeight="1">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-014</t>
         </is>
       </c>
-      <c r="B116" s="3" t="inlineStr">
+      <c r="B125" s="3" t="inlineStr">
         <is>
           <t>[실험체] 에스텔 - 선제대응(W) 이동 속도 감소 수치 확인</t>
         </is>
       </c>
-      <c r="C116" s="3" t="inlineStr">
+      <c r="C125" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 에스텔 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D116" s="3" t="inlineStr">
+      <c r="D125" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 에스텔 선택
@@ -4332,32 +4629,32 @@
 4. 이동 속도 감소 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E116" s="3" t="inlineStr">
+      <c r="E125" s="3" t="inlineStr">
         <is>
           <t>선제대응(W) 이동 속도 감소: 30%
 (변경 전: 25%)</t>
         </is>
       </c>
-      <c r="F116" s="3" t="inlineStr"/>
-    </row>
-    <row r="117" ht="60" customHeight="1">
-      <c r="A117" s="2" t="inlineStr">
+      <c r="F125" s="3" t="inlineStr"/>
+    </row>
+    <row r="126" ht="60" customHeight="1">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-015</t>
         </is>
       </c>
-      <c r="B117" s="3" t="inlineStr">
+      <c r="B126" s="3" t="inlineStr">
         <is>
           <t>[실험체] 엘레나 - 겨울여왕의 영지(P) 빙결 지속 시간 수치 확인</t>
         </is>
       </c>
-      <c r="C117" s="3" t="inlineStr">
+      <c r="C126" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 엘레나 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D117" s="3" t="inlineStr">
+      <c r="D126" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 엘레나 선택
@@ -4365,32 +4662,32 @@
 4. 빙결 지속 시간 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E117" s="3" t="inlineStr">
+      <c r="E126" s="3" t="inlineStr">
         <is>
           <t>겨울여왕의 영지(P) 빙결 지속 시간: 1.1초
 (변경 전: 1초)</t>
         </is>
       </c>
-      <c r="F117" s="3" t="inlineStr"/>
-    </row>
-    <row r="118" ht="60" customHeight="1">
-      <c r="A118" s="2" t="inlineStr">
+      <c r="F126" s="3" t="inlineStr"/>
+    </row>
+    <row r="127" ht="60" customHeight="1">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-016</t>
         </is>
       </c>
-      <c r="B118" s="3" t="inlineStr">
+      <c r="B127" s="3" t="inlineStr">
         <is>
           <t>[실험체] 엘레나 - 더블 악셀(W) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C118" s="3" t="inlineStr">
+      <c r="C127" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 엘레나 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D118" s="3" t="inlineStr">
+      <c r="D127" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 엘레나 선택
@@ -4398,32 +4695,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E118" s="3" t="inlineStr">
+      <c r="E127" s="3" t="inlineStr">
         <is>
           <t>더블 악셀(W) 피해량: 50/70/90/110/130(+스킬 증폭의 50%)(+추가 체력의 10%)
 (변경 전: 50/70/90/110/130(+스킬 증폭의 50%)(+추가 체력의 8%))</t>
         </is>
       </c>
-      <c r="F118" s="3" t="inlineStr"/>
-    </row>
-    <row r="119" ht="60" customHeight="1">
-      <c r="A119" s="2" t="inlineStr">
+      <c r="F127" s="3" t="inlineStr"/>
+    </row>
+    <row r="128" ht="60" customHeight="1">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-017</t>
         </is>
       </c>
-      <c r="B119" s="3" t="inlineStr">
+      <c r="B128" s="3" t="inlineStr">
         <is>
           <t>[실험체] 유스티나 - 부스트 대쉬(E) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C119" s="3" t="inlineStr">
+      <c r="C128" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 유스티나 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D119" s="3" t="inlineStr">
+      <c r="D128" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 유스티나 선택
@@ -4431,32 +4728,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E119" s="3" t="inlineStr">
+      <c r="E128" s="3" t="inlineStr">
         <is>
           <t>부스트 대쉬(E) 피해량: 50/75/100/125/150(+스킬 증폭의 30%)
 (변경 전: 40/60/80/100/120(+스킬 증폭의 30%))</t>
         </is>
       </c>
-      <c r="F119" s="3" t="inlineStr"/>
-    </row>
-    <row r="120" ht="60" customHeight="1">
-      <c r="A120" s="2" t="inlineStr">
+      <c r="F128" s="3" t="inlineStr"/>
+    </row>
+    <row r="129" ht="60" customHeight="1">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-018</t>
         </is>
       </c>
-      <c r="B120" s="3" t="inlineStr">
+      <c r="B129" s="3" t="inlineStr">
         <is>
           <t>[실험체] 이바 - 위상의 소용돌이(W)  수치 확인</t>
         </is>
       </c>
-      <c r="C120" s="3" t="inlineStr">
+      <c r="C129" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 이바 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D120" s="3" t="inlineStr">
+      <c r="D129" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 이바 선택
@@ -4464,32 +4761,32 @@
 4.  수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E120" s="3" t="inlineStr">
+      <c r="E129" s="3" t="inlineStr">
         <is>
           <t>위상의 소용돌이(W) : 40/70/100/130/160(+스킬 증폭의 40%)
 (변경 전: 1타 피해량 40/70/100/130/160(+스킬 증폭의 45%))</t>
         </is>
       </c>
-      <c r="F120" s="3" t="inlineStr"/>
-    </row>
-    <row r="121" ht="60" customHeight="1">
-      <c r="A121" s="2" t="inlineStr">
+      <c r="F129" s="3" t="inlineStr"/>
+    </row>
+    <row r="130" ht="60" customHeight="1">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-019</t>
         </is>
       </c>
-      <c r="B121" s="3" t="inlineStr">
+      <c r="B130" s="3" t="inlineStr">
         <is>
           <t>[실험체] 일레븐 - 다 덤벼보라구!(R) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C121" s="3" t="inlineStr">
+      <c r="C130" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 일레븐 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D121" s="3" t="inlineStr">
+      <c r="D130" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 일레븐 선택
@@ -4497,32 +4794,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E121" s="3" t="inlineStr">
+      <c r="E130" s="3" t="inlineStr">
         <is>
           <t>다 덤벼보라구!(R) 피해량: 10/15/20(+공격력의 3%)(+추가 체력의 3%)
 (변경 전: 6/9/12(+공격력의 3%)(+추가 체력의 3%))</t>
         </is>
       </c>
-      <c r="F121" s="3" t="inlineStr"/>
-    </row>
-    <row r="122" ht="60" customHeight="1">
-      <c r="A122" s="2" t="inlineStr">
+      <c r="F130" s="3" t="inlineStr"/>
+    </row>
+    <row r="131" ht="60" customHeight="1">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-020</t>
         </is>
       </c>
-      <c r="B122" s="3" t="inlineStr">
+      <c r="B131" s="3" t="inlineStr">
         <is>
           <t>[실험체] 제니 - 레드 카펫(W) 쿨다운 수치 확인</t>
         </is>
       </c>
-      <c r="C122" s="3" t="inlineStr">
+      <c r="C131" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 제니 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D122" s="3" t="inlineStr">
+      <c r="D131" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 제니 선택
@@ -4530,32 +4827,32 @@
 4. 쿨다운 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E122" s="3" t="inlineStr">
+      <c r="E131" s="3" t="inlineStr">
         <is>
           <t>레드 카펫(W) 쿨다운: 15초
 (변경 전: 16초)</t>
         </is>
       </c>
-      <c r="F122" s="3" t="inlineStr"/>
-    </row>
-    <row r="123" ht="60" customHeight="1">
-      <c r="A123" s="2" t="inlineStr">
+      <c r="F131" s="3" t="inlineStr"/>
+    </row>
+    <row r="132" ht="60" customHeight="1">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-021</t>
         </is>
       </c>
-      <c r="B123" s="3" t="inlineStr">
+      <c r="B132" s="3" t="inlineStr">
         <is>
           <t>[실험체] 제니 - 시상식의 여왕(R) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C123" s="3" t="inlineStr">
+      <c r="C132" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 제니 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D123" s="3" t="inlineStr">
+      <c r="D132" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 제니 선택
@@ -4563,32 +4860,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E123" s="3" t="inlineStr">
+      <c r="E132" s="3" t="inlineStr">
         <is>
           <t>시상식의 여왕(R) 피해량: 150/240/330(+스킬 증폭의 70%)
 (변경 전: 100/200/300(+스킬 증폭의 70%))</t>
         </is>
       </c>
-      <c r="F123" s="3" t="inlineStr"/>
-    </row>
-    <row r="124" ht="60" customHeight="1">
-      <c r="A124" s="2" t="inlineStr">
+      <c r="F132" s="3" t="inlineStr"/>
+    </row>
+    <row r="133" ht="60" customHeight="1">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-022</t>
         </is>
       </c>
-      <c r="B124" s="3" t="inlineStr">
+      <c r="B133" s="3" t="inlineStr">
         <is>
           <t>[실험체] 캐시 - 수쳐(E) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C124" s="3" t="inlineStr">
+      <c r="C133" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 캐시 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D124" s="3" t="inlineStr">
+      <c r="D133" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 캐시 선택
@@ -4596,32 +4893,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E124" s="3" t="inlineStr">
+      <c r="E133" s="3" t="inlineStr">
         <is>
           <t>수쳐(E) 피해량: 50/60/70/80/90(+스킬 증폭의 45%)
 (변경 전: 50/60/70/80/90(+스킬 증폭의 40%))</t>
         </is>
       </c>
-      <c r="F124" s="3" t="inlineStr"/>
-    </row>
-    <row r="125" ht="60" customHeight="1">
-      <c r="A125" s="2" t="inlineStr">
+      <c r="F133" s="3" t="inlineStr"/>
+    </row>
+    <row r="134" ht="60" customHeight="1">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-023</t>
         </is>
       </c>
-      <c r="B125" s="3" t="inlineStr">
+      <c r="B134" s="3" t="inlineStr">
         <is>
           <t>[실험체] 케네스 - 업화(W) 받는 피해 감소 수치 확인</t>
         </is>
       </c>
-      <c r="C125" s="3" t="inlineStr">
+      <c r="C134" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 케네스 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D125" s="3" t="inlineStr">
+      <c r="D134" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 케네스 선택
@@ -4629,32 +4926,32 @@
 4. 받는 피해 감소 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E125" s="3" t="inlineStr">
+      <c r="E134" s="3" t="inlineStr">
         <is>
           <t>업화(W) 받는 피해 감소: 2(+공격력의 3/3.25/3.5/3.75/4%)%
 (변경 전: 4(+공격력의 3/3.25/3.5/3.75/4%)%)</t>
         </is>
       </c>
-      <c r="F125" s="3" t="inlineStr"/>
-    </row>
-    <row r="126" ht="60" customHeight="1">
-      <c r="A126" s="2" t="inlineStr">
+      <c r="F134" s="3" t="inlineStr"/>
+    </row>
+    <row r="135" ht="60" customHeight="1">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-024</t>
         </is>
       </c>
-      <c r="B126" s="3" t="inlineStr">
+      <c r="B135" s="3" t="inlineStr">
         <is>
           <t>[실험체] 타지아 - 스틸레토(Q) 스파다 폭발 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C126" s="3" t="inlineStr">
+      <c r="C135" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 타지아 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D126" s="3" t="inlineStr">
+      <c r="D135" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 타지아 선택
@@ -4662,32 +4959,32 @@
 4. 스파다 폭발 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E126" s="3" t="inlineStr">
+      <c r="E135" s="3" t="inlineStr">
         <is>
           <t>스틸레토(Q) 스파다 폭발 피해량: 40/70/100/130/160(+스킬 증폭의 55%)
 (변경 전: 40/70/100/130/160(+스킬 증폭의 50%))</t>
         </is>
       </c>
-      <c r="F126" s="3" t="inlineStr"/>
-    </row>
-    <row r="127" ht="60" customHeight="1">
-      <c r="A127" s="2" t="inlineStr">
+      <c r="F135" s="3" t="inlineStr"/>
+    </row>
+    <row r="136" ht="60" customHeight="1">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-025</t>
         </is>
       </c>
-      <c r="B127" s="3" t="inlineStr">
+      <c r="B136" s="3" t="inlineStr">
         <is>
           <t>[실험체] 프리야 - 개화의 선율(Q) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C127" s="3" t="inlineStr">
+      <c r="C136" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 프리야 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D127" s="3" t="inlineStr">
+      <c r="D136" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 프리야 선택
@@ -4695,32 +4992,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E127" s="3" t="inlineStr">
+      <c r="E136" s="3" t="inlineStr">
         <is>
           <t>개화의 선율(Q) 피해량: 60/90/120/150/180(+스킬 증폭의 70%)
 (변경 전: 80/110/140/170/200(+스킬 증폭의 70%))</t>
         </is>
       </c>
-      <c r="F127" s="3" t="inlineStr"/>
-    </row>
-    <row r="128" ht="60" customHeight="1">
-      <c r="A128" s="2" t="inlineStr">
+      <c r="F136" s="3" t="inlineStr"/>
+    </row>
+    <row r="137" ht="60" customHeight="1">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-026</t>
         </is>
       </c>
-      <c r="B128" s="3" t="inlineStr">
+      <c r="B137" s="3" t="inlineStr">
         <is>
           <t>[실험체] 프리야 - 대지의 메아리(R) 쿨다운 수치 확인</t>
         </is>
       </c>
-      <c r="C128" s="3" t="inlineStr">
+      <c r="C137" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 프리야 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D128" s="3" t="inlineStr">
+      <c r="D137" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 프리야 선택
@@ -4728,32 +5025,32 @@
 4. 쿨다운 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E128" s="3" t="inlineStr">
+      <c r="E137" s="3" t="inlineStr">
         <is>
           <t>대지의 메아리(R) 쿨다운: 80/75/70초
 (변경 전: 80/70/60초)</t>
         </is>
       </c>
-      <c r="F128" s="3" t="inlineStr"/>
-    </row>
-    <row r="129" ht="60" customHeight="1">
-      <c r="A129" s="2" t="inlineStr">
+      <c r="F137" s="3" t="inlineStr"/>
+    </row>
+    <row r="138" ht="60" customHeight="1">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-027</t>
         </is>
       </c>
-      <c r="B129" s="3" t="inlineStr">
+      <c r="B138" s="3" t="inlineStr">
         <is>
           <t>[실험체] 피올로 - 사슬 묶기(E) 최대 충전까지 걸리는 시간 수치 확인</t>
         </is>
       </c>
-      <c r="C129" s="3" t="inlineStr">
+      <c r="C138" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 피올로 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D129" s="3" t="inlineStr">
+      <c r="D138" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 피올로 선택
@@ -4761,32 +5058,32 @@
 4. 최대 충전까지 걸리는 시간 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E129" s="3" t="inlineStr">
+      <c r="E138" s="3" t="inlineStr">
         <is>
           <t>사슬 묶기(E) 최대 충전까지 걸리는 시간: 1.2초
 (변경 전: 1.5초)</t>
         </is>
       </c>
-      <c r="F129" s="3" t="inlineStr"/>
-    </row>
-    <row r="130" ht="60" customHeight="1">
-      <c r="A130" s="2" t="inlineStr">
+      <c r="F138" s="3" t="inlineStr"/>
+    </row>
+    <row r="139" ht="60" customHeight="1">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-028</t>
         </is>
       </c>
-      <c r="B130" s="3" t="inlineStr">
+      <c r="B139" s="3" t="inlineStr">
         <is>
           <t>[실험체] 헤이즈 - 웨폰 케이스(P) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C130" s="3" t="inlineStr">
+      <c r="C139" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 헤이즈 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D130" s="3" t="inlineStr">
+      <c r="D139" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 헤이즈 선택
@@ -4794,32 +5091,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E130" s="3" t="inlineStr">
+      <c r="E139" s="3" t="inlineStr">
         <is>
           <t>웨폰 케이스(P) 피해량: 60/90/120(+스킬 증폭의 60%)
 (변경 전: 60/90/120(+스킬 증폭의 55%))</t>
         </is>
       </c>
-      <c r="F130" s="3" t="inlineStr"/>
-    </row>
-    <row r="131" ht="60" customHeight="1">
-      <c r="A131" s="4" t="inlineStr">
+      <c r="F139" s="3" t="inlineStr"/>
+    </row>
+    <row r="140" ht="60" customHeight="1">
+      <c r="A140" s="4" t="inlineStr">
         <is>
           <t>TC-10.5-029</t>
         </is>
       </c>
-      <c r="B131" s="5" t="inlineStr">
+      <c r="B140" s="5" t="inlineStr">
         <is>
           <t>[실험체] 가넷 - 기본 체력 수치 확인</t>
         </is>
       </c>
-      <c r="C131" s="5" t="inlineStr">
+      <c r="C140" s="5" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 가넷 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D131" s="5" t="inlineStr">
+      <c r="D140" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 가넷 선택
@@ -4827,32 +5124,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E131" s="5" t="inlineStr">
+      <c r="E140" s="5" t="inlineStr">
         <is>
           <t>기본 체력: 1000
 (변경 전: 950)</t>
         </is>
       </c>
-      <c r="F131" s="5" t="inlineStr"/>
-    </row>
-    <row r="132" ht="60" customHeight="1">
-      <c r="A132" s="4" t="inlineStr">
+      <c r="F140" s="5" t="inlineStr"/>
+    </row>
+    <row r="141" ht="60" customHeight="1">
+      <c r="A141" s="4" t="inlineStr">
         <is>
           <t>TC-10.5-030</t>
         </is>
       </c>
-      <c r="B132" s="5" t="inlineStr">
+      <c r="B141" s="5" t="inlineStr">
         <is>
           <t>[실험체] 로지 - 기본 방어력 수치 확인</t>
         </is>
       </c>
-      <c r="C132" s="5" t="inlineStr">
+      <c r="C141" s="5" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 로지 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D132" s="5" t="inlineStr">
+      <c r="D141" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 로지 선택
@@ -4860,32 +5157,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E132" s="5" t="inlineStr">
+      <c r="E141" s="5" t="inlineStr">
         <is>
           <t>기본 방어력: 50
 (변경 전: 53)</t>
         </is>
       </c>
-      <c r="F132" s="5" t="inlineStr"/>
-    </row>
-    <row r="133" ht="60" customHeight="1">
-      <c r="A133" s="4" t="inlineStr">
+      <c r="F141" s="5" t="inlineStr"/>
+    </row>
+    <row r="142" ht="60" customHeight="1">
+      <c r="A142" s="4" t="inlineStr">
         <is>
           <t>TC-10.5-031</t>
         </is>
       </c>
-      <c r="B133" s="5" t="inlineStr">
+      <c r="B142" s="5" t="inlineStr">
         <is>
           <t>[실험체] 마커스 - 도끼 무기 숙련도 레벨 당 기본 공격 증폭 수치 확인</t>
         </is>
       </c>
-      <c r="C133" s="5" t="inlineStr">
+      <c r="C142" s="5" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 마커스 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D133" s="5" t="inlineStr">
+      <c r="D142" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 마커스 선택
@@ -4893,32 +5190,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E133" s="5" t="inlineStr">
+      <c r="E142" s="5" t="inlineStr">
         <is>
           <t>도끼 무기 숙련도 레벨 당 기본 공격 증폭: 1.9%
 (변경 전: 1.8%)</t>
         </is>
       </c>
-      <c r="F133" s="5" t="inlineStr"/>
-    </row>
-    <row r="134" ht="60" customHeight="1">
-      <c r="A134" s="4" t="inlineStr">
+      <c r="F142" s="5" t="inlineStr"/>
+    </row>
+    <row r="143" ht="60" customHeight="1">
+      <c r="A143" s="4" t="inlineStr">
         <is>
           <t>TC-10.5-032</t>
         </is>
       </c>
-      <c r="B134" s="5" t="inlineStr">
+      <c r="B143" s="5" t="inlineStr">
         <is>
           <t>[실험체] 마커스 - 받는 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C134" s="5" t="inlineStr">
+      <c r="C143" s="5" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 마커스 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D134" s="5" t="inlineStr">
+      <c r="D143" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 마커스 선택
@@ -4926,32 +5223,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E134" s="5" t="inlineStr">
+      <c r="E143" s="5" t="inlineStr">
         <is>
           <t>받는 피해량: 100%
 (변경 전: 102%)</t>
         </is>
       </c>
-      <c r="F134" s="5" t="inlineStr"/>
-    </row>
-    <row r="135" ht="60" customHeight="1">
-      <c r="A135" s="4" t="inlineStr">
+      <c r="F143" s="5" t="inlineStr"/>
+    </row>
+    <row r="144" ht="60" customHeight="1">
+      <c r="A144" s="4" t="inlineStr">
         <is>
           <t>TC-10.5-033</t>
         </is>
       </c>
-      <c r="B135" s="5" t="inlineStr">
+      <c r="B144" s="5" t="inlineStr">
         <is>
           <t>[실험체] 매그너스 - 받는 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C135" s="5" t="inlineStr">
+      <c r="C144" s="5" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 매그너스 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D135" s="5" t="inlineStr">
+      <c r="D144" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 매그너스 선택
@@ -4959,32 +5256,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E135" s="5" t="inlineStr">
+      <c r="E144" s="5" t="inlineStr">
         <is>
           <t>받는 피해량: 100%
 (변경 전: 102%)</t>
         </is>
       </c>
-      <c r="F135" s="5" t="inlineStr"/>
-    </row>
-    <row r="136" ht="60" customHeight="1">
-      <c r="A136" s="4" t="inlineStr">
+      <c r="F144" s="5" t="inlineStr"/>
+    </row>
+    <row r="145" ht="60" customHeight="1">
+      <c r="A145" s="4" t="inlineStr">
         <is>
           <t>TC-10.5-034</t>
         </is>
       </c>
-      <c r="B136" s="5" t="inlineStr">
+      <c r="B145" s="5" t="inlineStr">
         <is>
           <t>[실험체] 아델라 - 레이피어 무기 숙련도 레벨 당 스킬 증폭 수치 확인</t>
         </is>
       </c>
-      <c r="C136" s="5" t="inlineStr">
+      <c r="C145" s="5" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 아델라 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D136" s="5" t="inlineStr">
+      <c r="D145" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 아델라 선택
@@ -4992,32 +5289,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E136" s="5" t="inlineStr">
+      <c r="E145" s="5" t="inlineStr">
         <is>
           <t>레이피어 무기 숙련도 레벨 당 스킬 증폭: 4.6%
 (변경 전: 4.7%)</t>
         </is>
       </c>
-      <c r="F136" s="5" t="inlineStr"/>
-    </row>
-    <row r="137" ht="60" customHeight="1">
-      <c r="A137" s="4" t="inlineStr">
+      <c r="F145" s="5" t="inlineStr"/>
+    </row>
+    <row r="146" ht="60" customHeight="1">
+      <c r="A146" s="4" t="inlineStr">
         <is>
           <t>TC-10.5-035</t>
         </is>
       </c>
-      <c r="B137" s="5" t="inlineStr">
+      <c r="B146" s="5" t="inlineStr">
         <is>
           <t>[실험체] 윌리엄 - 투척 무기 숙련도 레벨 당 기본 공격 증폭 수치 확인</t>
         </is>
       </c>
-      <c r="C137" s="5" t="inlineStr">
+      <c r="C146" s="5" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 윌리엄 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D137" s="5" t="inlineStr">
+      <c r="D146" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 윌리엄 선택
@@ -5025,32 +5322,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E137" s="5" t="inlineStr">
+      <c r="E146" s="5" t="inlineStr">
         <is>
           <t>투척 무기 숙련도 레벨 당 기본 공격 증폭: 1.4%
 (변경 전: 1.5%)</t>
         </is>
       </c>
-      <c r="F137" s="5" t="inlineStr"/>
-    </row>
-    <row r="138" ht="60" customHeight="1">
-      <c r="A138" s="4" t="inlineStr">
+      <c r="F146" s="5" t="inlineStr"/>
+    </row>
+    <row r="147" ht="60" customHeight="1">
+      <c r="A147" s="4" t="inlineStr">
         <is>
           <t>TC-10.5-036</t>
         </is>
       </c>
-      <c r="B138" s="5" t="inlineStr">
+      <c r="B147" s="5" t="inlineStr">
         <is>
           <t>[실험체] 이안 - 기본 공격력 수치 확인</t>
         </is>
       </c>
-      <c r="C138" s="5" t="inlineStr">
+      <c r="C147" s="5" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 이안 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D138" s="5" t="inlineStr">
+      <c r="D147" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 이안 선택
@@ -5058,32 +5355,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E138" s="5" t="inlineStr">
+      <c r="E147" s="5" t="inlineStr">
         <is>
           <t>기본 공격력: 38
 (변경 전: 40)</t>
         </is>
       </c>
-      <c r="F138" s="5" t="inlineStr"/>
-    </row>
-    <row r="139" ht="60" customHeight="1">
-      <c r="A139" s="4" t="inlineStr">
+      <c r="F147" s="5" t="inlineStr"/>
+    </row>
+    <row r="148" ht="60" customHeight="1">
+      <c r="A148" s="4" t="inlineStr">
         <is>
           <t>TC-10.5-037</t>
         </is>
       </c>
-      <c r="B139" s="5" t="inlineStr">
+      <c r="B148" s="5" t="inlineStr">
         <is>
           <t>[실험체] 일레븐 - 주는 회복 효과 수치 확인</t>
         </is>
       </c>
-      <c r="C139" s="5" t="inlineStr">
+      <c r="C148" s="5" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 일레븐 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D139" s="5" t="inlineStr">
+      <c r="D148" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 일레븐 선택
@@ -5091,32 +5388,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E139" s="5" t="inlineStr">
+      <c r="E148" s="5" t="inlineStr">
         <is>
           <t>주는 회복 효과: 100%
 (변경 전: 80%)</t>
         </is>
       </c>
-      <c r="F139" s="5" t="inlineStr"/>
-    </row>
-    <row r="140" ht="60" customHeight="1">
-      <c r="A140" s="4" t="inlineStr">
+      <c r="F148" s="5" t="inlineStr"/>
+    </row>
+    <row r="149" ht="60" customHeight="1">
+      <c r="A149" s="4" t="inlineStr">
         <is>
           <t>TC-10.5-038</t>
         </is>
       </c>
-      <c r="B140" s="5" t="inlineStr">
+      <c r="B149" s="5" t="inlineStr">
         <is>
           <t>[실험체] 카밀로 - 기본 공격력 수치 확인</t>
         </is>
       </c>
-      <c r="C140" s="5" t="inlineStr">
+      <c r="C149" s="5" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 카밀로 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D140" s="5" t="inlineStr">
+      <c r="D149" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 카밀로 선택
@@ -5124,32 +5421,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E140" s="5" t="inlineStr">
+      <c r="E149" s="5" t="inlineStr">
         <is>
           <t>기본 공격력: 31
 (변경 전: 34)</t>
         </is>
       </c>
-      <c r="F140" s="5" t="inlineStr"/>
-    </row>
-    <row r="141" ht="60" customHeight="1">
-      <c r="A141" s="4" t="inlineStr">
+      <c r="F149" s="5" t="inlineStr"/>
+    </row>
+    <row r="150" ht="60" customHeight="1">
+      <c r="A150" s="4" t="inlineStr">
         <is>
           <t>TC-10.5-039</t>
         </is>
       </c>
-      <c r="B141" s="5" t="inlineStr">
+      <c r="B150" s="5" t="inlineStr">
         <is>
           <t>[실험체] 피오라 - 레이피어 무기 숙련도 레벨 당 스킬 증폭 수치 확인</t>
         </is>
       </c>
-      <c r="C141" s="5" t="inlineStr">
+      <c r="C150" s="5" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 피오라 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D141" s="5" t="inlineStr">
+      <c r="D150" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 피오라 선택
@@ -5157,13 +5454,13 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E141" s="5" t="inlineStr">
+      <c r="E150" s="5" t="inlineStr">
         <is>
           <t>레이피어 무기 숙련도 레벨 당 스킬 증폭: 4.3%
 (변경 전: 4.5%)</t>
         </is>
       </c>
-      <c r="F141" s="5" t="inlineStr"/>
+      <c r="F150" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/patchnote_TC.xlsx
+++ b/patchnote_TC.xlsx
@@ -502,7 +502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F150"/>
+  <dimension ref="A1:F194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -548,21 +548,1473 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>TC-11.2-001</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>[실험체] 나타폰 - 스냅샷(Q) 피해량 수치 확인</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>· 11.2 패치 적용 완료
+· 나타폰 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 나타폰 선택
+3. 스냅샷(Q) 스킬 레벨 최대화 후 스킬 정보창 확인
+4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>스냅샷(Q) 피해량: 50/90/130/170/210(+스킬 증폭의 80%)
+(변경 전: 50/90/130/170/210(+스킬 증폭의 75%))</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr"/>
+    </row>
+    <row r="3" ht="60" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>TC-11.2-002</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>[실험체] 나타폰 - 인스턴트 포토(E) 이동 속도 감소 수치 확인</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>· 11.2 패치 적용 완료
+· 나타폰 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 나타폰 선택
+3. 인스턴트 포토(E) 스킬 레벨 최대화 후 스킬 정보창 확인
+4. 이동 속도 감소 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>인스턴트 포토(E) 이동 속도 감소: 55%
+(변경 전: 50%)</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>TC-11.2-003</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>[실험체] 니아 - K.O.(P) K.O. 중첩 당 저장되는 피해량 수치 확인</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>· 11.2 패치 적용 완료
+· 니아 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 니아 선택
+3. K.O.(P) 스킬 레벨 최대화 후 스킬 정보창 확인
+4. K.O. 중첩 당 저장되는 피해량 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>K.O.(P) K.O. 중첩 당 저장되는 피해량: 4/8/12(+스킬 증폭의 3%)
+(변경 전: 2/6/10(+스킬 증폭의 2.5%))</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr"/>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>TC-11.2-004</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>[실험체] 다니엘 - 그림자 이동(E) 피해량 수치 확인</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>· 11.2 패치 적용 완료
+· 다니엘 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 다니엘 선택
+3. 그림자 이동(E) 스킬 레벨 최대화 후 스킬 정보창 확인
+4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>그림자 이동(E) 피해량: 20/40/60/80/100(+추가 공격력의 60%)
+(변경 전: 20/40/60/80/100(+추가 공격력의 55%))</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>TC-11.2-005</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>[실험체] 다르코 - 수금(W) 이동 속도 감소 수치 확인</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>· 11.2 패치 적용 완료
+· 다르코 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 다르코 선택
+3. 수금(W) 스킬 레벨 최대화 후 스킬 정보창 확인
+4. 이동 속도 감소 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>수금(W) 이동 속도 감소: 25/27.5/30/32.5/35%
+(변경 전: 20/22.5/25/27.5/30%)</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr"/>
+    </row>
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>TC-11.2-006</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>[실험체] 다르코 - 추심(E) 에어본 지속 시간 수치 확인</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>· 11.2 패치 적용 완료
+· 다르코 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 다르코 선택
+3. 추심(E) 스킬 레벨 최대화 후 스킬 정보창 확인
+4. 에어본 지속 시간 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>추심(E) 에어본 지속 시간: 0.7초
+(변경 전: 0.6초)</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>TC-11.2-007</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>[실험체] 레녹스 - 휩쓸기(E) 쿨다운 수치 확인</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>· 11.2 패치 적용 완료
+· 레녹스 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 레녹스 선택
+3. 휩쓸기(E) 스킬 레벨 최대화 후 스킬 정보창 확인
+4. 쿨다운 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>휩쓸기(E) 쿨다운: 9초
+(변경 전: 8초)</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>TC-11.2-008</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>[실험체] 루크 - 애프터 서비스(R) 표식 중첩 당 추가 피해량 수치 확인</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>· 11.2 패치 적용 완료
+· 루크 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 루크 선택
+3. 애프터 서비스(R) 스킬 레벨 최대화 후 스킬 정보창 확인
+4. 표식 중첩 당 추가 피해량 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>애프터 서비스(R) 표식 중첩 당 추가 피해량: 20/45/70(+공격력의 13%)(+대상 최대 체력의 2%)
+(변경 전: 20/45/70(+공격력의 10%)(+대상 최대 체력의 2%))</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr"/>
+    </row>
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>TC-11.2-009</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>[실험체] 매그너스 - 17대 1(W) 피해량 수치 확인</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>· 11.2 패치 적용 완료
+· 매그너스 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 매그너스 선택
+3. 17대 1(W) 스킬 레벨 최대화 후 스킬 정보창 확인
+4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>17대 1(W) 피해량: 16/22/28/34/40(+추가 공격력의 45%)(+스킬 증폭의 20%)(+적 최대 체력의 2.5%)
+(변경 전: 16/22/28/34/40(+추가 공격력의 45%)(+스킬 증폭의 18%)(+적 최대 체력의 2.5%))</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>TC-11.2-010</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>[실험체] 비앙카 - 흡혈귀(P) 피해량 수치 확인</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>· 11.2 패치 적용 완료
+· 비앙카 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 비앙카 선택
+3. 흡혈귀(P) 스킬 레벨 최대화 후 스킬 정보창 확인
+4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>흡혈귀(P) 피해량: 30/70/110(+스킬 증폭의 40%)(+대상 최대 체력의 5%)
+(변경 전: 30/65/100(+스킬 증폭의 40%)(+대상 최대 체력의 4%))</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>TC-11.2-011</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>[실험체] 쇼우 - 소스범벅(Q) 피해량 수치 확인</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>· 11.2 패치 적용 완료
+· 쇼우 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 쇼우 선택
+3. 소스범벅(Q) 스킬 레벨 최대화 후 스킬 정보창 확인
+4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>소스범벅(Q) 피해량: 80/120/160/200/240(+스킬 증폭의 70%)(+대상 현재 체력의 25%)
+(변경 전: 60/100/140/180/220(+스킬 증폭의 70%)(+대상 현재 체력의 25%))</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>TC-11.2-012</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>[실험체] 슈린 - 결심응진(P) 체력 회복량 수치 확인</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>· 11.2 패치 적용 완료
+· 슈린 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 슈린 선택
+3. 결심응진(P) 스킬 레벨 최대화 후 스킬 정보창 확인
+4. 체력 회복량 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>결심응진(P) 체력 회복량: 10/25/40(+공격력의 35%)
+(변경 전: 10/25/40(+공격력의 30%))</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr"/>
+    </row>
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>TC-11.2-013</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>[실험체] 슈린 - 만검귀종(R) 강화 어검 피해량 수치 확인</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>· 11.2 패치 적용 완료
+· 슈린 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 슈린 선택
+3. 만검귀종(R) 스킬 레벨 최대화 후 스킬 정보창 확인
+4. 강화 어검 피해량 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>만검귀종(R) 강화 어검 피해량: 20/40/60(+공격력의 20/30/40%)
+(변경 전: 20/40/60(+공격력의 15/25/35%))</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr"/>
+    </row>
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>TC-11.2-014</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>[실험체] 아이작 - 강탈(R) 피해량 수치 확인</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>· 11.2 패치 적용 완료
+· 아이작 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 아이작 선택
+3. 강탈(R) 스킬 레벨 최대화 후 스킬 정보창 확인
+4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>강탈(R) 피해량: 120/180/240(+공격력의 100%)
+(변경 전: 80/140/200(+공격력의 100%))</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>TC-11.2-015</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>[실험체] 얀 - 쿼드라곤(R) 피해량 수치 확인</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>· 11.2 패치 적용 완료
+· 얀 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 얀 선택
+3. 쿼드라곤(R) 스킬 레벨 최대화 후 스킬 정보창 확인
+4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>쿼드라곤(R) 피해량: 100/200/300(+추가 공격력의 80%)(+스킬 증폭의 45%)
+(변경 전: 100/200/300(+추가 공격력의 80%)(+스킬 증폭의 40%))</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>TC-11.2-016</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>[실험체] 엘레나 - 겨울 여왕의 영지(P) 피해량 수치 확인</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>· 11.2 패치 적용 완료
+· 엘레나 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 엘레나 선택
+3. 겨울 여왕의 영지(P) 스킬 레벨 최대화 후 스킬 정보창 확인
+4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>겨울 여왕의 영지(P) 피해량: 10/30/50(+스킬 증폭의 30%)(+대상 최대 체력의 7/9/11%)
+(변경 전: 10/30/50(+스킬 증폭의 20%)(+대상 최대 체력의 6/8/10%))</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>TC-11.2-017</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>[실험체] 유스티나 - 집중 포격(W) 피해량 수치 확인</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>· 11.2 패치 적용 완료
+· 유스티나 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 유스티나 선택
+3. 집중 포격(W) 스킬 레벨 최대화 후 스킬 정보창 확인
+4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>집중 포격(W) 피해량: 50/75/100/125/150(+스킬 증폭의 35%)
+(변경 전: 50/70/90/110/130(+스킬 증폭의 35%))</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>TC-11.2-018</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>[실험체] 이바 - 빛의 트라이어드(Q) 폭발 피해량 수치 확인</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>· 11.2 패치 적용 완료
+· 이바 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 이바 선택
+3. 빛의 트라이어드(Q) 스킬 레벨 최대화 후 스킬 정보창 확인
+4. 폭발 피해량 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>빛의 트라이어드(Q) 폭발 피해량: 40/70/100/130/160(+스킬 증폭의 40%)
+(변경 전: 45/80/115/150/185(+스킬 증폭의 40%))</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>TC-11.2-019</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>[실험체] 이슈트반 - 양자 얽힘(W) 피해량 수치 확인</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>· 11.2 패치 적용 완료
+· 이슈트반 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 이슈트반 선택
+3. 양자 얽힘(W) 스킬 레벨 최대화 후 스킬 정보창 확인
+4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>양자 얽힘(W) 피해량: 60/90/120/150/180(+공격력의 90%)
+(변경 전: 60/85/110/135/160(+공격력의 90%))</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>TC-11.2-020</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>[실험체] 자히르 - 바이바야스트라(E) 투사체 속도 수치 확인</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>· 11.2 패치 적용 완료
+· 자히르 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 자히르 선택
+3. 바이바야스트라(E) 스킬 레벨 최대화 후 스킬 정보창 확인
+4. 투사체 속도 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>바이바야스트라(E) 투사체 속도: 8.5m/s
+(변경 전: 7.3m/s)</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr"/>
+    </row>
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>TC-11.2-021</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>[실험체] 자히르 - 사신의 눈(P) 피해량 수치 확인</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>· 11.2 패치 적용 완료
+· 자히르 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 자히르 선택
+3. 사신의 눈(P) 스킬 레벨 최대화 후 스킬 정보창 확인
+4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>사신의 눈(P) 피해량: 40/60/80(+스킬 증폭의 25%)
+(변경 전: 30/50/70(+스킬 증폭의 25%))</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr"/>
+    </row>
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>TC-11.2-022</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>[실험체] 칼라 - 작살 기동(E) 피해량 수치 확인</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>· 11.2 패치 적용 완료
+· 칼라 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 칼라 선택
+3. 작살 기동(E) 스킬 레벨 최대화 후 스킬 정보창 확인
+4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>작살 기동(E) 피해량: 60/100/140/180/220(+공격력의 50%)(+스킬 증폭의 80%)
+(변경 전: 60/100/140/180/220(+공격력의 50%)(+스킬 증폭의 60%))</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr"/>
+    </row>
+    <row r="24" ht="60" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>TC-11.2-023</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>[실험체] 케네스 - 맹공격(E) 피해량 수치 확인</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>· 11.2 패치 적용 완료
+· 케네스 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 케네스 선택
+3. 맹공격(E) 스킬 레벨 최대화 후 스킬 정보창 확인
+4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>맹공격(E) 피해량: 8/16/24/32/40(+공격력의 25%)
+(변경 전: 8/16/24/32/40(+공격력의 20%))</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>TC-11.2-024</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>[실험체] 케네스 - 억압된 분노(P) 체력 회복량 입힌 피해량의 수치 확인</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>· 11.2 패치 적용 완료
+· 케네스 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 케네스 선택
+3. 억압된 분노(P) 스킬 레벨 최대화 후 스킬 정보창 확인
+4. 체력 회복량 입힌 피해량의 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>억압된 분노(P) 체력 회복량 입힌 피해량의: 40(+공격력의 6%)%
+(변경 전: 40(+공격력의 5%)%)</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr"/>
+    </row>
+    <row r="26" ht="60" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>TC-11.2-025</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>[실험체] 케네스 - 억압된 분노(P) 체력 회복량 수치 확인</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>· 11.2 패치 적용 완료
+· 케네스 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 케네스 선택
+3. 억압된 분노(P) 스킬 레벨 최대화 후 스킬 정보창 확인
+4. 체력 회복량 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>억압된 분노(P) 체력 회복량: 30/40/50(+공격력의 6%)
+(변경 전: 최대치 20/30/40(+공격력의 5%))</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr"/>
+    </row>
+    <row r="27" ht="60" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>TC-11.2-026</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>[실험체] 코렐라인 - 이세계의 잔영(R) 이동 속도 증가 수치 확인</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>· 11.2 패치 적용 완료
+· 코렐라인 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 코렐라인 선택
+3. 이세계의 잔영(R) 스킬 레벨 최대화 후 스킬 정보창 확인
+4. 이동 속도 증가 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>이세계의 잔영(R) 이동 속도 증가: 10%
+(변경 전: 15%)</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28" ht="60" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>TC-11.2-027</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>[실험체] 피올로 - 쌍절난격&amp;내려치기(Q) 쌍절난격(Q1) 강화 피해량 수치 확인</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>· 11.2 패치 적용 완료
+· 피올로 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 피올로 선택
+3. 쌍절난격&amp;내려치기(Q) 스킬 레벨 최대화 후 스킬 정보창 확인
+4. 쌍절난격(Q1) 강화 피해량 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>쌍절난격&amp;내려치기(Q) 쌍절난격(Q1) 강화 피해량: 20/30/40/50/60(+스킬 증폭의 25%)
+(변경 전: 30/40/50/60/70(+스킬 증폭의 25%))</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>TC-11.2-028</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>[실험체] 피올로 - 쌍절난격&amp;내려치기(Q) 내려치기(Q2) 이동 속도 감소 수치 확인</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>· 11.2 패치 적용 완료
+· 피올로 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 피올로 선택
+3. 쌍절난격&amp;내려치기(Q) 스킬 레벨 최대화 후 스킬 정보창 확인
+4. 내려치기(Q2) 이동 속도 감소 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>쌍절난격&amp;내려치기(Q) 내려치기(Q2) 이동 속도 감소: 55%
+(변경 전: 60%)</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr"/>
+    </row>
+    <row r="30" ht="60" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>TC-11.2-029</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>[실험체] 현우 - 발 밟기(Q) 피해량 수치 확인</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>· 11.2 패치 적용 완료
+· 현우 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 현우 선택
+3. 발 밟기(Q) 스킬 레벨 최대화 후 스킬 정보창 확인
+4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>발 밟기(Q) 피해량: 50/100/150/200/250(+추가 공격력의 60%)(+스킬 증폭의 85%)
+(변경 전: 50/100/150/200/250(+추가 공격력의 60%)(+스킬 증폭의 80%))</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr"/>
+    </row>
+    <row r="31" ht="60" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>TC-11.2-030</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>[실험체] 히스이 - 쾌연격(Q)  수치 확인</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>· 11.2 패치 적용 완료
+· 히스이 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 히스이 선택
+3. 쾌연격(Q) 스킬 레벨 최대화 후 스킬 정보창 확인
+4.  수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>쾌연격(Q) : 70/85/100/115/130(+추가 공격력의 100/105/110/115/120%)
+(변경 전: 2타 피해량 70/85/100/115/130(+추가 공격력의 90/95/100/105/110%))</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr"/>
+    </row>
+    <row r="32" ht="60" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>TC-11.2-031</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>[실험체] 다니엘 - 레벨 당 공격력 수치 확인</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>· 11.2 패치 적용 완료
+· 다니엘 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 다니엘 선택
+3. 캐릭터 정보창(스탯창)에서 레벨 당 공격력 확인
+4. 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>레벨 당 공격력: 4.7
+(변경 전: 4.6)</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr"/>
+    </row>
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>TC-11.2-032</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>[실험체] 바냐 - 받는 피해량 수치 확인</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>· 11.2 패치 적용 완료
+· 바냐 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 바냐 선택
+3. 캐릭터 정보창(스탯창)에서 받는 피해량 확인
+4. 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>받는 피해량: 93%
+(변경 전: 95%)</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr"/>
+    </row>
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>TC-11.2-033</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>[실험체] 아야 - 기본 공격력 수치 확인</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>· 11.2 패치 적용 완료
+· 아야 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 아야 선택
+3. 캐릭터 정보창(스탯창)에서 기본 공격력 확인
+4. 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>기본 공격력: 40
+(변경 전: 43)</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr"/>
+    </row>
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>TC-11.2-034</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>[실험체] 아이솔 - 돌격 소총 무기 숙련도 레벨 당 기본 공격 증폭 수치 확인</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>· 11.2 패치 적용 완료
+· 아이솔 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 아이솔 선택
+3. 캐릭터 정보창(스탯창)에서 돌격 소총 무기 숙련도 레벨 당 기본 공격 증폭 확인
+4. 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>돌격 소총 무기 숙련도 레벨 당 기본 공격 증폭: 1.3%
+(변경 전: 1.4%)</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr"/>
+    </row>
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>TC-11.2-035</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>[실험체] 아이작 - 기본 방어력 수치 확인</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>· 11.2 패치 적용 완료
+· 아이작 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 아이작 선택
+3. 캐릭터 정보창(스탯창)에서 기본 방어력 확인
+4. 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>기본 방어력: 52
+(변경 전: 50)</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr"/>
+    </row>
+    <row r="37" ht="60" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>TC-11.2-036</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>[실험체] 윌리엄 - 레벨 당 공격력 수치 확인</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>· 11.2 패치 적용 완료
+· 윌리엄 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 윌리엄 선택
+3. 캐릭터 정보창(스탯창)에서 레벨 당 공격력 확인
+4. 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>레벨 당 공격력: 4.3
+(변경 전: 4.1)</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr"/>
+    </row>
+    <row r="38" ht="60" customHeight="1">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>TC-11.2-037</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>[실험체] 제니 - 받는 피해량 수치 확인</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>· 11.2 패치 적용 완료
+· 제니 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 제니 선택
+3. 캐릭터 정보창(스탯창)에서 받는 피해량 확인
+4. 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>받는 피해량: 93%
+(변경 전: 94%)</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr"/>
+    </row>
+    <row r="39" ht="60" customHeight="1">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>TC-11.2-038</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>[실험체] 카티야 - 레벨 당 공격력 수치 확인</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>· 11.2 패치 적용 완료
+· 카티야 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 카티야 선택
+3. 캐릭터 정보창(스탯창)에서 레벨 당 공격력 확인
+4. 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>레벨 당 공격력: 4.5
+(변경 전: 4.3)</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr"/>
+    </row>
+    <row r="40" ht="60" customHeight="1">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>TC-11.2-039</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>[실험체] 칼라 - 석궁 무기 숙련도 레벨 당 스킬 증폭 수치 확인</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>· 11.2 패치 적용 완료
+· 칼라 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 칼라 선택
+3. 캐릭터 정보창(스탯창)에서 석궁 무기 숙련도 레벨 당 스킬 증폭 확인
+4. 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>석궁 무기 숙련도 레벨 당 스킬 증폭: 4.1%
+(변경 전: 4%)</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr"/>
+    </row>
+    <row r="41" ht="60" customHeight="1">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>TC-11.2-040</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>[실험체] 캐시 - 쌍검 무기 숙련도 레벨 당 스킬 증폭 수치 확인</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>· 11.2 패치 적용 완료
+· 캐시 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 캐시 선택
+3. 캐릭터 정보창(스탯창)에서 쌍검 무기 숙련도 레벨 당 스킬 증폭 확인
+4. 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>쌍검 무기 숙련도 레벨 당 스킬 증폭: 4.8%
+(변경 전: 4.6%)</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr"/>
+    </row>
+    <row r="42" ht="60" customHeight="1">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>TC-11.2-041</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>[실험체] 펠릭스 - 창 무기 숙련도 레벨 당 기본 공격 증폭 수치 확인</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>· 11.2 패치 적용 완료
+· 펠릭스 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 펠릭스 선택
+3. 캐릭터 정보창(스탯창)에서 창 무기 숙련도 레벨 당 기본 공격 증폭 확인
+4. 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>창 무기 숙련도 레벨 당 기본 공격 증폭: 1.6%
+(변경 전: 1.5%)</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr"/>
+    </row>
+    <row r="43" ht="60" customHeight="1">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>TC-11.2-042</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>[실험체] 현우 - 받는 피해량 수치 확인</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>· 11.2 패치 적용 완료
+· 현우 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 현우 선택
+3. 캐릭터 정보창(스탯창)에서 받는 피해량 확인
+4. 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>받는 피해량: 95%
+(변경 전: 96%)</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr"/>
+    </row>
+    <row r="44" ht="60" customHeight="1">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>TC-11.2-043</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>[실험체] 혜진 - 암기 무기 숙련도 레벨 당 스킬 증폭 수치 확인</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>· 11.2 패치 적용 완료
+· 혜진 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 혜진 선택
+3. 캐릭터 정보창(스탯창)에서 암기 무기 숙련도 레벨 당 스킬 증폭 확인
+4. 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>암기 무기 숙련도 레벨 당 스킬 증폭: 4.8%
+(변경 전: 4.7%)</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr"/>
+    </row>
+    <row r="45" ht="60" customHeight="1">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>TC-11.2-044</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>[실험체] 혜진 - 레벨 당 방어력 수치 확인</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>· 11.2 패치 적용 완료
+· 혜진 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 혜진 선택
+3. 캐릭터 정보창(스탯창)에서 레벨 당 방어력 확인
+4. 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>레벨 당 방어력: 2.8
+(변경 전: 2.6)</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr"/>
+    </row>
+    <row r="46" ht="60" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
           <t>TC-11.1a-001</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B46" s="3" t="inlineStr">
         <is>
           <t>[실험체] 레니 - 곰돌이! 공격(P) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C46" s="3" t="inlineStr">
         <is>
           <t>· 11.1a 패치 적용 완료
 · 레니 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D46" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 레니 선택
@@ -570,32 +2022,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E46" s="3" t="inlineStr">
         <is>
           <t>곰돌이! 공격(P) 피해량: 15/25/35(+레니 레벨 *4)
 (변경 전: 20/30/40(+레니 레벨 *5))</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr"/>
-    </row>
-    <row r="3" ht="60" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="F46" s="3" t="inlineStr"/>
+    </row>
+    <row r="47" ht="60" customHeight="1">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>TC-11.1a-002</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B47" s="3" t="inlineStr">
         <is>
           <t>[실험체] 코렐라인 - 인과의 이면(P) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C47" s="3" t="inlineStr">
         <is>
           <t>· 11.1a 패치 적용 완료
 · 코렐라인 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D47" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 코렐라인 선택
@@ -603,32 +2055,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E47" s="3" t="inlineStr">
         <is>
           <t>인과의 이면(P) 피해량: 20/40/60/80/100(+스킬 증폭의 12%)
 (변경 전: 20/40/60/80/100(+스킬 증폭의 15%))</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr"/>
-    </row>
-    <row r="4" ht="60" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="F47" s="3" t="inlineStr"/>
+    </row>
+    <row r="48" ht="60" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>TC-11.1-001</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B48" s="3" t="inlineStr">
         <is>
           <t>[실험체] 레니 - 뿅! 망치(W) 이동 속도 증가 수치 확인</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C48" s="3" t="inlineStr">
         <is>
           <t>· 11.1 패치 적용 완료
 · 레니 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D48" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 레니 선택
@@ -636,32 +2088,32 @@
 4. 이동 속도 증가 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E48" s="3" t="inlineStr">
         <is>
           <t>뿅! 망치(W) 이동 속도 증가: 11/12/13/14/15(+레벨*1)%
 (변경 전: 16/17/18/19/20(+레벨*1)%)</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr"/>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="F48" s="3" t="inlineStr"/>
+    </row>
+    <row r="49" ht="60" customHeight="1">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>TC-11.1-002</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t>[실험체] 미르카 - 백스탭 러시(E) 받는 피해 감소 수치 확인</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C49" s="3" t="inlineStr">
         <is>
           <t>· 11.1 패치 적용 완료
 · 미르카 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D49" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 미르카 선택
@@ -669,32 +2121,32 @@
 4. 받는 피해 감소 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E49" s="3" t="inlineStr">
         <is>
           <t>백스탭 러시(E) 받는 피해 감소: 60%
 (변경 전: 80%)</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr"/>
-    </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="F49" s="3" t="inlineStr"/>
+    </row>
+    <row r="50" ht="60" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>TC-11.1-003</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B50" s="3" t="inlineStr">
         <is>
           <t>[실험체] 아드리아나 - 방화(Q) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C50" s="3" t="inlineStr">
         <is>
           <t>· 11.1 패치 적용 완료
 · 아드리아나 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D50" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 아드리아나 선택
@@ -702,32 +2154,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E50" s="3" t="inlineStr">
         <is>
           <t>방화(Q) 피해량: 35/45/55/65/75(+스킬 증폭의 25/27/29/31/33%)
 (변경 전: 30/40/50/60/70(+스킬 증폭의 25/27/29/31/33%))</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr"/>
-    </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="F50" s="3" t="inlineStr"/>
+    </row>
+    <row r="51" ht="60" customHeight="1">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>TC-11.1-004</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B51" s="3" t="inlineStr">
         <is>
           <t>[실험체] 자히르 - 간디바(W) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C51" s="3" t="inlineStr">
         <is>
           <t>· 11.1 패치 적용 완료
 · 자히르 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D51" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 자히르 선택
@@ -735,32 +2187,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E51" s="3" t="inlineStr">
         <is>
           <t>간디바(W) 피해량: 70/95/120/145/170(+스킬 증폭의 50%)
 (변경 전: 60/85/110/135/160(+스킬 증폭의 50%))</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr"/>
-    </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="F51" s="3" t="inlineStr"/>
+    </row>
+    <row r="52" ht="60" customHeight="1">
+      <c r="A52" s="4" t="inlineStr">
         <is>
           <t>TC-11.1-005</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B52" s="5" t="inlineStr">
         <is>
           <t>[실험체] 레온 - 톤파 무기 숙련도 레벨 당 스킬 증폭 수치 확인</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C52" s="5" t="inlineStr">
         <is>
           <t>· 11.1 패치 적용 완료
 · 레온 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D52" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 레온 선택
@@ -768,32 +2220,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E52" s="5" t="inlineStr">
         <is>
           <t>톤파 무기 숙련도 레벨 당 스킬 증폭: 4.8%
 (변경 전: 5%)</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr"/>
-    </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="F52" s="5" t="inlineStr"/>
+    </row>
+    <row r="53" ht="60" customHeight="1">
+      <c r="A53" s="4" t="inlineStr">
         <is>
           <t>TC-11.1-006</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B53" s="5" t="inlineStr">
         <is>
           <t>[실험체] 로지 - 기본 공격력 수치 확인</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C53" s="5" t="inlineStr">
         <is>
           <t>· 11.1 패치 적용 완료
 · 로지 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D53" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 로지 선택
@@ -801,32 +2253,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E53" s="5" t="inlineStr">
         <is>
           <t>기본 공격력: 32
 (변경 전: 35)</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr"/>
-    </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="F53" s="5" t="inlineStr"/>
+    </row>
+    <row r="54" ht="60" customHeight="1">
+      <c r="A54" s="4" t="inlineStr">
         <is>
           <t>TC-11.1-007</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B54" s="5" t="inlineStr">
         <is>
           <t>[실험체] 현우 - 글러브 무기 숙련도 레벨 당 기본 공격 증폭 수치 확인</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C54" s="5" t="inlineStr">
         <is>
           <t>· 11.1 패치 적용 완료
 · 현우 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D54" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 현우 선택
@@ -834,32 +2286,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E54" s="5" t="inlineStr">
         <is>
           <t>글러브 무기 숙련도 레벨 당 기본 공격 증폭: 2.2%
 (변경 전: 2.3%)</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr"/>
-    </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="F54" s="5" t="inlineStr"/>
+    </row>
+    <row r="55" ht="60" customHeight="1">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>TC-11.0-001</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B55" s="3" t="inlineStr">
         <is>
           <t>[실험체] 블레어 - 블레이드 시프트(P) 체력 회복량 입힌 피해의 수치 확인</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C55" s="3" t="inlineStr">
         <is>
           <t>· 11.0 패치 적용 완료
 · 블레어 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D55" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 블레어 선택
@@ -867,32 +2319,32 @@
 4. 체력 회복량 입힌 피해의 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E55" s="3" t="inlineStr">
         <is>
           <t>블레이드 시프트(P) 체력 회복량 입힌 피해의: 8(+추가 공격력의 5%)%
 (변경 전: 8(+추가 공격력의 4%)%)</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr"/>
-    </row>
-    <row r="12" ht="60" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="F55" s="3" t="inlineStr"/>
+    </row>
+    <row r="56" ht="60" customHeight="1">
+      <c r="A56" s="4" t="inlineStr">
         <is>
           <t>TC-11.0-002</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B56" s="5" t="inlineStr">
         <is>
           <t>[실험체] 블레어 - 기본 체력 수치 확인</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C56" s="5" t="inlineStr">
         <is>
           <t>· 11.0 패치 적용 완료
 · 블레어 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D56" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 블레어 선택
@@ -900,32 +2352,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E56" s="5" t="inlineStr">
         <is>
           <t>기본 체력: 970
 (변경 전: 940)</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr"/>
-    </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="F56" s="5" t="inlineStr"/>
+    </row>
+    <row r="57" ht="60" customHeight="1">
+      <c r="A57" s="4" t="inlineStr">
         <is>
           <t>TC-11.0-003</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B57" s="5" t="inlineStr">
         <is>
           <t>[실험체] 히스이 - 기본 체력 수치 확인</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C57" s="5" t="inlineStr">
         <is>
           <t>· 11.0 패치 적용 완료
 · 히스이 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D57" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 히스이 선택
@@ -933,32 +2385,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E57" s="5" t="inlineStr">
         <is>
           <t>기본 체력: 980
 (변경 전: 940)</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr"/>
-    </row>
-    <row r="14" ht="60" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="F57" s="5" t="inlineStr"/>
+    </row>
+    <row r="58" ht="60" customHeight="1">
+      <c r="A58" s="4" t="inlineStr">
         <is>
           <t>TC-11.0-004</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B58" s="5" t="inlineStr">
         <is>
           <t>[실험체] 히스이 - 기본 방어력 수치 확인</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C58" s="5" t="inlineStr">
         <is>
           <t>· 11.0 패치 적용 완료
 · 히스이 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D58" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 히스이 선택
@@ -966,32 +2418,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E58" s="5" t="inlineStr">
         <is>
           <t>기본 방어력: 54
 (변경 전: 52)</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr"/>
-    </row>
-    <row r="15" ht="60" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="F58" s="5" t="inlineStr"/>
+    </row>
+    <row r="59" ht="60" customHeight="1">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-001</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B59" s="3" t="inlineStr">
         <is>
           <t>[실험체] 가넷 - 억누른 고통(W) 받는 피해 감소 수치 확인</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C59" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 가넷 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D59" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 가넷 선택
@@ -999,32 +2451,32 @@
 4. 받는 피해 감소 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E59" s="3" t="inlineStr">
         <is>
           <t>억누른 고통(W) 받는 피해 감소: 50%
 (변경 전: 55%)</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr"/>
-    </row>
-    <row r="16" ht="60" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="F59" s="3" t="inlineStr"/>
+    </row>
+    <row r="60" ht="60" customHeight="1">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-002</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B60" s="3" t="inlineStr">
         <is>
           <t>[실험체] 라우라 - 날카로운 꽃(Q) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C60" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 라우라 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D60" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 라우라 선택
@@ -1032,32 +2484,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E60" s="3" t="inlineStr">
         <is>
           <t>날카로운 꽃(Q) 피해량: 50/75/100/125/150(+스킬 증폭의 55%)
 (변경 전: 50/75/100/125/150(+스킬 증폭의 60%))</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr"/>
-    </row>
-    <row r="17" ht="60" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="F60" s="3" t="inlineStr"/>
+    </row>
+    <row r="61" ht="60" customHeight="1">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-003</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B61" s="3" t="inlineStr">
         <is>
           <t>[실험체] 레니 - 스프링! 트랩(R) 쿨다운 수치 확인</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C61" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 레니 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D61" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 레니 선택
@@ -1065,32 +2517,32 @@
 4. 쿨다운 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="E61" s="3" t="inlineStr">
         <is>
           <t>스프링! 트랩(R) 쿨다운: 20/17/14초
 (변경 전: 20/16/12초)</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr"/>
-    </row>
-    <row r="18" ht="60" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="F61" s="3" t="inlineStr"/>
+    </row>
+    <row r="62" ht="60" customHeight="1">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-004</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B62" s="3" t="inlineStr">
         <is>
           <t>[실험체] 마이 - 오뜨꾸뛰르(P) 기본 공격 추가 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C62" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 마이 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D62" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 마이 선택
@@ -1098,32 +2550,32 @@
 4. 기본 공격 추가 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E62" s="3" t="inlineStr">
         <is>
           <t>오뜨꾸뛰르(P) 기본 공격 추가 피해량: 30(+추가 체력의 5/8/11%)
 (변경 전: 30(+추가 체력의 4/7/10%))</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr"/>
-    </row>
-    <row r="19" ht="60" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="F62" s="3" t="inlineStr"/>
+    </row>
+    <row r="63" ht="60" customHeight="1">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-005</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B63" s="3" t="inlineStr">
         <is>
           <t>[실험체] 마커스 - 파괴(W) 쿨다운 수치 확인</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C63" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 마커스 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D63" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 마커스 선택
@@ -1131,32 +2583,32 @@
 4. 쿨다운 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="E63" s="3" t="inlineStr">
         <is>
           <t>파괴(W) 쿨다운: 13/12/11/10/9초
 (변경 전: 12/11/10/9/8초)</t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr"/>
-    </row>
-    <row r="20" ht="60" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="F63" s="3" t="inlineStr"/>
+    </row>
+    <row r="64" ht="60" customHeight="1">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-006</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B64" s="3" t="inlineStr">
         <is>
           <t>[실험체] 매그너스 - 17대 1(W) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C64" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 매그너스 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D64" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 매그너스 선택
@@ -1164,32 +2616,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E64" s="3" t="inlineStr">
         <is>
           <t>17대 1(W) 피해량: 16/22/28/34/40(+추가 공격력의 45%)(+스킬 증폭의 18%)(+적 최대 체력의 2.5%)
 (변경 전: 16/22/28/34/40(+추가 공격력의 50%)(+스킬 증폭의 18%)(+적 최대 체력의 2.5%))</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr"/>
-    </row>
-    <row r="21" ht="60" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="F64" s="3" t="inlineStr"/>
+    </row>
+    <row r="65" ht="60" customHeight="1">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-007</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B65" s="3" t="inlineStr">
         <is>
           <t>[실험체] 쇼우 - 식사 시간(W) 방어력 증가 지속 시간 수치 확인</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C65" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 쇼우 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="D65" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 쇼우 선택
@@ -1197,32 +2649,32 @@
 4. 방어력 증가 지속 시간 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="E65" s="3" t="inlineStr">
         <is>
           <t>식사 시간(W) 방어력 증가 지속 시간: 2.5초
 (변경 전: 2초)</t>
         </is>
       </c>
-      <c r="F21" s="3" t="inlineStr"/>
-    </row>
-    <row r="22" ht="60" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="F65" s="3" t="inlineStr"/>
+    </row>
+    <row r="66" ht="60" customHeight="1">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-008</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B66" s="3" t="inlineStr">
         <is>
           <t>[실험체] 실비아 - 기동전(R) 방어력 증가 수치 확인</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C66" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 실비아 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D66" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 실비아 선택
@@ -1230,32 +2682,32 @@
 4. 방어력 증가 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="E66" s="3" t="inlineStr">
         <is>
           <t>기동전(R) 방어력 증가: 14/18/22
 (변경 전: 15/20/25)</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr"/>
-    </row>
-    <row r="23" ht="60" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="F66" s="3" t="inlineStr"/>
+    </row>
+    <row r="67" ht="60" customHeight="1">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-009</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B67" s="3" t="inlineStr">
         <is>
           <t>[실험체] 아비게일 - 워프 슬래시(E) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C67" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 아비게일 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="D67" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 아비게일 선택
@@ -1263,32 +2715,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E23" s="3" t="inlineStr">
+      <c r="E67" s="3" t="inlineStr">
         <is>
           <t>워프 슬래시(E) 피해량: 70/85/100/115/130(+스킬 증폭의 40%)
 (변경 전: 80/100/120/140/160(+스킬 증폭의 40%))</t>
         </is>
       </c>
-      <c r="F23" s="3" t="inlineStr"/>
-    </row>
-    <row r="24" ht="60" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="F67" s="3" t="inlineStr"/>
+    </row>
+    <row r="68" ht="60" customHeight="1">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-010</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B68" s="3" t="inlineStr">
         <is>
           <t>[실험체] 아비게일 - 티어링 블레이드(P) 방어력 감소 수치 확인</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C68" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 아비게일 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="D68" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 아비게일 선택
@@ -1296,32 +2748,32 @@
 4. 방어력 감소 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="E68" s="3" t="inlineStr">
         <is>
           <t>티어링 블레이드(P) 방어력 감소: 4/7/10
 (변경 전: 4/8/12)</t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr"/>
-    </row>
-    <row r="25" ht="60" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="F68" s="3" t="inlineStr"/>
+    </row>
+    <row r="69" ht="60" customHeight="1">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-011</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B69" s="3" t="inlineStr">
         <is>
           <t>[실험체] 아야 - 2연발(Q) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C69" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 아야 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="D69" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 아야 선택
@@ -1329,32 +2781,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E25" s="3" t="inlineStr">
+      <c r="E69" s="3" t="inlineStr">
         <is>
           <t>2연발(Q) 피해량: 40/70/100/130/160(+공격력의 30%)(+스킬 증폭의 65%)
 (변경 전: 40/70/100/130/160(+공격력의 30%)(+스킬 증폭의 70%))</t>
         </is>
       </c>
-      <c r="F25" s="3" t="inlineStr"/>
-    </row>
-    <row r="26" ht="60" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="F69" s="3" t="inlineStr"/>
+    </row>
+    <row r="70" ht="60" customHeight="1">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-012</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B70" s="3" t="inlineStr">
         <is>
           <t>[실험체] 알론소 - 마그네틱 펀치(Q) 기절 지속 시간 수치 확인</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C70" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 알론소 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D70" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 알론소 선택
@@ -1362,32 +2814,32 @@
 4. 기절 지속 시간 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="E70" s="3" t="inlineStr">
         <is>
           <t>마그네틱 펀치(Q) 기절 지속 시간: 0.9초
 (변경 전: 0.85초)</t>
         </is>
       </c>
-      <c r="F26" s="3" t="inlineStr"/>
-    </row>
-    <row r="27" ht="60" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="F70" s="3" t="inlineStr"/>
+    </row>
+    <row r="71" ht="60" customHeight="1">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-013</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B71" s="3" t="inlineStr">
         <is>
           <t>[실험체] 에이든 - 뇌격(Q) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C71" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 에이든 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="D71" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 에이든 선택
@@ -1395,32 +2847,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E27" s="3" t="inlineStr">
+      <c r="E71" s="3" t="inlineStr">
         <is>
           <t>뇌격(Q) 피해량: 70/100/130/160/190(+공격력의 75%) * (기본 공격 증폭)
 (변경 전: 60/90/120/150/180(+공격력의 75%) * (기본 공격 증폭))</t>
         </is>
       </c>
-      <c r="F27" s="3" t="inlineStr"/>
-    </row>
-    <row r="28" ht="60" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="F71" s="3" t="inlineStr"/>
+    </row>
+    <row r="72" ht="60" customHeight="1">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-014</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B72" s="3" t="inlineStr">
         <is>
           <t>[실험체] 에이든 - 전자포(과전하 Q) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C72" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 에이든 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="D72" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 에이든 선택
@@ -1428,32 +2880,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="E72" s="3" t="inlineStr">
         <is>
           <t>전자포(과전하 Q) 피해량: 70/100/130/160/190(+공격력의 75%) * (기본 공격 증폭)
 (변경 전: 60/90/120/150/180(+공격력의 75%) * (기본 공격 증폭))</t>
         </is>
       </c>
-      <c r="F28" s="3" t="inlineStr"/>
-    </row>
-    <row r="29" ht="60" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="F72" s="3" t="inlineStr"/>
+    </row>
+    <row r="73" ht="60" customHeight="1">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-015</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B73" s="3" t="inlineStr">
         <is>
           <t>[실험체] 일레븐 - 힘내자고!(P) 일레븐 버거 체력 회복량 수치 확인</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="C73" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 일레븐 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="D73" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 일레븐 선택
@@ -1461,32 +2913,32 @@
 4. 일레븐 버거 체력 회복량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E29" s="3" t="inlineStr">
+      <c r="E73" s="3" t="inlineStr">
         <is>
           <t>힘내자고!(P) 일레븐 버거 체력 회복량: 2/4/6%
 (변경 전: 최대 체력의 3/5/7%)</t>
         </is>
       </c>
-      <c r="F29" s="3" t="inlineStr"/>
-    </row>
-    <row r="30" ht="60" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="F73" s="3" t="inlineStr"/>
+    </row>
+    <row r="74" ht="60" customHeight="1">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-016</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B74" s="3" t="inlineStr">
         <is>
           <t>[실험체] 칼라 - 작살 장전(P) 완전 충전시 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="C74" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 칼라 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="D74" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 칼라 선택
@@ -1494,32 +2946,32 @@
 4. 완전 충전시 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E30" s="3" t="inlineStr">
+      <c r="E74" s="3" t="inlineStr">
         <is>
           <t>작살 장전(P) 완전 충전시 피해량: 10/25/40(+공격력의 100%)(+스킬 증폭의 25%)(+대상 최대 체력의 4/8/12%)
 (변경 전: 10/25/40(+공격력의 100%)(+스킬 증폭의 25%)(+대상 최대 체력의 4/7/10%))</t>
         </is>
       </c>
-      <c r="F30" s="3" t="inlineStr"/>
-    </row>
-    <row r="31" ht="60" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="F74" s="3" t="inlineStr"/>
+    </row>
+    <row r="75" ht="60" customHeight="1">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-017</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B75" s="3" t="inlineStr">
         <is>
           <t>[실험체] 케네스 - 분노의 일격(Q) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="C75" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 케네스 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="D75" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 케네스 선택
@@ -1527,32 +2979,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E31" s="3" t="inlineStr">
+      <c r="E75" s="3" t="inlineStr">
         <is>
           <t>분노의 일격(Q) 피해량: 30/40/50/60/70(+공격력의 165/170/175/180/185%)
 (변경 전: 30/40/50/60/70(+공격력의 150/155/160/165/170%))</t>
         </is>
       </c>
-      <c r="F31" s="3" t="inlineStr"/>
-    </row>
-    <row r="32" ht="60" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="F75" s="3" t="inlineStr"/>
+    </row>
+    <row r="76" ht="60" customHeight="1">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-018</t>
         </is>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B76" s="3" t="inlineStr">
         <is>
           <t>[실험체] 코렐라인 - 죄의 굴레(E) 거울 강화 시 투사체 속도 수치 확인</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="C76" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 코렐라인 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
+      <c r="D76" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 코렐라인 선택
@@ -1560,32 +3012,32 @@
 4. 거울 강화 시 투사체 속도 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E32" s="3" t="inlineStr">
+      <c r="E76" s="3" t="inlineStr">
         <is>
           <t>죄의 굴레(E) 거울 강화 시 투사체 속도: 13/ms
 (변경 전: 15m/s)</t>
         </is>
       </c>
-      <c r="F32" s="3" t="inlineStr"/>
-    </row>
-    <row r="33" ht="60" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="F76" s="3" t="inlineStr"/>
+    </row>
+    <row r="77" ht="60" customHeight="1">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-019</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B77" s="3" t="inlineStr">
         <is>
           <t>[실험체] 코렐라인 - 진실의 거울/거짓의 거울(W) 스킬 증폭 증가 수치 확인</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="C77" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 코렐라인 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
+      <c r="D77" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 코렐라인 선택
@@ -1593,32 +3045,32 @@
 4. 스킬 증폭 증가 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E33" s="3" t="inlineStr">
+      <c r="E77" s="3" t="inlineStr">
         <is>
           <t>진실의 거울/거짓의 거울(W) 스킬 증폭 증가: 3/5/7%
 (변경 전: 4/6/8%)</t>
         </is>
       </c>
-      <c r="F33" s="3" t="inlineStr"/>
-    </row>
-    <row r="34" ht="60" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="F77" s="3" t="inlineStr"/>
+    </row>
+    <row r="78" ht="60" customHeight="1">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-020</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B78" s="3" t="inlineStr">
         <is>
           <t>[실험체] 키아라 - 부정의 손길(Q) 체력 회복량 수치 확인</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="C78" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 키아라 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D34" s="3" t="inlineStr">
+      <c r="D78" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 키아라 선택
@@ -1626,32 +3078,32 @@
 4. 체력 회복량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E34" s="3" t="inlineStr">
+      <c r="E78" s="3" t="inlineStr">
         <is>
           <t>부정의 손길(Q) 체력 회복량: 13/16/19/22/25(+스킬 증폭의 4%)
 (변경 전: 10/13/16/19/22(+스킬 증폭의 3%))</t>
         </is>
       </c>
-      <c r="F34" s="3" t="inlineStr"/>
-    </row>
-    <row r="35" ht="60" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="F78" s="3" t="inlineStr"/>
+    </row>
+    <row r="79" ht="60" customHeight="1">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-021</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B79" s="3" t="inlineStr">
         <is>
           <t>[실험체] 타지아 - 스틸레토(Q) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="C79" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 타지아 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr">
+      <c r="D79" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 타지아 선택
@@ -1659,32 +3111,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E35" s="3" t="inlineStr">
+      <c r="E79" s="3" t="inlineStr">
         <is>
           <t>스틸레토(Q) 피해량: 30/60/90/120/150(+스킬 증폭의 40%)
 (변경 전: 30/55/80/105/130(+스킬 증폭의 40%))</t>
         </is>
       </c>
-      <c r="F35" s="3" t="inlineStr"/>
-    </row>
-    <row r="36" ht="60" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="F79" s="3" t="inlineStr"/>
+    </row>
+    <row r="80" ht="60" customHeight="1">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-022</t>
         </is>
       </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="B80" s="3" t="inlineStr">
         <is>
           <t>[실험체] 타지아 - 스틸레토(Q) 스파다(강화 Q) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="C80" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 타지아 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D36" s="3" t="inlineStr">
+      <c r="D80" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 타지아 선택
@@ -1692,32 +3144,32 @@
 4. 스파다(강화 Q) 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E36" s="3" t="inlineStr">
+      <c r="E80" s="3" t="inlineStr">
         <is>
           <t>스틸레토(Q) 스파다(강화 Q) 피해량: 30/60/90/120/150(+스킬 증폭의 50%)
 (변경 전: 30/55/80/105/130(+스킬 증폭의 50%))</t>
         </is>
       </c>
-      <c r="F36" s="3" t="inlineStr"/>
-    </row>
-    <row r="37" ht="60" customHeight="1">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="F80" s="3" t="inlineStr"/>
+    </row>
+    <row r="81" ht="60" customHeight="1">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-023</t>
         </is>
       </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B81" s="3" t="inlineStr">
         <is>
           <t>[실험체] 테오도르 - 에너지 필드(R) 이동 속도 증가 수치 확인</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="C81" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 테오도르 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr">
+      <c r="D81" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 테오도르 선택
@@ -1725,32 +3177,32 @@
 4. 이동 속도 증가 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E37" s="3" t="inlineStr">
+      <c r="E81" s="3" t="inlineStr">
         <is>
           <t>에너지 필드(R) 이동 속도 증가: 50/70/90%(+스킬 증폭의 2%)
 (변경 전: 60/80/100%(+스킬 증폭의 2%))</t>
         </is>
       </c>
-      <c r="F37" s="3" t="inlineStr"/>
-    </row>
-    <row r="38" ht="60" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="F81" s="3" t="inlineStr"/>
+    </row>
+    <row r="82" ht="60" customHeight="1">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-024</t>
         </is>
       </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B82" s="3" t="inlineStr">
         <is>
           <t>[실험체] 프리야 - 개화의 선율(Q) 만개 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
+      <c r="C82" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 프리야 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D38" s="3" t="inlineStr">
+      <c r="D82" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 프리야 선택
@@ -1758,32 +3210,32 @@
 4. 만개 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E38" s="3" t="inlineStr">
+      <c r="E82" s="3" t="inlineStr">
         <is>
           <t>개화의 선율(Q) 만개 피해량: 60/80/100/120/140(+스킬 증폭의 60%)
 (변경 전: 60/80/100/120/140(+스킬 증폭의 55%))</t>
         </is>
       </c>
-      <c r="F38" s="3" t="inlineStr"/>
-    </row>
-    <row r="39" ht="60" customHeight="1">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="F82" s="3" t="inlineStr"/>
+    </row>
+    <row r="83" ht="60" customHeight="1">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-025</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B83" s="3" t="inlineStr">
         <is>
           <t>[실험체] 프리야 - 포르타멘토(W) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="C83" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 프리야 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D39" s="3" t="inlineStr">
+      <c r="D83" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 프리야 선택
@@ -1791,32 +3243,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E39" s="3" t="inlineStr">
+      <c r="E83" s="3" t="inlineStr">
         <is>
           <t>포르타멘토(W) 피해량: 60/100/140/180/220(+스킬 증폭의 65%)
 (변경 전: 60/100/140/180/220(+스킬 증폭의 60%))</t>
         </is>
       </c>
-      <c r="F39" s="3" t="inlineStr"/>
-    </row>
-    <row r="40" ht="60" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="F83" s="3" t="inlineStr"/>
+    </row>
+    <row r="84" ht="60" customHeight="1">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-026</t>
         </is>
       </c>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="B84" s="3" t="inlineStr">
         <is>
           <t>[실험체] 헤이즈 - 산탄 포화(W) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
+      <c r="C84" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 헤이즈 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D40" s="3" t="inlineStr">
+      <c r="D84" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 헤이즈 선택
@@ -1824,32 +3276,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E40" s="3" t="inlineStr">
+      <c r="E84" s="3" t="inlineStr">
         <is>
           <t>산탄 포화(W) 피해량: 80/120/160/200/240(+스킬 증폭의 75%)
 (변경 전: 80/120/160/200/240(+스킬 증폭의 70%))</t>
         </is>
       </c>
-      <c r="F40" s="3" t="inlineStr"/>
-    </row>
-    <row r="41" ht="60" customHeight="1">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="F84" s="3" t="inlineStr"/>
+    </row>
+    <row r="85" ht="60" customHeight="1">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-027</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B85" s="3" t="inlineStr">
         <is>
           <t>[실험체] 헨리 - 시간 제어 장치(W) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
+      <c r="C85" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 헨리 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D41" s="3" t="inlineStr">
+      <c r="D85" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 헨리 선택
@@ -1857,32 +3309,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E41" s="3" t="inlineStr">
+      <c r="E85" s="3" t="inlineStr">
         <is>
           <t>시간 제어 장치(W) 피해량: 8/16/24/32/40(+스킬 증폭의 22%)(+대상 최대 체력의 1/1/2/2/3%)
 (변경 전: 8/16/24/32/40(+스킬 증폭의 20%)(+대상 최대 체력의 1/1/2/2/3%))</t>
         </is>
       </c>
-      <c r="F41" s="3" t="inlineStr"/>
-    </row>
-    <row r="42" ht="60" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="F85" s="3" t="inlineStr"/>
+    </row>
+    <row r="86" ht="60" customHeight="1">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-028</t>
         </is>
       </c>
-      <c r="B42" s="3" t="inlineStr">
+      <c r="B86" s="3" t="inlineStr">
         <is>
           <t>[실험체] 현우 - 핵펀치(R) 방어력 감소 수치 확인</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
+      <c r="C86" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 현우 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D42" s="3" t="inlineStr">
+      <c r="D86" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 현우 선택
@@ -1890,32 +3342,32 @@
 4. 방어력 감소 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E42" s="3" t="inlineStr">
+      <c r="E86" s="3" t="inlineStr">
         <is>
           <t>핵펀치(R) 방어력 감소: 10/15/20%
 (변경 전: 15/20/25%)</t>
         </is>
       </c>
-      <c r="F42" s="3" t="inlineStr"/>
-    </row>
-    <row r="43" ht="60" customHeight="1">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="F86" s="3" t="inlineStr"/>
+    </row>
+    <row r="87" ht="60" customHeight="1">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-029</t>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B87" s="3" t="inlineStr">
         <is>
           <t>[실험체] 혜진 - 오대존명왕진(R) 부적 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="C87" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 혜진 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D43" s="3" t="inlineStr">
+      <c r="D87" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 혜진 선택
@@ -1923,32 +3375,32 @@
 4. 부적 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E43" s="3" t="inlineStr">
+      <c r="E87" s="3" t="inlineStr">
         <is>
           <t>오대존명왕진(R) 부적 피해량: 80/105/130(+스킬 증폭의 50%)
 (변경 전: 80/115/150(+스킬 증폭의 50%))</t>
         </is>
       </c>
-      <c r="F43" s="3" t="inlineStr"/>
-    </row>
-    <row r="44" ht="60" customHeight="1">
-      <c r="A44" s="4" t="inlineStr">
+      <c r="F87" s="3" t="inlineStr"/>
+    </row>
+    <row r="88" ht="60" customHeight="1">
+      <c r="A88" s="4" t="inlineStr">
         <is>
           <t>TC-10.7-030</t>
         </is>
       </c>
-      <c r="B44" s="5" t="inlineStr">
+      <c r="B88" s="5" t="inlineStr">
         <is>
           <t>[실험체] 나딘 - 기본 공격력 수치 확인</t>
         </is>
       </c>
-      <c r="C44" s="5" t="inlineStr">
+      <c r="C88" s="5" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 나딘 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D44" s="5" t="inlineStr">
+      <c r="D88" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 나딘 선택
@@ -1956,32 +3408,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E44" s="5" t="inlineStr">
+      <c r="E88" s="5" t="inlineStr">
         <is>
           <t>기본 공격력: 33
 (변경 전: 35)</t>
         </is>
       </c>
-      <c r="F44" s="5" t="inlineStr"/>
-    </row>
-    <row r="45" ht="60" customHeight="1">
-      <c r="A45" s="4" t="inlineStr">
+      <c r="F88" s="5" t="inlineStr"/>
+    </row>
+    <row r="89" ht="60" customHeight="1">
+      <c r="A89" s="4" t="inlineStr">
         <is>
           <t>TC-10.7-031</t>
         </is>
       </c>
-      <c r="B45" s="5" t="inlineStr">
+      <c r="B89" s="5" t="inlineStr">
         <is>
           <t>[실험체] 나타폰 - 카메라 무기 숙련도 레벨 당 스킬 증폭 수치 확인</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr">
+      <c r="C89" s="5" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 나타폰 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="D89" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 나타폰 선택
@@ -1989,32 +3441,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E45" s="5" t="inlineStr">
+      <c r="E89" s="5" t="inlineStr">
         <is>
           <t>카메라 무기 숙련도 레벨 당 스킬 증폭: 4.4%
 (변경 전: 4.3%)</t>
         </is>
       </c>
-      <c r="F45" s="5" t="inlineStr"/>
-    </row>
-    <row r="46" ht="60" customHeight="1">
-      <c r="A46" s="4" t="inlineStr">
+      <c r="F89" s="5" t="inlineStr"/>
+    </row>
+    <row r="90" ht="60" customHeight="1">
+      <c r="A90" s="4" t="inlineStr">
         <is>
           <t>TC-10.7-032</t>
         </is>
       </c>
-      <c r="B46" s="5" t="inlineStr">
+      <c r="B90" s="5" t="inlineStr">
         <is>
           <t>[실험체] 르노어 - 받는 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C46" s="5" t="inlineStr">
+      <c r="C90" s="5" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 르노어 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="D90" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 르노어 선택
@@ -2022,32 +3474,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E46" s="5" t="inlineStr">
+      <c r="E90" s="5" t="inlineStr">
         <is>
           <t>받는 피해량: 100%
 (변경 전: 102%)</t>
         </is>
       </c>
-      <c r="F46" s="5" t="inlineStr"/>
-    </row>
-    <row r="47" ht="60" customHeight="1">
-      <c r="A47" s="4" t="inlineStr">
+      <c r="F90" s="5" t="inlineStr"/>
+    </row>
+    <row r="91" ht="60" customHeight="1">
+      <c r="A91" s="4" t="inlineStr">
         <is>
           <t>TC-10.7-033</t>
         </is>
       </c>
-      <c r="B47" s="5" t="inlineStr">
+      <c r="B91" s="5" t="inlineStr">
         <is>
           <t>[실험체] 리 다이린 - 글러브 무기 숙련도 레벨 당 기본 공격 증폭 수치 확인</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
+      <c r="C91" s="5" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 리 다이린 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D47" s="5" t="inlineStr">
+      <c r="D91" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 리 다이린 선택
@@ -2055,32 +3507,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E47" s="5" t="inlineStr">
+      <c r="E91" s="5" t="inlineStr">
         <is>
           <t>글러브 무기 숙련도 레벨 당 기본 공격 증폭: 1.9%
 (변경 전: 1.8%)</t>
         </is>
       </c>
-      <c r="F47" s="5" t="inlineStr"/>
-    </row>
-    <row r="48" ht="60" customHeight="1">
-      <c r="A48" s="4" t="inlineStr">
+      <c r="F91" s="5" t="inlineStr"/>
+    </row>
+    <row r="92" ht="60" customHeight="1">
+      <c r="A92" s="4" t="inlineStr">
         <is>
           <t>TC-10.7-034</t>
         </is>
       </c>
-      <c r="B48" s="5" t="inlineStr">
+      <c r="B92" s="5" t="inlineStr">
         <is>
           <t>[실험체] 마커스 - 레벨 당 체력 수치 확인</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
+      <c r="C92" s="5" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 마커스 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D48" s="5" t="inlineStr">
+      <c r="D92" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 마커스 선택
@@ -2088,32 +3540,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E48" s="5" t="inlineStr">
+      <c r="E92" s="5" t="inlineStr">
         <is>
           <t>레벨 당 체력: 94
 (변경 전: 97)</t>
         </is>
       </c>
-      <c r="F48" s="5" t="inlineStr"/>
-    </row>
-    <row r="49" ht="60" customHeight="1">
-      <c r="A49" s="4" t="inlineStr">
+      <c r="F92" s="5" t="inlineStr"/>
+    </row>
+    <row r="93" ht="60" customHeight="1">
+      <c r="A93" s="4" t="inlineStr">
         <is>
           <t>TC-10.7-035</t>
         </is>
       </c>
-      <c r="B49" s="5" t="inlineStr">
+      <c r="B93" s="5" t="inlineStr">
         <is>
           <t>[실험체] 미르카 - 기본 체력 수치 확인</t>
         </is>
       </c>
-      <c r="C49" s="5" t="inlineStr">
+      <c r="C93" s="5" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 미르카 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D49" s="5" t="inlineStr">
+      <c r="D93" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 미르카 선택
@@ -2121,32 +3573,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E49" s="5" t="inlineStr">
+      <c r="E93" s="5" t="inlineStr">
         <is>
           <t>기본 체력: 960
 (변경 전: 930)</t>
         </is>
       </c>
-      <c r="F49" s="5" t="inlineStr"/>
-    </row>
-    <row r="50" ht="60" customHeight="1">
-      <c r="A50" s="4" t="inlineStr">
+      <c r="F93" s="5" t="inlineStr"/>
+    </row>
+    <row r="94" ht="60" customHeight="1">
+      <c r="A94" s="4" t="inlineStr">
         <is>
           <t>TC-10.7-036</t>
         </is>
       </c>
-      <c r="B50" s="5" t="inlineStr">
+      <c r="B94" s="5" t="inlineStr">
         <is>
           <t>[실험체] 클로에 - 기본 공격력 수치 확인</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
+      <c r="C94" s="5" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 클로에 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D50" s="5" t="inlineStr">
+      <c r="D94" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 클로에 선택
@@ -2154,32 +3606,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E50" s="5" t="inlineStr">
+      <c r="E94" s="5" t="inlineStr">
         <is>
           <t>기본 공격력: 32
 (변경 전: 35)</t>
         </is>
       </c>
-      <c r="F50" s="5" t="inlineStr"/>
-    </row>
-    <row r="51" ht="60" customHeight="1">
-      <c r="A51" s="4" t="inlineStr">
+      <c r="F94" s="5" t="inlineStr"/>
+    </row>
+    <row r="95" ht="60" customHeight="1">
+      <c r="A95" s="4" t="inlineStr">
         <is>
           <t>TC-10.7-037</t>
         </is>
       </c>
-      <c r="B51" s="5" t="inlineStr">
+      <c r="B95" s="5" t="inlineStr">
         <is>
           <t>[실험체] 펜리르 - 레벨 당 공격력 수치 확인</t>
         </is>
       </c>
-      <c r="C51" s="5" t="inlineStr">
+      <c r="C95" s="5" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 펜리르 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D51" s="5" t="inlineStr">
+      <c r="D95" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 펜리르 선택
@@ -2187,32 +3639,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E51" s="5" t="inlineStr">
+      <c r="E95" s="5" t="inlineStr">
         <is>
           <t>레벨 당 공격력: 4.8
 (변경 전: 4.6)</t>
         </is>
       </c>
-      <c r="F51" s="5" t="inlineStr"/>
-    </row>
-    <row r="52" ht="60" customHeight="1">
-      <c r="A52" s="4" t="inlineStr">
+      <c r="F95" s="5" t="inlineStr"/>
+    </row>
+    <row r="96" ht="60" customHeight="1">
+      <c r="A96" s="4" t="inlineStr">
         <is>
           <t>TC-10.7-038</t>
         </is>
       </c>
-      <c r="B52" s="5" t="inlineStr">
+      <c r="B96" s="5" t="inlineStr">
         <is>
           <t>[실험체] 하트 - 기본 방어력 수치 확인</t>
         </is>
       </c>
-      <c r="C52" s="5" t="inlineStr">
+      <c r="C96" s="5" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 하트 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D52" s="5" t="inlineStr">
+      <c r="D96" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 하트 선택
@@ -2220,32 +3672,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E52" s="5" t="inlineStr">
+      <c r="E96" s="5" t="inlineStr">
         <is>
           <t>기본 방어력: 51
 (변경 전: 49)</t>
         </is>
       </c>
-      <c r="F52" s="5" t="inlineStr"/>
-    </row>
-    <row r="53" ht="60" customHeight="1">
-      <c r="A53" s="4" t="inlineStr">
+      <c r="F96" s="5" t="inlineStr"/>
+    </row>
+    <row r="97" ht="60" customHeight="1">
+      <c r="A97" s="4" t="inlineStr">
         <is>
           <t>TC-10.6c-001</t>
         </is>
       </c>
-      <c r="B53" s="5" t="inlineStr">
+      <c r="B97" s="5" t="inlineStr">
         <is>
           <t>[실험체] 코렐라인 - 아르카나 무기 숙련도 레벨 당 스킬 증폭 수치 확인</t>
         </is>
       </c>
-      <c r="C53" s="5" t="inlineStr">
+      <c r="C97" s="5" t="inlineStr">
         <is>
           <t>· 10.6c 패치 적용 완료
 · 코렐라인 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D53" s="5" t="inlineStr">
+      <c r="D97" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 코렐라인 선택
@@ -2253,32 +3705,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E53" s="5" t="inlineStr">
+      <c r="E97" s="5" t="inlineStr">
         <is>
           <t>아르카나 무기 숙련도 레벨 당 스킬 증폭: 4%
 (변경 전: 4.2%)</t>
         </is>
       </c>
-      <c r="F53" s="5" t="inlineStr"/>
-    </row>
-    <row r="54" ht="60" customHeight="1">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="F97" s="5" t="inlineStr"/>
+    </row>
+    <row r="98" ht="60" customHeight="1">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-001</t>
         </is>
       </c>
-      <c r="B54" s="3" t="inlineStr">
+      <c r="B98" s="3" t="inlineStr">
         <is>
           <t>[실험체] 가넷 - 억누른 고통(W) 쿨다운 수치 확인</t>
         </is>
       </c>
-      <c r="C54" s="3" t="inlineStr">
+      <c r="C98" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 가넷 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D54" s="3" t="inlineStr">
+      <c r="D98" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 가넷 선택
@@ -2286,32 +3738,32 @@
 4. 쿨다운 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E54" s="3" t="inlineStr">
+      <c r="E98" s="3" t="inlineStr">
         <is>
           <t>억누른 고통(W) 쿨다운: 14/13/12/11/10초
 (변경 전: 15/14/13/12/11초)</t>
         </is>
       </c>
-      <c r="F54" s="3" t="inlineStr"/>
-    </row>
-    <row r="55" ht="60" customHeight="1">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="F98" s="3" t="inlineStr"/>
+    </row>
+    <row r="99" ht="60" customHeight="1">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-002</t>
         </is>
       </c>
-      <c r="B55" s="3" t="inlineStr">
+      <c r="B99" s="3" t="inlineStr">
         <is>
           <t>[실험체] 가넷 - 짓뭉개기&amp;꿰뚫기(Q) 이동 속도 감소 수치 확인</t>
         </is>
       </c>
-      <c r="C55" s="3" t="inlineStr">
+      <c r="C99" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 가넷 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D55" s="3" t="inlineStr">
+      <c r="D99" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 가넷 선택
@@ -2319,32 +3771,32 @@
 4. 이동 속도 감소 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E55" s="3" t="inlineStr">
+      <c r="E99" s="3" t="inlineStr">
         <is>
           <t>짓뭉개기&amp;꿰뚫기(Q) 이동 속도 감소: 40%
 (변경 전: 35%)</t>
         </is>
       </c>
-      <c r="F55" s="3" t="inlineStr"/>
-    </row>
-    <row r="56" ht="60" customHeight="1">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="F99" s="3" t="inlineStr"/>
+    </row>
+    <row r="100" ht="60" customHeight="1">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-003</t>
         </is>
       </c>
-      <c r="B56" s="3" t="inlineStr">
+      <c r="B100" s="3" t="inlineStr">
         <is>
           <t>[실험체] 라우라 - 황혼의 도둑(R) 폭발 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C56" s="3" t="inlineStr">
+      <c r="C100" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 라우라 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D56" s="3" t="inlineStr">
+      <c r="D100" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 라우라 선택
@@ -2352,32 +3804,32 @@
 4. 폭발 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E56" s="3" t="inlineStr">
+      <c r="E100" s="3" t="inlineStr">
         <is>
           <t>황혼의 도둑(R) 폭발 피해량: 180/260/340(+스킬 증폭의 90%)
 (변경 전: 180/260/340(+스킬 증폭의 85%))</t>
         </is>
       </c>
-      <c r="F56" s="3" t="inlineStr"/>
-    </row>
-    <row r="57" ht="60" customHeight="1">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="F100" s="3" t="inlineStr"/>
+    </row>
+    <row r="101" ht="60" customHeight="1">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-004</t>
         </is>
       </c>
-      <c r="B57" s="3" t="inlineStr">
+      <c r="B101" s="3" t="inlineStr">
         <is>
           <t>[실험체] 라우라 - 황혼의 도둑(R) 보호막량 수치 확인</t>
         </is>
       </c>
-      <c r="C57" s="3" t="inlineStr">
+      <c r="C101" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 라우라 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D57" s="3" t="inlineStr">
+      <c r="D101" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 라우라 선택
@@ -2385,32 +3837,32 @@
 4. 보호막량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E57" s="3" t="inlineStr">
+      <c r="E101" s="3" t="inlineStr">
         <is>
           <t>황혼의 도둑(R) 보호막량: 90/120/150(+스킬 증폭의 20%)
 (변경 전: 90/120/150(+스킬 증폭의 15%))</t>
         </is>
       </c>
-      <c r="F57" s="3" t="inlineStr"/>
-    </row>
-    <row r="58" ht="60" customHeight="1">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="F101" s="3" t="inlineStr"/>
+    </row>
+    <row r="102" ht="60" customHeight="1">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-005</t>
         </is>
       </c>
-      <c r="B58" s="3" t="inlineStr">
+      <c r="B102" s="3" t="inlineStr">
         <is>
           <t>[실험체] 레니 - 당근! 바주카(Q) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C58" s="3" t="inlineStr">
+      <c r="C102" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 레니 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D58" s="3" t="inlineStr">
+      <c r="D102" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 레니 선택
@@ -2418,32 +3870,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E58" s="3" t="inlineStr">
+      <c r="E102" s="3" t="inlineStr">
         <is>
           <t>당근! 바주카(Q) 피해량: 40/55/70/85/100(+레니 레벨*18)(+스킬 증폭의 35%)
 (변경 전: 40/55/70/85/100(+레니 레벨*18)(+스킬 증폭의 30%))</t>
         </is>
       </c>
-      <c r="F58" s="3" t="inlineStr"/>
-    </row>
-    <row r="59" ht="60" customHeight="1">
-      <c r="A59" s="2" t="inlineStr">
+      <c r="F102" s="3" t="inlineStr"/>
+    </row>
+    <row r="103" ht="60" customHeight="1">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-006</t>
         </is>
       </c>
-      <c r="B59" s="3" t="inlineStr">
+      <c r="B103" s="3" t="inlineStr">
         <is>
           <t>[실험체] 레니 - 당근! 바주카(Q) 회복량 수치 확인</t>
         </is>
       </c>
-      <c r="C59" s="3" t="inlineStr">
+      <c r="C103" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 레니 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D59" s="3" t="inlineStr">
+      <c r="D103" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 레니 선택
@@ -2451,32 +3903,32 @@
 4. 회복량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E59" s="3" t="inlineStr">
+      <c r="E103" s="3" t="inlineStr">
         <is>
           <t>당근! 바주카(Q) 회복량: 10/20/30/40/50(+레니 레벨*2)(+스킬 증폭의 20%)
 (변경 전: 10/20/30/40/50(+레니 레벨*2)(+스킬 증폭의 18%))</t>
         </is>
       </c>
-      <c r="F59" s="3" t="inlineStr"/>
-    </row>
-    <row r="60" ht="60" customHeight="1">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="F103" s="3" t="inlineStr"/>
+    </row>
+    <row r="104" ht="60" customHeight="1">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-007</t>
         </is>
       </c>
-      <c r="B60" s="3" t="inlineStr">
+      <c r="B104" s="3" t="inlineStr">
         <is>
           <t>[실험체] 레온 - 물보라(W) 레온 보호막 흡수량 수치 확인</t>
         </is>
       </c>
-      <c r="C60" s="3" t="inlineStr">
+      <c r="C104" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 레온 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D60" s="3" t="inlineStr">
+      <c r="D104" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 레온 선택
@@ -2484,32 +3936,32 @@
 4. 레온 보호막 흡수량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E60" s="3" t="inlineStr">
+      <c r="E104" s="3" t="inlineStr">
         <is>
           <t>물보라(W) 레온 보호막 흡수량: 80/110/140/170/200(+스킬 증폭의 40%)
 (변경 전: 80/110/140/170/200(+스킬 증폭의 35%))</t>
         </is>
       </c>
-      <c r="F60" s="3" t="inlineStr"/>
-    </row>
-    <row r="61" ht="60" customHeight="1">
-      <c r="A61" s="2" t="inlineStr">
+      <c r="F104" s="3" t="inlineStr"/>
+    </row>
+    <row r="105" ht="60" customHeight="1">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-008</t>
         </is>
       </c>
-      <c r="B61" s="3" t="inlineStr">
+      <c r="B105" s="3" t="inlineStr">
         <is>
           <t>[실험체] 르노어 - 고통의 선율(P) 아첼레란도 중첩 당 쿨다운 감소 수치 확인</t>
         </is>
       </c>
-      <c r="C61" s="3" t="inlineStr">
+      <c r="C105" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 르노어 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D61" s="3" t="inlineStr">
+      <c r="D105" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 르노어 선택
@@ -2517,32 +3969,32 @@
 4. 아첼레란도 중첩 당 쿨다운 감소 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E61" s="3" t="inlineStr">
+      <c r="E105" s="3" t="inlineStr">
         <is>
           <t>고통의 선율(P) 아첼레란도 중첩 당 쿨다운 감소: 3
 (변경 전: 2)</t>
         </is>
       </c>
-      <c r="F61" s="3" t="inlineStr"/>
-    </row>
-    <row r="62" ht="60" customHeight="1">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="F105" s="3" t="inlineStr"/>
+    </row>
+    <row r="106" ht="60" customHeight="1">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-009</t>
         </is>
       </c>
-      <c r="B62" s="3" t="inlineStr">
+      <c r="B106" s="3" t="inlineStr">
         <is>
           <t>[실험체] 르노어 - 고통의 선율(P) 쿨다운 감소 수치 확인</t>
         </is>
       </c>
-      <c r="C62" s="3" t="inlineStr">
+      <c r="C106" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 르노어 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D62" s="3" t="inlineStr">
+      <c r="D106" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 르노어 선택
@@ -2550,32 +4002,32 @@
 4. 쿨다운 감소 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E62" s="3" t="inlineStr">
+      <c r="E106" s="3" t="inlineStr">
         <is>
           <t>고통의 선율(P) 쿨다운 감소: 2
 (변경 전: 40 이후 아첼레란도 중첩 당 궁극기 쿨다운 감소 3)</t>
         </is>
       </c>
-      <c r="F62" s="3" t="inlineStr"/>
-    </row>
-    <row r="63" ht="60" customHeight="1">
-      <c r="A63" s="2" t="inlineStr">
+      <c r="F106" s="3" t="inlineStr"/>
+    </row>
+    <row r="107" ht="60" customHeight="1">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-010</t>
         </is>
       </c>
-      <c r="B63" s="3" t="inlineStr">
+      <c r="B107" s="3" t="inlineStr">
         <is>
           <t>[실험체] 마르티나 - 일시정지 - 방송 중(W) 속박 지속 시간 수치 확인</t>
         </is>
       </c>
-      <c r="C63" s="3" t="inlineStr">
+      <c r="C107" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 마르티나 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D63" s="3" t="inlineStr">
+      <c r="D107" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 마르티나 선택
@@ -2583,32 +4035,32 @@
 4. 속박 지속 시간 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E63" s="3" t="inlineStr">
+      <c r="E107" s="3" t="inlineStr">
         <is>
           <t>일시정지 - 방송 중(W) 속박 지속 시간: 1.2초
 (변경 전: 1초)</t>
         </is>
       </c>
-      <c r="F63" s="3" t="inlineStr"/>
-    </row>
-    <row r="64" ht="60" customHeight="1">
-      <c r="A64" s="2" t="inlineStr">
+      <c r="F107" s="3" t="inlineStr"/>
+    </row>
+    <row r="108" ht="60" customHeight="1">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-011</t>
         </is>
       </c>
-      <c r="B64" s="3" t="inlineStr">
+      <c r="B108" s="3" t="inlineStr">
         <is>
           <t>[실험체] 마이 - 숄 장막(W) 이동 속도 증가 수치 확인</t>
         </is>
       </c>
-      <c r="C64" s="3" t="inlineStr">
+      <c r="C108" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 마이 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D64" s="3" t="inlineStr">
+      <c r="D108" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 마이 선택
@@ -2616,32 +4068,32 @@
 4. 이동 속도 증가 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E64" s="3" t="inlineStr">
+      <c r="E108" s="3" t="inlineStr">
         <is>
           <t>숄 장막(W) 이동 속도 증가: 10/14/18/22/26%
 (변경 전: 8/11/14/17/20%)</t>
         </is>
       </c>
-      <c r="F64" s="3" t="inlineStr"/>
-    </row>
-    <row r="65" ht="60" customHeight="1">
-      <c r="A65" s="2" t="inlineStr">
+      <c r="F108" s="3" t="inlineStr"/>
+    </row>
+    <row r="109" ht="60" customHeight="1">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-012</t>
         </is>
       </c>
-      <c r="B65" s="3" t="inlineStr">
+      <c r="B109" s="3" t="inlineStr">
         <is>
           <t>[실험체] 바바라 - BT-Mk2 센트리건(Q) 센트리건 기본 공격 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C65" s="3" t="inlineStr">
+      <c r="C109" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 바바라 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D65" s="3" t="inlineStr">
+      <c r="D109" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 바바라 선택
@@ -2649,32 +4101,32 @@
 4. 센트리건 기본 공격 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E65" s="3" t="inlineStr">
+      <c r="E109" s="3" t="inlineStr">
         <is>
           <t>BT-Mk2 센트리건(Q) 센트리건 기본 공격 피해량: 30/40/50/60/70(+스킬 증폭의 18%)
 (변경 전: 30/40/50/60/70(+스킬 증폭의 20%))</t>
         </is>
       </c>
-      <c r="F65" s="3" t="inlineStr"/>
-    </row>
-    <row r="66" ht="60" customHeight="1">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="F109" s="3" t="inlineStr"/>
+    </row>
+    <row r="110" ht="60" customHeight="1">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-013</t>
         </is>
       </c>
-      <c r="B66" s="3" t="inlineStr">
+      <c r="B110" s="3" t="inlineStr">
         <is>
           <t>[실험체] 셀린 - 자력 융합(R) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C66" s="3" t="inlineStr">
+      <c r="C110" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 셀린 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D66" s="3" t="inlineStr">
+      <c r="D110" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 셀린 선택
@@ -2682,32 +4134,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E66" s="3" t="inlineStr">
+      <c r="E110" s="3" t="inlineStr">
         <is>
           <t>자력 융합(R) 피해량: 60/80/100/120/140(+스킬 증폭의 37%)
 (변경 전: 60/80/100/120/140(+스킬 증폭의 36%))</t>
         </is>
       </c>
-      <c r="F66" s="3" t="inlineStr"/>
-    </row>
-    <row r="67" ht="60" customHeight="1">
-      <c r="A67" s="2" t="inlineStr">
+      <c r="F110" s="3" t="inlineStr"/>
+    </row>
+    <row r="111" ht="60" customHeight="1">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-014</t>
         </is>
       </c>
-      <c r="B67" s="3" t="inlineStr">
+      <c r="B111" s="3" t="inlineStr">
         <is>
           <t>[실험체] 쇼이치 - 비약(W) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C67" s="3" t="inlineStr">
+      <c r="C111" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 쇼이치 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D67" s="3" t="inlineStr">
+      <c r="D111" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 쇼이치 선택
@@ -2715,32 +4167,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E67" s="3" t="inlineStr">
+      <c r="E111" s="3" t="inlineStr">
         <is>
           <t>비약(W) 피해량: 30/50/70/90/110(+스킬 증폭의 60%)
 (변경 전: 40/60/80/100/120(+스킬 증폭의 60%))</t>
         </is>
       </c>
-      <c r="F67" s="3" t="inlineStr"/>
-    </row>
-    <row r="68" ht="60" customHeight="1">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="F111" s="3" t="inlineStr"/>
+    </row>
+    <row r="112" ht="60" customHeight="1">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-015</t>
         </is>
       </c>
-      <c r="B68" s="3" t="inlineStr">
+      <c r="B112" s="3" t="inlineStr">
         <is>
           <t>[실험체] 수아 - 기억력(R) 쿨다운 수치 확인</t>
         </is>
       </c>
-      <c r="C68" s="3" t="inlineStr">
+      <c r="C112" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 수아 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D68" s="3" t="inlineStr">
+      <c r="D112" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 수아 선택
@@ -2748,32 +4200,32 @@
 4. 쿨다운 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E68" s="3" t="inlineStr">
+      <c r="E112" s="3" t="inlineStr">
         <is>
           <t>기억력(R) 쿨다운: 26/22/18초
 (변경 전: 30/24/18초)</t>
         </is>
       </c>
-      <c r="F68" s="3" t="inlineStr"/>
-    </row>
-    <row r="69" ht="60" customHeight="1">
-      <c r="A69" s="2" t="inlineStr">
+      <c r="F112" s="3" t="inlineStr"/>
+    </row>
+    <row r="113" ht="60" customHeight="1">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-016</t>
         </is>
       </c>
-      <c r="B69" s="3" t="inlineStr">
+      <c r="B113" s="3" t="inlineStr">
         <is>
           <t>[실험체] 시셀라 - 삶은 고통이에요.(P) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C69" s="3" t="inlineStr">
+      <c r="C113" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 시셀라 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D69" s="3" t="inlineStr">
+      <c r="D113" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 시셀라 선택
@@ -2781,32 +4233,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E69" s="3" t="inlineStr">
+      <c r="E113" s="3" t="inlineStr">
         <is>
           <t>삶은 고통이에요.(P) 피해량: 30(+스킬 증폭의 45%)(+캐릭터 레벨*9)
 (변경 전: 30(+스킬 증폭의 40%)(+캐릭터 레벨*9))</t>
         </is>
       </c>
-      <c r="F69" s="3" t="inlineStr"/>
-    </row>
-    <row r="70" ht="60" customHeight="1">
-      <c r="A70" s="2" t="inlineStr">
+      <c r="F113" s="3" t="inlineStr"/>
+    </row>
+    <row r="114" ht="60" customHeight="1">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-017</t>
         </is>
       </c>
-      <c r="B70" s="3" t="inlineStr">
+      <c r="B114" s="3" t="inlineStr">
         <is>
           <t>[실험체] 아디나 - 폴 디그니티(E) 별 컨정션 효과 체력 회복량 수치 확인</t>
         </is>
       </c>
-      <c r="C70" s="3" t="inlineStr">
+      <c r="C114" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 아디나 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D70" s="3" t="inlineStr">
+      <c r="D114" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 아디나 선택
@@ -2814,32 +4266,32 @@
 4. 별 컨정션 효과 체력 회복량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E70" s="3" t="inlineStr">
+      <c r="E114" s="3" t="inlineStr">
         <is>
           <t>폴 디그니티(E) 별 컨정션 효과 체력 회복량: 20/30/40/50(+스킬 증폭의 6%)
 (변경 전: 20/30/40/50(+스킬 증폭의 4%))</t>
         </is>
       </c>
-      <c r="F70" s="3" t="inlineStr"/>
-    </row>
-    <row r="71" ht="60" customHeight="1">
-      <c r="A71" s="2" t="inlineStr">
+      <c r="F114" s="3" t="inlineStr"/>
+    </row>
+    <row r="115" ht="60" customHeight="1">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-018</t>
         </is>
       </c>
-      <c r="B71" s="3" t="inlineStr">
+      <c r="B115" s="3" t="inlineStr">
         <is>
           <t>[실험체] 아이작 - 현장 급습(Q) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C71" s="3" t="inlineStr">
+      <c r="C115" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 아이작 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D71" s="3" t="inlineStr">
+      <c r="D115" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 아이작 선택
@@ -2847,32 +4299,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E71" s="3" t="inlineStr">
+      <c r="E115" s="3" t="inlineStr">
         <is>
           <t>현장 급습(Q) 피해량: 20/60/100/140/180(+공격력의 70%)
 (변경 전: 30/70/110/150/190(+공격력의 70%))</t>
         </is>
       </c>
-      <c r="F71" s="3" t="inlineStr"/>
-    </row>
-    <row r="72" ht="60" customHeight="1">
-      <c r="A72" s="2" t="inlineStr">
+      <c r="F115" s="3" t="inlineStr"/>
+    </row>
+    <row r="116" ht="60" customHeight="1">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-019</t>
         </is>
       </c>
-      <c r="B72" s="3" t="inlineStr">
+      <c r="B116" s="3" t="inlineStr">
         <is>
           <t>[실험체] 알렉스 - 플라즈마 마인(W) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C72" s="3" t="inlineStr">
+      <c r="C116" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 알렉스 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D72" s="3" t="inlineStr">
+      <c r="D116" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 알렉스 선택
@@ -2880,32 +4332,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E72" s="3" t="inlineStr">
+      <c r="E116" s="3" t="inlineStr">
         <is>
           <t>플라즈마 마인(W) 피해량: 40/75/110/145/180(+공격력의 80%)
 (변경 전: 40/80/120/160/200(+공격력의 80%))</t>
         </is>
       </c>
-      <c r="F72" s="3" t="inlineStr"/>
-    </row>
-    <row r="73" ht="60" customHeight="1">
-      <c r="A73" s="2" t="inlineStr">
+      <c r="F116" s="3" t="inlineStr"/>
+    </row>
+    <row r="117" ht="60" customHeight="1">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-020</t>
         </is>
       </c>
-      <c r="B73" s="3" t="inlineStr">
+      <c r="B117" s="3" t="inlineStr">
         <is>
           <t>[실험체] 에스텔 - 헬기호출(R) 보호막 흡수량 수치 확인</t>
         </is>
       </c>
-      <c r="C73" s="3" t="inlineStr">
+      <c r="C117" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 에스텔 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D73" s="3" t="inlineStr">
+      <c r="D117" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 에스텔 선택
@@ -2913,32 +4365,32 @@
 4. 보호막 흡수량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E73" s="3" t="inlineStr">
+      <c r="E117" s="3" t="inlineStr">
         <is>
           <t>헬기호출(R) 보호막 흡수량: 100/150/200(+스킬 증폭의 55%)(+잃은 체력의 20%)
 (변경 전: 100/150/200(+스킬 증폭의 50%)(+잃은 체력의 20%))</t>
         </is>
       </c>
-      <c r="F73" s="3" t="inlineStr"/>
-    </row>
-    <row r="74" ht="60" customHeight="1">
-      <c r="A74" s="2" t="inlineStr">
+      <c r="F117" s="3" t="inlineStr"/>
+    </row>
+    <row r="118" ht="60" customHeight="1">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-021</t>
         </is>
       </c>
-      <c r="B74" s="3" t="inlineStr">
+      <c r="B118" s="3" t="inlineStr">
         <is>
           <t>[실험체] 에스텔 - 헬기호출(R) 아군 보호막 흡수량 수치 확인</t>
         </is>
       </c>
-      <c r="C74" s="3" t="inlineStr">
+      <c r="C118" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 에스텔 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D74" s="3" t="inlineStr">
+      <c r="D118" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 에스텔 선택
@@ -2946,32 +4398,32 @@
 4. 아군 보호막 흡수량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E74" s="3" t="inlineStr">
+      <c r="E118" s="3" t="inlineStr">
         <is>
           <t>헬기호출(R) 아군 보호막 흡수량: 100/200/300(+스킬 증폭의 55%)(+대상의 잃은 체력의 15%)
 (변경 전: 100/200/300(+스킬 증폭의 50%)(+대상의 잃은 체력의 15%))</t>
         </is>
       </c>
-      <c r="F74" s="3" t="inlineStr"/>
-    </row>
-    <row r="75" ht="60" customHeight="1">
-      <c r="A75" s="2" t="inlineStr">
+      <c r="F118" s="3" t="inlineStr"/>
+    </row>
+    <row r="119" ht="60" customHeight="1">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-022</t>
         </is>
       </c>
-      <c r="B75" s="3" t="inlineStr">
+      <c r="B119" s="3" t="inlineStr">
         <is>
           <t>[실험체] 에키온 - VF 폭주(R) 독사의 진노[블랙맘바] 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C75" s="3" t="inlineStr">
+      <c r="C119" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 에키온 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D75" s="3" t="inlineStr">
+      <c r="D119" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 에키온 선택
@@ -2979,32 +4431,32 @@
 4. 독사의 진노[블랙맘바] 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E75" s="3" t="inlineStr">
+      <c r="E119" s="3" t="inlineStr">
         <is>
           <t>VF 폭주(R) 독사의 진노[블랙맘바] 피해량: 50/120/175/220(+공격력의 80%)(+추가 체력의 12%)
 (변경 전: 50/120/175/220(+공격력의 80%)(+추가 체력의 10%))</t>
         </is>
       </c>
-      <c r="F75" s="3" t="inlineStr"/>
-    </row>
-    <row r="76" ht="60" customHeight="1">
-      <c r="A76" s="2" t="inlineStr">
+      <c r="F119" s="3" t="inlineStr"/>
+    </row>
+    <row r="120" ht="60" customHeight="1">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-023</t>
         </is>
       </c>
-      <c r="B76" s="3" t="inlineStr">
+      <c r="B120" s="3" t="inlineStr">
         <is>
           <t>[실험체] 엠마 - 마술 토끼(E) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C76" s="3" t="inlineStr">
+      <c r="C120" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 엠마 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D76" s="3" t="inlineStr">
+      <c r="D120" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 엠마 선택
@@ -3012,32 +4464,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E76" s="3" t="inlineStr">
+      <c r="E120" s="3" t="inlineStr">
         <is>
           <t>마술 토끼(E) 피해량: 30/55/80/105/130(+스킬 증폭의 30%)
 (변경 전: 20/40/60/80/100(+스킬 증폭의 30%))</t>
         </is>
       </c>
-      <c r="F76" s="3" t="inlineStr"/>
-    </row>
-    <row r="77" ht="60" customHeight="1">
-      <c r="A77" s="2" t="inlineStr">
+      <c r="F120" s="3" t="inlineStr"/>
+    </row>
+    <row r="121" ht="60" customHeight="1">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-024</t>
         </is>
       </c>
-      <c r="B77" s="3" t="inlineStr">
+      <c r="B121" s="3" t="inlineStr">
         <is>
           <t>[실험체] 엠마 - 마술 토끼(E) 변이 지속 시간 수치 확인</t>
         </is>
       </c>
-      <c r="C77" s="3" t="inlineStr">
+      <c r="C121" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 엠마 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D77" s="3" t="inlineStr">
+      <c r="D121" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 엠마 선택
@@ -3045,32 +4497,32 @@
 4. 변이 지속 시간 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E77" s="3" t="inlineStr">
+      <c r="E121" s="3" t="inlineStr">
         <is>
           <t>마술 토끼(E) 변이 지속 시간: 0.8/0.85/0.9/0.95/1초
 (변경 전: 0.6/0.7/0.8/0.9/1초)</t>
         </is>
       </c>
-      <c r="F77" s="3" t="inlineStr"/>
-    </row>
-    <row r="78" ht="60" customHeight="1">
-      <c r="A78" s="2" t="inlineStr">
+      <c r="F121" s="3" t="inlineStr"/>
+    </row>
+    <row r="122" ht="60" customHeight="1">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-025</t>
         </is>
       </c>
-      <c r="B78" s="3" t="inlineStr">
+      <c r="B122" s="3" t="inlineStr">
         <is>
           <t>[실험체] 유키 - 머리치기!(Q) 쿨다운 수치 확인</t>
         </is>
       </c>
-      <c r="C78" s="3" t="inlineStr">
+      <c r="C122" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 유키 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D78" s="3" t="inlineStr">
+      <c r="D122" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 유키 선택
@@ -3078,32 +4530,32 @@
 4. 쿨다운 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E78" s="3" t="inlineStr">
+      <c r="E122" s="3" t="inlineStr">
         <is>
           <t>머리치기!(Q) 쿨다운: 5초
 (변경 전: 6초)</t>
         </is>
       </c>
-      <c r="F78" s="3" t="inlineStr"/>
-    </row>
-    <row r="79" ht="60" customHeight="1">
-      <c r="A79" s="2" t="inlineStr">
+      <c r="F122" s="3" t="inlineStr"/>
+    </row>
+    <row r="123" ht="60" customHeight="1">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-026</t>
         </is>
       </c>
-      <c r="B79" s="3" t="inlineStr">
+      <c r="B123" s="3" t="inlineStr">
         <is>
           <t>[실험체] 이슈트반 - 관측(Q) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C79" s="3" t="inlineStr">
+      <c r="C123" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 이슈트반 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D79" s="3" t="inlineStr">
+      <c r="D123" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 이슈트반 선택
@@ -3111,32 +4563,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E79" s="3" t="inlineStr">
+      <c r="E123" s="3" t="inlineStr">
         <is>
           <t>관측(Q) 피해량: 40/80/120/160/200(+공격력의 100%)
 (변경 전: 40/80/120/160/200(+공격력의 110%))</t>
         </is>
       </c>
-      <c r="F79" s="3" t="inlineStr"/>
-    </row>
-    <row r="80" ht="60" customHeight="1">
-      <c r="A80" s="2" t="inlineStr">
+      <c r="F123" s="3" t="inlineStr"/>
+    </row>
+    <row r="124" ht="60" customHeight="1">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-027</t>
         </is>
       </c>
-      <c r="B80" s="3" t="inlineStr">
+      <c r="B124" s="3" t="inlineStr">
         <is>
           <t>[실험체] 이슈트반 - 관측(Q) 다른 가능성 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C80" s="3" t="inlineStr">
+      <c r="C124" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 이슈트반 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D80" s="3" t="inlineStr">
+      <c r="D124" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 이슈트반 선택
@@ -3144,32 +4596,32 @@
 4. 다른 가능성 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E80" s="3" t="inlineStr">
+      <c r="E124" s="3" t="inlineStr">
         <is>
           <t>관측(Q) 다른 가능성 피해량: 40/80/120/160/200(+공격력의 100%)
 (변경 전: 40/80/120/160/200(+공격력의 110%))</t>
         </is>
       </c>
-      <c r="F80" s="3" t="inlineStr"/>
-    </row>
-    <row r="81" ht="60" customHeight="1">
-      <c r="A81" s="2" t="inlineStr">
+      <c r="F124" s="3" t="inlineStr"/>
+    </row>
+    <row r="125" ht="60" customHeight="1">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-028</t>
         </is>
       </c>
-      <c r="B81" s="3" t="inlineStr">
+      <c r="B125" s="3" t="inlineStr">
         <is>
           <t>[실험체] 츠바메 - 오의 - 생사 각인(P) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C81" s="3" t="inlineStr">
+      <c r="C125" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 츠바메 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D81" s="3" t="inlineStr">
+      <c r="D125" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 츠바메 선택
@@ -3177,32 +4629,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E81" s="3" t="inlineStr">
+      <c r="E125" s="3" t="inlineStr">
         <is>
           <t>오의 - 생사 각인(P) 피해량: 30(+추가 공격력의 25%)(+대상 최대 체력의 4/7/10(+추가 공격력의 4%)%)
 (변경 전: 30(+추가 공격력의 45%)(+대상 최대 체력의 4/7/10(+추가 공격력의 4%)%))</t>
         </is>
       </c>
-      <c r="F81" s="3" t="inlineStr"/>
-    </row>
-    <row r="82" ht="60" customHeight="1">
-      <c r="A82" s="2" t="inlineStr">
+      <c r="F125" s="3" t="inlineStr"/>
+    </row>
+    <row r="126" ht="60" customHeight="1">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-029</t>
         </is>
       </c>
-      <c r="B82" s="3" t="inlineStr">
+      <c r="B126" s="3" t="inlineStr">
         <is>
           <t>[실험체] 코렐라인 - 단죄의 섬광(Q) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C82" s="3" t="inlineStr">
+      <c r="C126" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 코렐라인 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D82" s="3" t="inlineStr">
+      <c r="D126" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 코렐라인 선택
@@ -3210,32 +4662,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E82" s="3" t="inlineStr">
+      <c r="E126" s="3" t="inlineStr">
         <is>
           <t>단죄의 섬광(Q) 피해량: 50/90/130/170/210(+스킬 증폭의 80%)
 (변경 전: 50/90/130/170/210(+스킬 증폭의 75%))</t>
         </is>
       </c>
-      <c r="F82" s="3" t="inlineStr"/>
-    </row>
-    <row r="83" ht="60" customHeight="1">
-      <c r="A83" s="2" t="inlineStr">
+      <c r="F126" s="3" t="inlineStr"/>
+    </row>
+    <row r="127" ht="60" customHeight="1">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-030</t>
         </is>
       </c>
-      <c r="B83" s="3" t="inlineStr">
+      <c r="B127" s="3" t="inlineStr">
         <is>
           <t>[실험체] 코렐라인 - 죄의 굴레(E) 백경 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C83" s="3" t="inlineStr">
+      <c r="C127" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 코렐라인 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D83" s="3" t="inlineStr">
+      <c r="D127" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 코렐라인 선택
@@ -3243,32 +4695,32 @@
 4. 백경 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E83" s="3" t="inlineStr">
+      <c r="E127" s="3" t="inlineStr">
         <is>
           <t>죄의 굴레(E) 백경 피해량: 80/110/140/170/200(+스킬 증폭의 65%)
 (변경 전: 80/110/140/170/200(+스킬 증폭의 70%))</t>
         </is>
       </c>
-      <c r="F83" s="3" t="inlineStr"/>
-    </row>
-    <row r="84" ht="60" customHeight="1">
-      <c r="A84" s="2" t="inlineStr">
+      <c r="F127" s="3" t="inlineStr"/>
+    </row>
+    <row r="128" ht="60" customHeight="1">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-031</t>
         </is>
       </c>
-      <c r="B84" s="3" t="inlineStr">
+      <c r="B128" s="3" t="inlineStr">
         <is>
           <t>[실험체] 코렐라인 - 죄의 굴레(E) 흑경 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C84" s="3" t="inlineStr">
+      <c r="C128" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 코렐라인 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D84" s="3" t="inlineStr">
+      <c r="D128" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 코렐라인 선택
@@ -3276,32 +4728,32 @@
 4. 흑경 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E84" s="3" t="inlineStr">
+      <c r="E128" s="3" t="inlineStr">
         <is>
           <t>죄의 굴레(E) 흑경 피해량: 80/110/140/170/200(+스킬 증폭의 65%)
 (변경 전: 80/110/140/170/200(+스킬 증폭의 70%))</t>
         </is>
       </c>
-      <c r="F84" s="3" t="inlineStr"/>
-    </row>
-    <row r="85" ht="60" customHeight="1">
-      <c r="A85" s="2" t="inlineStr">
+      <c r="F128" s="3" t="inlineStr"/>
+    </row>
+    <row r="129" ht="60" customHeight="1">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-032</t>
         </is>
       </c>
-      <c r="B85" s="3" t="inlineStr">
+      <c r="B129" s="3" t="inlineStr">
         <is>
           <t>[실험체] 코렐라인 - 죄의 굴레(E) 흑경 방어력 감소량 수치 확인</t>
         </is>
       </c>
-      <c r="C85" s="3" t="inlineStr">
+      <c r="C129" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 코렐라인 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D85" s="3" t="inlineStr">
+      <c r="D129" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 코렐라인 선택
@@ -3309,32 +4761,32 @@
 4. 흑경 방어력 감소량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E85" s="3" t="inlineStr">
+      <c r="E129" s="3" t="inlineStr">
         <is>
           <t>죄의 굴레(E) 흑경 방어력 감소량: 10/11/12/13/14%
 (변경 전: 12/13/14/15/16%)</t>
         </is>
       </c>
-      <c r="F85" s="3" t="inlineStr"/>
-    </row>
-    <row r="86" ht="60" customHeight="1">
-      <c r="A86" s="2" t="inlineStr">
+      <c r="F129" s="3" t="inlineStr"/>
+    </row>
+    <row r="130" ht="60" customHeight="1">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-033</t>
         </is>
       </c>
-      <c r="B86" s="3" t="inlineStr">
+      <c r="B130" s="3" t="inlineStr">
         <is>
           <t>[실험체] 클로에 - 살아 있는 마리오네트(P) 니나 부활 시 클로에 체력 소모량 현재 체력의 수치 확인</t>
         </is>
       </c>
-      <c r="C86" s="3" t="inlineStr">
+      <c r="C130" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 클로에 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D86" s="3" t="inlineStr">
+      <c r="D130" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 클로에 선택
@@ -3342,32 +4794,32 @@
 4. 니나 부활 시 클로에 체력 소모량 현재 체력의 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E86" s="3" t="inlineStr">
+      <c r="E130" s="3" t="inlineStr">
         <is>
           <t>살아 있는 마리오네트(P) 니나 부활 시 클로에 체력 소모량 현재 체력의: 20%
 (변경 전: 30%)</t>
         </is>
       </c>
-      <c r="F86" s="3" t="inlineStr"/>
-    </row>
-    <row r="87" ht="60" customHeight="1">
-      <c r="A87" s="2" t="inlineStr">
+      <c r="F130" s="3" t="inlineStr"/>
+    </row>
+    <row r="131" ht="60" customHeight="1">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-034</t>
         </is>
       </c>
-      <c r="B87" s="3" t="inlineStr">
+      <c r="B131" s="3" t="inlineStr">
         <is>
           <t>[실험체] 키아라 - 뒤틀린 기도(W) 최소 보호막량 수치 확인</t>
         </is>
       </c>
-      <c r="C87" s="3" t="inlineStr">
+      <c r="C131" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 키아라 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D87" s="3" t="inlineStr">
+      <c r="D131" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 키아라 선택
@@ -3375,32 +4827,32 @@
 4. 최소 보호막량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E87" s="3" t="inlineStr">
+      <c r="E131" s="3" t="inlineStr">
         <is>
           <t>뒤틀린 기도(W) 최소 보호막량: 110/130/150/170/190(+스킬 증폭의 50%)
 (변경 전: 90/110/130/150/170(+스킬 증폭의 50%))</t>
         </is>
       </c>
-      <c r="F87" s="3" t="inlineStr"/>
-    </row>
-    <row r="88" ht="60" customHeight="1">
-      <c r="A88" s="2" t="inlineStr">
+      <c r="F131" s="3" t="inlineStr"/>
+    </row>
+    <row r="132" ht="60" customHeight="1">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-035</t>
         </is>
       </c>
-      <c r="B88" s="3" t="inlineStr">
+      <c r="B132" s="3" t="inlineStr">
         <is>
           <t>[실험체] 키아라 - 뒤틀린 기도(W) 최대 보호막량 수치 확인</t>
         </is>
       </c>
-      <c r="C88" s="3" t="inlineStr">
+      <c r="C132" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 키아라 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D88" s="3" t="inlineStr">
+      <c r="D132" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 키아라 선택
@@ -3408,32 +4860,32 @@
 4. 최대 보호막량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E88" s="3" t="inlineStr">
+      <c r="E132" s="3" t="inlineStr">
         <is>
           <t>뒤틀린 기도(W) 최대 보호막량: 165/195/225/255/285(+스킬 증폭의 75%)
 (변경 전: 135/165/195/225/255(+스킬 증폭의 75%))</t>
         </is>
       </c>
-      <c r="F88" s="3" t="inlineStr"/>
-    </row>
-    <row r="89" ht="60" customHeight="1">
-      <c r="A89" s="2" t="inlineStr">
+      <c r="F132" s="3" t="inlineStr"/>
+    </row>
+    <row r="133" ht="60" customHeight="1">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-036</t>
         </is>
       </c>
-      <c r="B89" s="3" t="inlineStr">
+      <c r="B133" s="3" t="inlineStr">
         <is>
           <t>[실험체] 펜리르 - 먹잇감 추적(W) 본능적 후퇴(W2) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C89" s="3" t="inlineStr">
+      <c r="C133" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 펜리르 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D89" s="3" t="inlineStr">
+      <c r="D133" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 펜리르 선택
@@ -3441,32 +4893,32 @@
 4. 본능적 후퇴(W2) 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E89" s="3" t="inlineStr">
+      <c r="E133" s="3" t="inlineStr">
         <is>
           <t>먹잇감 추적(W) 본능적 후퇴(W2) 피해량: 30/55/80/105/130(+공격력의 60%)
 (변경 전: 20/40/60/80/100(+공격력의 60%))</t>
         </is>
       </c>
-      <c r="F89" s="3" t="inlineStr"/>
-    </row>
-    <row r="90" ht="60" customHeight="1">
-      <c r="A90" s="2" t="inlineStr">
+      <c r="F133" s="3" t="inlineStr"/>
+    </row>
+    <row r="134" ht="60" customHeight="1">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-037</t>
         </is>
       </c>
-      <c r="B90" s="3" t="inlineStr">
+      <c r="B134" s="3" t="inlineStr">
         <is>
           <t>[실험체] 프리야 - 대지의 메아리(R) 받는 피해 감소 수치 확인</t>
         </is>
       </c>
-      <c r="C90" s="3" t="inlineStr">
+      <c r="C134" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 프리야 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D90" s="3" t="inlineStr">
+      <c r="D134" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 프리야 선택
@@ -3474,32 +4926,32 @@
 4. 받는 피해 감소 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E90" s="3" t="inlineStr">
+      <c r="E134" s="3" t="inlineStr">
         <is>
           <t>대지의 메아리(R) 받는 피해 감소: 40%
 (변경 전: 50%)</t>
         </is>
       </c>
-      <c r="F90" s="3" t="inlineStr"/>
-    </row>
-    <row r="91" ht="60" customHeight="1">
-      <c r="A91" s="2" t="inlineStr">
+      <c r="F134" s="3" t="inlineStr"/>
+    </row>
+    <row r="135" ht="60" customHeight="1">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-038</t>
         </is>
       </c>
-      <c r="B91" s="3" t="inlineStr">
+      <c r="B135" s="3" t="inlineStr">
         <is>
           <t>[실험체] 프리야 - 포르타멘토(W) 아군 이동 속도 증가 수치 확인</t>
         </is>
       </c>
-      <c r="C91" s="3" t="inlineStr">
+      <c r="C135" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 프리야 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D91" s="3" t="inlineStr">
+      <c r="D135" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 프리야 선택
@@ -3507,32 +4959,32 @@
 4. 아군 이동 속도 증가 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E91" s="3" t="inlineStr">
+      <c r="E135" s="3" t="inlineStr">
         <is>
           <t>포르타멘토(W) 아군 이동 속도 증가: 8/9/10/11/12%
 (변경 전: 10/11/12/13/14%)</t>
         </is>
       </c>
-      <c r="F91" s="3" t="inlineStr"/>
-    </row>
-    <row r="92" ht="60" customHeight="1">
-      <c r="A92" s="2" t="inlineStr">
+      <c r="F135" s="3" t="inlineStr"/>
+    </row>
+    <row r="136" ht="60" customHeight="1">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-039</t>
         </is>
       </c>
-      <c r="B92" s="3" t="inlineStr">
+      <c r="B136" s="3" t="inlineStr">
         <is>
           <t>[실험체] 현우 - 허세(W) 방어력 증가 수치 확인</t>
         </is>
       </c>
-      <c r="C92" s="3" t="inlineStr">
+      <c r="C136" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 현우 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D92" s="3" t="inlineStr">
+      <c r="D136" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 현우 선택
@@ -3540,32 +4992,32 @@
 4. 방어력 증가 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E92" s="3" t="inlineStr">
+      <c r="E136" s="3" t="inlineStr">
         <is>
           <t>허세(W) 방어력 증가: 14/21/28/35/42(+방어력 10당 1)
 (변경 전: 14/23/32/41/50(+방어력 10당 1))</t>
         </is>
       </c>
-      <c r="F92" s="3" t="inlineStr"/>
-    </row>
-    <row r="93" ht="60" customHeight="1">
-      <c r="A93" s="4" t="inlineStr">
+      <c r="F136" s="3" t="inlineStr"/>
+    </row>
+    <row r="137" ht="60" customHeight="1">
+      <c r="A137" s="4" t="inlineStr">
         <is>
           <t>TC-10.6-040</t>
         </is>
       </c>
-      <c r="B93" s="5" t="inlineStr">
+      <c r="B137" s="5" t="inlineStr">
         <is>
           <t>[실험체] 라우라 - 채찍 무기 숙련도 레벨 당 공격 속도 수치 확인</t>
         </is>
       </c>
-      <c r="C93" s="5" t="inlineStr">
+      <c r="C137" s="5" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 라우라 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D93" s="5" t="inlineStr">
+      <c r="D137" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 라우라 선택
@@ -3573,32 +5025,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E93" s="5" t="inlineStr">
+      <c r="E137" s="5" t="inlineStr">
         <is>
           <t>채찍 무기 숙련도 레벨 당 공격 속도: 3.3%
 (변경 전: 2.8%)</t>
         </is>
       </c>
-      <c r="F93" s="5" t="inlineStr"/>
-    </row>
-    <row r="94" ht="60" customHeight="1">
-      <c r="A94" s="4" t="inlineStr">
+      <c r="F137" s="5" t="inlineStr"/>
+    </row>
+    <row r="138" ht="60" customHeight="1">
+      <c r="A138" s="4" t="inlineStr">
         <is>
           <t>TC-10.6-041</t>
         </is>
       </c>
-      <c r="B94" s="5" t="inlineStr">
+      <c r="B138" s="5" t="inlineStr">
         <is>
           <t>[실험체] 레니 - 주는 보호막 효과 수치 확인</t>
         </is>
       </c>
-      <c r="C94" s="5" t="inlineStr">
+      <c r="C138" s="5" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 레니 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D94" s="5" t="inlineStr">
+      <c r="D138" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 레니 선택
@@ -3606,32 +5058,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E94" s="5" t="inlineStr">
+      <c r="E138" s="5" t="inlineStr">
         <is>
           <t>주는 보호막 효과: 70%
 (변경 전: 65%)</t>
         </is>
       </c>
-      <c r="F94" s="5" t="inlineStr"/>
-    </row>
-    <row r="95" ht="60" customHeight="1">
-      <c r="A95" s="4" t="inlineStr">
+      <c r="F138" s="5" t="inlineStr"/>
+    </row>
+    <row r="139" ht="60" customHeight="1">
+      <c r="A139" s="4" t="inlineStr">
         <is>
           <t>TC-10.6-042</t>
         </is>
       </c>
-      <c r="B95" s="5" t="inlineStr">
+      <c r="B139" s="5" t="inlineStr">
         <is>
           <t>[실험체] 리 다이린 - 레벨 당 공격력 수치 확인</t>
         </is>
       </c>
-      <c r="C95" s="5" t="inlineStr">
+      <c r="C139" s="5" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 리 다이린 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D95" s="5" t="inlineStr">
+      <c r="D139" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 리 다이린 선택
@@ -3639,32 +5091,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E95" s="5" t="inlineStr">
+      <c r="E139" s="5" t="inlineStr">
         <is>
           <t>레벨 당 공격력: 5
 (변경 전: 4.8)</t>
         </is>
       </c>
-      <c r="F95" s="5" t="inlineStr"/>
-    </row>
-    <row r="96" ht="60" customHeight="1">
-      <c r="A96" s="4" t="inlineStr">
+      <c r="F139" s="5" t="inlineStr"/>
+    </row>
+    <row r="140" ht="60" customHeight="1">
+      <c r="A140" s="4" t="inlineStr">
         <is>
           <t>TC-10.6-043</t>
         </is>
       </c>
-      <c r="B96" s="5" t="inlineStr">
+      <c r="B140" s="5" t="inlineStr">
         <is>
           <t>[실험체] 버니스 - 기본 공격력 수치 확인</t>
         </is>
       </c>
-      <c r="C96" s="5" t="inlineStr">
+      <c r="C140" s="5" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 버니스 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D96" s="5" t="inlineStr">
+      <c r="D140" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 버니스 선택
@@ -3672,32 +5124,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E96" s="5" t="inlineStr">
+      <c r="E140" s="5" t="inlineStr">
         <is>
           <t>기본 공격력: 37
 (변경 전: 35)</t>
         </is>
       </c>
-      <c r="F96" s="5" t="inlineStr"/>
-    </row>
-    <row r="97" ht="60" customHeight="1">
-      <c r="A97" s="4" t="inlineStr">
+      <c r="F140" s="5" t="inlineStr"/>
+    </row>
+    <row r="141" ht="60" customHeight="1">
+      <c r="A141" s="4" t="inlineStr">
         <is>
           <t>TC-10.6-044</t>
         </is>
       </c>
-      <c r="B97" s="5" t="inlineStr">
+      <c r="B141" s="5" t="inlineStr">
         <is>
           <t>[실험체] 샬럿 - 주는 보호막 효과 수치 확인</t>
         </is>
       </c>
-      <c r="C97" s="5" t="inlineStr">
+      <c r="C141" s="5" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 샬럿 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D97" s="5" t="inlineStr">
+      <c r="D141" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 샬럿 선택
@@ -3705,32 +5157,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E97" s="5" t="inlineStr">
+      <c r="E141" s="5" t="inlineStr">
         <is>
           <t>주는 보호막 효과: 70%
 (변경 전: 65%)</t>
         </is>
       </c>
-      <c r="F97" s="5" t="inlineStr"/>
-    </row>
-    <row r="98" ht="60" customHeight="1">
-      <c r="A98" s="4" t="inlineStr">
+      <c r="F141" s="5" t="inlineStr"/>
+    </row>
+    <row r="142" ht="60" customHeight="1">
+      <c r="A142" s="4" t="inlineStr">
         <is>
           <t>TC-10.6-045</t>
         </is>
       </c>
-      <c r="B98" s="5" t="inlineStr">
+      <c r="B142" s="5" t="inlineStr">
         <is>
           <t>[실험체] 슈린 - 레벨 당 공격력 수치 확인</t>
         </is>
       </c>
-      <c r="C98" s="5" t="inlineStr">
+      <c r="C142" s="5" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 슈린 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D98" s="5" t="inlineStr">
+      <c r="D142" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 슈린 선택
@@ -3738,32 +5190,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E98" s="5" t="inlineStr">
+      <c r="E142" s="5" t="inlineStr">
         <is>
           <t>레벨 당 공격력: 4.6
 (변경 전: 4.3)</t>
         </is>
       </c>
-      <c r="F98" s="5" t="inlineStr"/>
-    </row>
-    <row r="99" ht="60" customHeight="1">
-      <c r="A99" s="4" t="inlineStr">
+      <c r="F142" s="5" t="inlineStr"/>
+    </row>
+    <row r="143" ht="60" customHeight="1">
+      <c r="A143" s="4" t="inlineStr">
         <is>
           <t>TC-10.6-046</t>
         </is>
       </c>
-      <c r="B99" s="5" t="inlineStr">
+      <c r="B143" s="5" t="inlineStr">
         <is>
           <t>[실험체] 실비아 - 주는 회복 효과 수치 확인</t>
         </is>
       </c>
-      <c r="C99" s="5" t="inlineStr">
+      <c r="C143" s="5" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 실비아 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D99" s="5" t="inlineStr">
+      <c r="D143" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 실비아 선택
@@ -3771,32 +5223,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E99" s="5" t="inlineStr">
+      <c r="E143" s="5" t="inlineStr">
         <is>
           <t>주는 회복 효과: 70%
 (변경 전: 65%)</t>
         </is>
       </c>
-      <c r="F99" s="5" t="inlineStr"/>
-    </row>
-    <row r="100" ht="60" customHeight="1">
-      <c r="A100" s="4" t="inlineStr">
+      <c r="F143" s="5" t="inlineStr"/>
+    </row>
+    <row r="144" ht="60" customHeight="1">
+      <c r="A144" s="4" t="inlineStr">
         <is>
           <t>TC-10.6-047</t>
         </is>
       </c>
-      <c r="B100" s="5" t="inlineStr">
+      <c r="B144" s="5" t="inlineStr">
         <is>
           <t>[실험체] 아르다 - 주는 회복 효과 수치 확인</t>
         </is>
       </c>
-      <c r="C100" s="5" t="inlineStr">
+      <c r="C144" s="5" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 아르다 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D100" s="5" t="inlineStr">
+      <c r="D144" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 아르다 선택
@@ -3804,32 +5256,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E100" s="5" t="inlineStr">
+      <c r="E144" s="5" t="inlineStr">
         <is>
           <t>주는 회복 효과: 70%
 (변경 전: 65%)</t>
         </is>
       </c>
-      <c r="F100" s="5" t="inlineStr"/>
-    </row>
-    <row r="101" ht="60" customHeight="1">
-      <c r="A101" s="4" t="inlineStr">
+      <c r="F144" s="5" t="inlineStr"/>
+    </row>
+    <row r="145" ht="60" customHeight="1">
+      <c r="A145" s="4" t="inlineStr">
         <is>
           <t>TC-10.6-048</t>
         </is>
       </c>
-      <c r="B101" s="5" t="inlineStr">
+      <c r="B145" s="5" t="inlineStr">
         <is>
           <t>[실험체] 아이솔 - 권총 무기 숙련도 레벨 당 스킬 증폭 수치 확인</t>
         </is>
       </c>
-      <c r="C101" s="5" t="inlineStr">
+      <c r="C145" s="5" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 아이솔 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D101" s="5" t="inlineStr">
+      <c r="D145" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 아이솔 선택
@@ -3837,32 +5289,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E101" s="5" t="inlineStr">
+      <c r="E145" s="5" t="inlineStr">
         <is>
           <t>권총 무기 숙련도 레벨 당 스킬 증폭: 4.5%
 (변경 전: 4.4%)</t>
         </is>
       </c>
-      <c r="F101" s="5" t="inlineStr"/>
-    </row>
-    <row r="102" ht="60" customHeight="1">
-      <c r="A102" s="4" t="inlineStr">
+      <c r="F145" s="5" t="inlineStr"/>
+    </row>
+    <row r="146" ht="60" customHeight="1">
+      <c r="A146" s="4" t="inlineStr">
         <is>
           <t>TC-10.6-049</t>
         </is>
       </c>
-      <c r="B102" s="5" t="inlineStr">
+      <c r="B146" s="5" t="inlineStr">
         <is>
           <t>[실험체] 에키온 - 기본 공격력 수치 확인</t>
         </is>
       </c>
-      <c r="C102" s="5" t="inlineStr">
+      <c r="C146" s="5" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 에키온 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D102" s="5" t="inlineStr">
+      <c r="D146" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 에키온 선택
@@ -3870,32 +5322,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E102" s="5" t="inlineStr">
+      <c r="E146" s="5" t="inlineStr">
         <is>
           <t>기본 공격력: 35
 (변경 전: 39)</t>
         </is>
       </c>
-      <c r="F102" s="5" t="inlineStr"/>
-    </row>
-    <row r="103" ht="60" customHeight="1">
-      <c r="A103" s="4" t="inlineStr">
+      <c r="F146" s="5" t="inlineStr"/>
+    </row>
+    <row r="147" ht="60" customHeight="1">
+      <c r="A147" s="4" t="inlineStr">
         <is>
           <t>TC-10.6-050</t>
         </is>
       </c>
-      <c r="B103" s="5" t="inlineStr">
+      <c r="B147" s="5" t="inlineStr">
         <is>
           <t>[실험체] 이렘 - 투척 무기 숙련도 레벨 당 공격 속도 수치 확인</t>
         </is>
       </c>
-      <c r="C103" s="5" t="inlineStr">
+      <c r="C147" s="5" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 이렘 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D103" s="5" t="inlineStr">
+      <c r="D147" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 이렘 선택
@@ -3903,32 +5355,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E103" s="5" t="inlineStr">
+      <c r="E147" s="5" t="inlineStr">
         <is>
           <t>투척 무기 숙련도 레벨 당 공격 속도: 2.2%
 (변경 전: 1.6%)</t>
         </is>
       </c>
-      <c r="F103" s="5" t="inlineStr"/>
-    </row>
-    <row r="104" ht="60" customHeight="1">
-      <c r="A104" s="4" t="inlineStr">
+      <c r="F147" s="5" t="inlineStr"/>
+    </row>
+    <row r="148" ht="60" customHeight="1">
+      <c r="A148" s="4" t="inlineStr">
         <is>
           <t>TC-10.6-051</t>
         </is>
       </c>
-      <c r="B104" s="5" t="inlineStr">
+      <c r="B148" s="5" t="inlineStr">
         <is>
           <t>[실험체] 카밀로 - 레이피어 무기 숙련도 레벨 당 기본 공격 증폭 수치 확인</t>
         </is>
       </c>
-      <c r="C104" s="5" t="inlineStr">
+      <c r="C148" s="5" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 카밀로 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D104" s="5" t="inlineStr">
+      <c r="D148" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 카밀로 선택
@@ -3936,32 +5388,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E104" s="5" t="inlineStr">
+      <c r="E148" s="5" t="inlineStr">
         <is>
           <t>레이피어 무기 숙련도 레벨 당 기본 공격 증폭: 1.4%
 (변경 전: 1.5%)</t>
         </is>
       </c>
-      <c r="F104" s="5" t="inlineStr"/>
-    </row>
-    <row r="105" ht="60" customHeight="1">
-      <c r="A105" s="4" t="inlineStr">
+      <c r="F148" s="5" t="inlineStr"/>
+    </row>
+    <row r="149" ht="60" customHeight="1">
+      <c r="A149" s="4" t="inlineStr">
         <is>
           <t>TC-10.6-052</t>
         </is>
       </c>
-      <c r="B105" s="5" t="inlineStr">
+      <c r="B149" s="5" t="inlineStr">
         <is>
           <t>[실험체] 캐시 - 기본 체력 수치 확인</t>
         </is>
       </c>
-      <c r="C105" s="5" t="inlineStr">
+      <c r="C149" s="5" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 캐시 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D105" s="5" t="inlineStr">
+      <c r="D149" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 캐시 선택
@@ -3969,32 +5421,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E105" s="5" t="inlineStr">
+      <c r="E149" s="5" t="inlineStr">
         <is>
           <t>기본 체력: 970
 (변경 전: 940)</t>
         </is>
       </c>
-      <c r="F105" s="5" t="inlineStr"/>
-    </row>
-    <row r="106" ht="60" customHeight="1">
-      <c r="A106" s="4" t="inlineStr">
+      <c r="F149" s="5" t="inlineStr"/>
+    </row>
+    <row r="150" ht="60" customHeight="1">
+      <c r="A150" s="4" t="inlineStr">
         <is>
           <t>TC-10.6-053</t>
         </is>
       </c>
-      <c r="B106" s="5" t="inlineStr">
+      <c r="B150" s="5" t="inlineStr">
         <is>
           <t>[실험체] 펜리르 - 레벨 당 체력 수치 확인</t>
         </is>
       </c>
-      <c r="C106" s="5" t="inlineStr">
+      <c r="C150" s="5" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 펜리르 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D106" s="5" t="inlineStr">
+      <c r="D150" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 펜리르 선택
@@ -4002,32 +5454,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E106" s="5" t="inlineStr">
+      <c r="E150" s="5" t="inlineStr">
         <is>
           <t>레벨 당 체력: 94
 (변경 전: 92)</t>
         </is>
       </c>
-      <c r="F106" s="5" t="inlineStr"/>
-    </row>
-    <row r="107" ht="60" customHeight="1">
-      <c r="A107" s="4" t="inlineStr">
+      <c r="F150" s="5" t="inlineStr"/>
+    </row>
+    <row r="151" ht="60" customHeight="1">
+      <c r="A151" s="4" t="inlineStr">
         <is>
           <t>TC-10.6-054</t>
         </is>
       </c>
-      <c r="B107" s="5" t="inlineStr">
+      <c r="B151" s="5" t="inlineStr">
         <is>
           <t>[실험체] 피오라 - 레이피어 무기 숙련도 레벨 당 스킬 증폭 수치 확인</t>
         </is>
       </c>
-      <c r="C107" s="5" t="inlineStr">
+      <c r="C151" s="5" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 피오라 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D107" s="5" t="inlineStr">
+      <c r="D151" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 피오라 선택
@@ -4035,32 +5487,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E107" s="5" t="inlineStr">
+      <c r="E151" s="5" t="inlineStr">
         <is>
           <t>레이피어 무기 숙련도 레벨 당 스킬 증폭: 4.2%
 (변경 전: 4.3%)</t>
         </is>
       </c>
-      <c r="F107" s="5" t="inlineStr"/>
-    </row>
-    <row r="108" ht="60" customHeight="1">
-      <c r="A108" s="4" t="inlineStr">
+      <c r="F151" s="5" t="inlineStr"/>
+    </row>
+    <row r="152" ht="60" customHeight="1">
+      <c r="A152" s="4" t="inlineStr">
         <is>
           <t>TC-10.6-055</t>
         </is>
       </c>
-      <c r="B108" s="5" t="inlineStr">
+      <c r="B152" s="5" t="inlineStr">
         <is>
           <t>[실험체] 현우 - 톤파 무기 숙련도 레벨 당 스킬 증폭 수치 확인</t>
         </is>
       </c>
-      <c r="C108" s="5" t="inlineStr">
+      <c r="C152" s="5" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 현우 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D108" s="5" t="inlineStr">
+      <c r="D152" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 현우 선택
@@ -4068,32 +5520,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E108" s="5" t="inlineStr">
+      <c r="E152" s="5" t="inlineStr">
         <is>
           <t>톤파 무기 숙련도 레벨 당 스킬 증폭: 4.5%
 (변경 전: 4.3%)</t>
         </is>
       </c>
-      <c r="F108" s="5" t="inlineStr"/>
-    </row>
-    <row r="109" ht="60" customHeight="1">
-      <c r="A109" s="2" t="inlineStr">
+      <c r="F152" s="5" t="inlineStr"/>
+    </row>
+    <row r="153" ht="60" customHeight="1">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>TC-10.5a-001</t>
         </is>
       </c>
-      <c r="B109" s="3" t="inlineStr">
+      <c r="B153" s="3" t="inlineStr">
         <is>
           <t>[실험체] 코렐라인 - 단죄의 섬광(Q) 백경 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C109" s="3" t="inlineStr">
+      <c r="C153" s="3" t="inlineStr">
         <is>
           <t>· 10.5a 패치 적용 완료
 · 코렐라인 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D109" s="3" t="inlineStr">
+      <c r="D153" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 코렐라인 선택
@@ -4101,32 +5553,32 @@
 4. 백경 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E109" s="3" t="inlineStr">
+      <c r="E153" s="3" t="inlineStr">
         <is>
           <t>단죄의 섬광(Q) 백경 피해량: 60/105/150/195/240(+스킬 증폭의 80%)(+현재 체력의 4/6/8/10/12%)
 (변경 전: 60/105/150/195/240(+스킬 증폭의 85%)(+현재 체력의 4/6/8/10/12%))</t>
         </is>
       </c>
-      <c r="F109" s="3" t="inlineStr"/>
-    </row>
-    <row r="110" ht="60" customHeight="1">
-      <c r="A110" s="2" t="inlineStr">
+      <c r="F153" s="3" t="inlineStr"/>
+    </row>
+    <row r="154" ht="60" customHeight="1">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>TC-10.5a-002</t>
         </is>
       </c>
-      <c r="B110" s="3" t="inlineStr">
+      <c r="B154" s="3" t="inlineStr">
         <is>
           <t>[실험체] 코렐라인 - 단죄의 섬광(Q) 흑경 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C110" s="3" t="inlineStr">
+      <c r="C154" s="3" t="inlineStr">
         <is>
           <t>· 10.5a 패치 적용 완료
 · 코렐라인 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D110" s="3" t="inlineStr">
+      <c r="D154" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 코렐라인 선택
@@ -4134,32 +5586,32 @@
 4. 흑경 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E110" s="3" t="inlineStr">
+      <c r="E154" s="3" t="inlineStr">
         <is>
           <t>단죄의 섬광(Q) 흑경 피해량: 60/105/150/195/240(+스킬 증폭의 80%)(+잃은 체력의 3/6/9/12/15%)
 (변경 전: 60/105/150/195/240(+스킬 증폭의 85%)(+잃은 체력의 3/6/9/12/15%))</t>
         </is>
       </c>
-      <c r="F110" s="3" t="inlineStr"/>
-    </row>
-    <row r="111" ht="60" customHeight="1">
-      <c r="A111" s="4" t="inlineStr">
+      <c r="F154" s="3" t="inlineStr"/>
+    </row>
+    <row r="155" ht="60" customHeight="1">
+      <c r="A155" s="4" t="inlineStr">
         <is>
           <t>TC-10.5a-003</t>
         </is>
       </c>
-      <c r="B111" s="5" t="inlineStr">
+      <c r="B155" s="5" t="inlineStr">
         <is>
           <t>[실험체] 현우 - 최대 체력 수치 확인</t>
         </is>
       </c>
-      <c r="C111" s="5" t="inlineStr">
+      <c r="C155" s="5" t="inlineStr">
         <is>
           <t>· 10.5a 패치 적용 완료
 · 현우 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D111" s="5" t="inlineStr">
+      <c r="D155" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 현우 선택
@@ -4167,32 +5619,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E111" s="5" t="inlineStr">
+      <c r="E155" s="5" t="inlineStr">
         <is>
           <t>최대 체력: 960
 (변경 전: 1000)</t>
         </is>
       </c>
-      <c r="F111" s="5" t="inlineStr"/>
-    </row>
-    <row r="112" ht="60" customHeight="1">
-      <c r="A112" s="2" t="inlineStr">
+      <c r="F155" s="5" t="inlineStr"/>
+    </row>
+    <row r="156" ht="60" customHeight="1">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-001</t>
         </is>
       </c>
-      <c r="B112" s="3" t="inlineStr">
+      <c r="B156" s="3" t="inlineStr">
         <is>
           <t>[실험체] 나타폰 - 슬로우 셔터(P) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C112" s="3" t="inlineStr">
+      <c r="C156" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 나타폰 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D112" s="3" t="inlineStr">
+      <c r="D156" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 나타폰 선택
@@ -4200,32 +5652,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E112" s="3" t="inlineStr">
+      <c r="E156" s="3" t="inlineStr">
         <is>
           <t>슬로우 셔터(P) 피해량: 30/60/90(+공격 속도의 20%)(+스킬 증폭의 65%)
 (변경 전: 40/70/100(+공격 속도의 20%)(+스킬 증폭의 65%))</t>
         </is>
       </c>
-      <c r="F112" s="3" t="inlineStr"/>
-    </row>
-    <row r="113" ht="60" customHeight="1">
-      <c r="A113" s="2" t="inlineStr">
+      <c r="F156" s="3" t="inlineStr"/>
+    </row>
+    <row r="157" ht="60" customHeight="1">
+      <c r="A157" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-002</t>
         </is>
       </c>
-      <c r="B113" s="3" t="inlineStr">
+      <c r="B157" s="3" t="inlineStr">
         <is>
           <t>[실험체] 다르코 - 고리대금(Q) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C113" s="3" t="inlineStr">
+      <c r="C157" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 다르코 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D113" s="3" t="inlineStr">
+      <c r="D157" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 다르코 선택
@@ -4233,32 +5685,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E113" s="3" t="inlineStr">
+      <c r="E157" s="3" t="inlineStr">
         <is>
           <t>고리대금(Q) 피해량: 20/40/60/80/100(+공격력의 40%)(+대상 최대 체력의 2/3/4/5/6%)
 (변경 전: 20/40/60/80/100(+공격력의 40%)(+대상 최대 체력의 1/2/3/4/5%))</t>
         </is>
       </c>
-      <c r="F113" s="3" t="inlineStr"/>
-    </row>
-    <row r="114" ht="60" customHeight="1">
-      <c r="A114" s="2" t="inlineStr">
+      <c r="F157" s="3" t="inlineStr"/>
+    </row>
+    <row r="158" ht="60" customHeight="1">
+      <c r="A158" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-003</t>
         </is>
       </c>
-      <c r="B114" s="3" t="inlineStr">
+      <c r="B158" s="3" t="inlineStr">
         <is>
           <t>[실험체] 띠아 - 색칠놀이(E) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C114" s="3" t="inlineStr">
+      <c r="C158" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 띠아 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D114" s="3" t="inlineStr">
+      <c r="D158" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 띠아 선택
@@ -4266,32 +5718,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E114" s="3" t="inlineStr">
+      <c r="E158" s="3" t="inlineStr">
         <is>
           <t>색칠놀이(E) 피해량: 40/90/140/190/240(+스킬 증폭의 90%)
 (변경 전: 40/90/140/190/240(+스킬 증폭의 80%))</t>
         </is>
       </c>
-      <c r="F114" s="3" t="inlineStr"/>
-    </row>
-    <row r="115" ht="60" customHeight="1">
-      <c r="A115" s="2" t="inlineStr">
+      <c r="F158" s="3" t="inlineStr"/>
+    </row>
+    <row r="159" ht="60" customHeight="1">
+      <c r="A159" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-004</t>
         </is>
       </c>
-      <c r="B115" s="3" t="inlineStr">
+      <c r="B159" s="3" t="inlineStr">
         <is>
           <t>[실험체] 라우라 - 날카로운 꽃(Q) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C115" s="3" t="inlineStr">
+      <c r="C159" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 라우라 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D115" s="3" t="inlineStr">
+      <c r="D159" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 라우라 선택
@@ -4299,32 +5751,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E115" s="3" t="inlineStr">
+      <c r="E159" s="3" t="inlineStr">
         <is>
           <t>날카로운 꽃(Q) 피해량: 50/75/100/125/150(+스킬 증폭의 60%)
 (변경 전: 50/75/100/125/150(+스킬 증폭의 55%))</t>
         </is>
       </c>
-      <c r="F115" s="3" t="inlineStr"/>
-    </row>
-    <row r="116" ht="60" customHeight="1">
-      <c r="A116" s="2" t="inlineStr">
+      <c r="F159" s="3" t="inlineStr"/>
+    </row>
+    <row r="160" ht="60" customHeight="1">
+      <c r="A160" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-005</t>
         </is>
       </c>
-      <c r="B116" s="3" t="inlineStr">
+      <c r="B160" s="3" t="inlineStr">
         <is>
           <t>[실험체] 레녹스 - 위풍당당(P) 쿨다운 수치 확인</t>
         </is>
       </c>
-      <c r="C116" s="3" t="inlineStr">
+      <c r="C160" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 레녹스 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D116" s="3" t="inlineStr">
+      <c r="D160" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 레녹스 선택
@@ -4332,32 +5784,32 @@
 4. 쿨다운 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E116" s="3" t="inlineStr">
+      <c r="E160" s="3" t="inlineStr">
         <is>
           <t>위풍당당(P) 쿨다운: 15/13/11초
 (변경 전: 14/12/10초)</t>
         </is>
       </c>
-      <c r="F116" s="3" t="inlineStr"/>
-    </row>
-    <row r="117" ht="60" customHeight="1">
-      <c r="A117" s="2" t="inlineStr">
+      <c r="F160" s="3" t="inlineStr"/>
+    </row>
+    <row r="161" ht="60" customHeight="1">
+      <c r="A161" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-006</t>
         </is>
       </c>
-      <c r="B117" s="3" t="inlineStr">
+      <c r="B161" s="3" t="inlineStr">
         <is>
           <t>[실험체] 마르티나 - 되감기 - 방송 중(E) 체력 회복량 받은 피해의 수치 확인</t>
         </is>
       </c>
-      <c r="C117" s="3" t="inlineStr">
+      <c r="C161" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 마르티나 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D117" s="3" t="inlineStr">
+      <c r="D161" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 마르티나 선택
@@ -4365,32 +5817,32 @@
 4. 체력 회복량 받은 피해의 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E117" s="3" t="inlineStr">
+      <c r="E161" s="3" t="inlineStr">
         <is>
           <t>되감기 - 방송 중(E) 체력 회복량 받은 피해의: 40/45/50/55/60%
 (변경 전: 37/41/45/49/53%)</t>
         </is>
       </c>
-      <c r="F117" s="3" t="inlineStr"/>
-    </row>
-    <row r="118" ht="60" customHeight="1">
-      <c r="A118" s="2" t="inlineStr">
+      <c r="F161" s="3" t="inlineStr"/>
+    </row>
+    <row r="162" ht="60" customHeight="1">
+      <c r="A162" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-007</t>
         </is>
       </c>
-      <c r="B118" s="3" t="inlineStr">
+      <c r="B162" s="3" t="inlineStr">
         <is>
           <t>[실험체] 마이 - 캣 워크(E) 보호막 흡수량 수치 확인</t>
         </is>
       </c>
-      <c r="C118" s="3" t="inlineStr">
+      <c r="C162" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 마이 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D118" s="3" t="inlineStr">
+      <c r="D162" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 마이 선택
@@ -4398,32 +5850,32 @@
 4. 보호막 흡수량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E118" s="3" t="inlineStr">
+      <c r="E162" s="3" t="inlineStr">
         <is>
           <t>캣 워크(E) 보호막 흡수량: 60/90/120/150/180(+스킬 증폭의 40%)(+최대 체력의 7%)
 (변경 전: 60/90/120/150/180(+스킬 증폭의 40%)(+최대 체력의 6%))</t>
         </is>
       </c>
-      <c r="F118" s="3" t="inlineStr"/>
-    </row>
-    <row r="119" ht="60" customHeight="1">
-      <c r="A119" s="2" t="inlineStr">
+      <c r="F162" s="3" t="inlineStr"/>
+    </row>
+    <row r="163" ht="60" customHeight="1">
+      <c r="A163" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-008</t>
         </is>
       </c>
-      <c r="B119" s="3" t="inlineStr">
+      <c r="B163" s="3" t="inlineStr">
         <is>
           <t>[실험체] 비앙카 - 진조의 군림(R)  수치 확인</t>
         </is>
       </c>
-      <c r="C119" s="3" t="inlineStr">
+      <c r="C163" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 비앙카 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D119" s="3" t="inlineStr">
+      <c r="D163" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 비앙카 선택
@@ -4431,32 +5883,32 @@
 4.  수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E119" s="3" t="inlineStr">
+      <c r="E163" s="3" t="inlineStr">
         <is>
           <t>진조의 군림(R) : 50/100/150(+스킬 증폭의 40%)(+대상 최대 체력의 11%)
 (변경 전: 1타 피해량 50/100/150(+스킬 증폭의 50%)(+대상 최대 체력의 11%))</t>
         </is>
       </c>
-      <c r="F119" s="3" t="inlineStr"/>
-    </row>
-    <row r="120" ht="60" customHeight="1">
-      <c r="A120" s="2" t="inlineStr">
+      <c r="F163" s="3" t="inlineStr"/>
+    </row>
+    <row r="164" ht="60" customHeight="1">
+      <c r="A164" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-009</t>
         </is>
       </c>
-      <c r="B120" s="3" t="inlineStr">
+      <c r="B164" s="3" t="inlineStr">
         <is>
           <t>[실험체] 시셀라 - 모두 해방이에요.(R) 패시브 효과 증가 지속 시간 수치 확인</t>
         </is>
       </c>
-      <c r="C120" s="3" t="inlineStr">
+      <c r="C164" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 시셀라 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D120" s="3" t="inlineStr">
+      <c r="D164" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 시셀라 선택
@@ -4464,32 +5916,32 @@
 4. 패시브 효과 증가 지속 시간 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E120" s="3" t="inlineStr">
+      <c r="E164" s="3" t="inlineStr">
         <is>
           <t>모두 해방이에요.(R) 패시브 효과 증가 지속 시간: 7/8/9초
 (변경 전: 6/7/8초)</t>
         </is>
       </c>
-      <c r="F120" s="3" t="inlineStr"/>
-    </row>
-    <row r="121" ht="60" customHeight="1">
-      <c r="A121" s="2" t="inlineStr">
+      <c r="F164" s="3" t="inlineStr"/>
+    </row>
+    <row r="165" ht="60" customHeight="1">
+      <c r="A165" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-010</t>
         </is>
       </c>
-      <c r="B121" s="3" t="inlineStr">
+      <c r="B165" s="3" t="inlineStr">
         <is>
           <t>[실험체] 시셀라 - 어딨어 윌슨?(W) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C121" s="3" t="inlineStr">
+      <c r="C165" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 시셀라 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D121" s="3" t="inlineStr">
+      <c r="D165" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 시셀라 선택
@@ -4497,32 +5949,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E121" s="3" t="inlineStr">
+      <c r="E165" s="3" t="inlineStr">
         <is>
           <t>어딨어 윌슨?(W) 피해량: 100/135/170/205/240(+스킬 증폭의 80%)
 (변경 전: 100/135/170/205/240(+스킬 증폭의 70%))</t>
         </is>
       </c>
-      <c r="F121" s="3" t="inlineStr"/>
-    </row>
-    <row r="122" ht="60" customHeight="1">
-      <c r="A122" s="2" t="inlineStr">
+      <c r="F165" s="3" t="inlineStr"/>
+    </row>
+    <row r="166" ht="60" customHeight="1">
+      <c r="A166" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-011</t>
         </is>
       </c>
-      <c r="B122" s="3" t="inlineStr">
+      <c r="B166" s="3" t="inlineStr">
         <is>
           <t>[실험체] 아야 - 고정 사격(W) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C122" s="3" t="inlineStr">
+      <c r="C166" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 아야 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D122" s="3" t="inlineStr">
+      <c r="D166" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 아야 선택
@@ -4530,32 +5982,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E122" s="3" t="inlineStr">
+      <c r="E166" s="3" t="inlineStr">
         <is>
           <t>고정 사격(W) 피해량: 30/40/50/60/70(+공격력의 50%)(+스킬 증폭의 30/35/40/45/50%)
 (변경 전: 20/30/40/50/60(+공격력의 50%)(+스킬 증폭의 30/35/40/45/50%))</t>
         </is>
       </c>
-      <c r="F122" s="3" t="inlineStr"/>
-    </row>
-    <row r="123" ht="60" customHeight="1">
-      <c r="A123" s="2" t="inlineStr">
+      <c r="F166" s="3" t="inlineStr"/>
+    </row>
+    <row r="167" ht="60" customHeight="1">
+      <c r="A167" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-012</t>
         </is>
       </c>
-      <c r="B123" s="3" t="inlineStr">
+      <c r="B167" s="3" t="inlineStr">
         <is>
           <t>[실험체] 알론소 - 어트랙션 슬램!(E) 속박 지속 시간 수치 확인</t>
         </is>
       </c>
-      <c r="C123" s="3" t="inlineStr">
+      <c r="C167" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 알론소 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D123" s="3" t="inlineStr">
+      <c r="D167" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 알론소 선택
@@ -4563,32 +6015,32 @@
 4. 속박 지속 시간 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E123" s="3" t="inlineStr">
+      <c r="E167" s="3" t="inlineStr">
         <is>
           <t>어트랙션 슬램!(E) 속박 지속 시간: 0.8/0.9/1/1.1/1.2초
 (변경 전: 0.7/0.8/0.9/1/1.1초)</t>
         </is>
       </c>
-      <c r="F123" s="3" t="inlineStr"/>
-    </row>
-    <row r="124" ht="60" customHeight="1">
-      <c r="A124" s="2" t="inlineStr">
+      <c r="F167" s="3" t="inlineStr"/>
+    </row>
+    <row r="168" ht="60" customHeight="1">
+      <c r="A168" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-013</t>
         </is>
       </c>
-      <c r="B124" s="3" t="inlineStr">
+      <c r="B168" s="3" t="inlineStr">
         <is>
           <t>[실험체] 얀 - 니 스트라이크(Q) 리핑 니 스트라이크(Q2) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C124" s="3" t="inlineStr">
+      <c r="C168" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 얀 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D124" s="3" t="inlineStr">
+      <c r="D168" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 얀 선택
@@ -4596,32 +6048,32 @@
 4. 리핑 니 스트라이크(Q2) 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E124" s="3" t="inlineStr">
+      <c r="E168" s="3" t="inlineStr">
         <is>
           <t>니 스트라이크(Q) 리핑 니 스트라이크(Q2) 피해량: 65/90/115/140/165(+추가 공격력의 90%)(+스킬 증폭의 70%)(+적 최대 체력의 6%)
 (변경 전: 65/90/115/140/165(+추가 공격력의 90%)(+스킬 증폭의 60%)(+적 최대 체력의 6%))</t>
         </is>
       </c>
-      <c r="F124" s="3" t="inlineStr"/>
-    </row>
-    <row r="125" ht="60" customHeight="1">
-      <c r="A125" s="2" t="inlineStr">
+      <c r="F168" s="3" t="inlineStr"/>
+    </row>
+    <row r="169" ht="60" customHeight="1">
+      <c r="A169" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-014</t>
         </is>
       </c>
-      <c r="B125" s="3" t="inlineStr">
+      <c r="B169" s="3" t="inlineStr">
         <is>
           <t>[실험체] 에스텔 - 선제대응(W) 이동 속도 감소 수치 확인</t>
         </is>
       </c>
-      <c r="C125" s="3" t="inlineStr">
+      <c r="C169" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 에스텔 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D125" s="3" t="inlineStr">
+      <c r="D169" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 에스텔 선택
@@ -4629,32 +6081,32 @@
 4. 이동 속도 감소 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E125" s="3" t="inlineStr">
+      <c r="E169" s="3" t="inlineStr">
         <is>
           <t>선제대응(W) 이동 속도 감소: 30%
 (변경 전: 25%)</t>
         </is>
       </c>
-      <c r="F125" s="3" t="inlineStr"/>
-    </row>
-    <row r="126" ht="60" customHeight="1">
-      <c r="A126" s="2" t="inlineStr">
+      <c r="F169" s="3" t="inlineStr"/>
+    </row>
+    <row r="170" ht="60" customHeight="1">
+      <c r="A170" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-015</t>
         </is>
       </c>
-      <c r="B126" s="3" t="inlineStr">
+      <c r="B170" s="3" t="inlineStr">
         <is>
           <t>[실험체] 엘레나 - 겨울여왕의 영지(P) 빙결 지속 시간 수치 확인</t>
         </is>
       </c>
-      <c r="C126" s="3" t="inlineStr">
+      <c r="C170" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 엘레나 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D126" s="3" t="inlineStr">
+      <c r="D170" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 엘레나 선택
@@ -4662,32 +6114,32 @@
 4. 빙결 지속 시간 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E126" s="3" t="inlineStr">
+      <c r="E170" s="3" t="inlineStr">
         <is>
           <t>겨울여왕의 영지(P) 빙결 지속 시간: 1.1초
 (변경 전: 1초)</t>
         </is>
       </c>
-      <c r="F126" s="3" t="inlineStr"/>
-    </row>
-    <row r="127" ht="60" customHeight="1">
-      <c r="A127" s="2" t="inlineStr">
+      <c r="F170" s="3" t="inlineStr"/>
+    </row>
+    <row r="171" ht="60" customHeight="1">
+      <c r="A171" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-016</t>
         </is>
       </c>
-      <c r="B127" s="3" t="inlineStr">
+      <c r="B171" s="3" t="inlineStr">
         <is>
           <t>[실험체] 엘레나 - 더블 악셀(W) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C127" s="3" t="inlineStr">
+      <c r="C171" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 엘레나 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D127" s="3" t="inlineStr">
+      <c r="D171" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 엘레나 선택
@@ -4695,32 +6147,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E127" s="3" t="inlineStr">
+      <c r="E171" s="3" t="inlineStr">
         <is>
           <t>더블 악셀(W) 피해량: 50/70/90/110/130(+스킬 증폭의 50%)(+추가 체력의 10%)
 (변경 전: 50/70/90/110/130(+스킬 증폭의 50%)(+추가 체력의 8%))</t>
         </is>
       </c>
-      <c r="F127" s="3" t="inlineStr"/>
-    </row>
-    <row r="128" ht="60" customHeight="1">
-      <c r="A128" s="2" t="inlineStr">
+      <c r="F171" s="3" t="inlineStr"/>
+    </row>
+    <row r="172" ht="60" customHeight="1">
+      <c r="A172" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-017</t>
         </is>
       </c>
-      <c r="B128" s="3" t="inlineStr">
+      <c r="B172" s="3" t="inlineStr">
         <is>
           <t>[실험체] 유스티나 - 부스트 대쉬(E) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C128" s="3" t="inlineStr">
+      <c r="C172" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 유스티나 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D128" s="3" t="inlineStr">
+      <c r="D172" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 유스티나 선택
@@ -4728,32 +6180,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E128" s="3" t="inlineStr">
+      <c r="E172" s="3" t="inlineStr">
         <is>
           <t>부스트 대쉬(E) 피해량: 50/75/100/125/150(+스킬 증폭의 30%)
 (변경 전: 40/60/80/100/120(+스킬 증폭의 30%))</t>
         </is>
       </c>
-      <c r="F128" s="3" t="inlineStr"/>
-    </row>
-    <row r="129" ht="60" customHeight="1">
-      <c r="A129" s="2" t="inlineStr">
+      <c r="F172" s="3" t="inlineStr"/>
+    </row>
+    <row r="173" ht="60" customHeight="1">
+      <c r="A173" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-018</t>
         </is>
       </c>
-      <c r="B129" s="3" t="inlineStr">
+      <c r="B173" s="3" t="inlineStr">
         <is>
           <t>[실험체] 이바 - 위상의 소용돌이(W)  수치 확인</t>
         </is>
       </c>
-      <c r="C129" s="3" t="inlineStr">
+      <c r="C173" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 이바 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D129" s="3" t="inlineStr">
+      <c r="D173" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 이바 선택
@@ -4761,32 +6213,32 @@
 4.  수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E129" s="3" t="inlineStr">
+      <c r="E173" s="3" t="inlineStr">
         <is>
           <t>위상의 소용돌이(W) : 40/70/100/130/160(+스킬 증폭의 40%)
 (변경 전: 1타 피해량 40/70/100/130/160(+스킬 증폭의 45%))</t>
         </is>
       </c>
-      <c r="F129" s="3" t="inlineStr"/>
-    </row>
-    <row r="130" ht="60" customHeight="1">
-      <c r="A130" s="2" t="inlineStr">
+      <c r="F173" s="3" t="inlineStr"/>
+    </row>
+    <row r="174" ht="60" customHeight="1">
+      <c r="A174" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-019</t>
         </is>
       </c>
-      <c r="B130" s="3" t="inlineStr">
+      <c r="B174" s="3" t="inlineStr">
         <is>
           <t>[실험체] 일레븐 - 다 덤벼보라구!(R) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C130" s="3" t="inlineStr">
+      <c r="C174" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 일레븐 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D130" s="3" t="inlineStr">
+      <c r="D174" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 일레븐 선택
@@ -4794,32 +6246,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E130" s="3" t="inlineStr">
+      <c r="E174" s="3" t="inlineStr">
         <is>
           <t>다 덤벼보라구!(R) 피해량: 10/15/20(+공격력의 3%)(+추가 체력의 3%)
 (변경 전: 6/9/12(+공격력의 3%)(+추가 체력의 3%))</t>
         </is>
       </c>
-      <c r="F130" s="3" t="inlineStr"/>
-    </row>
-    <row r="131" ht="60" customHeight="1">
-      <c r="A131" s="2" t="inlineStr">
+      <c r="F174" s="3" t="inlineStr"/>
+    </row>
+    <row r="175" ht="60" customHeight="1">
+      <c r="A175" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-020</t>
         </is>
       </c>
-      <c r="B131" s="3" t="inlineStr">
+      <c r="B175" s="3" t="inlineStr">
         <is>
           <t>[실험체] 제니 - 레드 카펫(W) 쿨다운 수치 확인</t>
         </is>
       </c>
-      <c r="C131" s="3" t="inlineStr">
+      <c r="C175" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 제니 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D131" s="3" t="inlineStr">
+      <c r="D175" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 제니 선택
@@ -4827,32 +6279,32 @@
 4. 쿨다운 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E131" s="3" t="inlineStr">
+      <c r="E175" s="3" t="inlineStr">
         <is>
           <t>레드 카펫(W) 쿨다운: 15초
 (변경 전: 16초)</t>
         </is>
       </c>
-      <c r="F131" s="3" t="inlineStr"/>
-    </row>
-    <row r="132" ht="60" customHeight="1">
-      <c r="A132" s="2" t="inlineStr">
+      <c r="F175" s="3" t="inlineStr"/>
+    </row>
+    <row r="176" ht="60" customHeight="1">
+      <c r="A176" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-021</t>
         </is>
       </c>
-      <c r="B132" s="3" t="inlineStr">
+      <c r="B176" s="3" t="inlineStr">
         <is>
           <t>[실험체] 제니 - 시상식의 여왕(R) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C132" s="3" t="inlineStr">
+      <c r="C176" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 제니 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D132" s="3" t="inlineStr">
+      <c r="D176" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 제니 선택
@@ -4860,32 +6312,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E132" s="3" t="inlineStr">
+      <c r="E176" s="3" t="inlineStr">
         <is>
           <t>시상식의 여왕(R) 피해량: 150/240/330(+스킬 증폭의 70%)
 (변경 전: 100/200/300(+스킬 증폭의 70%))</t>
         </is>
       </c>
-      <c r="F132" s="3" t="inlineStr"/>
-    </row>
-    <row r="133" ht="60" customHeight="1">
-      <c r="A133" s="2" t="inlineStr">
+      <c r="F176" s="3" t="inlineStr"/>
+    </row>
+    <row r="177" ht="60" customHeight="1">
+      <c r="A177" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-022</t>
         </is>
       </c>
-      <c r="B133" s="3" t="inlineStr">
+      <c r="B177" s="3" t="inlineStr">
         <is>
           <t>[실험체] 캐시 - 수쳐(E) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C133" s="3" t="inlineStr">
+      <c r="C177" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 캐시 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D133" s="3" t="inlineStr">
+      <c r="D177" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 캐시 선택
@@ -4893,32 +6345,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E133" s="3" t="inlineStr">
+      <c r="E177" s="3" t="inlineStr">
         <is>
           <t>수쳐(E) 피해량: 50/60/70/80/90(+스킬 증폭의 45%)
 (변경 전: 50/60/70/80/90(+스킬 증폭의 40%))</t>
         </is>
       </c>
-      <c r="F133" s="3" t="inlineStr"/>
-    </row>
-    <row r="134" ht="60" customHeight="1">
-      <c r="A134" s="2" t="inlineStr">
+      <c r="F177" s="3" t="inlineStr"/>
+    </row>
+    <row r="178" ht="60" customHeight="1">
+      <c r="A178" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-023</t>
         </is>
       </c>
-      <c r="B134" s="3" t="inlineStr">
+      <c r="B178" s="3" t="inlineStr">
         <is>
           <t>[실험체] 케네스 - 업화(W) 받는 피해 감소 수치 확인</t>
         </is>
       </c>
-      <c r="C134" s="3" t="inlineStr">
+      <c r="C178" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 케네스 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D134" s="3" t="inlineStr">
+      <c r="D178" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 케네스 선택
@@ -4926,32 +6378,32 @@
 4. 받는 피해 감소 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E134" s="3" t="inlineStr">
+      <c r="E178" s="3" t="inlineStr">
         <is>
           <t>업화(W) 받는 피해 감소: 2(+공격력의 3/3.25/3.5/3.75/4%)%
 (변경 전: 4(+공격력의 3/3.25/3.5/3.75/4%)%)</t>
         </is>
       </c>
-      <c r="F134" s="3" t="inlineStr"/>
-    </row>
-    <row r="135" ht="60" customHeight="1">
-      <c r="A135" s="2" t="inlineStr">
+      <c r="F178" s="3" t="inlineStr"/>
+    </row>
+    <row r="179" ht="60" customHeight="1">
+      <c r="A179" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-024</t>
         </is>
       </c>
-      <c r="B135" s="3" t="inlineStr">
+      <c r="B179" s="3" t="inlineStr">
         <is>
           <t>[실험체] 타지아 - 스틸레토(Q) 스파다 폭발 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C135" s="3" t="inlineStr">
+      <c r="C179" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 타지아 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D135" s="3" t="inlineStr">
+      <c r="D179" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 타지아 선택
@@ -4959,32 +6411,32 @@
 4. 스파다 폭발 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E135" s="3" t="inlineStr">
+      <c r="E179" s="3" t="inlineStr">
         <is>
           <t>스틸레토(Q) 스파다 폭발 피해량: 40/70/100/130/160(+스킬 증폭의 55%)
 (변경 전: 40/70/100/130/160(+스킬 증폭의 50%))</t>
         </is>
       </c>
-      <c r="F135" s="3" t="inlineStr"/>
-    </row>
-    <row r="136" ht="60" customHeight="1">
-      <c r="A136" s="2" t="inlineStr">
+      <c r="F179" s="3" t="inlineStr"/>
+    </row>
+    <row r="180" ht="60" customHeight="1">
+      <c r="A180" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-025</t>
         </is>
       </c>
-      <c r="B136" s="3" t="inlineStr">
+      <c r="B180" s="3" t="inlineStr">
         <is>
           <t>[실험체] 프리야 - 개화의 선율(Q) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C136" s="3" t="inlineStr">
+      <c r="C180" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 프리야 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D136" s="3" t="inlineStr">
+      <c r="D180" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 프리야 선택
@@ -4992,32 +6444,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E136" s="3" t="inlineStr">
+      <c r="E180" s="3" t="inlineStr">
         <is>
           <t>개화의 선율(Q) 피해량: 60/90/120/150/180(+스킬 증폭의 70%)
 (변경 전: 80/110/140/170/200(+스킬 증폭의 70%))</t>
         </is>
       </c>
-      <c r="F136" s="3" t="inlineStr"/>
-    </row>
-    <row r="137" ht="60" customHeight="1">
-      <c r="A137" s="2" t="inlineStr">
+      <c r="F180" s="3" t="inlineStr"/>
+    </row>
+    <row r="181" ht="60" customHeight="1">
+      <c r="A181" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-026</t>
         </is>
       </c>
-      <c r="B137" s="3" t="inlineStr">
+      <c r="B181" s="3" t="inlineStr">
         <is>
           <t>[실험체] 프리야 - 대지의 메아리(R) 쿨다운 수치 확인</t>
         </is>
       </c>
-      <c r="C137" s="3" t="inlineStr">
+      <c r="C181" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 프리야 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D137" s="3" t="inlineStr">
+      <c r="D181" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 프리야 선택
@@ -5025,32 +6477,32 @@
 4. 쿨다운 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E137" s="3" t="inlineStr">
+      <c r="E181" s="3" t="inlineStr">
         <is>
           <t>대지의 메아리(R) 쿨다운: 80/75/70초
 (변경 전: 80/70/60초)</t>
         </is>
       </c>
-      <c r="F137" s="3" t="inlineStr"/>
-    </row>
-    <row r="138" ht="60" customHeight="1">
-      <c r="A138" s="2" t="inlineStr">
+      <c r="F181" s="3" t="inlineStr"/>
+    </row>
+    <row r="182" ht="60" customHeight="1">
+      <c r="A182" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-027</t>
         </is>
       </c>
-      <c r="B138" s="3" t="inlineStr">
+      <c r="B182" s="3" t="inlineStr">
         <is>
           <t>[실험체] 피올로 - 사슬 묶기(E) 최대 충전까지 걸리는 시간 수치 확인</t>
         </is>
       </c>
-      <c r="C138" s="3" t="inlineStr">
+      <c r="C182" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 피올로 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D138" s="3" t="inlineStr">
+      <c r="D182" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 피올로 선택
@@ -5058,32 +6510,32 @@
 4. 최대 충전까지 걸리는 시간 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E138" s="3" t="inlineStr">
+      <c r="E182" s="3" t="inlineStr">
         <is>
           <t>사슬 묶기(E) 최대 충전까지 걸리는 시간: 1.2초
 (변경 전: 1.5초)</t>
         </is>
       </c>
-      <c r="F138" s="3" t="inlineStr"/>
-    </row>
-    <row r="139" ht="60" customHeight="1">
-      <c r="A139" s="2" t="inlineStr">
+      <c r="F182" s="3" t="inlineStr"/>
+    </row>
+    <row r="183" ht="60" customHeight="1">
+      <c r="A183" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-028</t>
         </is>
       </c>
-      <c r="B139" s="3" t="inlineStr">
+      <c r="B183" s="3" t="inlineStr">
         <is>
           <t>[실험체] 헤이즈 - 웨폰 케이스(P) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C139" s="3" t="inlineStr">
+      <c r="C183" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 헤이즈 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D139" s="3" t="inlineStr">
+      <c r="D183" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 헤이즈 선택
@@ -5091,32 +6543,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E139" s="3" t="inlineStr">
+      <c r="E183" s="3" t="inlineStr">
         <is>
           <t>웨폰 케이스(P) 피해량: 60/90/120(+스킬 증폭의 60%)
 (변경 전: 60/90/120(+스킬 증폭의 55%))</t>
         </is>
       </c>
-      <c r="F139" s="3" t="inlineStr"/>
-    </row>
-    <row r="140" ht="60" customHeight="1">
-      <c r="A140" s="4" t="inlineStr">
+      <c r="F183" s="3" t="inlineStr"/>
+    </row>
+    <row r="184" ht="60" customHeight="1">
+      <c r="A184" s="4" t="inlineStr">
         <is>
           <t>TC-10.5-029</t>
         </is>
       </c>
-      <c r="B140" s="5" t="inlineStr">
+      <c r="B184" s="5" t="inlineStr">
         <is>
           <t>[실험체] 가넷 - 기본 체력 수치 확인</t>
         </is>
       </c>
-      <c r="C140" s="5" t="inlineStr">
+      <c r="C184" s="5" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 가넷 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D140" s="5" t="inlineStr">
+      <c r="D184" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 가넷 선택
@@ -5124,32 +6576,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E140" s="5" t="inlineStr">
+      <c r="E184" s="5" t="inlineStr">
         <is>
           <t>기본 체력: 1000
 (변경 전: 950)</t>
         </is>
       </c>
-      <c r="F140" s="5" t="inlineStr"/>
-    </row>
-    <row r="141" ht="60" customHeight="1">
-      <c r="A141" s="4" t="inlineStr">
+      <c r="F184" s="5" t="inlineStr"/>
+    </row>
+    <row r="185" ht="60" customHeight="1">
+      <c r="A185" s="4" t="inlineStr">
         <is>
           <t>TC-10.5-030</t>
         </is>
       </c>
-      <c r="B141" s="5" t="inlineStr">
+      <c r="B185" s="5" t="inlineStr">
         <is>
           <t>[실험체] 로지 - 기본 방어력 수치 확인</t>
         </is>
       </c>
-      <c r="C141" s="5" t="inlineStr">
+      <c r="C185" s="5" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 로지 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D141" s="5" t="inlineStr">
+      <c r="D185" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 로지 선택
@@ -5157,32 +6609,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E141" s="5" t="inlineStr">
+      <c r="E185" s="5" t="inlineStr">
         <is>
           <t>기본 방어력: 50
 (변경 전: 53)</t>
         </is>
       </c>
-      <c r="F141" s="5" t="inlineStr"/>
-    </row>
-    <row r="142" ht="60" customHeight="1">
-      <c r="A142" s="4" t="inlineStr">
+      <c r="F185" s="5" t="inlineStr"/>
+    </row>
+    <row r="186" ht="60" customHeight="1">
+      <c r="A186" s="4" t="inlineStr">
         <is>
           <t>TC-10.5-031</t>
         </is>
       </c>
-      <c r="B142" s="5" t="inlineStr">
+      <c r="B186" s="5" t="inlineStr">
         <is>
           <t>[실험체] 마커스 - 도끼 무기 숙련도 레벨 당 기본 공격 증폭 수치 확인</t>
         </is>
       </c>
-      <c r="C142" s="5" t="inlineStr">
+      <c r="C186" s="5" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 마커스 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D142" s="5" t="inlineStr">
+      <c r="D186" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 마커스 선택
@@ -5190,32 +6642,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E142" s="5" t="inlineStr">
+      <c r="E186" s="5" t="inlineStr">
         <is>
           <t>도끼 무기 숙련도 레벨 당 기본 공격 증폭: 1.9%
 (변경 전: 1.8%)</t>
         </is>
       </c>
-      <c r="F142" s="5" t="inlineStr"/>
-    </row>
-    <row r="143" ht="60" customHeight="1">
-      <c r="A143" s="4" t="inlineStr">
+      <c r="F186" s="5" t="inlineStr"/>
+    </row>
+    <row r="187" ht="60" customHeight="1">
+      <c r="A187" s="4" t="inlineStr">
         <is>
           <t>TC-10.5-032</t>
         </is>
       </c>
-      <c r="B143" s="5" t="inlineStr">
+      <c r="B187" s="5" t="inlineStr">
         <is>
           <t>[실험체] 마커스 - 받는 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C143" s="5" t="inlineStr">
+      <c r="C187" s="5" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 마커스 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D143" s="5" t="inlineStr">
+      <c r="D187" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 마커스 선택
@@ -5223,32 +6675,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E143" s="5" t="inlineStr">
+      <c r="E187" s="5" t="inlineStr">
         <is>
           <t>받는 피해량: 100%
 (변경 전: 102%)</t>
         </is>
       </c>
-      <c r="F143" s="5" t="inlineStr"/>
-    </row>
-    <row r="144" ht="60" customHeight="1">
-      <c r="A144" s="4" t="inlineStr">
+      <c r="F187" s="5" t="inlineStr"/>
+    </row>
+    <row r="188" ht="60" customHeight="1">
+      <c r="A188" s="4" t="inlineStr">
         <is>
           <t>TC-10.5-033</t>
         </is>
       </c>
-      <c r="B144" s="5" t="inlineStr">
+      <c r="B188" s="5" t="inlineStr">
         <is>
           <t>[실험체] 매그너스 - 받는 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C144" s="5" t="inlineStr">
+      <c r="C188" s="5" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 매그너스 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D144" s="5" t="inlineStr">
+      <c r="D188" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 매그너스 선택
@@ -5256,32 +6708,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E144" s="5" t="inlineStr">
+      <c r="E188" s="5" t="inlineStr">
         <is>
           <t>받는 피해량: 100%
 (변경 전: 102%)</t>
         </is>
       </c>
-      <c r="F144" s="5" t="inlineStr"/>
-    </row>
-    <row r="145" ht="60" customHeight="1">
-      <c r="A145" s="4" t="inlineStr">
+      <c r="F188" s="5" t="inlineStr"/>
+    </row>
+    <row r="189" ht="60" customHeight="1">
+      <c r="A189" s="4" t="inlineStr">
         <is>
           <t>TC-10.5-034</t>
         </is>
       </c>
-      <c r="B145" s="5" t="inlineStr">
+      <c r="B189" s="5" t="inlineStr">
         <is>
           <t>[실험체] 아델라 - 레이피어 무기 숙련도 레벨 당 스킬 증폭 수치 확인</t>
         </is>
       </c>
-      <c r="C145" s="5" t="inlineStr">
+      <c r="C189" s="5" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 아델라 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D145" s="5" t="inlineStr">
+      <c r="D189" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 아델라 선택
@@ -5289,32 +6741,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E145" s="5" t="inlineStr">
+      <c r="E189" s="5" t="inlineStr">
         <is>
           <t>레이피어 무기 숙련도 레벨 당 스킬 증폭: 4.6%
 (변경 전: 4.7%)</t>
         </is>
       </c>
-      <c r="F145" s="5" t="inlineStr"/>
-    </row>
-    <row r="146" ht="60" customHeight="1">
-      <c r="A146" s="4" t="inlineStr">
+      <c r="F189" s="5" t="inlineStr"/>
+    </row>
+    <row r="190" ht="60" customHeight="1">
+      <c r="A190" s="4" t="inlineStr">
         <is>
           <t>TC-10.5-035</t>
         </is>
       </c>
-      <c r="B146" s="5" t="inlineStr">
+      <c r="B190" s="5" t="inlineStr">
         <is>
           <t>[실험체] 윌리엄 - 투척 무기 숙련도 레벨 당 기본 공격 증폭 수치 확인</t>
         </is>
       </c>
-      <c r="C146" s="5" t="inlineStr">
+      <c r="C190" s="5" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 윌리엄 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D146" s="5" t="inlineStr">
+      <c r="D190" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 윌리엄 선택
@@ -5322,32 +6774,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E146" s="5" t="inlineStr">
+      <c r="E190" s="5" t="inlineStr">
         <is>
           <t>투척 무기 숙련도 레벨 당 기본 공격 증폭: 1.4%
 (변경 전: 1.5%)</t>
         </is>
       </c>
-      <c r="F146" s="5" t="inlineStr"/>
-    </row>
-    <row r="147" ht="60" customHeight="1">
-      <c r="A147" s="4" t="inlineStr">
+      <c r="F190" s="5" t="inlineStr"/>
+    </row>
+    <row r="191" ht="60" customHeight="1">
+      <c r="A191" s="4" t="inlineStr">
         <is>
           <t>TC-10.5-036</t>
         </is>
       </c>
-      <c r="B147" s="5" t="inlineStr">
+      <c r="B191" s="5" t="inlineStr">
         <is>
           <t>[실험체] 이안 - 기본 공격력 수치 확인</t>
         </is>
       </c>
-      <c r="C147" s="5" t="inlineStr">
+      <c r="C191" s="5" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 이안 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D147" s="5" t="inlineStr">
+      <c r="D191" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 이안 선택
@@ -5355,32 +6807,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E147" s="5" t="inlineStr">
+      <c r="E191" s="5" t="inlineStr">
         <is>
           <t>기본 공격력: 38
 (변경 전: 40)</t>
         </is>
       </c>
-      <c r="F147" s="5" t="inlineStr"/>
-    </row>
-    <row r="148" ht="60" customHeight="1">
-      <c r="A148" s="4" t="inlineStr">
+      <c r="F191" s="5" t="inlineStr"/>
+    </row>
+    <row r="192" ht="60" customHeight="1">
+      <c r="A192" s="4" t="inlineStr">
         <is>
           <t>TC-10.5-037</t>
         </is>
       </c>
-      <c r="B148" s="5" t="inlineStr">
+      <c r="B192" s="5" t="inlineStr">
         <is>
           <t>[실험체] 일레븐 - 주는 회복 효과 수치 확인</t>
         </is>
       </c>
-      <c r="C148" s="5" t="inlineStr">
+      <c r="C192" s="5" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 일레븐 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D148" s="5" t="inlineStr">
+      <c r="D192" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 일레븐 선택
@@ -5388,32 +6840,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E148" s="5" t="inlineStr">
+      <c r="E192" s="5" t="inlineStr">
         <is>
           <t>주는 회복 효과: 100%
 (변경 전: 80%)</t>
         </is>
       </c>
-      <c r="F148" s="5" t="inlineStr"/>
-    </row>
-    <row r="149" ht="60" customHeight="1">
-      <c r="A149" s="4" t="inlineStr">
+      <c r="F192" s="5" t="inlineStr"/>
+    </row>
+    <row r="193" ht="60" customHeight="1">
+      <c r="A193" s="4" t="inlineStr">
         <is>
           <t>TC-10.5-038</t>
         </is>
       </c>
-      <c r="B149" s="5" t="inlineStr">
+      <c r="B193" s="5" t="inlineStr">
         <is>
           <t>[실험체] 카밀로 - 기본 공격력 수치 확인</t>
         </is>
       </c>
-      <c r="C149" s="5" t="inlineStr">
+      <c r="C193" s="5" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 카밀로 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D149" s="5" t="inlineStr">
+      <c r="D193" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 카밀로 선택
@@ -5421,32 +6873,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E149" s="5" t="inlineStr">
+      <c r="E193" s="5" t="inlineStr">
         <is>
           <t>기본 공격력: 31
 (변경 전: 34)</t>
         </is>
       </c>
-      <c r="F149" s="5" t="inlineStr"/>
-    </row>
-    <row r="150" ht="60" customHeight="1">
-      <c r="A150" s="4" t="inlineStr">
+      <c r="F193" s="5" t="inlineStr"/>
+    </row>
+    <row r="194" ht="60" customHeight="1">
+      <c r="A194" s="4" t="inlineStr">
         <is>
           <t>TC-10.5-039</t>
         </is>
       </c>
-      <c r="B150" s="5" t="inlineStr">
+      <c r="B194" s="5" t="inlineStr">
         <is>
           <t>[실험체] 피오라 - 레이피어 무기 숙련도 레벨 당 스킬 증폭 수치 확인</t>
         </is>
       </c>
-      <c r="C150" s="5" t="inlineStr">
+      <c r="C194" s="5" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 피오라 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D150" s="5" t="inlineStr">
+      <c r="D194" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 피오라 선택
@@ -5454,13 +6906,13 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E150" s="5" t="inlineStr">
+      <c r="E194" s="5" t="inlineStr">
         <is>
           <t>레이피어 무기 숙련도 레벨 당 스킬 증폭: 4.3%
 (변경 전: 4.5%)</t>
         </is>
       </c>
-      <c r="F150" s="5" t="inlineStr"/>
+      <c r="F194" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/patchnote_TC.xlsx
+++ b/patchnote_TC.xlsx
@@ -502,7 +502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F194"/>
+  <dimension ref="A1:F234"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -548,21 +548,1341 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>TC-11.3-001</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>[실험체] 다르코 - 수금(W) 보호막량 수치 확인</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>· 11.3 패치 적용 완료
+· 다르코 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 다르코 선택
+3. 수금(W) 스킬 레벨 최대화 후 스킬 정보창 확인
+4. 보호막량 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>수금(W) 보호막량: 50/90/130/170/210(+공격력의 55%)
+(변경 전: 50/75/100/125/150(+공격력의 55%))</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr"/>
+    </row>
+    <row r="3" ht="60" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>TC-11.3-002</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>[실험체] 레니 - 에어 호른! 건(E) 기절 지속 시간 수치 확인</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>· 11.3 패치 적용 완료
+· 레니 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 레니 선택
+3. 에어 호른! 건(E) 스킬 레벨 최대화 후 스킬 정보창 확인
+4. 기절 지속 시간 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>에어 호른! 건(E) 기절 지속 시간: 0.5초
+(변경 전: 0.6초)</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>TC-11.3-003</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>[실험체] 레온 - 인간 어뢰(P) 이동 속도 증가 수치 확인</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>· 11.3 패치 적용 완료
+· 레온 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 레온 선택
+3. 인간 어뢰(P) 스킬 레벨 최대화 후 스킬 정보창 확인
+4. 이동 속도 증가 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>인간 어뢰(P) 이동 속도 증가: 16/22/28%
+(변경 전: 12/18/24%)</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr"/>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>TC-11.3-004</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>[실험체] 로지 - 스핀샷(W) 방어력 감소 수치 확인</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>· 11.3 패치 적용 완료
+· 로지 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 로지 선택
+3. 스핀샷(W) 스킬 레벨 최대화 후 스킬 정보창 확인
+4. 방어력 감소 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>스핀샷(W) 방어력 감소: 8/9/10/11/12%
+(변경 전: 11/12/13/14/15%)</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>TC-11.3-005</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>[실험체] 마이 - 익스클루시브(R) 사거리 수치 확인</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>· 11.3 패치 적용 완료
+· 마이 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 마이 선택
+3. 익스클루시브(R) 스킬 레벨 최대화 후 스킬 정보창 확인
+4. 사거리 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>익스클루시브(R) 사거리: 5.5m
+(변경 전: 5m)</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr"/>
+    </row>
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>TC-11.3-006</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>[실험체] 마이 - 익스클루시브(R) 체력 회복량 수치 확인</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>· 11.3 패치 적용 완료
+· 마이 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 마이 선택
+3. 익스클루시브(R) 스킬 레벨 최대화 후 스킬 정보창 확인
+4. 체력 회복량 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>익스클루시브(R) 체력 회복량: 50/100/150(+스킬 증폭의 35%)(+대상 잃은 체력의 15%)
+(변경 전: 50/100/150(+스킬 증폭의 35%)(+대상 잃은 체력의 10%))</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>TC-11.3-007</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>[실험체] 샬럿 - 빛무리(Q) 피해량 수치 확인</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>· 11.3 패치 적용 완료
+· 샬럿 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 샬럿 선택
+3. 빛무리(Q) 스킬 레벨 최대화 후 스킬 정보창 확인
+4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>빛무리(Q) 피해량: 120/150/180/210/240(+스킬 증폭의 100%)
+(변경 전: 120/150/180/210/240(+스킬 증폭의 95%))</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>TC-11.3-008</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>[실험체] 쇼우 - 소스범벅(Q) 이동 속도 감소 지속 시간 수치 확인</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>· 11.3 패치 적용 완료
+· 쇼우 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 쇼우 선택
+3. 소스범벅(Q) 스킬 레벨 최대화 후 스킬 정보창 확인
+4. 이동 속도 감소 지속 시간 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>소스범벅(Q) 이동 속도 감소 지속 시간: 0.5초
+(변경 전: 0.2초)</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr"/>
+    </row>
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>TC-11.3-009</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>[실험체] 쇼이치 - 협상(E) 피해량 수치 확인</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>· 11.3 패치 적용 완료
+· 쇼이치 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 쇼이치 선택
+3. 협상(E) 스킬 레벨 최대화 후 스킬 정보창 확인
+4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>협상(E) 피해량: 60/100/140/180/220(+스킬 증폭의 75%)
+(변경 전: 60/100/140/180/220(+스킬 증폭의 65%))</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>TC-11.3-010</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>[실험체] 아드리아나 - 불길 쇄도(E) 쿨다운 수치 확인</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>· 11.3 패치 적용 완료
+· 아드리아나 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 아드리아나 선택
+3. 불길 쇄도(E) 스킬 레벨 최대화 후 스킬 정보창 확인
+4. 쿨다운 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>불길 쇄도(E) 쿨다운: 18/17/16/15/14초
+(변경 전: 19/18/17/16/15초)</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>TC-11.3-011</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>[실험체] 아디나 - 별 읽기(P) 이동 속도 증가 수치 확인</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>· 11.3 패치 적용 완료
+· 아디나 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 아디나 선택
+3. 별 읽기(P) 스킬 레벨 최대화 후 스킬 정보창 확인
+4. 이동 속도 증가 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>별 읽기(P) 이동 속도 증가: 7/10/13%(+스킬 증폭의 1%)
+(변경 전: 4/7/10%(+스킬 증폭의 1%))</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>TC-11.3-012</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>[실험체] 아르다 - 잠들어있는 힘(R) 쿨다운 수치 확인</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>· 11.3 패치 적용 완료
+· 아르다 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 아르다 선택
+3. 잠들어있는 힘(R) 스킬 레벨 최대화 후 스킬 정보창 확인
+4. 쿨다운 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>잠들어있는 힘(R) 쿨다운: 20/18/16초
+(변경 전: 19/17/15초)</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr"/>
+    </row>
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>TC-11.3-013</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>[실험체] 아이작 - 착취(P) 입힌 피해량 비례 체력 회복량 수치 확인</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>· 11.3 패치 적용 완료
+· 아이작 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 아이작 선택
+3. 착취(P) 스킬 레벨 최대화 후 스킬 정보창 확인
+4. 입힌 피해량 비례 체력 회복량 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>착취(P) 입힌 피해량 비례 체력 회복량: 120/140/160%
+(변경 전: 100/125/150%)</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr"/>
+    </row>
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>TC-11.3-014</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>[실험체] 얀 - 니 스트라이크(Q) 피해량 수치 확인</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>· 11.3 패치 적용 완료
+· 얀 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 얀 선택
+3. 니 스트라이크(Q) 스킬 레벨 최대화 후 스킬 정보창 확인
+4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>니 스트라이크(Q) 피해량: 100/120/140/160/180(+추가 공격력의 65%)(+스킬 증폭의 55%)(+적 최대 체력의 6%)
+(변경 전: 100/120/140/160/180(+추가 공격력의 65%)(+스킬 증폭의 50%)(+적 최대 체력의 6%))</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>TC-11.3-015</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>[실험체] 에스텔 - 방패방어(E) 방패돌진(E2) 피해량 수치 확인</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>· 11.3 패치 적용 완료
+· 에스텔 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 에스텔 선택
+3. 방패방어(E) 스킬 레벨 최대화 후 스킬 정보창 확인
+4. 방패돌진(E2) 피해량 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>방패방어(E) 방패돌진(E2) 피해량: 60/85/110/135/160(+스킬 증폭의 70%)(+최대 체력의 10%)
+(변경 전: 60/85/110/135/160(+스킬 증폭의 60%)(+최대 체력의 10%))</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>TC-11.3-016</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>[실험체] 에스텔 - 선제대응(W) 피해량 수치 확인</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>· 11.3 패치 적용 완료
+· 에스텔 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 에스텔 선택
+3. 선제대응(W) 스킬 레벨 최대화 후 스킬 정보창 확인
+4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>선제대응(W) 피해량: 20/50/80/110/140(+스킬 증폭의 55%)(+대상 최대 체력의 3%)
+(변경 전: 20/50/80/110/140(+스킬 증폭의 55%)(+대상 최대 체력의 2.5%))</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>TC-11.3-017</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>[실험체] 유민 - 선풍(Q) 바람 지대 피해량 수치 확인</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>· 11.3 패치 적용 완료
+· 유민 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 유민 선택
+3. 선풍(Q) 스킬 레벨 최대화 후 스킬 정보창 확인
+4. 바람 지대 피해량 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>선풍(Q) 바람 지대 피해량: 40/60/80/100/120(+스킬 증폭의 40%)
+(변경 전: 50/70/90/110/130(+스킬 증폭의 40%))</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>TC-11.3-018</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>[실험체] 이렘 - 고양이의 습성(P) 이렘일 때 공격 속도 증가 수치 확인</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>· 11.3 패치 적용 완료
+· 이렘 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 이렘 선택
+3. 고양이의 습성(P) 스킬 레벨 최대화 후 스킬 정보창 확인
+4. 이렘일 때 공격 속도 증가 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>고양이의 습성(P) 이렘일 때 공격 속도 증가: 20/30/40%
+(변경 전: 10/20/30%)</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>TC-11.3-019</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>[실험체] 이렘 - 고양이의 습성(P) 고양이일 때 방어력 증가 수치 확인</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>· 11.3 패치 적용 완료
+· 이렘 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 이렘 선택
+3. 고양이의 습성(P) 스킬 레벨 최대화 후 스킬 정보창 확인
+4. 고양이일 때 방어력 증가 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>고양이의 습성(P) 고양이일 때 방어력 증가: 8/12/16
+(변경 전: 6/10/14)</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>TC-11.3-020</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>[실험체] 제니 - 죽음의 연기(P) 쿨다운 수치 확인</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>· 11.3 패치 적용 완료
+· 제니 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 제니 선택
+3. 죽음의 연기(P) 스킬 레벨 최대화 후 스킬 정보창 확인
+4. 쿨다운 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>죽음의 연기(P) 쿨다운: 70초
+(변경 전: 90초)</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr"/>
+    </row>
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>TC-11.3-021</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>[실험체] 츠바메 - 오의 - 생사 각인(P) 피해량 수치 확인</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>· 11.3 패치 적용 완료
+· 츠바메 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 츠바메 선택
+3. 오의 - 생사 각인(P) 스킬 레벨 최대화 후 스킬 정보창 확인
+4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>오의 - 생사 각인(P) 피해량: 30(+추가 공격력의 25%)(+대상 최대 체력의 4/7/10(+추가 공격력의 5%)%)
+(변경 전: 30(+추가 공격력의 25%)(+대상 최대 체력의 4/7/10(+추가 공격력의 4%)%))</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr"/>
+    </row>
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>TC-11.3-022</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>[실험체] 케네스 - 업화(W) 받는 피해 감소 수치 확인</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>· 11.3 패치 적용 완료
+· 케네스 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 케네스 선택
+3. 업화(W) 스킬 레벨 최대화 후 스킬 정보창 확인
+4. 받는 피해 감소 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>업화(W) 받는 피해 감소: 2(+공격력의 4/4.25/4.5/4.75/5%)%
+(변경 전: 2(+공격력의 3/3.25/3.5/3.75/4%)%)</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr"/>
+    </row>
+    <row r="24" ht="60" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>TC-11.3-023</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>[실험체] 코렐라인 - 단죄의 섬광(Q) 거울 강화 시 투사체 속도 수치 확인</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>· 11.3 패치 적용 완료
+· 코렐라인 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 코렐라인 선택
+3. 단죄의 섬광(Q) 스킬 레벨 최대화 후 스킬 정보창 확인
+4. 거울 강화 시 투사체 속도 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>단죄의 섬광(Q) 거울 강화 시 투사체 속도: 15m/s
+(변경 전: 16m/s)</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>TC-11.3-024</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>[실험체] 프리야 - 프리비티의 노래(E) 피해량 수치 확인</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>· 11.3 패치 적용 완료
+· 프리야 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 프리야 선택
+3. 프리비티의 노래(E) 스킬 레벨 최대화 후 스킬 정보창 확인
+4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>프리비티의 노래(E) 피해량: 60/90/120/150/180(+스킬 증폭의 65%)
+(변경 전: 60/90/120/150/180(+스킬 증폭의 60%))</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr"/>
+    </row>
+    <row r="26" ht="60" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>TC-11.3-025</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>[실험체] 피오라 - 아따끄 꽁뽀제(W) 피해량 수치 확인</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>· 11.3 패치 적용 완료
+· 피오라 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 피오라 선택
+3. 아따끄 꽁뽀제(W) 스킬 레벨 최대화 후 스킬 정보창 확인
+4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>아따끄 꽁뽀제(W) 피해량: 30/65/100/135/170(+스킬 증폭의 30%)
+(변경 전: 40/75/110/145/180(+스킬 증폭의 30%))</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr"/>
+    </row>
+    <row r="27" ht="60" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>TC-11.3-026</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>[실험체] 피올로 - 쌍절난격&amp;내려치기(Q) 내려치기(Q2) 중앙 피해량 수치 확인</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>· 11.3 패치 적용 완료
+· 피올로 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 피올로 선택
+3. 쌍절난격&amp;내려치기(Q) 스킬 레벨 최대화 후 스킬 정보창 확인
+4. 내려치기(Q2) 중앙 피해량 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>쌍절난격&amp;내려치기(Q) 내려치기(Q2) 중앙 피해량: 50/80/110/140/170(+스킬 증폭의 85%)
+(변경 전: 60/95/130/165/200(+스킬 증폭의 85%))</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28" ht="60" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>TC-11.3-027</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>[실험체] 피올로 - 튕겨내기&amp;휘두르기(W) 휘두르기(W2) 피해량 수치 확인</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>· 11.3 패치 적용 완료
+· 피올로 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 피올로 선택
+3. 튕겨내기&amp;휘두르기(W) 스킬 레벨 최대화 후 스킬 정보창 확인
+4. 휘두르기(W2) 피해량 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>튕겨내기&amp;휘두르기(W) 휘두르기(W2) 피해량: 70/115/160/205/250(+스킬 증폭의 85%)
+(변경 전: 90/135/180/225/270(+스킬 증폭의 85%))</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>TC-11.3-028</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>[실험체] 나딘 - 석궁 무기 숙련도 레벨 당 공격 속도 수치 확인</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>· 11.3 패치 적용 완료
+· 나딘 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 나딘 선택
+3. 캐릭터 정보창(스탯창)에서 석궁 무기 숙련도 레벨 당 공격 속도 확인
+4. 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>석궁 무기 숙련도 레벨 당 공격 속도: 3.4%
+(변경 전: 2.8%)</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr"/>
+    </row>
+    <row r="30" ht="60" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>TC-11.3-029</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>[실험체] 라우라 - 채찍 무기 숙련도 레벨 당 스킬 증폭 수치 확인</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>· 11.3 패치 적용 완료
+· 라우라 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 라우라 선택
+3. 캐릭터 정보창(스탯창)에서 채찍 무기 숙련도 레벨 당 스킬 증폭 확인
+4. 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>채찍 무기 숙련도 레벨 당 스킬 증폭: 4.1%
+(변경 전: 4%)</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31" ht="60" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>TC-11.3-030</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>[실험체] 라우라 - 기본 이동 속도 수치 확인</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>· 11.3 패치 적용 완료
+· 라우라 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 라우라 선택
+3. 캐릭터 정보창(스탯창)에서 기본 이동 속도 확인
+4. 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>기본 이동 속도: 3.5
+(변경 전: 3.45)</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr"/>
+    </row>
+    <row r="32" ht="60" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>TC-11.3-031</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>[실험체] 레니 - 기본 방어력 수치 확인</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>· 11.3 패치 적용 완료
+· 레니 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 레니 선택
+3. 캐릭터 정보창(스탯창)에서 기본 방어력 확인
+4. 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>기본 방어력: 50
+(변경 전: 52)</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr"/>
+    </row>
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>TC-11.3-032</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>[실험체] 블레어 - 쌍날검 수치 확인</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>· 11.3 패치 적용 완료
+· 블레어 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 블레어 선택
+3. 캐릭터 정보창(스탯창)에서 쌍날검 확인
+4. 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>쌍날검: 40/65/90/115/140(+공격력의 75%)
+(변경 전: 1, 2타 피해량 40/65/90/115/140(+공격력의 80%))</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr"/>
+    </row>
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>TC-11.3-033</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>[실험체] 시셀라 - 기본 체력 수치 확인</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>· 11.3 패치 적용 완료
+· 시셀라 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 시셀라 선택
+3. 캐릭터 정보창(스탯창)에서 기본 체력 확인
+4. 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>기본 체력: 920
+(변경 전: 890)</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr"/>
+    </row>
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>TC-11.3-034</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>[실험체] 시셀라 - 기본 방어력 수치 확인</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>· 11.3 패치 적용 완료
+· 시셀라 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 시셀라 선택
+3. 캐릭터 정보창(스탯창)에서 기본 방어력 확인
+4. 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>기본 방어력: 50
+(변경 전: 49)</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr"/>
+    </row>
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>TC-11.3-035</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>[실험체] 아이작 - 레벨 당 공격력 수치 확인</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>· 11.3 패치 적용 완료
+· 아이작 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 아이작 선택
+3. 캐릭터 정보창(스탯창)에서 레벨 당 공격력 확인
+4. 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>레벨 당 공격력: 4.9
+(변경 전: 4.7)</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr"/>
+    </row>
+    <row r="37" ht="60" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>TC-11.3-036</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>[실험체] 이안 - 피해량 수치 확인</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>· 11.3 패치 적용 완료
+· 이안 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 이안 선택
+3. 캐릭터 정보창(스탯창)에서 피해량 확인
+4. 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>피해량: 30/60/90/120/150(+공격력의 65%)
+(변경 전: 20/50/80/110/140(+공격력의 65%))</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr"/>
+    </row>
+    <row r="38" ht="60" customHeight="1">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>TC-11.3-037</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>[실험체] 자히르 - 암기 무기 숙련도 레벨 당 스킬 증폭 수치 확인</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>· 11.3 패치 적용 완료
+· 자히르 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 자히르 선택
+3. 캐릭터 정보창(스탯창)에서 암기 무기 숙련도 레벨 당 스킬 증폭 확인
+4. 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>암기 무기 숙련도 레벨 당 스킬 증폭: 3.9%
+(변경 전: 4%)</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr"/>
+    </row>
+    <row r="39" ht="60" customHeight="1">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>TC-11.3-038</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>[실험체] 카티야 - 레벨 당 공격력 수치 확인</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>· 11.3 패치 적용 완료
+· 카티야 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 카티야 선택
+3. 캐릭터 정보창(스탯창)에서 레벨 당 공격력 확인
+4. 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>레벨 당 공격력: 4.7
+(변경 전: 4.5)</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr"/>
+    </row>
+    <row r="40" ht="60" customHeight="1">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>TC-11.3-039</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>[실험체] 하트 - 레벨 당 공격력 수치 확인</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>· 11.3 패치 적용 완료
+· 하트 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 하트 선택
+3. 캐릭터 정보창(스탯창)에서 레벨 당 공격력 확인
+4. 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>레벨 당 공격력: 4.4
+(변경 전: 4.2)</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr"/>
+    </row>
+    <row r="41" ht="60" customHeight="1">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>TC-11.3-040</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>[실험체] 헨리 - 레벨 당 체력 수치 확인</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>· 11.3 패치 적용 완료
+· 헨리 실험체 선택 가능 상태</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>1. 게임 클라이언트 실행 및 패치 버전 확인
+2. 훈련 모드 진입 후 헨리 선택
+3. 캐릭터 정보창(스탯창)에서 레벨 당 체력 확인
+4. 수치가 패치 내용과 일치하는지 검증</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>레벨 당 체력: 78
+(변경 전: 81)</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr"/>
+    </row>
+    <row r="42" ht="60" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
           <t>TC-11.2-001</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B42" s="3" t="inlineStr">
         <is>
           <t>[실험체] 나타폰 - 스냅샷(Q) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C42" s="3" t="inlineStr">
         <is>
           <t>· 11.2 패치 적용 완료
 · 나타폰 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D42" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 나타폰 선택
@@ -570,32 +1890,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E42" s="3" t="inlineStr">
         <is>
           <t>스냅샷(Q) 피해량: 50/90/130/170/210(+스킬 증폭의 80%)
 (변경 전: 50/90/130/170/210(+스킬 증폭의 75%))</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr"/>
-    </row>
-    <row r="3" ht="60" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="F42" s="3" t="inlineStr"/>
+    </row>
+    <row r="43" ht="60" customHeight="1">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>TC-11.2-002</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>[실험체] 나타폰 - 인스턴트 포토(E) 이동 속도 감소 수치 확인</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr">
         <is>
           <t>· 11.2 패치 적용 완료
 · 나타폰 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D43" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 나타폰 선택
@@ -603,32 +1923,32 @@
 4. 이동 속도 감소 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E43" s="3" t="inlineStr">
         <is>
           <t>인스턴트 포토(E) 이동 속도 감소: 55%
 (변경 전: 50%)</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr"/>
-    </row>
-    <row r="4" ht="60" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="F43" s="3" t="inlineStr"/>
+    </row>
+    <row r="44" ht="60" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>TC-11.2-003</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B44" s="3" t="inlineStr">
         <is>
           <t>[실험체] 니아 - K.O.(P) K.O. 중첩 당 저장되는 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C44" s="3" t="inlineStr">
         <is>
           <t>· 11.2 패치 적용 완료
 · 니아 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D44" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 니아 선택
@@ -636,32 +1956,32 @@
 4. K.O. 중첩 당 저장되는 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E44" s="3" t="inlineStr">
         <is>
           <t>K.O.(P) K.O. 중첩 당 저장되는 피해량: 4/8/12(+스킬 증폭의 3%)
 (변경 전: 2/6/10(+스킬 증폭의 2.5%))</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr"/>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="F44" s="3" t="inlineStr"/>
+    </row>
+    <row r="45" ht="60" customHeight="1">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>TC-11.2-004</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B45" s="3" t="inlineStr">
         <is>
           <t>[실험체] 다니엘 - 그림자 이동(E) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C45" s="3" t="inlineStr">
         <is>
           <t>· 11.2 패치 적용 완료
 · 다니엘 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D45" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 다니엘 선택
@@ -669,32 +1989,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E45" s="3" t="inlineStr">
         <is>
           <t>그림자 이동(E) 피해량: 20/40/60/80/100(+추가 공격력의 60%)
 (변경 전: 20/40/60/80/100(+추가 공격력의 55%))</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr"/>
-    </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="F45" s="3" t="inlineStr"/>
+    </row>
+    <row r="46" ht="60" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>TC-11.2-005</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B46" s="3" t="inlineStr">
         <is>
           <t>[실험체] 다르코 - 수금(W) 이동 속도 감소 수치 확인</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C46" s="3" t="inlineStr">
         <is>
           <t>· 11.2 패치 적용 완료
 · 다르코 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D46" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 다르코 선택
@@ -702,32 +2022,32 @@
 4. 이동 속도 감소 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E46" s="3" t="inlineStr">
         <is>
           <t>수금(W) 이동 속도 감소: 25/27.5/30/32.5/35%
 (변경 전: 20/22.5/25/27.5/30%)</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr"/>
-    </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="F46" s="3" t="inlineStr"/>
+    </row>
+    <row r="47" ht="60" customHeight="1">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>TC-11.2-006</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B47" s="3" t="inlineStr">
         <is>
           <t>[실험체] 다르코 - 추심(E) 에어본 지속 시간 수치 확인</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C47" s="3" t="inlineStr">
         <is>
           <t>· 11.2 패치 적용 완료
 · 다르코 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D47" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 다르코 선택
@@ -735,32 +2055,32 @@
 4. 에어본 지속 시간 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E47" s="3" t="inlineStr">
         <is>
           <t>추심(E) 에어본 지속 시간: 0.7초
 (변경 전: 0.6초)</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr"/>
-    </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="F47" s="3" t="inlineStr"/>
+    </row>
+    <row r="48" ht="60" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>TC-11.2-007</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B48" s="3" t="inlineStr">
         <is>
           <t>[실험체] 레녹스 - 휩쓸기(E) 쿨다운 수치 확인</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C48" s="3" t="inlineStr">
         <is>
           <t>· 11.2 패치 적용 완료
 · 레녹스 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D48" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 레녹스 선택
@@ -768,32 +2088,32 @@
 4. 쿨다운 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E48" s="3" t="inlineStr">
         <is>
           <t>휩쓸기(E) 쿨다운: 9초
 (변경 전: 8초)</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr"/>
-    </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="F48" s="3" t="inlineStr"/>
+    </row>
+    <row r="49" ht="60" customHeight="1">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>TC-11.2-008</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t>[실험체] 루크 - 애프터 서비스(R) 표식 중첩 당 추가 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C49" s="3" t="inlineStr">
         <is>
           <t>· 11.2 패치 적용 완료
 · 루크 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D49" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 루크 선택
@@ -801,32 +2121,32 @@
 4. 표식 중첩 당 추가 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E49" s="3" t="inlineStr">
         <is>
           <t>애프터 서비스(R) 표식 중첩 당 추가 피해량: 20/45/70(+공격력의 13%)(+대상 최대 체력의 2%)
 (변경 전: 20/45/70(+공격력의 10%)(+대상 최대 체력의 2%))</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr"/>
-    </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="F49" s="3" t="inlineStr"/>
+    </row>
+    <row r="50" ht="60" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>TC-11.2-009</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B50" s="3" t="inlineStr">
         <is>
           <t>[실험체] 매그너스 - 17대 1(W) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C50" s="3" t="inlineStr">
         <is>
           <t>· 11.2 패치 적용 완료
 · 매그너스 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D50" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 매그너스 선택
@@ -834,32 +2154,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E50" s="3" t="inlineStr">
         <is>
           <t>17대 1(W) 피해량: 16/22/28/34/40(+추가 공격력의 45%)(+스킬 증폭의 20%)(+적 최대 체력의 2.5%)
 (변경 전: 16/22/28/34/40(+추가 공격력의 45%)(+스킬 증폭의 18%)(+적 최대 체력의 2.5%))</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr"/>
-    </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="F50" s="3" t="inlineStr"/>
+    </row>
+    <row r="51" ht="60" customHeight="1">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>TC-11.2-010</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B51" s="3" t="inlineStr">
         <is>
           <t>[실험체] 비앙카 - 흡혈귀(P) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C51" s="3" t="inlineStr">
         <is>
           <t>· 11.2 패치 적용 완료
 · 비앙카 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D51" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 비앙카 선택
@@ -867,32 +2187,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E51" s="3" t="inlineStr">
         <is>
           <t>흡혈귀(P) 피해량: 30/70/110(+스킬 증폭의 40%)(+대상 최대 체력의 5%)
 (변경 전: 30/65/100(+스킬 증폭의 40%)(+대상 최대 체력의 4%))</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr"/>
-    </row>
-    <row r="12" ht="60" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="F51" s="3" t="inlineStr"/>
+    </row>
+    <row r="52" ht="60" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>TC-11.2-011</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B52" s="3" t="inlineStr">
         <is>
           <t>[실험체] 쇼우 - 소스범벅(Q) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C52" s="3" t="inlineStr">
         <is>
           <t>· 11.2 패치 적용 완료
 · 쇼우 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D52" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 쇼우 선택
@@ -900,32 +2220,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E52" s="3" t="inlineStr">
         <is>
           <t>소스범벅(Q) 피해량: 80/120/160/200/240(+스킬 증폭의 70%)(+대상 현재 체력의 25%)
 (변경 전: 60/100/140/180/220(+스킬 증폭의 70%)(+대상 현재 체력의 25%))</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr"/>
-    </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="F52" s="3" t="inlineStr"/>
+    </row>
+    <row r="53" ht="60" customHeight="1">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>TC-11.2-012</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B53" s="3" t="inlineStr">
         <is>
           <t>[실험체] 슈린 - 결심응진(P) 체력 회복량 수치 확인</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C53" s="3" t="inlineStr">
         <is>
           <t>· 11.2 패치 적용 완료
 · 슈린 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D53" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 슈린 선택
@@ -933,32 +2253,32 @@
 4. 체력 회복량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E53" s="3" t="inlineStr">
         <is>
           <t>결심응진(P) 체력 회복량: 10/25/40(+공격력의 35%)
 (변경 전: 10/25/40(+공격력의 30%))</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr"/>
-    </row>
-    <row r="14" ht="60" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="F53" s="3" t="inlineStr"/>
+    </row>
+    <row r="54" ht="60" customHeight="1">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>TC-11.2-013</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B54" s="3" t="inlineStr">
         <is>
           <t>[실험체] 슈린 - 만검귀종(R) 강화 어검 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C54" s="3" t="inlineStr">
         <is>
           <t>· 11.2 패치 적용 완료
 · 슈린 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D54" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 슈린 선택
@@ -966,32 +2286,32 @@
 4. 강화 어검 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E54" s="3" t="inlineStr">
         <is>
           <t>만검귀종(R) 강화 어검 피해량: 20/40/60(+공격력의 20/30/40%)
 (변경 전: 20/40/60(+공격력의 15/25/35%))</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr"/>
-    </row>
-    <row r="15" ht="60" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="F54" s="3" t="inlineStr"/>
+    </row>
+    <row r="55" ht="60" customHeight="1">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>TC-11.2-014</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B55" s="3" t="inlineStr">
         <is>
           <t>[실험체] 아이작 - 강탈(R) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C55" s="3" t="inlineStr">
         <is>
           <t>· 11.2 패치 적용 완료
 · 아이작 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D55" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 아이작 선택
@@ -999,32 +2319,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E55" s="3" t="inlineStr">
         <is>
           <t>강탈(R) 피해량: 120/180/240(+공격력의 100%)
 (변경 전: 80/140/200(+공격력의 100%))</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr"/>
-    </row>
-    <row r="16" ht="60" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="F55" s="3" t="inlineStr"/>
+    </row>
+    <row r="56" ht="60" customHeight="1">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>TC-11.2-015</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B56" s="3" t="inlineStr">
         <is>
           <t>[실험체] 얀 - 쿼드라곤(R) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C56" s="3" t="inlineStr">
         <is>
           <t>· 11.2 패치 적용 완료
 · 얀 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D56" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 얀 선택
@@ -1032,32 +2352,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E56" s="3" t="inlineStr">
         <is>
           <t>쿼드라곤(R) 피해량: 100/200/300(+추가 공격력의 80%)(+스킬 증폭의 45%)
 (변경 전: 100/200/300(+추가 공격력의 80%)(+스킬 증폭의 40%))</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr"/>
-    </row>
-    <row r="17" ht="60" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="F56" s="3" t="inlineStr"/>
+    </row>
+    <row r="57" ht="60" customHeight="1">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>TC-11.2-016</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B57" s="3" t="inlineStr">
         <is>
           <t>[실험체] 엘레나 - 겨울 여왕의 영지(P) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C57" s="3" t="inlineStr">
         <is>
           <t>· 11.2 패치 적용 완료
 · 엘레나 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D57" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 엘레나 선택
@@ -1065,32 +2385,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="E57" s="3" t="inlineStr">
         <is>
           <t>겨울 여왕의 영지(P) 피해량: 10/30/50(+스킬 증폭의 30%)(+대상 최대 체력의 7/9/11%)
 (변경 전: 10/30/50(+스킬 증폭의 20%)(+대상 최대 체력의 6/8/10%))</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr"/>
-    </row>
-    <row r="18" ht="60" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="F57" s="3" t="inlineStr"/>
+    </row>
+    <row r="58" ht="60" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>TC-11.2-017</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B58" s="3" t="inlineStr">
         <is>
           <t>[실험체] 유스티나 - 집중 포격(W) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C58" s="3" t="inlineStr">
         <is>
           <t>· 11.2 패치 적용 완료
 · 유스티나 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D58" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 유스티나 선택
@@ -1098,32 +2418,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E58" s="3" t="inlineStr">
         <is>
           <t>집중 포격(W) 피해량: 50/75/100/125/150(+스킬 증폭의 35%)
 (변경 전: 50/70/90/110/130(+스킬 증폭의 35%))</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr"/>
-    </row>
-    <row r="19" ht="60" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="F58" s="3" t="inlineStr"/>
+    </row>
+    <row r="59" ht="60" customHeight="1">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>TC-11.2-018</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B59" s="3" t="inlineStr">
         <is>
           <t>[실험체] 이바 - 빛의 트라이어드(Q) 폭발 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C59" s="3" t="inlineStr">
         <is>
           <t>· 11.2 패치 적용 완료
 · 이바 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D59" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 이바 선택
@@ -1131,32 +2451,32 @@
 4. 폭발 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="E59" s="3" t="inlineStr">
         <is>
           <t>빛의 트라이어드(Q) 폭발 피해량: 40/70/100/130/160(+스킬 증폭의 40%)
 (변경 전: 45/80/115/150/185(+스킬 증폭의 40%))</t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr"/>
-    </row>
-    <row r="20" ht="60" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="F59" s="3" t="inlineStr"/>
+    </row>
+    <row r="60" ht="60" customHeight="1">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>TC-11.2-019</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B60" s="3" t="inlineStr">
         <is>
           <t>[실험체] 이슈트반 - 양자 얽힘(W) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C60" s="3" t="inlineStr">
         <is>
           <t>· 11.2 패치 적용 완료
 · 이슈트반 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D60" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 이슈트반 선택
@@ -1164,32 +2484,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E60" s="3" t="inlineStr">
         <is>
           <t>양자 얽힘(W) 피해량: 60/90/120/150/180(+공격력의 90%)
 (변경 전: 60/85/110/135/160(+공격력의 90%))</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr"/>
-    </row>
-    <row r="21" ht="60" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="F60" s="3" t="inlineStr"/>
+    </row>
+    <row r="61" ht="60" customHeight="1">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>TC-11.2-020</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B61" s="3" t="inlineStr">
         <is>
           <t>[실험체] 자히르 - 바이바야스트라(E) 투사체 속도 수치 확인</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C61" s="3" t="inlineStr">
         <is>
           <t>· 11.2 패치 적용 완료
 · 자히르 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="D61" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 자히르 선택
@@ -1197,32 +2517,32 @@
 4. 투사체 속도 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="E61" s="3" t="inlineStr">
         <is>
           <t>바이바야스트라(E) 투사체 속도: 8.5m/s
 (변경 전: 7.3m/s)</t>
         </is>
       </c>
-      <c r="F21" s="3" t="inlineStr"/>
-    </row>
-    <row r="22" ht="60" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="F61" s="3" t="inlineStr"/>
+    </row>
+    <row r="62" ht="60" customHeight="1">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>TC-11.2-021</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B62" s="3" t="inlineStr">
         <is>
           <t>[실험체] 자히르 - 사신의 눈(P) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C62" s="3" t="inlineStr">
         <is>
           <t>· 11.2 패치 적용 완료
 · 자히르 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D62" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 자히르 선택
@@ -1230,32 +2550,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="E62" s="3" t="inlineStr">
         <is>
           <t>사신의 눈(P) 피해량: 40/60/80(+스킬 증폭의 25%)
 (변경 전: 30/50/70(+스킬 증폭의 25%))</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr"/>
-    </row>
-    <row r="23" ht="60" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="F62" s="3" t="inlineStr"/>
+    </row>
+    <row r="63" ht="60" customHeight="1">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>TC-11.2-022</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B63" s="3" t="inlineStr">
         <is>
           <t>[실험체] 칼라 - 작살 기동(E) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C63" s="3" t="inlineStr">
         <is>
           <t>· 11.2 패치 적용 완료
 · 칼라 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="D63" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 칼라 선택
@@ -1263,32 +2583,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E23" s="3" t="inlineStr">
+      <c r="E63" s="3" t="inlineStr">
         <is>
           <t>작살 기동(E) 피해량: 60/100/140/180/220(+공격력의 50%)(+스킬 증폭의 80%)
 (변경 전: 60/100/140/180/220(+공격력의 50%)(+스킬 증폭의 60%))</t>
         </is>
       </c>
-      <c r="F23" s="3" t="inlineStr"/>
-    </row>
-    <row r="24" ht="60" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="F63" s="3" t="inlineStr"/>
+    </row>
+    <row r="64" ht="60" customHeight="1">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>TC-11.2-023</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B64" s="3" t="inlineStr">
         <is>
           <t>[실험체] 케네스 - 맹공격(E) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C64" s="3" t="inlineStr">
         <is>
           <t>· 11.2 패치 적용 완료
 · 케네스 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="D64" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 케네스 선택
@@ -1296,32 +2616,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="E64" s="3" t="inlineStr">
         <is>
           <t>맹공격(E) 피해량: 8/16/24/32/40(+공격력의 25%)
 (변경 전: 8/16/24/32/40(+공격력의 20%))</t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr"/>
-    </row>
-    <row r="25" ht="60" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="F64" s="3" t="inlineStr"/>
+    </row>
+    <row r="65" ht="60" customHeight="1">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>TC-11.2-024</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B65" s="3" t="inlineStr">
         <is>
           <t>[실험체] 케네스 - 억압된 분노(P) 체력 회복량 입힌 피해량의 수치 확인</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C65" s="3" t="inlineStr">
         <is>
           <t>· 11.2 패치 적용 완료
 · 케네스 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="D65" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 케네스 선택
@@ -1329,32 +2649,32 @@
 4. 체력 회복량 입힌 피해량의 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E25" s="3" t="inlineStr">
+      <c r="E65" s="3" t="inlineStr">
         <is>
           <t>억압된 분노(P) 체력 회복량 입힌 피해량의: 40(+공격력의 6%)%
 (변경 전: 40(+공격력의 5%)%)</t>
         </is>
       </c>
-      <c r="F25" s="3" t="inlineStr"/>
-    </row>
-    <row r="26" ht="60" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="F65" s="3" t="inlineStr"/>
+    </row>
+    <row r="66" ht="60" customHeight="1">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>TC-11.2-025</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B66" s="3" t="inlineStr">
         <is>
           <t>[실험체] 케네스 - 억압된 분노(P) 체력 회복량 수치 확인</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C66" s="3" t="inlineStr">
         <is>
           <t>· 11.2 패치 적용 완료
 · 케네스 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D66" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 케네스 선택
@@ -1362,32 +2682,32 @@
 4. 체력 회복량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="E66" s="3" t="inlineStr">
         <is>
           <t>억압된 분노(P) 체력 회복량: 30/40/50(+공격력의 6%)
 (변경 전: 최대치 20/30/40(+공격력의 5%))</t>
         </is>
       </c>
-      <c r="F26" s="3" t="inlineStr"/>
-    </row>
-    <row r="27" ht="60" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="F66" s="3" t="inlineStr"/>
+    </row>
+    <row r="67" ht="60" customHeight="1">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>TC-11.2-026</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B67" s="3" t="inlineStr">
         <is>
           <t>[실험체] 코렐라인 - 이세계의 잔영(R) 이동 속도 증가 수치 확인</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C67" s="3" t="inlineStr">
         <is>
           <t>· 11.2 패치 적용 완료
 · 코렐라인 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="D67" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 코렐라인 선택
@@ -1395,32 +2715,32 @@
 4. 이동 속도 증가 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E27" s="3" t="inlineStr">
+      <c r="E67" s="3" t="inlineStr">
         <is>
           <t>이세계의 잔영(R) 이동 속도 증가: 10%
 (변경 전: 15%)</t>
         </is>
       </c>
-      <c r="F27" s="3" t="inlineStr"/>
-    </row>
-    <row r="28" ht="60" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="F67" s="3" t="inlineStr"/>
+    </row>
+    <row r="68" ht="60" customHeight="1">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>TC-11.2-027</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B68" s="3" t="inlineStr">
         <is>
           <t>[실험체] 피올로 - 쌍절난격&amp;내려치기(Q) 쌍절난격(Q1) 강화 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C68" s="3" t="inlineStr">
         <is>
           <t>· 11.2 패치 적용 완료
 · 피올로 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="D68" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 피올로 선택
@@ -1428,32 +2748,32 @@
 4. 쌍절난격(Q1) 강화 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="E68" s="3" t="inlineStr">
         <is>
           <t>쌍절난격&amp;내려치기(Q) 쌍절난격(Q1) 강화 피해량: 20/30/40/50/60(+스킬 증폭의 25%)
 (변경 전: 30/40/50/60/70(+스킬 증폭의 25%))</t>
         </is>
       </c>
-      <c r="F28" s="3" t="inlineStr"/>
-    </row>
-    <row r="29" ht="60" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="F68" s="3" t="inlineStr"/>
+    </row>
+    <row r="69" ht="60" customHeight="1">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>TC-11.2-028</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B69" s="3" t="inlineStr">
         <is>
           <t>[실험체] 피올로 - 쌍절난격&amp;내려치기(Q) 내려치기(Q2) 이동 속도 감소 수치 확인</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="C69" s="3" t="inlineStr">
         <is>
           <t>· 11.2 패치 적용 완료
 · 피올로 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="D69" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 피올로 선택
@@ -1461,32 +2781,32 @@
 4. 내려치기(Q2) 이동 속도 감소 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E29" s="3" t="inlineStr">
+      <c r="E69" s="3" t="inlineStr">
         <is>
           <t>쌍절난격&amp;내려치기(Q) 내려치기(Q2) 이동 속도 감소: 55%
 (변경 전: 60%)</t>
         </is>
       </c>
-      <c r="F29" s="3" t="inlineStr"/>
-    </row>
-    <row r="30" ht="60" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="F69" s="3" t="inlineStr"/>
+    </row>
+    <row r="70" ht="60" customHeight="1">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>TC-11.2-029</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B70" s="3" t="inlineStr">
         <is>
           <t>[실험체] 현우 - 발 밟기(Q) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="C70" s="3" t="inlineStr">
         <is>
           <t>· 11.2 패치 적용 완료
 · 현우 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="D70" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 현우 선택
@@ -1494,32 +2814,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E30" s="3" t="inlineStr">
+      <c r="E70" s="3" t="inlineStr">
         <is>
           <t>발 밟기(Q) 피해량: 50/100/150/200/250(+추가 공격력의 60%)(+스킬 증폭의 85%)
 (변경 전: 50/100/150/200/250(+추가 공격력의 60%)(+스킬 증폭의 80%))</t>
         </is>
       </c>
-      <c r="F30" s="3" t="inlineStr"/>
-    </row>
-    <row r="31" ht="60" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="F70" s="3" t="inlineStr"/>
+    </row>
+    <row r="71" ht="60" customHeight="1">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>TC-11.2-030</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B71" s="3" t="inlineStr">
         <is>
           <t>[실험체] 히스이 - 쾌연격(Q)  수치 확인</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="C71" s="3" t="inlineStr">
         <is>
           <t>· 11.2 패치 적용 완료
 · 히스이 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="D71" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 히스이 선택
@@ -1527,32 +2847,32 @@
 4.  수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E31" s="3" t="inlineStr">
+      <c r="E71" s="3" t="inlineStr">
         <is>
           <t>쾌연격(Q) : 70/85/100/115/130(+추가 공격력의 100/105/110/115/120%)
 (변경 전: 2타 피해량 70/85/100/115/130(+추가 공격력의 90/95/100/105/110%))</t>
         </is>
       </c>
-      <c r="F31" s="3" t="inlineStr"/>
-    </row>
-    <row r="32" ht="60" customHeight="1">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="F71" s="3" t="inlineStr"/>
+    </row>
+    <row r="72" ht="60" customHeight="1">
+      <c r="A72" s="4" t="inlineStr">
         <is>
           <t>TC-11.2-031</t>
         </is>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B72" s="5" t="inlineStr">
         <is>
           <t>[실험체] 다니엘 - 레벨 당 공격력 수치 확인</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="C72" s="5" t="inlineStr">
         <is>
           <t>· 11.2 패치 적용 완료
 · 다니엘 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="D72" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 다니엘 선택
@@ -1560,32 +2880,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="E72" s="5" t="inlineStr">
         <is>
           <t>레벨 당 공격력: 4.7
 (변경 전: 4.6)</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr"/>
-    </row>
-    <row r="33" ht="60" customHeight="1">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="F72" s="5" t="inlineStr"/>
+    </row>
+    <row r="73" ht="60" customHeight="1">
+      <c r="A73" s="4" t="inlineStr">
         <is>
           <t>TC-11.2-032</t>
         </is>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B73" s="5" t="inlineStr">
         <is>
           <t>[실험체] 바냐 - 받는 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="C73" s="5" t="inlineStr">
         <is>
           <t>· 11.2 패치 적용 완료
 · 바냐 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="D73" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 바냐 선택
@@ -1593,32 +2913,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E33" s="5" t="inlineStr">
+      <c r="E73" s="5" t="inlineStr">
         <is>
           <t>받는 피해량: 93%
 (변경 전: 95%)</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr"/>
-    </row>
-    <row r="34" ht="60" customHeight="1">
-      <c r="A34" s="4" t="inlineStr">
+      <c r="F73" s="5" t="inlineStr"/>
+    </row>
+    <row r="74" ht="60" customHeight="1">
+      <c r="A74" s="4" t="inlineStr">
         <is>
           <t>TC-11.2-033</t>
         </is>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B74" s="5" t="inlineStr">
         <is>
           <t>[실험체] 아야 - 기본 공격력 수치 확인</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C74" s="5" t="inlineStr">
         <is>
           <t>· 11.2 패치 적용 완료
 · 아야 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="D74" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 아야 선택
@@ -1626,32 +2946,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E34" s="5" t="inlineStr">
+      <c r="E74" s="5" t="inlineStr">
         <is>
           <t>기본 공격력: 40
 (변경 전: 43)</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr"/>
-    </row>
-    <row r="35" ht="60" customHeight="1">
-      <c r="A35" s="4" t="inlineStr">
+      <c r="F74" s="5" t="inlineStr"/>
+    </row>
+    <row r="75" ht="60" customHeight="1">
+      <c r="A75" s="4" t="inlineStr">
         <is>
           <t>TC-11.2-034</t>
         </is>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B75" s="5" t="inlineStr">
         <is>
           <t>[실험체] 아이솔 - 돌격 소총 무기 숙련도 레벨 당 기본 공격 증폭 수치 확인</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="C75" s="5" t="inlineStr">
         <is>
           <t>· 11.2 패치 적용 완료
 · 아이솔 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="D75" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 아이솔 선택
@@ -1659,32 +2979,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr">
+      <c r="E75" s="5" t="inlineStr">
         <is>
           <t>돌격 소총 무기 숙련도 레벨 당 기본 공격 증폭: 1.3%
 (변경 전: 1.4%)</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr"/>
-    </row>
-    <row r="36" ht="60" customHeight="1">
-      <c r="A36" s="4" t="inlineStr">
+      <c r="F75" s="5" t="inlineStr"/>
+    </row>
+    <row r="76" ht="60" customHeight="1">
+      <c r="A76" s="4" t="inlineStr">
         <is>
           <t>TC-11.2-035</t>
         </is>
       </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="B76" s="5" t="inlineStr">
         <is>
           <t>[실험체] 아이작 - 기본 방어력 수치 확인</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
+      <c r="C76" s="5" t="inlineStr">
         <is>
           <t>· 11.2 패치 적용 완료
 · 아이작 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="D76" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 아이작 선택
@@ -1692,32 +3012,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E36" s="5" t="inlineStr">
+      <c r="E76" s="5" t="inlineStr">
         <is>
           <t>기본 방어력: 52
 (변경 전: 50)</t>
         </is>
       </c>
-      <c r="F36" s="5" t="inlineStr"/>
-    </row>
-    <row r="37" ht="60" customHeight="1">
-      <c r="A37" s="4" t="inlineStr">
+      <c r="F76" s="5" t="inlineStr"/>
+    </row>
+    <row r="77" ht="60" customHeight="1">
+      <c r="A77" s="4" t="inlineStr">
         <is>
           <t>TC-11.2-036</t>
         </is>
       </c>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="B77" s="5" t="inlineStr">
         <is>
           <t>[실험체] 윌리엄 - 레벨 당 공격력 수치 확인</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
+      <c r="C77" s="5" t="inlineStr">
         <is>
           <t>· 11.2 패치 적용 완료
 · 윌리엄 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D77" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 윌리엄 선택
@@ -1725,32 +3045,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E37" s="5" t="inlineStr">
+      <c r="E77" s="5" t="inlineStr">
         <is>
           <t>레벨 당 공격력: 4.3
 (변경 전: 4.1)</t>
         </is>
       </c>
-      <c r="F37" s="5" t="inlineStr"/>
-    </row>
-    <row r="38" ht="60" customHeight="1">
-      <c r="A38" s="4" t="inlineStr">
+      <c r="F77" s="5" t="inlineStr"/>
+    </row>
+    <row r="78" ht="60" customHeight="1">
+      <c r="A78" s="4" t="inlineStr">
         <is>
           <t>TC-11.2-037</t>
         </is>
       </c>
-      <c r="B38" s="5" t="inlineStr">
+      <c r="B78" s="5" t="inlineStr">
         <is>
           <t>[실험체] 제니 - 받는 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr">
+      <c r="C78" s="5" t="inlineStr">
         <is>
           <t>· 11.2 패치 적용 완료
 · 제니 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="D78" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 제니 선택
@@ -1758,32 +3078,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E38" s="5" t="inlineStr">
+      <c r="E78" s="5" t="inlineStr">
         <is>
           <t>받는 피해량: 93%
 (변경 전: 94%)</t>
         </is>
       </c>
-      <c r="F38" s="5" t="inlineStr"/>
-    </row>
-    <row r="39" ht="60" customHeight="1">
-      <c r="A39" s="4" t="inlineStr">
+      <c r="F78" s="5" t="inlineStr"/>
+    </row>
+    <row r="79" ht="60" customHeight="1">
+      <c r="A79" s="4" t="inlineStr">
         <is>
           <t>TC-11.2-038</t>
         </is>
       </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="B79" s="5" t="inlineStr">
         <is>
           <t>[실험체] 카티야 - 레벨 당 공격력 수치 확인</t>
         </is>
       </c>
-      <c r="C39" s="5" t="inlineStr">
+      <c r="C79" s="5" t="inlineStr">
         <is>
           <t>· 11.2 패치 적용 완료
 · 카티야 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="D79" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 카티야 선택
@@ -1791,32 +3111,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E39" s="5" t="inlineStr">
+      <c r="E79" s="5" t="inlineStr">
         <is>
           <t>레벨 당 공격력: 4.5
 (변경 전: 4.3)</t>
         </is>
       </c>
-      <c r="F39" s="5" t="inlineStr"/>
-    </row>
-    <row r="40" ht="60" customHeight="1">
-      <c r="A40" s="4" t="inlineStr">
+      <c r="F79" s="5" t="inlineStr"/>
+    </row>
+    <row r="80" ht="60" customHeight="1">
+      <c r="A80" s="4" t="inlineStr">
         <is>
           <t>TC-11.2-039</t>
         </is>
       </c>
-      <c r="B40" s="5" t="inlineStr">
+      <c r="B80" s="5" t="inlineStr">
         <is>
           <t>[실험체] 칼라 - 석궁 무기 숙련도 레벨 당 스킬 증폭 수치 확인</t>
         </is>
       </c>
-      <c r="C40" s="5" t="inlineStr">
+      <c r="C80" s="5" t="inlineStr">
         <is>
           <t>· 11.2 패치 적용 완료
 · 칼라 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D40" s="5" t="inlineStr">
+      <c r="D80" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 칼라 선택
@@ -1824,32 +3144,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E40" s="5" t="inlineStr">
+      <c r="E80" s="5" t="inlineStr">
         <is>
           <t>석궁 무기 숙련도 레벨 당 스킬 증폭: 4.1%
 (변경 전: 4%)</t>
         </is>
       </c>
-      <c r="F40" s="5" t="inlineStr"/>
-    </row>
-    <row r="41" ht="60" customHeight="1">
-      <c r="A41" s="4" t="inlineStr">
+      <c r="F80" s="5" t="inlineStr"/>
+    </row>
+    <row r="81" ht="60" customHeight="1">
+      <c r="A81" s="4" t="inlineStr">
         <is>
           <t>TC-11.2-040</t>
         </is>
       </c>
-      <c r="B41" s="5" t="inlineStr">
+      <c r="B81" s="5" t="inlineStr">
         <is>
           <t>[실험체] 캐시 - 쌍검 무기 숙련도 레벨 당 스킬 증폭 수치 확인</t>
         </is>
       </c>
-      <c r="C41" s="5" t="inlineStr">
+      <c r="C81" s="5" t="inlineStr">
         <is>
           <t>· 11.2 패치 적용 완료
 · 캐시 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="D81" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 캐시 선택
@@ -1857,32 +3177,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E41" s="5" t="inlineStr">
+      <c r="E81" s="5" t="inlineStr">
         <is>
           <t>쌍검 무기 숙련도 레벨 당 스킬 증폭: 4.8%
 (변경 전: 4.6%)</t>
         </is>
       </c>
-      <c r="F41" s="5" t="inlineStr"/>
-    </row>
-    <row r="42" ht="60" customHeight="1">
-      <c r="A42" s="4" t="inlineStr">
+      <c r="F81" s="5" t="inlineStr"/>
+    </row>
+    <row r="82" ht="60" customHeight="1">
+      <c r="A82" s="4" t="inlineStr">
         <is>
           <t>TC-11.2-041</t>
         </is>
       </c>
-      <c r="B42" s="5" t="inlineStr">
+      <c r="B82" s="5" t="inlineStr">
         <is>
           <t>[실험체] 펠릭스 - 창 무기 숙련도 레벨 당 기본 공격 증폭 수치 확인</t>
         </is>
       </c>
-      <c r="C42" s="5" t="inlineStr">
+      <c r="C82" s="5" t="inlineStr">
         <is>
           <t>· 11.2 패치 적용 완료
 · 펠릭스 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="D82" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 펠릭스 선택
@@ -1890,32 +3210,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E42" s="5" t="inlineStr">
+      <c r="E82" s="5" t="inlineStr">
         <is>
           <t>창 무기 숙련도 레벨 당 기본 공격 증폭: 1.6%
 (변경 전: 1.5%)</t>
         </is>
       </c>
-      <c r="F42" s="5" t="inlineStr"/>
-    </row>
-    <row r="43" ht="60" customHeight="1">
-      <c r="A43" s="4" t="inlineStr">
+      <c r="F82" s="5" t="inlineStr"/>
+    </row>
+    <row r="83" ht="60" customHeight="1">
+      <c r="A83" s="4" t="inlineStr">
         <is>
           <t>TC-11.2-042</t>
         </is>
       </c>
-      <c r="B43" s="5" t="inlineStr">
+      <c r="B83" s="5" t="inlineStr">
         <is>
           <t>[실험체] 현우 - 받는 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C43" s="5" t="inlineStr">
+      <c r="C83" s="5" t="inlineStr">
         <is>
           <t>· 11.2 패치 적용 완료
 · 현우 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="D83" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 현우 선택
@@ -1923,32 +3243,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E43" s="5" t="inlineStr">
+      <c r="E83" s="5" t="inlineStr">
         <is>
           <t>받는 피해량: 95%
 (변경 전: 96%)</t>
         </is>
       </c>
-      <c r="F43" s="5" t="inlineStr"/>
-    </row>
-    <row r="44" ht="60" customHeight="1">
-      <c r="A44" s="4" t="inlineStr">
+      <c r="F83" s="5" t="inlineStr"/>
+    </row>
+    <row r="84" ht="60" customHeight="1">
+      <c r="A84" s="4" t="inlineStr">
         <is>
           <t>TC-11.2-043</t>
         </is>
       </c>
-      <c r="B44" s="5" t="inlineStr">
+      <c r="B84" s="5" t="inlineStr">
         <is>
           <t>[실험체] 혜진 - 암기 무기 숙련도 레벨 당 스킬 증폭 수치 확인</t>
         </is>
       </c>
-      <c r="C44" s="5" t="inlineStr">
+      <c r="C84" s="5" t="inlineStr">
         <is>
           <t>· 11.2 패치 적용 완료
 · 혜진 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D44" s="5" t="inlineStr">
+      <c r="D84" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 혜진 선택
@@ -1956,32 +3276,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E44" s="5" t="inlineStr">
+      <c r="E84" s="5" t="inlineStr">
         <is>
           <t>암기 무기 숙련도 레벨 당 스킬 증폭: 4.8%
 (변경 전: 4.7%)</t>
         </is>
       </c>
-      <c r="F44" s="5" t="inlineStr"/>
-    </row>
-    <row r="45" ht="60" customHeight="1">
-      <c r="A45" s="4" t="inlineStr">
+      <c r="F84" s="5" t="inlineStr"/>
+    </row>
+    <row r="85" ht="60" customHeight="1">
+      <c r="A85" s="4" t="inlineStr">
         <is>
           <t>TC-11.2-044</t>
         </is>
       </c>
-      <c r="B45" s="5" t="inlineStr">
+      <c r="B85" s="5" t="inlineStr">
         <is>
           <t>[실험체] 혜진 - 레벨 당 방어력 수치 확인</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr">
+      <c r="C85" s="5" t="inlineStr">
         <is>
           <t>· 11.2 패치 적용 완료
 · 혜진 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="D85" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 혜진 선택
@@ -1989,32 +3309,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E45" s="5" t="inlineStr">
+      <c r="E85" s="5" t="inlineStr">
         <is>
           <t>레벨 당 방어력: 2.8
 (변경 전: 2.6)</t>
         </is>
       </c>
-      <c r="F45" s="5" t="inlineStr"/>
-    </row>
-    <row r="46" ht="60" customHeight="1">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="F85" s="5" t="inlineStr"/>
+    </row>
+    <row r="86" ht="60" customHeight="1">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>TC-11.1a-001</t>
         </is>
       </c>
-      <c r="B46" s="3" t="inlineStr">
+      <c r="B86" s="3" t="inlineStr">
         <is>
           <t>[실험체] 레니 - 곰돌이! 공격(P) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr">
+      <c r="C86" s="3" t="inlineStr">
         <is>
           <t>· 11.1a 패치 적용 완료
 · 레니 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D46" s="3" t="inlineStr">
+      <c r="D86" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 레니 선택
@@ -2022,32 +3342,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E46" s="3" t="inlineStr">
+      <c r="E86" s="3" t="inlineStr">
         <is>
           <t>곰돌이! 공격(P) 피해량: 15/25/35(+레니 레벨 *4)
 (변경 전: 20/30/40(+레니 레벨 *5))</t>
         </is>
       </c>
-      <c r="F46" s="3" t="inlineStr"/>
-    </row>
-    <row r="47" ht="60" customHeight="1">
-      <c r="A47" s="2" t="inlineStr">
+      <c r="F86" s="3" t="inlineStr"/>
+    </row>
+    <row r="87" ht="60" customHeight="1">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>TC-11.1a-002</t>
         </is>
       </c>
-      <c r="B47" s="3" t="inlineStr">
+      <c r="B87" s="3" t="inlineStr">
         <is>
           <t>[실험체] 코렐라인 - 인과의 이면(P) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C47" s="3" t="inlineStr">
+      <c r="C87" s="3" t="inlineStr">
         <is>
           <t>· 11.1a 패치 적용 완료
 · 코렐라인 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D47" s="3" t="inlineStr">
+      <c r="D87" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 코렐라인 선택
@@ -2055,32 +3375,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E47" s="3" t="inlineStr">
+      <c r="E87" s="3" t="inlineStr">
         <is>
           <t>인과의 이면(P) 피해량: 20/40/60/80/100(+스킬 증폭의 12%)
 (변경 전: 20/40/60/80/100(+스킬 증폭의 15%))</t>
         </is>
       </c>
-      <c r="F47" s="3" t="inlineStr"/>
-    </row>
-    <row r="48" ht="60" customHeight="1">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="F87" s="3" t="inlineStr"/>
+    </row>
+    <row r="88" ht="60" customHeight="1">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>TC-11.1-001</t>
         </is>
       </c>
-      <c r="B48" s="3" t="inlineStr">
+      <c r="B88" s="3" t="inlineStr">
         <is>
           <t>[실험체] 레니 - 뿅! 망치(W) 이동 속도 증가 수치 확인</t>
         </is>
       </c>
-      <c r="C48" s="3" t="inlineStr">
+      <c r="C88" s="3" t="inlineStr">
         <is>
           <t>· 11.1 패치 적용 완료
 · 레니 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D48" s="3" t="inlineStr">
+      <c r="D88" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 레니 선택
@@ -2088,32 +3408,32 @@
 4. 이동 속도 증가 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E48" s="3" t="inlineStr">
+      <c r="E88" s="3" t="inlineStr">
         <is>
           <t>뿅! 망치(W) 이동 속도 증가: 11/12/13/14/15(+레벨*1)%
 (변경 전: 16/17/18/19/20(+레벨*1)%)</t>
         </is>
       </c>
-      <c r="F48" s="3" t="inlineStr"/>
-    </row>
-    <row r="49" ht="60" customHeight="1">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="F88" s="3" t="inlineStr"/>
+    </row>
+    <row r="89" ht="60" customHeight="1">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>TC-11.1-002</t>
         </is>
       </c>
-      <c r="B49" s="3" t="inlineStr">
+      <c r="B89" s="3" t="inlineStr">
         <is>
           <t>[실험체] 미르카 - 백스탭 러시(E) 받는 피해 감소 수치 확인</t>
         </is>
       </c>
-      <c r="C49" s="3" t="inlineStr">
+      <c r="C89" s="3" t="inlineStr">
         <is>
           <t>· 11.1 패치 적용 완료
 · 미르카 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D49" s="3" t="inlineStr">
+      <c r="D89" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 미르카 선택
@@ -2121,32 +3441,32 @@
 4. 받는 피해 감소 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E49" s="3" t="inlineStr">
+      <c r="E89" s="3" t="inlineStr">
         <is>
           <t>백스탭 러시(E) 받는 피해 감소: 60%
 (변경 전: 80%)</t>
         </is>
       </c>
-      <c r="F49" s="3" t="inlineStr"/>
-    </row>
-    <row r="50" ht="60" customHeight="1">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="F89" s="3" t="inlineStr"/>
+    </row>
+    <row r="90" ht="60" customHeight="1">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>TC-11.1-003</t>
         </is>
       </c>
-      <c r="B50" s="3" t="inlineStr">
+      <c r="B90" s="3" t="inlineStr">
         <is>
           <t>[실험체] 아드리아나 - 방화(Q) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C50" s="3" t="inlineStr">
+      <c r="C90" s="3" t="inlineStr">
         <is>
           <t>· 11.1 패치 적용 완료
 · 아드리아나 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D50" s="3" t="inlineStr">
+      <c r="D90" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 아드리아나 선택
@@ -2154,32 +3474,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E50" s="3" t="inlineStr">
+      <c r="E90" s="3" t="inlineStr">
         <is>
           <t>방화(Q) 피해량: 35/45/55/65/75(+스킬 증폭의 25/27/29/31/33%)
 (변경 전: 30/40/50/60/70(+스킬 증폭의 25/27/29/31/33%))</t>
         </is>
       </c>
-      <c r="F50" s="3" t="inlineStr"/>
-    </row>
-    <row r="51" ht="60" customHeight="1">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="F90" s="3" t="inlineStr"/>
+    </row>
+    <row r="91" ht="60" customHeight="1">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>TC-11.1-004</t>
         </is>
       </c>
-      <c r="B51" s="3" t="inlineStr">
+      <c r="B91" s="3" t="inlineStr">
         <is>
           <t>[실험체] 자히르 - 간디바(W) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C51" s="3" t="inlineStr">
+      <c r="C91" s="3" t="inlineStr">
         <is>
           <t>· 11.1 패치 적용 완료
 · 자히르 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D51" s="3" t="inlineStr">
+      <c r="D91" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 자히르 선택
@@ -2187,32 +3507,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E51" s="3" t="inlineStr">
+      <c r="E91" s="3" t="inlineStr">
         <is>
           <t>간디바(W) 피해량: 70/95/120/145/170(+스킬 증폭의 50%)
 (변경 전: 60/85/110/135/160(+스킬 증폭의 50%))</t>
         </is>
       </c>
-      <c r="F51" s="3" t="inlineStr"/>
-    </row>
-    <row r="52" ht="60" customHeight="1">
-      <c r="A52" s="4" t="inlineStr">
+      <c r="F91" s="3" t="inlineStr"/>
+    </row>
+    <row r="92" ht="60" customHeight="1">
+      <c r="A92" s="4" t="inlineStr">
         <is>
           <t>TC-11.1-005</t>
         </is>
       </c>
-      <c r="B52" s="5" t="inlineStr">
+      <c r="B92" s="5" t="inlineStr">
         <is>
           <t>[실험체] 레온 - 톤파 무기 숙련도 레벨 당 스킬 증폭 수치 확인</t>
         </is>
       </c>
-      <c r="C52" s="5" t="inlineStr">
+      <c r="C92" s="5" t="inlineStr">
         <is>
           <t>· 11.1 패치 적용 완료
 · 레온 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D52" s="5" t="inlineStr">
+      <c r="D92" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 레온 선택
@@ -2220,32 +3540,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E52" s="5" t="inlineStr">
+      <c r="E92" s="5" t="inlineStr">
         <is>
           <t>톤파 무기 숙련도 레벨 당 스킬 증폭: 4.8%
 (변경 전: 5%)</t>
         </is>
       </c>
-      <c r="F52" s="5" t="inlineStr"/>
-    </row>
-    <row r="53" ht="60" customHeight="1">
-      <c r="A53" s="4" t="inlineStr">
+      <c r="F92" s="5" t="inlineStr"/>
+    </row>
+    <row r="93" ht="60" customHeight="1">
+      <c r="A93" s="4" t="inlineStr">
         <is>
           <t>TC-11.1-006</t>
         </is>
       </c>
-      <c r="B53" s="5" t="inlineStr">
+      <c r="B93" s="5" t="inlineStr">
         <is>
           <t>[실험체] 로지 - 기본 공격력 수치 확인</t>
         </is>
       </c>
-      <c r="C53" s="5" t="inlineStr">
+      <c r="C93" s="5" t="inlineStr">
         <is>
           <t>· 11.1 패치 적용 완료
 · 로지 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D53" s="5" t="inlineStr">
+      <c r="D93" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 로지 선택
@@ -2253,32 +3573,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E53" s="5" t="inlineStr">
+      <c r="E93" s="5" t="inlineStr">
         <is>
           <t>기본 공격력: 32
 (변경 전: 35)</t>
         </is>
       </c>
-      <c r="F53" s="5" t="inlineStr"/>
-    </row>
-    <row r="54" ht="60" customHeight="1">
-      <c r="A54" s="4" t="inlineStr">
+      <c r="F93" s="5" t="inlineStr"/>
+    </row>
+    <row r="94" ht="60" customHeight="1">
+      <c r="A94" s="4" t="inlineStr">
         <is>
           <t>TC-11.1-007</t>
         </is>
       </c>
-      <c r="B54" s="5" t="inlineStr">
+      <c r="B94" s="5" t="inlineStr">
         <is>
           <t>[실험체] 현우 - 글러브 무기 숙련도 레벨 당 기본 공격 증폭 수치 확인</t>
         </is>
       </c>
-      <c r="C54" s="5" t="inlineStr">
+      <c r="C94" s="5" t="inlineStr">
         <is>
           <t>· 11.1 패치 적용 완료
 · 현우 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D54" s="5" t="inlineStr">
+      <c r="D94" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 현우 선택
@@ -2286,32 +3606,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E54" s="5" t="inlineStr">
+      <c r="E94" s="5" t="inlineStr">
         <is>
           <t>글러브 무기 숙련도 레벨 당 기본 공격 증폭: 2.2%
 (변경 전: 2.3%)</t>
         </is>
       </c>
-      <c r="F54" s="5" t="inlineStr"/>
-    </row>
-    <row r="55" ht="60" customHeight="1">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="F94" s="5" t="inlineStr"/>
+    </row>
+    <row r="95" ht="60" customHeight="1">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>TC-11.0-001</t>
         </is>
       </c>
-      <c r="B55" s="3" t="inlineStr">
+      <c r="B95" s="3" t="inlineStr">
         <is>
           <t>[실험체] 블레어 - 블레이드 시프트(P) 체력 회복량 입힌 피해의 수치 확인</t>
         </is>
       </c>
-      <c r="C55" s="3" t="inlineStr">
+      <c r="C95" s="3" t="inlineStr">
         <is>
           <t>· 11.0 패치 적용 완료
 · 블레어 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D55" s="3" t="inlineStr">
+      <c r="D95" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 블레어 선택
@@ -2319,32 +3639,32 @@
 4. 체력 회복량 입힌 피해의 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E55" s="3" t="inlineStr">
+      <c r="E95" s="3" t="inlineStr">
         <is>
           <t>블레이드 시프트(P) 체력 회복량 입힌 피해의: 8(+추가 공격력의 5%)%
 (변경 전: 8(+추가 공격력의 4%)%)</t>
         </is>
       </c>
-      <c r="F55" s="3" t="inlineStr"/>
-    </row>
-    <row r="56" ht="60" customHeight="1">
-      <c r="A56" s="4" t="inlineStr">
+      <c r="F95" s="3" t="inlineStr"/>
+    </row>
+    <row r="96" ht="60" customHeight="1">
+      <c r="A96" s="4" t="inlineStr">
         <is>
           <t>TC-11.0-002</t>
         </is>
       </c>
-      <c r="B56" s="5" t="inlineStr">
+      <c r="B96" s="5" t="inlineStr">
         <is>
           <t>[실험체] 블레어 - 기본 체력 수치 확인</t>
         </is>
       </c>
-      <c r="C56" s="5" t="inlineStr">
+      <c r="C96" s="5" t="inlineStr">
         <is>
           <t>· 11.0 패치 적용 완료
 · 블레어 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D56" s="5" t="inlineStr">
+      <c r="D96" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 블레어 선택
@@ -2352,32 +3672,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E56" s="5" t="inlineStr">
+      <c r="E96" s="5" t="inlineStr">
         <is>
           <t>기본 체력: 970
 (변경 전: 940)</t>
         </is>
       </c>
-      <c r="F56" s="5" t="inlineStr"/>
-    </row>
-    <row r="57" ht="60" customHeight="1">
-      <c r="A57" s="4" t="inlineStr">
+      <c r="F96" s="5" t="inlineStr"/>
+    </row>
+    <row r="97" ht="60" customHeight="1">
+      <c r="A97" s="4" t="inlineStr">
         <is>
           <t>TC-11.0-003</t>
         </is>
       </c>
-      <c r="B57" s="5" t="inlineStr">
+      <c r="B97" s="5" t="inlineStr">
         <is>
           <t>[실험체] 히스이 - 기본 체력 수치 확인</t>
         </is>
       </c>
-      <c r="C57" s="5" t="inlineStr">
+      <c r="C97" s="5" t="inlineStr">
         <is>
           <t>· 11.0 패치 적용 완료
 · 히스이 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D57" s="5" t="inlineStr">
+      <c r="D97" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 히스이 선택
@@ -2385,32 +3705,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E57" s="5" t="inlineStr">
+      <c r="E97" s="5" t="inlineStr">
         <is>
           <t>기본 체력: 980
 (변경 전: 940)</t>
         </is>
       </c>
-      <c r="F57" s="5" t="inlineStr"/>
-    </row>
-    <row r="58" ht="60" customHeight="1">
-      <c r="A58" s="4" t="inlineStr">
+      <c r="F97" s="5" t="inlineStr"/>
+    </row>
+    <row r="98" ht="60" customHeight="1">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t>TC-11.0-004</t>
         </is>
       </c>
-      <c r="B58" s="5" t="inlineStr">
+      <c r="B98" s="5" t="inlineStr">
         <is>
           <t>[실험체] 히스이 - 기본 방어력 수치 확인</t>
         </is>
       </c>
-      <c r="C58" s="5" t="inlineStr">
+      <c r="C98" s="5" t="inlineStr">
         <is>
           <t>· 11.0 패치 적용 완료
 · 히스이 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D58" s="5" t="inlineStr">
+      <c r="D98" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 히스이 선택
@@ -2418,32 +3738,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E58" s="5" t="inlineStr">
+      <c r="E98" s="5" t="inlineStr">
         <is>
           <t>기본 방어력: 54
 (변경 전: 52)</t>
         </is>
       </c>
-      <c r="F58" s="5" t="inlineStr"/>
-    </row>
-    <row r="59" ht="60" customHeight="1">
-      <c r="A59" s="2" t="inlineStr">
+      <c r="F98" s="5" t="inlineStr"/>
+    </row>
+    <row r="99" ht="60" customHeight="1">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-001</t>
         </is>
       </c>
-      <c r="B59" s="3" t="inlineStr">
+      <c r="B99" s="3" t="inlineStr">
         <is>
           <t>[실험체] 가넷 - 억누른 고통(W) 받는 피해 감소 수치 확인</t>
         </is>
       </c>
-      <c r="C59" s="3" t="inlineStr">
+      <c r="C99" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 가넷 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D59" s="3" t="inlineStr">
+      <c r="D99" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 가넷 선택
@@ -2451,32 +3771,32 @@
 4. 받는 피해 감소 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E59" s="3" t="inlineStr">
+      <c r="E99" s="3" t="inlineStr">
         <is>
           <t>억누른 고통(W) 받는 피해 감소: 50%
 (변경 전: 55%)</t>
         </is>
       </c>
-      <c r="F59" s="3" t="inlineStr"/>
-    </row>
-    <row r="60" ht="60" customHeight="1">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="F99" s="3" t="inlineStr"/>
+    </row>
+    <row r="100" ht="60" customHeight="1">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-002</t>
         </is>
       </c>
-      <c r="B60" s="3" t="inlineStr">
+      <c r="B100" s="3" t="inlineStr">
         <is>
           <t>[실험체] 라우라 - 날카로운 꽃(Q) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C60" s="3" t="inlineStr">
+      <c r="C100" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 라우라 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D60" s="3" t="inlineStr">
+      <c r="D100" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 라우라 선택
@@ -2484,32 +3804,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E60" s="3" t="inlineStr">
+      <c r="E100" s="3" t="inlineStr">
         <is>
           <t>날카로운 꽃(Q) 피해량: 50/75/100/125/150(+스킬 증폭의 55%)
 (변경 전: 50/75/100/125/150(+스킬 증폭의 60%))</t>
         </is>
       </c>
-      <c r="F60" s="3" t="inlineStr"/>
-    </row>
-    <row r="61" ht="60" customHeight="1">
-      <c r="A61" s="2" t="inlineStr">
+      <c r="F100" s="3" t="inlineStr"/>
+    </row>
+    <row r="101" ht="60" customHeight="1">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-003</t>
         </is>
       </c>
-      <c r="B61" s="3" t="inlineStr">
+      <c r="B101" s="3" t="inlineStr">
         <is>
           <t>[실험체] 레니 - 스프링! 트랩(R) 쿨다운 수치 확인</t>
         </is>
       </c>
-      <c r="C61" s="3" t="inlineStr">
+      <c r="C101" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 레니 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D61" s="3" t="inlineStr">
+      <c r="D101" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 레니 선택
@@ -2517,32 +3837,32 @@
 4. 쿨다운 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E61" s="3" t="inlineStr">
+      <c r="E101" s="3" t="inlineStr">
         <is>
           <t>스프링! 트랩(R) 쿨다운: 20/17/14초
 (변경 전: 20/16/12초)</t>
         </is>
       </c>
-      <c r="F61" s="3" t="inlineStr"/>
-    </row>
-    <row r="62" ht="60" customHeight="1">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="F101" s="3" t="inlineStr"/>
+    </row>
+    <row r="102" ht="60" customHeight="1">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-004</t>
         </is>
       </c>
-      <c r="B62" s="3" t="inlineStr">
+      <c r="B102" s="3" t="inlineStr">
         <is>
           <t>[실험체] 마이 - 오뜨꾸뛰르(P) 기본 공격 추가 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C62" s="3" t="inlineStr">
+      <c r="C102" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 마이 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D62" s="3" t="inlineStr">
+      <c r="D102" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 마이 선택
@@ -2550,32 +3870,32 @@
 4. 기본 공격 추가 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E62" s="3" t="inlineStr">
+      <c r="E102" s="3" t="inlineStr">
         <is>
           <t>오뜨꾸뛰르(P) 기본 공격 추가 피해량: 30(+추가 체력의 5/8/11%)
 (변경 전: 30(+추가 체력의 4/7/10%))</t>
         </is>
       </c>
-      <c r="F62" s="3" t="inlineStr"/>
-    </row>
-    <row r="63" ht="60" customHeight="1">
-      <c r="A63" s="2" t="inlineStr">
+      <c r="F102" s="3" t="inlineStr"/>
+    </row>
+    <row r="103" ht="60" customHeight="1">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-005</t>
         </is>
       </c>
-      <c r="B63" s="3" t="inlineStr">
+      <c r="B103" s="3" t="inlineStr">
         <is>
           <t>[실험체] 마커스 - 파괴(W) 쿨다운 수치 확인</t>
         </is>
       </c>
-      <c r="C63" s="3" t="inlineStr">
+      <c r="C103" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 마커스 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D63" s="3" t="inlineStr">
+      <c r="D103" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 마커스 선택
@@ -2583,32 +3903,32 @@
 4. 쿨다운 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E63" s="3" t="inlineStr">
+      <c r="E103" s="3" t="inlineStr">
         <is>
           <t>파괴(W) 쿨다운: 13/12/11/10/9초
 (변경 전: 12/11/10/9/8초)</t>
         </is>
       </c>
-      <c r="F63" s="3" t="inlineStr"/>
-    </row>
-    <row r="64" ht="60" customHeight="1">
-      <c r="A64" s="2" t="inlineStr">
+      <c r="F103" s="3" t="inlineStr"/>
+    </row>
+    <row r="104" ht="60" customHeight="1">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-006</t>
         </is>
       </c>
-      <c r="B64" s="3" t="inlineStr">
+      <c r="B104" s="3" t="inlineStr">
         <is>
           <t>[실험체] 매그너스 - 17대 1(W) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C64" s="3" t="inlineStr">
+      <c r="C104" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 매그너스 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D64" s="3" t="inlineStr">
+      <c r="D104" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 매그너스 선택
@@ -2616,32 +3936,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E64" s="3" t="inlineStr">
+      <c r="E104" s="3" t="inlineStr">
         <is>
           <t>17대 1(W) 피해량: 16/22/28/34/40(+추가 공격력의 45%)(+스킬 증폭의 18%)(+적 최대 체력의 2.5%)
 (변경 전: 16/22/28/34/40(+추가 공격력의 50%)(+스킬 증폭의 18%)(+적 최대 체력의 2.5%))</t>
         </is>
       </c>
-      <c r="F64" s="3" t="inlineStr"/>
-    </row>
-    <row r="65" ht="60" customHeight="1">
-      <c r="A65" s="2" t="inlineStr">
+      <c r="F104" s="3" t="inlineStr"/>
+    </row>
+    <row r="105" ht="60" customHeight="1">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-007</t>
         </is>
       </c>
-      <c r="B65" s="3" t="inlineStr">
+      <c r="B105" s="3" t="inlineStr">
         <is>
           <t>[실험체] 쇼우 - 식사 시간(W) 방어력 증가 지속 시간 수치 확인</t>
         </is>
       </c>
-      <c r="C65" s="3" t="inlineStr">
+      <c r="C105" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 쇼우 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D65" s="3" t="inlineStr">
+      <c r="D105" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 쇼우 선택
@@ -2649,32 +3969,32 @@
 4. 방어력 증가 지속 시간 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E65" s="3" t="inlineStr">
+      <c r="E105" s="3" t="inlineStr">
         <is>
           <t>식사 시간(W) 방어력 증가 지속 시간: 2.5초
 (변경 전: 2초)</t>
         </is>
       </c>
-      <c r="F65" s="3" t="inlineStr"/>
-    </row>
-    <row r="66" ht="60" customHeight="1">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="F105" s="3" t="inlineStr"/>
+    </row>
+    <row r="106" ht="60" customHeight="1">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-008</t>
         </is>
       </c>
-      <c r="B66" s="3" t="inlineStr">
+      <c r="B106" s="3" t="inlineStr">
         <is>
           <t>[실험체] 실비아 - 기동전(R) 방어력 증가 수치 확인</t>
         </is>
       </c>
-      <c r="C66" s="3" t="inlineStr">
+      <c r="C106" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 실비아 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D66" s="3" t="inlineStr">
+      <c r="D106" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 실비아 선택
@@ -2682,32 +4002,32 @@
 4. 방어력 증가 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E66" s="3" t="inlineStr">
+      <c r="E106" s="3" t="inlineStr">
         <is>
           <t>기동전(R) 방어력 증가: 14/18/22
 (변경 전: 15/20/25)</t>
         </is>
       </c>
-      <c r="F66" s="3" t="inlineStr"/>
-    </row>
-    <row r="67" ht="60" customHeight="1">
-      <c r="A67" s="2" t="inlineStr">
+      <c r="F106" s="3" t="inlineStr"/>
+    </row>
+    <row r="107" ht="60" customHeight="1">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-009</t>
         </is>
       </c>
-      <c r="B67" s="3" t="inlineStr">
+      <c r="B107" s="3" t="inlineStr">
         <is>
           <t>[실험체] 아비게일 - 워프 슬래시(E) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C67" s="3" t="inlineStr">
+      <c r="C107" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 아비게일 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D67" s="3" t="inlineStr">
+      <c r="D107" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 아비게일 선택
@@ -2715,32 +4035,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E67" s="3" t="inlineStr">
+      <c r="E107" s="3" t="inlineStr">
         <is>
           <t>워프 슬래시(E) 피해량: 70/85/100/115/130(+스킬 증폭의 40%)
 (변경 전: 80/100/120/140/160(+스킬 증폭의 40%))</t>
         </is>
       </c>
-      <c r="F67" s="3" t="inlineStr"/>
-    </row>
-    <row r="68" ht="60" customHeight="1">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="F107" s="3" t="inlineStr"/>
+    </row>
+    <row r="108" ht="60" customHeight="1">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-010</t>
         </is>
       </c>
-      <c r="B68" s="3" t="inlineStr">
+      <c r="B108" s="3" t="inlineStr">
         <is>
           <t>[실험체] 아비게일 - 티어링 블레이드(P) 방어력 감소 수치 확인</t>
         </is>
       </c>
-      <c r="C68" s="3" t="inlineStr">
+      <c r="C108" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 아비게일 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D68" s="3" t="inlineStr">
+      <c r="D108" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 아비게일 선택
@@ -2748,32 +4068,32 @@
 4. 방어력 감소 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E68" s="3" t="inlineStr">
+      <c r="E108" s="3" t="inlineStr">
         <is>
           <t>티어링 블레이드(P) 방어력 감소: 4/7/10
 (변경 전: 4/8/12)</t>
         </is>
       </c>
-      <c r="F68" s="3" t="inlineStr"/>
-    </row>
-    <row r="69" ht="60" customHeight="1">
-      <c r="A69" s="2" t="inlineStr">
+      <c r="F108" s="3" t="inlineStr"/>
+    </row>
+    <row r="109" ht="60" customHeight="1">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-011</t>
         </is>
       </c>
-      <c r="B69" s="3" t="inlineStr">
+      <c r="B109" s="3" t="inlineStr">
         <is>
           <t>[실험체] 아야 - 2연발(Q) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C69" s="3" t="inlineStr">
+      <c r="C109" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 아야 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D69" s="3" t="inlineStr">
+      <c r="D109" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 아야 선택
@@ -2781,32 +4101,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E69" s="3" t="inlineStr">
+      <c r="E109" s="3" t="inlineStr">
         <is>
           <t>2연발(Q) 피해량: 40/70/100/130/160(+공격력의 30%)(+스킬 증폭의 65%)
 (변경 전: 40/70/100/130/160(+공격력의 30%)(+스킬 증폭의 70%))</t>
         </is>
       </c>
-      <c r="F69" s="3" t="inlineStr"/>
-    </row>
-    <row r="70" ht="60" customHeight="1">
-      <c r="A70" s="2" t="inlineStr">
+      <c r="F109" s="3" t="inlineStr"/>
+    </row>
+    <row r="110" ht="60" customHeight="1">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-012</t>
         </is>
       </c>
-      <c r="B70" s="3" t="inlineStr">
+      <c r="B110" s="3" t="inlineStr">
         <is>
           <t>[실험체] 알론소 - 마그네틱 펀치(Q) 기절 지속 시간 수치 확인</t>
         </is>
       </c>
-      <c r="C70" s="3" t="inlineStr">
+      <c r="C110" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 알론소 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D70" s="3" t="inlineStr">
+      <c r="D110" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 알론소 선택
@@ -2814,32 +4134,32 @@
 4. 기절 지속 시간 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E70" s="3" t="inlineStr">
+      <c r="E110" s="3" t="inlineStr">
         <is>
           <t>마그네틱 펀치(Q) 기절 지속 시간: 0.9초
 (변경 전: 0.85초)</t>
         </is>
       </c>
-      <c r="F70" s="3" t="inlineStr"/>
-    </row>
-    <row r="71" ht="60" customHeight="1">
-      <c r="A71" s="2" t="inlineStr">
+      <c r="F110" s="3" t="inlineStr"/>
+    </row>
+    <row r="111" ht="60" customHeight="1">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-013</t>
         </is>
       </c>
-      <c r="B71" s="3" t="inlineStr">
+      <c r="B111" s="3" t="inlineStr">
         <is>
           <t>[실험체] 에이든 - 뇌격(Q) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C71" s="3" t="inlineStr">
+      <c r="C111" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 에이든 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D71" s="3" t="inlineStr">
+      <c r="D111" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 에이든 선택
@@ -2847,32 +4167,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E71" s="3" t="inlineStr">
+      <c r="E111" s="3" t="inlineStr">
         <is>
           <t>뇌격(Q) 피해량: 70/100/130/160/190(+공격력의 75%) * (기본 공격 증폭)
 (변경 전: 60/90/120/150/180(+공격력의 75%) * (기본 공격 증폭))</t>
         </is>
       </c>
-      <c r="F71" s="3" t="inlineStr"/>
-    </row>
-    <row r="72" ht="60" customHeight="1">
-      <c r="A72" s="2" t="inlineStr">
+      <c r="F111" s="3" t="inlineStr"/>
+    </row>
+    <row r="112" ht="60" customHeight="1">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-014</t>
         </is>
       </c>
-      <c r="B72" s="3" t="inlineStr">
+      <c r="B112" s="3" t="inlineStr">
         <is>
           <t>[실험체] 에이든 - 전자포(과전하 Q) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C72" s="3" t="inlineStr">
+      <c r="C112" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 에이든 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D72" s="3" t="inlineStr">
+      <c r="D112" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 에이든 선택
@@ -2880,32 +4200,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E72" s="3" t="inlineStr">
+      <c r="E112" s="3" t="inlineStr">
         <is>
           <t>전자포(과전하 Q) 피해량: 70/100/130/160/190(+공격력의 75%) * (기본 공격 증폭)
 (변경 전: 60/90/120/150/180(+공격력의 75%) * (기본 공격 증폭))</t>
         </is>
       </c>
-      <c r="F72" s="3" t="inlineStr"/>
-    </row>
-    <row r="73" ht="60" customHeight="1">
-      <c r="A73" s="2" t="inlineStr">
+      <c r="F112" s="3" t="inlineStr"/>
+    </row>
+    <row r="113" ht="60" customHeight="1">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-015</t>
         </is>
       </c>
-      <c r="B73" s="3" t="inlineStr">
+      <c r="B113" s="3" t="inlineStr">
         <is>
           <t>[실험체] 일레븐 - 힘내자고!(P) 일레븐 버거 체력 회복량 수치 확인</t>
         </is>
       </c>
-      <c r="C73" s="3" t="inlineStr">
+      <c r="C113" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 일레븐 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D73" s="3" t="inlineStr">
+      <c r="D113" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 일레븐 선택
@@ -2913,32 +4233,32 @@
 4. 일레븐 버거 체력 회복량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E73" s="3" t="inlineStr">
+      <c r="E113" s="3" t="inlineStr">
         <is>
           <t>힘내자고!(P) 일레븐 버거 체력 회복량: 2/4/6%
 (변경 전: 최대 체력의 3/5/7%)</t>
         </is>
       </c>
-      <c r="F73" s="3" t="inlineStr"/>
-    </row>
-    <row r="74" ht="60" customHeight="1">
-      <c r="A74" s="2" t="inlineStr">
+      <c r="F113" s="3" t="inlineStr"/>
+    </row>
+    <row r="114" ht="60" customHeight="1">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-016</t>
         </is>
       </c>
-      <c r="B74" s="3" t="inlineStr">
+      <c r="B114" s="3" t="inlineStr">
         <is>
           <t>[실험체] 칼라 - 작살 장전(P) 완전 충전시 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C74" s="3" t="inlineStr">
+      <c r="C114" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 칼라 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D74" s="3" t="inlineStr">
+      <c r="D114" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 칼라 선택
@@ -2946,32 +4266,32 @@
 4. 완전 충전시 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E74" s="3" t="inlineStr">
+      <c r="E114" s="3" t="inlineStr">
         <is>
           <t>작살 장전(P) 완전 충전시 피해량: 10/25/40(+공격력의 100%)(+스킬 증폭의 25%)(+대상 최대 체력의 4/8/12%)
 (변경 전: 10/25/40(+공격력의 100%)(+스킬 증폭의 25%)(+대상 최대 체력의 4/7/10%))</t>
         </is>
       </c>
-      <c r="F74" s="3" t="inlineStr"/>
-    </row>
-    <row r="75" ht="60" customHeight="1">
-      <c r="A75" s="2" t="inlineStr">
+      <c r="F114" s="3" t="inlineStr"/>
+    </row>
+    <row r="115" ht="60" customHeight="1">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-017</t>
         </is>
       </c>
-      <c r="B75" s="3" t="inlineStr">
+      <c r="B115" s="3" t="inlineStr">
         <is>
           <t>[실험체] 케네스 - 분노의 일격(Q) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C75" s="3" t="inlineStr">
+      <c r="C115" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 케네스 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D75" s="3" t="inlineStr">
+      <c r="D115" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 케네스 선택
@@ -2979,32 +4299,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E75" s="3" t="inlineStr">
+      <c r="E115" s="3" t="inlineStr">
         <is>
           <t>분노의 일격(Q) 피해량: 30/40/50/60/70(+공격력의 165/170/175/180/185%)
 (변경 전: 30/40/50/60/70(+공격력의 150/155/160/165/170%))</t>
         </is>
       </c>
-      <c r="F75" s="3" t="inlineStr"/>
-    </row>
-    <row r="76" ht="60" customHeight="1">
-      <c r="A76" s="2" t="inlineStr">
+      <c r="F115" s="3" t="inlineStr"/>
+    </row>
+    <row r="116" ht="60" customHeight="1">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-018</t>
         </is>
       </c>
-      <c r="B76" s="3" t="inlineStr">
+      <c r="B116" s="3" t="inlineStr">
         <is>
           <t>[실험체] 코렐라인 - 죄의 굴레(E) 거울 강화 시 투사체 속도 수치 확인</t>
         </is>
       </c>
-      <c r="C76" s="3" t="inlineStr">
+      <c r="C116" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 코렐라인 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D76" s="3" t="inlineStr">
+      <c r="D116" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 코렐라인 선택
@@ -3012,32 +4332,32 @@
 4. 거울 강화 시 투사체 속도 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E76" s="3" t="inlineStr">
+      <c r="E116" s="3" t="inlineStr">
         <is>
           <t>죄의 굴레(E) 거울 강화 시 투사체 속도: 13/ms
 (변경 전: 15m/s)</t>
         </is>
       </c>
-      <c r="F76" s="3" t="inlineStr"/>
-    </row>
-    <row r="77" ht="60" customHeight="1">
-      <c r="A77" s="2" t="inlineStr">
+      <c r="F116" s="3" t="inlineStr"/>
+    </row>
+    <row r="117" ht="60" customHeight="1">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-019</t>
         </is>
       </c>
-      <c r="B77" s="3" t="inlineStr">
+      <c r="B117" s="3" t="inlineStr">
         <is>
           <t>[실험체] 코렐라인 - 진실의 거울/거짓의 거울(W) 스킬 증폭 증가 수치 확인</t>
         </is>
       </c>
-      <c r="C77" s="3" t="inlineStr">
+      <c r="C117" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 코렐라인 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D77" s="3" t="inlineStr">
+      <c r="D117" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 코렐라인 선택
@@ -3045,32 +4365,32 @@
 4. 스킬 증폭 증가 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E77" s="3" t="inlineStr">
+      <c r="E117" s="3" t="inlineStr">
         <is>
           <t>진실의 거울/거짓의 거울(W) 스킬 증폭 증가: 3/5/7%
 (변경 전: 4/6/8%)</t>
         </is>
       </c>
-      <c r="F77" s="3" t="inlineStr"/>
-    </row>
-    <row r="78" ht="60" customHeight="1">
-      <c r="A78" s="2" t="inlineStr">
+      <c r="F117" s="3" t="inlineStr"/>
+    </row>
+    <row r="118" ht="60" customHeight="1">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-020</t>
         </is>
       </c>
-      <c r="B78" s="3" t="inlineStr">
+      <c r="B118" s="3" t="inlineStr">
         <is>
           <t>[실험체] 키아라 - 부정의 손길(Q) 체력 회복량 수치 확인</t>
         </is>
       </c>
-      <c r="C78" s="3" t="inlineStr">
+      <c r="C118" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 키아라 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D78" s="3" t="inlineStr">
+      <c r="D118" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 키아라 선택
@@ -3078,32 +4398,32 @@
 4. 체력 회복량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E78" s="3" t="inlineStr">
+      <c r="E118" s="3" t="inlineStr">
         <is>
           <t>부정의 손길(Q) 체력 회복량: 13/16/19/22/25(+스킬 증폭의 4%)
 (변경 전: 10/13/16/19/22(+스킬 증폭의 3%))</t>
         </is>
       </c>
-      <c r="F78" s="3" t="inlineStr"/>
-    </row>
-    <row r="79" ht="60" customHeight="1">
-      <c r="A79" s="2" t="inlineStr">
+      <c r="F118" s="3" t="inlineStr"/>
+    </row>
+    <row r="119" ht="60" customHeight="1">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-021</t>
         </is>
       </c>
-      <c r="B79" s="3" t="inlineStr">
+      <c r="B119" s="3" t="inlineStr">
         <is>
           <t>[실험체] 타지아 - 스틸레토(Q) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C79" s="3" t="inlineStr">
+      <c r="C119" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 타지아 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D79" s="3" t="inlineStr">
+      <c r="D119" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 타지아 선택
@@ -3111,32 +4431,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E79" s="3" t="inlineStr">
+      <c r="E119" s="3" t="inlineStr">
         <is>
           <t>스틸레토(Q) 피해량: 30/60/90/120/150(+스킬 증폭의 40%)
 (변경 전: 30/55/80/105/130(+스킬 증폭의 40%))</t>
         </is>
       </c>
-      <c r="F79" s="3" t="inlineStr"/>
-    </row>
-    <row r="80" ht="60" customHeight="1">
-      <c r="A80" s="2" t="inlineStr">
+      <c r="F119" s="3" t="inlineStr"/>
+    </row>
+    <row r="120" ht="60" customHeight="1">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-022</t>
         </is>
       </c>
-      <c r="B80" s="3" t="inlineStr">
+      <c r="B120" s="3" t="inlineStr">
         <is>
           <t>[실험체] 타지아 - 스틸레토(Q) 스파다(강화 Q) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C80" s="3" t="inlineStr">
+      <c r="C120" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 타지아 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D80" s="3" t="inlineStr">
+      <c r="D120" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 타지아 선택
@@ -3144,32 +4464,32 @@
 4. 스파다(강화 Q) 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E80" s="3" t="inlineStr">
+      <c r="E120" s="3" t="inlineStr">
         <is>
           <t>스틸레토(Q) 스파다(강화 Q) 피해량: 30/60/90/120/150(+스킬 증폭의 50%)
 (변경 전: 30/55/80/105/130(+스킬 증폭의 50%))</t>
         </is>
       </c>
-      <c r="F80" s="3" t="inlineStr"/>
-    </row>
-    <row r="81" ht="60" customHeight="1">
-      <c r="A81" s="2" t="inlineStr">
+      <c r="F120" s="3" t="inlineStr"/>
+    </row>
+    <row r="121" ht="60" customHeight="1">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-023</t>
         </is>
       </c>
-      <c r="B81" s="3" t="inlineStr">
+      <c r="B121" s="3" t="inlineStr">
         <is>
           <t>[실험체] 테오도르 - 에너지 필드(R) 이동 속도 증가 수치 확인</t>
         </is>
       </c>
-      <c r="C81" s="3" t="inlineStr">
+      <c r="C121" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 테오도르 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D81" s="3" t="inlineStr">
+      <c r="D121" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 테오도르 선택
@@ -3177,32 +4497,32 @@
 4. 이동 속도 증가 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E81" s="3" t="inlineStr">
+      <c r="E121" s="3" t="inlineStr">
         <is>
           <t>에너지 필드(R) 이동 속도 증가: 50/70/90%(+스킬 증폭의 2%)
 (변경 전: 60/80/100%(+스킬 증폭의 2%))</t>
         </is>
       </c>
-      <c r="F81" s="3" t="inlineStr"/>
-    </row>
-    <row r="82" ht="60" customHeight="1">
-      <c r="A82" s="2" t="inlineStr">
+      <c r="F121" s="3" t="inlineStr"/>
+    </row>
+    <row r="122" ht="60" customHeight="1">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-024</t>
         </is>
       </c>
-      <c r="B82" s="3" t="inlineStr">
+      <c r="B122" s="3" t="inlineStr">
         <is>
           <t>[실험체] 프리야 - 개화의 선율(Q) 만개 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C82" s="3" t="inlineStr">
+      <c r="C122" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 프리야 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D82" s="3" t="inlineStr">
+      <c r="D122" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 프리야 선택
@@ -3210,32 +4530,32 @@
 4. 만개 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E82" s="3" t="inlineStr">
+      <c r="E122" s="3" t="inlineStr">
         <is>
           <t>개화의 선율(Q) 만개 피해량: 60/80/100/120/140(+스킬 증폭의 60%)
 (변경 전: 60/80/100/120/140(+스킬 증폭의 55%))</t>
         </is>
       </c>
-      <c r="F82" s="3" t="inlineStr"/>
-    </row>
-    <row r="83" ht="60" customHeight="1">
-      <c r="A83" s="2" t="inlineStr">
+      <c r="F122" s="3" t="inlineStr"/>
+    </row>
+    <row r="123" ht="60" customHeight="1">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-025</t>
         </is>
       </c>
-      <c r="B83" s="3" t="inlineStr">
+      <c r="B123" s="3" t="inlineStr">
         <is>
           <t>[실험체] 프리야 - 포르타멘토(W) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C83" s="3" t="inlineStr">
+      <c r="C123" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 프리야 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D83" s="3" t="inlineStr">
+      <c r="D123" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 프리야 선택
@@ -3243,32 +4563,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E83" s="3" t="inlineStr">
+      <c r="E123" s="3" t="inlineStr">
         <is>
           <t>포르타멘토(W) 피해량: 60/100/140/180/220(+스킬 증폭의 65%)
 (변경 전: 60/100/140/180/220(+스킬 증폭의 60%))</t>
         </is>
       </c>
-      <c r="F83" s="3" t="inlineStr"/>
-    </row>
-    <row r="84" ht="60" customHeight="1">
-      <c r="A84" s="2" t="inlineStr">
+      <c r="F123" s="3" t="inlineStr"/>
+    </row>
+    <row r="124" ht="60" customHeight="1">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-026</t>
         </is>
       </c>
-      <c r="B84" s="3" t="inlineStr">
+      <c r="B124" s="3" t="inlineStr">
         <is>
           <t>[실험체] 헤이즈 - 산탄 포화(W) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C84" s="3" t="inlineStr">
+      <c r="C124" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 헤이즈 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D84" s="3" t="inlineStr">
+      <c r="D124" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 헤이즈 선택
@@ -3276,32 +4596,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E84" s="3" t="inlineStr">
+      <c r="E124" s="3" t="inlineStr">
         <is>
           <t>산탄 포화(W) 피해량: 80/120/160/200/240(+스킬 증폭의 75%)
 (변경 전: 80/120/160/200/240(+스킬 증폭의 70%))</t>
         </is>
       </c>
-      <c r="F84" s="3" t="inlineStr"/>
-    </row>
-    <row r="85" ht="60" customHeight="1">
-      <c r="A85" s="2" t="inlineStr">
+      <c r="F124" s="3" t="inlineStr"/>
+    </row>
+    <row r="125" ht="60" customHeight="1">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-027</t>
         </is>
       </c>
-      <c r="B85" s="3" t="inlineStr">
+      <c r="B125" s="3" t="inlineStr">
         <is>
           <t>[실험체] 헨리 - 시간 제어 장치(W) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C85" s="3" t="inlineStr">
+      <c r="C125" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 헨리 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D85" s="3" t="inlineStr">
+      <c r="D125" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 헨리 선택
@@ -3309,32 +4629,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E85" s="3" t="inlineStr">
+      <c r="E125" s="3" t="inlineStr">
         <is>
           <t>시간 제어 장치(W) 피해량: 8/16/24/32/40(+스킬 증폭의 22%)(+대상 최대 체력의 1/1/2/2/3%)
 (변경 전: 8/16/24/32/40(+스킬 증폭의 20%)(+대상 최대 체력의 1/1/2/2/3%))</t>
         </is>
       </c>
-      <c r="F85" s="3" t="inlineStr"/>
-    </row>
-    <row r="86" ht="60" customHeight="1">
-      <c r="A86" s="2" t="inlineStr">
+      <c r="F125" s="3" t="inlineStr"/>
+    </row>
+    <row r="126" ht="60" customHeight="1">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-028</t>
         </is>
       </c>
-      <c r="B86" s="3" t="inlineStr">
+      <c r="B126" s="3" t="inlineStr">
         <is>
           <t>[실험체] 현우 - 핵펀치(R) 방어력 감소 수치 확인</t>
         </is>
       </c>
-      <c r="C86" s="3" t="inlineStr">
+      <c r="C126" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 현우 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D86" s="3" t="inlineStr">
+      <c r="D126" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 현우 선택
@@ -3342,32 +4662,32 @@
 4. 방어력 감소 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E86" s="3" t="inlineStr">
+      <c r="E126" s="3" t="inlineStr">
         <is>
           <t>핵펀치(R) 방어력 감소: 10/15/20%
 (변경 전: 15/20/25%)</t>
         </is>
       </c>
-      <c r="F86" s="3" t="inlineStr"/>
-    </row>
-    <row r="87" ht="60" customHeight="1">
-      <c r="A87" s="2" t="inlineStr">
+      <c r="F126" s="3" t="inlineStr"/>
+    </row>
+    <row r="127" ht="60" customHeight="1">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>TC-10.7-029</t>
         </is>
       </c>
-      <c r="B87" s="3" t="inlineStr">
+      <c r="B127" s="3" t="inlineStr">
         <is>
           <t>[실험체] 혜진 - 오대존명왕진(R) 부적 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C87" s="3" t="inlineStr">
+      <c r="C127" s="3" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 혜진 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D87" s="3" t="inlineStr">
+      <c r="D127" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 혜진 선택
@@ -3375,32 +4695,32 @@
 4. 부적 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E87" s="3" t="inlineStr">
+      <c r="E127" s="3" t="inlineStr">
         <is>
           <t>오대존명왕진(R) 부적 피해량: 80/105/130(+스킬 증폭의 50%)
 (변경 전: 80/115/150(+스킬 증폭의 50%))</t>
         </is>
       </c>
-      <c r="F87" s="3" t="inlineStr"/>
-    </row>
-    <row r="88" ht="60" customHeight="1">
-      <c r="A88" s="4" t="inlineStr">
+      <c r="F127" s="3" t="inlineStr"/>
+    </row>
+    <row r="128" ht="60" customHeight="1">
+      <c r="A128" s="4" t="inlineStr">
         <is>
           <t>TC-10.7-030</t>
         </is>
       </c>
-      <c r="B88" s="5" t="inlineStr">
+      <c r="B128" s="5" t="inlineStr">
         <is>
           <t>[실험체] 나딘 - 기본 공격력 수치 확인</t>
         </is>
       </c>
-      <c r="C88" s="5" t="inlineStr">
+      <c r="C128" s="5" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 나딘 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D88" s="5" t="inlineStr">
+      <c r="D128" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 나딘 선택
@@ -3408,32 +4728,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E88" s="5" t="inlineStr">
+      <c r="E128" s="5" t="inlineStr">
         <is>
           <t>기본 공격력: 33
 (변경 전: 35)</t>
         </is>
       </c>
-      <c r="F88" s="5" t="inlineStr"/>
-    </row>
-    <row r="89" ht="60" customHeight="1">
-      <c r="A89" s="4" t="inlineStr">
+      <c r="F128" s="5" t="inlineStr"/>
+    </row>
+    <row r="129" ht="60" customHeight="1">
+      <c r="A129" s="4" t="inlineStr">
         <is>
           <t>TC-10.7-031</t>
         </is>
       </c>
-      <c r="B89" s="5" t="inlineStr">
+      <c r="B129" s="5" t="inlineStr">
         <is>
           <t>[실험체] 나타폰 - 카메라 무기 숙련도 레벨 당 스킬 증폭 수치 확인</t>
         </is>
       </c>
-      <c r="C89" s="5" t="inlineStr">
+      <c r="C129" s="5" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 나타폰 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D89" s="5" t="inlineStr">
+      <c r="D129" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 나타폰 선택
@@ -3441,32 +4761,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E89" s="5" t="inlineStr">
+      <c r="E129" s="5" t="inlineStr">
         <is>
           <t>카메라 무기 숙련도 레벨 당 스킬 증폭: 4.4%
 (변경 전: 4.3%)</t>
         </is>
       </c>
-      <c r="F89" s="5" t="inlineStr"/>
-    </row>
-    <row r="90" ht="60" customHeight="1">
-      <c r="A90" s="4" t="inlineStr">
+      <c r="F129" s="5" t="inlineStr"/>
+    </row>
+    <row r="130" ht="60" customHeight="1">
+      <c r="A130" s="4" t="inlineStr">
         <is>
           <t>TC-10.7-032</t>
         </is>
       </c>
-      <c r="B90" s="5" t="inlineStr">
+      <c r="B130" s="5" t="inlineStr">
         <is>
           <t>[실험체] 르노어 - 받는 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C90" s="5" t="inlineStr">
+      <c r="C130" s="5" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 르노어 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D90" s="5" t="inlineStr">
+      <c r="D130" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 르노어 선택
@@ -3474,32 +4794,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E90" s="5" t="inlineStr">
+      <c r="E130" s="5" t="inlineStr">
         <is>
           <t>받는 피해량: 100%
 (변경 전: 102%)</t>
         </is>
       </c>
-      <c r="F90" s="5" t="inlineStr"/>
-    </row>
-    <row r="91" ht="60" customHeight="1">
-      <c r="A91" s="4" t="inlineStr">
+      <c r="F130" s="5" t="inlineStr"/>
+    </row>
+    <row r="131" ht="60" customHeight="1">
+      <c r="A131" s="4" t="inlineStr">
         <is>
           <t>TC-10.7-033</t>
         </is>
       </c>
-      <c r="B91" s="5" t="inlineStr">
+      <c r="B131" s="5" t="inlineStr">
         <is>
           <t>[실험체] 리 다이린 - 글러브 무기 숙련도 레벨 당 기본 공격 증폭 수치 확인</t>
         </is>
       </c>
-      <c r="C91" s="5" t="inlineStr">
+      <c r="C131" s="5" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 리 다이린 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D91" s="5" t="inlineStr">
+      <c r="D131" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 리 다이린 선택
@@ -3507,32 +4827,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E91" s="5" t="inlineStr">
+      <c r="E131" s="5" t="inlineStr">
         <is>
           <t>글러브 무기 숙련도 레벨 당 기본 공격 증폭: 1.9%
 (변경 전: 1.8%)</t>
         </is>
       </c>
-      <c r="F91" s="5" t="inlineStr"/>
-    </row>
-    <row r="92" ht="60" customHeight="1">
-      <c r="A92" s="4" t="inlineStr">
+      <c r="F131" s="5" t="inlineStr"/>
+    </row>
+    <row r="132" ht="60" customHeight="1">
+      <c r="A132" s="4" t="inlineStr">
         <is>
           <t>TC-10.7-034</t>
         </is>
       </c>
-      <c r="B92" s="5" t="inlineStr">
+      <c r="B132" s="5" t="inlineStr">
         <is>
           <t>[실험체] 마커스 - 레벨 당 체력 수치 확인</t>
         </is>
       </c>
-      <c r="C92" s="5" t="inlineStr">
+      <c r="C132" s="5" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 마커스 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D92" s="5" t="inlineStr">
+      <c r="D132" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 마커스 선택
@@ -3540,32 +4860,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E92" s="5" t="inlineStr">
+      <c r="E132" s="5" t="inlineStr">
         <is>
           <t>레벨 당 체력: 94
 (변경 전: 97)</t>
         </is>
       </c>
-      <c r="F92" s="5" t="inlineStr"/>
-    </row>
-    <row r="93" ht="60" customHeight="1">
-      <c r="A93" s="4" t="inlineStr">
+      <c r="F132" s="5" t="inlineStr"/>
+    </row>
+    <row r="133" ht="60" customHeight="1">
+      <c r="A133" s="4" t="inlineStr">
         <is>
           <t>TC-10.7-035</t>
         </is>
       </c>
-      <c r="B93" s="5" t="inlineStr">
+      <c r="B133" s="5" t="inlineStr">
         <is>
           <t>[실험체] 미르카 - 기본 체력 수치 확인</t>
         </is>
       </c>
-      <c r="C93" s="5" t="inlineStr">
+      <c r="C133" s="5" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 미르카 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D93" s="5" t="inlineStr">
+      <c r="D133" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 미르카 선택
@@ -3573,32 +4893,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E93" s="5" t="inlineStr">
+      <c r="E133" s="5" t="inlineStr">
         <is>
           <t>기본 체력: 960
 (변경 전: 930)</t>
         </is>
       </c>
-      <c r="F93" s="5" t="inlineStr"/>
-    </row>
-    <row r="94" ht="60" customHeight="1">
-      <c r="A94" s="4" t="inlineStr">
+      <c r="F133" s="5" t="inlineStr"/>
+    </row>
+    <row r="134" ht="60" customHeight="1">
+      <c r="A134" s="4" t="inlineStr">
         <is>
           <t>TC-10.7-036</t>
         </is>
       </c>
-      <c r="B94" s="5" t="inlineStr">
+      <c r="B134" s="5" t="inlineStr">
         <is>
           <t>[실험체] 클로에 - 기본 공격력 수치 확인</t>
         </is>
       </c>
-      <c r="C94" s="5" t="inlineStr">
+      <c r="C134" s="5" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 클로에 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D94" s="5" t="inlineStr">
+      <c r="D134" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 클로에 선택
@@ -3606,32 +4926,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E94" s="5" t="inlineStr">
+      <c r="E134" s="5" t="inlineStr">
         <is>
           <t>기본 공격력: 32
 (변경 전: 35)</t>
         </is>
       </c>
-      <c r="F94" s="5" t="inlineStr"/>
-    </row>
-    <row r="95" ht="60" customHeight="1">
-      <c r="A95" s="4" t="inlineStr">
+      <c r="F134" s="5" t="inlineStr"/>
+    </row>
+    <row r="135" ht="60" customHeight="1">
+      <c r="A135" s="4" t="inlineStr">
         <is>
           <t>TC-10.7-037</t>
         </is>
       </c>
-      <c r="B95" s="5" t="inlineStr">
+      <c r="B135" s="5" t="inlineStr">
         <is>
           <t>[실험체] 펜리르 - 레벨 당 공격력 수치 확인</t>
         </is>
       </c>
-      <c r="C95" s="5" t="inlineStr">
+      <c r="C135" s="5" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 펜리르 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D95" s="5" t="inlineStr">
+      <c r="D135" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 펜리르 선택
@@ -3639,32 +4959,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E95" s="5" t="inlineStr">
+      <c r="E135" s="5" t="inlineStr">
         <is>
           <t>레벨 당 공격력: 4.8
 (변경 전: 4.6)</t>
         </is>
       </c>
-      <c r="F95" s="5" t="inlineStr"/>
-    </row>
-    <row r="96" ht="60" customHeight="1">
-      <c r="A96" s="4" t="inlineStr">
+      <c r="F135" s="5" t="inlineStr"/>
+    </row>
+    <row r="136" ht="60" customHeight="1">
+      <c r="A136" s="4" t="inlineStr">
         <is>
           <t>TC-10.7-038</t>
         </is>
       </c>
-      <c r="B96" s="5" t="inlineStr">
+      <c r="B136" s="5" t="inlineStr">
         <is>
           <t>[실험체] 하트 - 기본 방어력 수치 확인</t>
         </is>
       </c>
-      <c r="C96" s="5" t="inlineStr">
+      <c r="C136" s="5" t="inlineStr">
         <is>
           <t>· 10.7 패치 적용 완료
 · 하트 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D96" s="5" t="inlineStr">
+      <c r="D136" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 하트 선택
@@ -3672,32 +4992,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E96" s="5" t="inlineStr">
+      <c r="E136" s="5" t="inlineStr">
         <is>
           <t>기본 방어력: 51
 (변경 전: 49)</t>
         </is>
       </c>
-      <c r="F96" s="5" t="inlineStr"/>
-    </row>
-    <row r="97" ht="60" customHeight="1">
-      <c r="A97" s="4" t="inlineStr">
+      <c r="F136" s="5" t="inlineStr"/>
+    </row>
+    <row r="137" ht="60" customHeight="1">
+      <c r="A137" s="4" t="inlineStr">
         <is>
           <t>TC-10.6c-001</t>
         </is>
       </c>
-      <c r="B97" s="5" t="inlineStr">
+      <c r="B137" s="5" t="inlineStr">
         <is>
           <t>[실험체] 코렐라인 - 아르카나 무기 숙련도 레벨 당 스킬 증폭 수치 확인</t>
         </is>
       </c>
-      <c r="C97" s="5" t="inlineStr">
+      <c r="C137" s="5" t="inlineStr">
         <is>
           <t>· 10.6c 패치 적용 완료
 · 코렐라인 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D97" s="5" t="inlineStr">
+      <c r="D137" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 코렐라인 선택
@@ -3705,32 +5025,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E97" s="5" t="inlineStr">
+      <c r="E137" s="5" t="inlineStr">
         <is>
           <t>아르카나 무기 숙련도 레벨 당 스킬 증폭: 4%
 (변경 전: 4.2%)</t>
         </is>
       </c>
-      <c r="F97" s="5" t="inlineStr"/>
-    </row>
-    <row r="98" ht="60" customHeight="1">
-      <c r="A98" s="2" t="inlineStr">
+      <c r="F137" s="5" t="inlineStr"/>
+    </row>
+    <row r="138" ht="60" customHeight="1">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-001</t>
         </is>
       </c>
-      <c r="B98" s="3" t="inlineStr">
+      <c r="B138" s="3" t="inlineStr">
         <is>
           <t>[실험체] 가넷 - 억누른 고통(W) 쿨다운 수치 확인</t>
         </is>
       </c>
-      <c r="C98" s="3" t="inlineStr">
+      <c r="C138" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 가넷 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D98" s="3" t="inlineStr">
+      <c r="D138" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 가넷 선택
@@ -3738,32 +5058,32 @@
 4. 쿨다운 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E98" s="3" t="inlineStr">
+      <c r="E138" s="3" t="inlineStr">
         <is>
           <t>억누른 고통(W) 쿨다운: 14/13/12/11/10초
 (변경 전: 15/14/13/12/11초)</t>
         </is>
       </c>
-      <c r="F98" s="3" t="inlineStr"/>
-    </row>
-    <row r="99" ht="60" customHeight="1">
-      <c r="A99" s="2" t="inlineStr">
+      <c r="F138" s="3" t="inlineStr"/>
+    </row>
+    <row r="139" ht="60" customHeight="1">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-002</t>
         </is>
       </c>
-      <c r="B99" s="3" t="inlineStr">
+      <c r="B139" s="3" t="inlineStr">
         <is>
           <t>[실험체] 가넷 - 짓뭉개기&amp;꿰뚫기(Q) 이동 속도 감소 수치 확인</t>
         </is>
       </c>
-      <c r="C99" s="3" t="inlineStr">
+      <c r="C139" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 가넷 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D99" s="3" t="inlineStr">
+      <c r="D139" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 가넷 선택
@@ -3771,32 +5091,32 @@
 4. 이동 속도 감소 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E99" s="3" t="inlineStr">
+      <c r="E139" s="3" t="inlineStr">
         <is>
           <t>짓뭉개기&amp;꿰뚫기(Q) 이동 속도 감소: 40%
 (변경 전: 35%)</t>
         </is>
       </c>
-      <c r="F99" s="3" t="inlineStr"/>
-    </row>
-    <row r="100" ht="60" customHeight="1">
-      <c r="A100" s="2" t="inlineStr">
+      <c r="F139" s="3" t="inlineStr"/>
+    </row>
+    <row r="140" ht="60" customHeight="1">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-003</t>
         </is>
       </c>
-      <c r="B100" s="3" t="inlineStr">
+      <c r="B140" s="3" t="inlineStr">
         <is>
           <t>[실험체] 라우라 - 황혼의 도둑(R) 폭발 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C100" s="3" t="inlineStr">
+      <c r="C140" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 라우라 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D100" s="3" t="inlineStr">
+      <c r="D140" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 라우라 선택
@@ -3804,32 +5124,32 @@
 4. 폭발 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E100" s="3" t="inlineStr">
+      <c r="E140" s="3" t="inlineStr">
         <is>
           <t>황혼의 도둑(R) 폭발 피해량: 180/260/340(+스킬 증폭의 90%)
 (변경 전: 180/260/340(+스킬 증폭의 85%))</t>
         </is>
       </c>
-      <c r="F100" s="3" t="inlineStr"/>
-    </row>
-    <row r="101" ht="60" customHeight="1">
-      <c r="A101" s="2" t="inlineStr">
+      <c r="F140" s="3" t="inlineStr"/>
+    </row>
+    <row r="141" ht="60" customHeight="1">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-004</t>
         </is>
       </c>
-      <c r="B101" s="3" t="inlineStr">
+      <c r="B141" s="3" t="inlineStr">
         <is>
           <t>[실험체] 라우라 - 황혼의 도둑(R) 보호막량 수치 확인</t>
         </is>
       </c>
-      <c r="C101" s="3" t="inlineStr">
+      <c r="C141" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 라우라 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D101" s="3" t="inlineStr">
+      <c r="D141" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 라우라 선택
@@ -3837,32 +5157,32 @@
 4. 보호막량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E101" s="3" t="inlineStr">
+      <c r="E141" s="3" t="inlineStr">
         <is>
           <t>황혼의 도둑(R) 보호막량: 90/120/150(+스킬 증폭의 20%)
 (변경 전: 90/120/150(+스킬 증폭의 15%))</t>
         </is>
       </c>
-      <c r="F101" s="3" t="inlineStr"/>
-    </row>
-    <row r="102" ht="60" customHeight="1">
-      <c r="A102" s="2" t="inlineStr">
+      <c r="F141" s="3" t="inlineStr"/>
+    </row>
+    <row r="142" ht="60" customHeight="1">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-005</t>
         </is>
       </c>
-      <c r="B102" s="3" t="inlineStr">
+      <c r="B142" s="3" t="inlineStr">
         <is>
           <t>[실험체] 레니 - 당근! 바주카(Q) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C102" s="3" t="inlineStr">
+      <c r="C142" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 레니 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D102" s="3" t="inlineStr">
+      <c r="D142" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 레니 선택
@@ -3870,32 +5190,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E102" s="3" t="inlineStr">
+      <c r="E142" s="3" t="inlineStr">
         <is>
           <t>당근! 바주카(Q) 피해량: 40/55/70/85/100(+레니 레벨*18)(+스킬 증폭의 35%)
 (변경 전: 40/55/70/85/100(+레니 레벨*18)(+스킬 증폭의 30%))</t>
         </is>
       </c>
-      <c r="F102" s="3" t="inlineStr"/>
-    </row>
-    <row r="103" ht="60" customHeight="1">
-      <c r="A103" s="2" t="inlineStr">
+      <c r="F142" s="3" t="inlineStr"/>
+    </row>
+    <row r="143" ht="60" customHeight="1">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-006</t>
         </is>
       </c>
-      <c r="B103" s="3" t="inlineStr">
+      <c r="B143" s="3" t="inlineStr">
         <is>
           <t>[실험체] 레니 - 당근! 바주카(Q) 회복량 수치 확인</t>
         </is>
       </c>
-      <c r="C103" s="3" t="inlineStr">
+      <c r="C143" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 레니 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D103" s="3" t="inlineStr">
+      <c r="D143" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 레니 선택
@@ -3903,32 +5223,32 @@
 4. 회복량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E103" s="3" t="inlineStr">
+      <c r="E143" s="3" t="inlineStr">
         <is>
           <t>당근! 바주카(Q) 회복량: 10/20/30/40/50(+레니 레벨*2)(+스킬 증폭의 20%)
 (변경 전: 10/20/30/40/50(+레니 레벨*2)(+스킬 증폭의 18%))</t>
         </is>
       </c>
-      <c r="F103" s="3" t="inlineStr"/>
-    </row>
-    <row r="104" ht="60" customHeight="1">
-      <c r="A104" s="2" t="inlineStr">
+      <c r="F143" s="3" t="inlineStr"/>
+    </row>
+    <row r="144" ht="60" customHeight="1">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-007</t>
         </is>
       </c>
-      <c r="B104" s="3" t="inlineStr">
+      <c r="B144" s="3" t="inlineStr">
         <is>
           <t>[실험체] 레온 - 물보라(W) 레온 보호막 흡수량 수치 확인</t>
         </is>
       </c>
-      <c r="C104" s="3" t="inlineStr">
+      <c r="C144" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 레온 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D104" s="3" t="inlineStr">
+      <c r="D144" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 레온 선택
@@ -3936,32 +5256,32 @@
 4. 레온 보호막 흡수량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E104" s="3" t="inlineStr">
+      <c r="E144" s="3" t="inlineStr">
         <is>
           <t>물보라(W) 레온 보호막 흡수량: 80/110/140/170/200(+스킬 증폭의 40%)
 (변경 전: 80/110/140/170/200(+스킬 증폭의 35%))</t>
         </is>
       </c>
-      <c r="F104" s="3" t="inlineStr"/>
-    </row>
-    <row r="105" ht="60" customHeight="1">
-      <c r="A105" s="2" t="inlineStr">
+      <c r="F144" s="3" t="inlineStr"/>
+    </row>
+    <row r="145" ht="60" customHeight="1">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-008</t>
         </is>
       </c>
-      <c r="B105" s="3" t="inlineStr">
+      <c r="B145" s="3" t="inlineStr">
         <is>
           <t>[실험체] 르노어 - 고통의 선율(P) 아첼레란도 중첩 당 쿨다운 감소 수치 확인</t>
         </is>
       </c>
-      <c r="C105" s="3" t="inlineStr">
+      <c r="C145" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 르노어 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D105" s="3" t="inlineStr">
+      <c r="D145" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 르노어 선택
@@ -3969,32 +5289,32 @@
 4. 아첼레란도 중첩 당 쿨다운 감소 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E105" s="3" t="inlineStr">
+      <c r="E145" s="3" t="inlineStr">
         <is>
           <t>고통의 선율(P) 아첼레란도 중첩 당 쿨다운 감소: 3
 (변경 전: 2)</t>
         </is>
       </c>
-      <c r="F105" s="3" t="inlineStr"/>
-    </row>
-    <row r="106" ht="60" customHeight="1">
-      <c r="A106" s="2" t="inlineStr">
+      <c r="F145" s="3" t="inlineStr"/>
+    </row>
+    <row r="146" ht="60" customHeight="1">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-009</t>
         </is>
       </c>
-      <c r="B106" s="3" t="inlineStr">
+      <c r="B146" s="3" t="inlineStr">
         <is>
           <t>[실험체] 르노어 - 고통의 선율(P) 쿨다운 감소 수치 확인</t>
         </is>
       </c>
-      <c r="C106" s="3" t="inlineStr">
+      <c r="C146" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 르노어 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D106" s="3" t="inlineStr">
+      <c r="D146" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 르노어 선택
@@ -4002,32 +5322,32 @@
 4. 쿨다운 감소 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E106" s="3" t="inlineStr">
+      <c r="E146" s="3" t="inlineStr">
         <is>
           <t>고통의 선율(P) 쿨다운 감소: 2
 (변경 전: 40 이후 아첼레란도 중첩 당 궁극기 쿨다운 감소 3)</t>
         </is>
       </c>
-      <c r="F106" s="3" t="inlineStr"/>
-    </row>
-    <row r="107" ht="60" customHeight="1">
-      <c r="A107" s="2" t="inlineStr">
+      <c r="F146" s="3" t="inlineStr"/>
+    </row>
+    <row r="147" ht="60" customHeight="1">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-010</t>
         </is>
       </c>
-      <c r="B107" s="3" t="inlineStr">
+      <c r="B147" s="3" t="inlineStr">
         <is>
           <t>[실험체] 마르티나 - 일시정지 - 방송 중(W) 속박 지속 시간 수치 확인</t>
         </is>
       </c>
-      <c r="C107" s="3" t="inlineStr">
+      <c r="C147" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 마르티나 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D107" s="3" t="inlineStr">
+      <c r="D147" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 마르티나 선택
@@ -4035,32 +5355,32 @@
 4. 속박 지속 시간 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E107" s="3" t="inlineStr">
+      <c r="E147" s="3" t="inlineStr">
         <is>
           <t>일시정지 - 방송 중(W) 속박 지속 시간: 1.2초
 (변경 전: 1초)</t>
         </is>
       </c>
-      <c r="F107" s="3" t="inlineStr"/>
-    </row>
-    <row r="108" ht="60" customHeight="1">
-      <c r="A108" s="2" t="inlineStr">
+      <c r="F147" s="3" t="inlineStr"/>
+    </row>
+    <row r="148" ht="60" customHeight="1">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-011</t>
         </is>
       </c>
-      <c r="B108" s="3" t="inlineStr">
+      <c r="B148" s="3" t="inlineStr">
         <is>
           <t>[실험체] 마이 - 숄 장막(W) 이동 속도 증가 수치 확인</t>
         </is>
       </c>
-      <c r="C108" s="3" t="inlineStr">
+      <c r="C148" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 마이 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D108" s="3" t="inlineStr">
+      <c r="D148" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 마이 선택
@@ -4068,32 +5388,32 @@
 4. 이동 속도 증가 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E108" s="3" t="inlineStr">
+      <c r="E148" s="3" t="inlineStr">
         <is>
           <t>숄 장막(W) 이동 속도 증가: 10/14/18/22/26%
 (변경 전: 8/11/14/17/20%)</t>
         </is>
       </c>
-      <c r="F108" s="3" t="inlineStr"/>
-    </row>
-    <row r="109" ht="60" customHeight="1">
-      <c r="A109" s="2" t="inlineStr">
+      <c r="F148" s="3" t="inlineStr"/>
+    </row>
+    <row r="149" ht="60" customHeight="1">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-012</t>
         </is>
       </c>
-      <c r="B109" s="3" t="inlineStr">
+      <c r="B149" s="3" t="inlineStr">
         <is>
           <t>[실험체] 바바라 - BT-Mk2 센트리건(Q) 센트리건 기본 공격 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C109" s="3" t="inlineStr">
+      <c r="C149" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 바바라 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D109" s="3" t="inlineStr">
+      <c r="D149" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 바바라 선택
@@ -4101,32 +5421,32 @@
 4. 센트리건 기본 공격 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E109" s="3" t="inlineStr">
+      <c r="E149" s="3" t="inlineStr">
         <is>
           <t>BT-Mk2 센트리건(Q) 센트리건 기본 공격 피해량: 30/40/50/60/70(+스킬 증폭의 18%)
 (변경 전: 30/40/50/60/70(+스킬 증폭의 20%))</t>
         </is>
       </c>
-      <c r="F109" s="3" t="inlineStr"/>
-    </row>
-    <row r="110" ht="60" customHeight="1">
-      <c r="A110" s="2" t="inlineStr">
+      <c r="F149" s="3" t="inlineStr"/>
+    </row>
+    <row r="150" ht="60" customHeight="1">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-013</t>
         </is>
       </c>
-      <c r="B110" s="3" t="inlineStr">
+      <c r="B150" s="3" t="inlineStr">
         <is>
           <t>[실험체] 셀린 - 자력 융합(R) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C110" s="3" t="inlineStr">
+      <c r="C150" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 셀린 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D110" s="3" t="inlineStr">
+      <c r="D150" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 셀린 선택
@@ -4134,32 +5454,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E110" s="3" t="inlineStr">
+      <c r="E150" s="3" t="inlineStr">
         <is>
           <t>자력 융합(R) 피해량: 60/80/100/120/140(+스킬 증폭의 37%)
 (변경 전: 60/80/100/120/140(+스킬 증폭의 36%))</t>
         </is>
       </c>
-      <c r="F110" s="3" t="inlineStr"/>
-    </row>
-    <row r="111" ht="60" customHeight="1">
-      <c r="A111" s="2" t="inlineStr">
+      <c r="F150" s="3" t="inlineStr"/>
+    </row>
+    <row r="151" ht="60" customHeight="1">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-014</t>
         </is>
       </c>
-      <c r="B111" s="3" t="inlineStr">
+      <c r="B151" s="3" t="inlineStr">
         <is>
           <t>[실험체] 쇼이치 - 비약(W) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C111" s="3" t="inlineStr">
+      <c r="C151" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 쇼이치 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D111" s="3" t="inlineStr">
+      <c r="D151" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 쇼이치 선택
@@ -4167,32 +5487,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E111" s="3" t="inlineStr">
+      <c r="E151" s="3" t="inlineStr">
         <is>
           <t>비약(W) 피해량: 30/50/70/90/110(+스킬 증폭의 60%)
 (변경 전: 40/60/80/100/120(+스킬 증폭의 60%))</t>
         </is>
       </c>
-      <c r="F111" s="3" t="inlineStr"/>
-    </row>
-    <row r="112" ht="60" customHeight="1">
-      <c r="A112" s="2" t="inlineStr">
+      <c r="F151" s="3" t="inlineStr"/>
+    </row>
+    <row r="152" ht="60" customHeight="1">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-015</t>
         </is>
       </c>
-      <c r="B112" s="3" t="inlineStr">
+      <c r="B152" s="3" t="inlineStr">
         <is>
           <t>[실험체] 수아 - 기억력(R) 쿨다운 수치 확인</t>
         </is>
       </c>
-      <c r="C112" s="3" t="inlineStr">
+      <c r="C152" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 수아 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D112" s="3" t="inlineStr">
+      <c r="D152" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 수아 선택
@@ -4200,32 +5520,32 @@
 4. 쿨다운 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E112" s="3" t="inlineStr">
+      <c r="E152" s="3" t="inlineStr">
         <is>
           <t>기억력(R) 쿨다운: 26/22/18초
 (변경 전: 30/24/18초)</t>
         </is>
       </c>
-      <c r="F112" s="3" t="inlineStr"/>
-    </row>
-    <row r="113" ht="60" customHeight="1">
-      <c r="A113" s="2" t="inlineStr">
+      <c r="F152" s="3" t="inlineStr"/>
+    </row>
+    <row r="153" ht="60" customHeight="1">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-016</t>
         </is>
       </c>
-      <c r="B113" s="3" t="inlineStr">
+      <c r="B153" s="3" t="inlineStr">
         <is>
           <t>[실험체] 시셀라 - 삶은 고통이에요.(P) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C113" s="3" t="inlineStr">
+      <c r="C153" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 시셀라 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D113" s="3" t="inlineStr">
+      <c r="D153" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 시셀라 선택
@@ -4233,32 +5553,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E113" s="3" t="inlineStr">
+      <c r="E153" s="3" t="inlineStr">
         <is>
           <t>삶은 고통이에요.(P) 피해량: 30(+스킬 증폭의 45%)(+캐릭터 레벨*9)
 (변경 전: 30(+스킬 증폭의 40%)(+캐릭터 레벨*9))</t>
         </is>
       </c>
-      <c r="F113" s="3" t="inlineStr"/>
-    </row>
-    <row r="114" ht="60" customHeight="1">
-      <c r="A114" s="2" t="inlineStr">
+      <c r="F153" s="3" t="inlineStr"/>
+    </row>
+    <row r="154" ht="60" customHeight="1">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-017</t>
         </is>
       </c>
-      <c r="B114" s="3" t="inlineStr">
+      <c r="B154" s="3" t="inlineStr">
         <is>
           <t>[실험체] 아디나 - 폴 디그니티(E) 별 컨정션 효과 체력 회복량 수치 확인</t>
         </is>
       </c>
-      <c r="C114" s="3" t="inlineStr">
+      <c r="C154" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 아디나 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D114" s="3" t="inlineStr">
+      <c r="D154" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 아디나 선택
@@ -4266,32 +5586,32 @@
 4. 별 컨정션 효과 체력 회복량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E114" s="3" t="inlineStr">
+      <c r="E154" s="3" t="inlineStr">
         <is>
           <t>폴 디그니티(E) 별 컨정션 효과 체력 회복량: 20/30/40/50(+스킬 증폭의 6%)
 (변경 전: 20/30/40/50(+스킬 증폭의 4%))</t>
         </is>
       </c>
-      <c r="F114" s="3" t="inlineStr"/>
-    </row>
-    <row r="115" ht="60" customHeight="1">
-      <c r="A115" s="2" t="inlineStr">
+      <c r="F154" s="3" t="inlineStr"/>
+    </row>
+    <row r="155" ht="60" customHeight="1">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-018</t>
         </is>
       </c>
-      <c r="B115" s="3" t="inlineStr">
+      <c r="B155" s="3" t="inlineStr">
         <is>
           <t>[실험체] 아이작 - 현장 급습(Q) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C115" s="3" t="inlineStr">
+      <c r="C155" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 아이작 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D115" s="3" t="inlineStr">
+      <c r="D155" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 아이작 선택
@@ -4299,32 +5619,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E115" s="3" t="inlineStr">
+      <c r="E155" s="3" t="inlineStr">
         <is>
           <t>현장 급습(Q) 피해량: 20/60/100/140/180(+공격력의 70%)
 (변경 전: 30/70/110/150/190(+공격력의 70%))</t>
         </is>
       </c>
-      <c r="F115" s="3" t="inlineStr"/>
-    </row>
-    <row r="116" ht="60" customHeight="1">
-      <c r="A116" s="2" t="inlineStr">
+      <c r="F155" s="3" t="inlineStr"/>
+    </row>
+    <row r="156" ht="60" customHeight="1">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-019</t>
         </is>
       </c>
-      <c r="B116" s="3" t="inlineStr">
+      <c r="B156" s="3" t="inlineStr">
         <is>
           <t>[실험체] 알렉스 - 플라즈마 마인(W) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C116" s="3" t="inlineStr">
+      <c r="C156" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 알렉스 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D116" s="3" t="inlineStr">
+      <c r="D156" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 알렉스 선택
@@ -4332,32 +5652,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E116" s="3" t="inlineStr">
+      <c r="E156" s="3" t="inlineStr">
         <is>
           <t>플라즈마 마인(W) 피해량: 40/75/110/145/180(+공격력의 80%)
 (변경 전: 40/80/120/160/200(+공격력의 80%))</t>
         </is>
       </c>
-      <c r="F116" s="3" t="inlineStr"/>
-    </row>
-    <row r="117" ht="60" customHeight="1">
-      <c r="A117" s="2" t="inlineStr">
+      <c r="F156" s="3" t="inlineStr"/>
+    </row>
+    <row r="157" ht="60" customHeight="1">
+      <c r="A157" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-020</t>
         </is>
       </c>
-      <c r="B117" s="3" t="inlineStr">
+      <c r="B157" s="3" t="inlineStr">
         <is>
           <t>[실험체] 에스텔 - 헬기호출(R) 보호막 흡수량 수치 확인</t>
         </is>
       </c>
-      <c r="C117" s="3" t="inlineStr">
+      <c r="C157" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 에스텔 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D117" s="3" t="inlineStr">
+      <c r="D157" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 에스텔 선택
@@ -4365,32 +5685,32 @@
 4. 보호막 흡수량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E117" s="3" t="inlineStr">
+      <c r="E157" s="3" t="inlineStr">
         <is>
           <t>헬기호출(R) 보호막 흡수량: 100/150/200(+스킬 증폭의 55%)(+잃은 체력의 20%)
 (변경 전: 100/150/200(+스킬 증폭의 50%)(+잃은 체력의 20%))</t>
         </is>
       </c>
-      <c r="F117" s="3" t="inlineStr"/>
-    </row>
-    <row r="118" ht="60" customHeight="1">
-      <c r="A118" s="2" t="inlineStr">
+      <c r="F157" s="3" t="inlineStr"/>
+    </row>
+    <row r="158" ht="60" customHeight="1">
+      <c r="A158" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-021</t>
         </is>
       </c>
-      <c r="B118" s="3" t="inlineStr">
+      <c r="B158" s="3" t="inlineStr">
         <is>
           <t>[실험체] 에스텔 - 헬기호출(R) 아군 보호막 흡수량 수치 확인</t>
         </is>
       </c>
-      <c r="C118" s="3" t="inlineStr">
+      <c r="C158" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 에스텔 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D118" s="3" t="inlineStr">
+      <c r="D158" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 에스텔 선택
@@ -4398,32 +5718,32 @@
 4. 아군 보호막 흡수량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E118" s="3" t="inlineStr">
+      <c r="E158" s="3" t="inlineStr">
         <is>
           <t>헬기호출(R) 아군 보호막 흡수량: 100/200/300(+스킬 증폭의 55%)(+대상의 잃은 체력의 15%)
 (변경 전: 100/200/300(+스킬 증폭의 50%)(+대상의 잃은 체력의 15%))</t>
         </is>
       </c>
-      <c r="F118" s="3" t="inlineStr"/>
-    </row>
-    <row r="119" ht="60" customHeight="1">
-      <c r="A119" s="2" t="inlineStr">
+      <c r="F158" s="3" t="inlineStr"/>
+    </row>
+    <row r="159" ht="60" customHeight="1">
+      <c r="A159" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-022</t>
         </is>
       </c>
-      <c r="B119" s="3" t="inlineStr">
+      <c r="B159" s="3" t="inlineStr">
         <is>
           <t>[실험체] 에키온 - VF 폭주(R) 독사의 진노[블랙맘바] 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C119" s="3" t="inlineStr">
+      <c r="C159" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 에키온 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D119" s="3" t="inlineStr">
+      <c r="D159" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 에키온 선택
@@ -4431,32 +5751,32 @@
 4. 독사의 진노[블랙맘바] 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E119" s="3" t="inlineStr">
+      <c r="E159" s="3" t="inlineStr">
         <is>
           <t>VF 폭주(R) 독사의 진노[블랙맘바] 피해량: 50/120/175/220(+공격력의 80%)(+추가 체력의 12%)
 (변경 전: 50/120/175/220(+공격력의 80%)(+추가 체력의 10%))</t>
         </is>
       </c>
-      <c r="F119" s="3" t="inlineStr"/>
-    </row>
-    <row r="120" ht="60" customHeight="1">
-      <c r="A120" s="2" t="inlineStr">
+      <c r="F159" s="3" t="inlineStr"/>
+    </row>
+    <row r="160" ht="60" customHeight="1">
+      <c r="A160" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-023</t>
         </is>
       </c>
-      <c r="B120" s="3" t="inlineStr">
+      <c r="B160" s="3" t="inlineStr">
         <is>
           <t>[실험체] 엠마 - 마술 토끼(E) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C120" s="3" t="inlineStr">
+      <c r="C160" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 엠마 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D120" s="3" t="inlineStr">
+      <c r="D160" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 엠마 선택
@@ -4464,32 +5784,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E120" s="3" t="inlineStr">
+      <c r="E160" s="3" t="inlineStr">
         <is>
           <t>마술 토끼(E) 피해량: 30/55/80/105/130(+스킬 증폭의 30%)
 (변경 전: 20/40/60/80/100(+스킬 증폭의 30%))</t>
         </is>
       </c>
-      <c r="F120" s="3" t="inlineStr"/>
-    </row>
-    <row r="121" ht="60" customHeight="1">
-      <c r="A121" s="2" t="inlineStr">
+      <c r="F160" s="3" t="inlineStr"/>
+    </row>
+    <row r="161" ht="60" customHeight="1">
+      <c r="A161" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-024</t>
         </is>
       </c>
-      <c r="B121" s="3" t="inlineStr">
+      <c r="B161" s="3" t="inlineStr">
         <is>
           <t>[실험체] 엠마 - 마술 토끼(E) 변이 지속 시간 수치 확인</t>
         </is>
       </c>
-      <c r="C121" s="3" t="inlineStr">
+      <c r="C161" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 엠마 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D121" s="3" t="inlineStr">
+      <c r="D161" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 엠마 선택
@@ -4497,32 +5817,32 @@
 4. 변이 지속 시간 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E121" s="3" t="inlineStr">
+      <c r="E161" s="3" t="inlineStr">
         <is>
           <t>마술 토끼(E) 변이 지속 시간: 0.8/0.85/0.9/0.95/1초
 (변경 전: 0.6/0.7/0.8/0.9/1초)</t>
         </is>
       </c>
-      <c r="F121" s="3" t="inlineStr"/>
-    </row>
-    <row r="122" ht="60" customHeight="1">
-      <c r="A122" s="2" t="inlineStr">
+      <c r="F161" s="3" t="inlineStr"/>
+    </row>
+    <row r="162" ht="60" customHeight="1">
+      <c r="A162" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-025</t>
         </is>
       </c>
-      <c r="B122" s="3" t="inlineStr">
+      <c r="B162" s="3" t="inlineStr">
         <is>
           <t>[실험체] 유키 - 머리치기!(Q) 쿨다운 수치 확인</t>
         </is>
       </c>
-      <c r="C122" s="3" t="inlineStr">
+      <c r="C162" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 유키 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D122" s="3" t="inlineStr">
+      <c r="D162" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 유키 선택
@@ -4530,32 +5850,32 @@
 4. 쿨다운 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E122" s="3" t="inlineStr">
+      <c r="E162" s="3" t="inlineStr">
         <is>
           <t>머리치기!(Q) 쿨다운: 5초
 (변경 전: 6초)</t>
         </is>
       </c>
-      <c r="F122" s="3" t="inlineStr"/>
-    </row>
-    <row r="123" ht="60" customHeight="1">
-      <c r="A123" s="2" t="inlineStr">
+      <c r="F162" s="3" t="inlineStr"/>
+    </row>
+    <row r="163" ht="60" customHeight="1">
+      <c r="A163" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-026</t>
         </is>
       </c>
-      <c r="B123" s="3" t="inlineStr">
+      <c r="B163" s="3" t="inlineStr">
         <is>
           <t>[실험체] 이슈트반 - 관측(Q) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C123" s="3" t="inlineStr">
+      <c r="C163" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 이슈트반 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D123" s="3" t="inlineStr">
+      <c r="D163" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 이슈트반 선택
@@ -4563,32 +5883,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E123" s="3" t="inlineStr">
+      <c r="E163" s="3" t="inlineStr">
         <is>
           <t>관측(Q) 피해량: 40/80/120/160/200(+공격력의 100%)
 (변경 전: 40/80/120/160/200(+공격력의 110%))</t>
         </is>
       </c>
-      <c r="F123" s="3" t="inlineStr"/>
-    </row>
-    <row r="124" ht="60" customHeight="1">
-      <c r="A124" s="2" t="inlineStr">
+      <c r="F163" s="3" t="inlineStr"/>
+    </row>
+    <row r="164" ht="60" customHeight="1">
+      <c r="A164" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-027</t>
         </is>
       </c>
-      <c r="B124" s="3" t="inlineStr">
+      <c r="B164" s="3" t="inlineStr">
         <is>
           <t>[실험체] 이슈트반 - 관측(Q) 다른 가능성 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C124" s="3" t="inlineStr">
+      <c r="C164" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 이슈트반 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D124" s="3" t="inlineStr">
+      <c r="D164" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 이슈트반 선택
@@ -4596,32 +5916,32 @@
 4. 다른 가능성 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E124" s="3" t="inlineStr">
+      <c r="E164" s="3" t="inlineStr">
         <is>
           <t>관측(Q) 다른 가능성 피해량: 40/80/120/160/200(+공격력의 100%)
 (변경 전: 40/80/120/160/200(+공격력의 110%))</t>
         </is>
       </c>
-      <c r="F124" s="3" t="inlineStr"/>
-    </row>
-    <row r="125" ht="60" customHeight="1">
-      <c r="A125" s="2" t="inlineStr">
+      <c r="F164" s="3" t="inlineStr"/>
+    </row>
+    <row r="165" ht="60" customHeight="1">
+      <c r="A165" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-028</t>
         </is>
       </c>
-      <c r="B125" s="3" t="inlineStr">
+      <c r="B165" s="3" t="inlineStr">
         <is>
           <t>[실험체] 츠바메 - 오의 - 생사 각인(P) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C125" s="3" t="inlineStr">
+      <c r="C165" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 츠바메 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D125" s="3" t="inlineStr">
+      <c r="D165" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 츠바메 선택
@@ -4629,32 +5949,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E125" s="3" t="inlineStr">
+      <c r="E165" s="3" t="inlineStr">
         <is>
           <t>오의 - 생사 각인(P) 피해량: 30(+추가 공격력의 25%)(+대상 최대 체력의 4/7/10(+추가 공격력의 4%)%)
 (변경 전: 30(+추가 공격력의 45%)(+대상 최대 체력의 4/7/10(+추가 공격력의 4%)%))</t>
         </is>
       </c>
-      <c r="F125" s="3" t="inlineStr"/>
-    </row>
-    <row r="126" ht="60" customHeight="1">
-      <c r="A126" s="2" t="inlineStr">
+      <c r="F165" s="3" t="inlineStr"/>
+    </row>
+    <row r="166" ht="60" customHeight="1">
+      <c r="A166" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-029</t>
         </is>
       </c>
-      <c r="B126" s="3" t="inlineStr">
+      <c r="B166" s="3" t="inlineStr">
         <is>
           <t>[실험체] 코렐라인 - 단죄의 섬광(Q) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C126" s="3" t="inlineStr">
+      <c r="C166" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 코렐라인 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D126" s="3" t="inlineStr">
+      <c r="D166" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 코렐라인 선택
@@ -4662,32 +5982,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E126" s="3" t="inlineStr">
+      <c r="E166" s="3" t="inlineStr">
         <is>
           <t>단죄의 섬광(Q) 피해량: 50/90/130/170/210(+스킬 증폭의 80%)
 (변경 전: 50/90/130/170/210(+스킬 증폭의 75%))</t>
         </is>
       </c>
-      <c r="F126" s="3" t="inlineStr"/>
-    </row>
-    <row r="127" ht="60" customHeight="1">
-      <c r="A127" s="2" t="inlineStr">
+      <c r="F166" s="3" t="inlineStr"/>
+    </row>
+    <row r="167" ht="60" customHeight="1">
+      <c r="A167" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-030</t>
         </is>
       </c>
-      <c r="B127" s="3" t="inlineStr">
+      <c r="B167" s="3" t="inlineStr">
         <is>
           <t>[실험체] 코렐라인 - 죄의 굴레(E) 백경 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C127" s="3" t="inlineStr">
+      <c r="C167" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 코렐라인 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D127" s="3" t="inlineStr">
+      <c r="D167" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 코렐라인 선택
@@ -4695,32 +6015,32 @@
 4. 백경 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E127" s="3" t="inlineStr">
+      <c r="E167" s="3" t="inlineStr">
         <is>
           <t>죄의 굴레(E) 백경 피해량: 80/110/140/170/200(+스킬 증폭의 65%)
 (변경 전: 80/110/140/170/200(+스킬 증폭의 70%))</t>
         </is>
       </c>
-      <c r="F127" s="3" t="inlineStr"/>
-    </row>
-    <row r="128" ht="60" customHeight="1">
-      <c r="A128" s="2" t="inlineStr">
+      <c r="F167" s="3" t="inlineStr"/>
+    </row>
+    <row r="168" ht="60" customHeight="1">
+      <c r="A168" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-031</t>
         </is>
       </c>
-      <c r="B128" s="3" t="inlineStr">
+      <c r="B168" s="3" t="inlineStr">
         <is>
           <t>[실험체] 코렐라인 - 죄의 굴레(E) 흑경 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C128" s="3" t="inlineStr">
+      <c r="C168" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 코렐라인 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D128" s="3" t="inlineStr">
+      <c r="D168" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 코렐라인 선택
@@ -4728,32 +6048,32 @@
 4. 흑경 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E128" s="3" t="inlineStr">
+      <c r="E168" s="3" t="inlineStr">
         <is>
           <t>죄의 굴레(E) 흑경 피해량: 80/110/140/170/200(+스킬 증폭의 65%)
 (변경 전: 80/110/140/170/200(+스킬 증폭의 70%))</t>
         </is>
       </c>
-      <c r="F128" s="3" t="inlineStr"/>
-    </row>
-    <row r="129" ht="60" customHeight="1">
-      <c r="A129" s="2" t="inlineStr">
+      <c r="F168" s="3" t="inlineStr"/>
+    </row>
+    <row r="169" ht="60" customHeight="1">
+      <c r="A169" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-032</t>
         </is>
       </c>
-      <c r="B129" s="3" t="inlineStr">
+      <c r="B169" s="3" t="inlineStr">
         <is>
           <t>[실험체] 코렐라인 - 죄의 굴레(E) 흑경 방어력 감소량 수치 확인</t>
         </is>
       </c>
-      <c r="C129" s="3" t="inlineStr">
+      <c r="C169" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 코렐라인 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D129" s="3" t="inlineStr">
+      <c r="D169" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 코렐라인 선택
@@ -4761,32 +6081,32 @@
 4. 흑경 방어력 감소량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E129" s="3" t="inlineStr">
+      <c r="E169" s="3" t="inlineStr">
         <is>
           <t>죄의 굴레(E) 흑경 방어력 감소량: 10/11/12/13/14%
 (변경 전: 12/13/14/15/16%)</t>
         </is>
       </c>
-      <c r="F129" s="3" t="inlineStr"/>
-    </row>
-    <row r="130" ht="60" customHeight="1">
-      <c r="A130" s="2" t="inlineStr">
+      <c r="F169" s="3" t="inlineStr"/>
+    </row>
+    <row r="170" ht="60" customHeight="1">
+      <c r="A170" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-033</t>
         </is>
       </c>
-      <c r="B130" s="3" t="inlineStr">
+      <c r="B170" s="3" t="inlineStr">
         <is>
           <t>[실험체] 클로에 - 살아 있는 마리오네트(P) 니나 부활 시 클로에 체력 소모량 현재 체력의 수치 확인</t>
         </is>
       </c>
-      <c r="C130" s="3" t="inlineStr">
+      <c r="C170" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 클로에 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D130" s="3" t="inlineStr">
+      <c r="D170" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 클로에 선택
@@ -4794,32 +6114,32 @@
 4. 니나 부활 시 클로에 체력 소모량 현재 체력의 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E130" s="3" t="inlineStr">
+      <c r="E170" s="3" t="inlineStr">
         <is>
           <t>살아 있는 마리오네트(P) 니나 부활 시 클로에 체력 소모량 현재 체력의: 20%
 (변경 전: 30%)</t>
         </is>
       </c>
-      <c r="F130" s="3" t="inlineStr"/>
-    </row>
-    <row r="131" ht="60" customHeight="1">
-      <c r="A131" s="2" t="inlineStr">
+      <c r="F170" s="3" t="inlineStr"/>
+    </row>
+    <row r="171" ht="60" customHeight="1">
+      <c r="A171" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-034</t>
         </is>
       </c>
-      <c r="B131" s="3" t="inlineStr">
+      <c r="B171" s="3" t="inlineStr">
         <is>
           <t>[실험체] 키아라 - 뒤틀린 기도(W) 최소 보호막량 수치 확인</t>
         </is>
       </c>
-      <c r="C131" s="3" t="inlineStr">
+      <c r="C171" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 키아라 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D131" s="3" t="inlineStr">
+      <c r="D171" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 키아라 선택
@@ -4827,32 +6147,32 @@
 4. 최소 보호막량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E131" s="3" t="inlineStr">
+      <c r="E171" s="3" t="inlineStr">
         <is>
           <t>뒤틀린 기도(W) 최소 보호막량: 110/130/150/170/190(+스킬 증폭의 50%)
 (변경 전: 90/110/130/150/170(+스킬 증폭의 50%))</t>
         </is>
       </c>
-      <c r="F131" s="3" t="inlineStr"/>
-    </row>
-    <row r="132" ht="60" customHeight="1">
-      <c r="A132" s="2" t="inlineStr">
+      <c r="F171" s="3" t="inlineStr"/>
+    </row>
+    <row r="172" ht="60" customHeight="1">
+      <c r="A172" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-035</t>
         </is>
       </c>
-      <c r="B132" s="3" t="inlineStr">
+      <c r="B172" s="3" t="inlineStr">
         <is>
           <t>[실험체] 키아라 - 뒤틀린 기도(W) 최대 보호막량 수치 확인</t>
         </is>
       </c>
-      <c r="C132" s="3" t="inlineStr">
+      <c r="C172" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 키아라 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D132" s="3" t="inlineStr">
+      <c r="D172" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 키아라 선택
@@ -4860,32 +6180,32 @@
 4. 최대 보호막량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E132" s="3" t="inlineStr">
+      <c r="E172" s="3" t="inlineStr">
         <is>
           <t>뒤틀린 기도(W) 최대 보호막량: 165/195/225/255/285(+스킬 증폭의 75%)
 (변경 전: 135/165/195/225/255(+스킬 증폭의 75%))</t>
         </is>
       </c>
-      <c r="F132" s="3" t="inlineStr"/>
-    </row>
-    <row r="133" ht="60" customHeight="1">
-      <c r="A133" s="2" t="inlineStr">
+      <c r="F172" s="3" t="inlineStr"/>
+    </row>
+    <row r="173" ht="60" customHeight="1">
+      <c r="A173" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-036</t>
         </is>
       </c>
-      <c r="B133" s="3" t="inlineStr">
+      <c r="B173" s="3" t="inlineStr">
         <is>
           <t>[실험체] 펜리르 - 먹잇감 추적(W) 본능적 후퇴(W2) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C133" s="3" t="inlineStr">
+      <c r="C173" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 펜리르 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D133" s="3" t="inlineStr">
+      <c r="D173" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 펜리르 선택
@@ -4893,32 +6213,32 @@
 4. 본능적 후퇴(W2) 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E133" s="3" t="inlineStr">
+      <c r="E173" s="3" t="inlineStr">
         <is>
           <t>먹잇감 추적(W) 본능적 후퇴(W2) 피해량: 30/55/80/105/130(+공격력의 60%)
 (변경 전: 20/40/60/80/100(+공격력의 60%))</t>
         </is>
       </c>
-      <c r="F133" s="3" t="inlineStr"/>
-    </row>
-    <row r="134" ht="60" customHeight="1">
-      <c r="A134" s="2" t="inlineStr">
+      <c r="F173" s="3" t="inlineStr"/>
+    </row>
+    <row r="174" ht="60" customHeight="1">
+      <c r="A174" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-037</t>
         </is>
       </c>
-      <c r="B134" s="3" t="inlineStr">
+      <c r="B174" s="3" t="inlineStr">
         <is>
           <t>[실험체] 프리야 - 대지의 메아리(R) 받는 피해 감소 수치 확인</t>
         </is>
       </c>
-      <c r="C134" s="3" t="inlineStr">
+      <c r="C174" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 프리야 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D134" s="3" t="inlineStr">
+      <c r="D174" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 프리야 선택
@@ -4926,32 +6246,32 @@
 4. 받는 피해 감소 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E134" s="3" t="inlineStr">
+      <c r="E174" s="3" t="inlineStr">
         <is>
           <t>대지의 메아리(R) 받는 피해 감소: 40%
 (변경 전: 50%)</t>
         </is>
       </c>
-      <c r="F134" s="3" t="inlineStr"/>
-    </row>
-    <row r="135" ht="60" customHeight="1">
-      <c r="A135" s="2" t="inlineStr">
+      <c r="F174" s="3" t="inlineStr"/>
+    </row>
+    <row r="175" ht="60" customHeight="1">
+      <c r="A175" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-038</t>
         </is>
       </c>
-      <c r="B135" s="3" t="inlineStr">
+      <c r="B175" s="3" t="inlineStr">
         <is>
           <t>[실험체] 프리야 - 포르타멘토(W) 아군 이동 속도 증가 수치 확인</t>
         </is>
       </c>
-      <c r="C135" s="3" t="inlineStr">
+      <c r="C175" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 프리야 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D135" s="3" t="inlineStr">
+      <c r="D175" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 프리야 선택
@@ -4959,32 +6279,32 @@
 4. 아군 이동 속도 증가 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E135" s="3" t="inlineStr">
+      <c r="E175" s="3" t="inlineStr">
         <is>
           <t>포르타멘토(W) 아군 이동 속도 증가: 8/9/10/11/12%
 (변경 전: 10/11/12/13/14%)</t>
         </is>
       </c>
-      <c r="F135" s="3" t="inlineStr"/>
-    </row>
-    <row r="136" ht="60" customHeight="1">
-      <c r="A136" s="2" t="inlineStr">
+      <c r="F175" s="3" t="inlineStr"/>
+    </row>
+    <row r="176" ht="60" customHeight="1">
+      <c r="A176" s="2" t="inlineStr">
         <is>
           <t>TC-10.6-039</t>
         </is>
       </c>
-      <c r="B136" s="3" t="inlineStr">
+      <c r="B176" s="3" t="inlineStr">
         <is>
           <t>[실험체] 현우 - 허세(W) 방어력 증가 수치 확인</t>
         </is>
       </c>
-      <c r="C136" s="3" t="inlineStr">
+      <c r="C176" s="3" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 현우 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D136" s="3" t="inlineStr">
+      <c r="D176" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 현우 선택
@@ -4992,32 +6312,32 @@
 4. 방어력 증가 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E136" s="3" t="inlineStr">
+      <c r="E176" s="3" t="inlineStr">
         <is>
           <t>허세(W) 방어력 증가: 14/21/28/35/42(+방어력 10당 1)
 (변경 전: 14/23/32/41/50(+방어력 10당 1))</t>
         </is>
       </c>
-      <c r="F136" s="3" t="inlineStr"/>
-    </row>
-    <row r="137" ht="60" customHeight="1">
-      <c r="A137" s="4" t="inlineStr">
+      <c r="F176" s="3" t="inlineStr"/>
+    </row>
+    <row r="177" ht="60" customHeight="1">
+      <c r="A177" s="4" t="inlineStr">
         <is>
           <t>TC-10.6-040</t>
         </is>
       </c>
-      <c r="B137" s="5" t="inlineStr">
+      <c r="B177" s="5" t="inlineStr">
         <is>
           <t>[실험체] 라우라 - 채찍 무기 숙련도 레벨 당 공격 속도 수치 확인</t>
         </is>
       </c>
-      <c r="C137" s="5" t="inlineStr">
+      <c r="C177" s="5" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 라우라 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D137" s="5" t="inlineStr">
+      <c r="D177" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 라우라 선택
@@ -5025,32 +6345,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E137" s="5" t="inlineStr">
+      <c r="E177" s="5" t="inlineStr">
         <is>
           <t>채찍 무기 숙련도 레벨 당 공격 속도: 3.3%
 (변경 전: 2.8%)</t>
         </is>
       </c>
-      <c r="F137" s="5" t="inlineStr"/>
-    </row>
-    <row r="138" ht="60" customHeight="1">
-      <c r="A138" s="4" t="inlineStr">
+      <c r="F177" s="5" t="inlineStr"/>
+    </row>
+    <row r="178" ht="60" customHeight="1">
+      <c r="A178" s="4" t="inlineStr">
         <is>
           <t>TC-10.6-041</t>
         </is>
       </c>
-      <c r="B138" s="5" t="inlineStr">
+      <c r="B178" s="5" t="inlineStr">
         <is>
           <t>[실험체] 레니 - 주는 보호막 효과 수치 확인</t>
         </is>
       </c>
-      <c r="C138" s="5" t="inlineStr">
+      <c r="C178" s="5" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 레니 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D138" s="5" t="inlineStr">
+      <c r="D178" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 레니 선택
@@ -5058,32 +6378,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E138" s="5" t="inlineStr">
+      <c r="E178" s="5" t="inlineStr">
         <is>
           <t>주는 보호막 효과: 70%
 (변경 전: 65%)</t>
         </is>
       </c>
-      <c r="F138" s="5" t="inlineStr"/>
-    </row>
-    <row r="139" ht="60" customHeight="1">
-      <c r="A139" s="4" t="inlineStr">
+      <c r="F178" s="5" t="inlineStr"/>
+    </row>
+    <row r="179" ht="60" customHeight="1">
+      <c r="A179" s="4" t="inlineStr">
         <is>
           <t>TC-10.6-042</t>
         </is>
       </c>
-      <c r="B139" s="5" t="inlineStr">
+      <c r="B179" s="5" t="inlineStr">
         <is>
           <t>[실험체] 리 다이린 - 레벨 당 공격력 수치 확인</t>
         </is>
       </c>
-      <c r="C139" s="5" t="inlineStr">
+      <c r="C179" s="5" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 리 다이린 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D139" s="5" t="inlineStr">
+      <c r="D179" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 리 다이린 선택
@@ -5091,32 +6411,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E139" s="5" t="inlineStr">
+      <c r="E179" s="5" t="inlineStr">
         <is>
           <t>레벨 당 공격력: 5
 (변경 전: 4.8)</t>
         </is>
       </c>
-      <c r="F139" s="5" t="inlineStr"/>
-    </row>
-    <row r="140" ht="60" customHeight="1">
-      <c r="A140" s="4" t="inlineStr">
+      <c r="F179" s="5" t="inlineStr"/>
+    </row>
+    <row r="180" ht="60" customHeight="1">
+      <c r="A180" s="4" t="inlineStr">
         <is>
           <t>TC-10.6-043</t>
         </is>
       </c>
-      <c r="B140" s="5" t="inlineStr">
+      <c r="B180" s="5" t="inlineStr">
         <is>
           <t>[실험체] 버니스 - 기본 공격력 수치 확인</t>
         </is>
       </c>
-      <c r="C140" s="5" t="inlineStr">
+      <c r="C180" s="5" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 버니스 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D140" s="5" t="inlineStr">
+      <c r="D180" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 버니스 선택
@@ -5124,32 +6444,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E140" s="5" t="inlineStr">
+      <c r="E180" s="5" t="inlineStr">
         <is>
           <t>기본 공격력: 37
 (변경 전: 35)</t>
         </is>
       </c>
-      <c r="F140" s="5" t="inlineStr"/>
-    </row>
-    <row r="141" ht="60" customHeight="1">
-      <c r="A141" s="4" t="inlineStr">
+      <c r="F180" s="5" t="inlineStr"/>
+    </row>
+    <row r="181" ht="60" customHeight="1">
+      <c r="A181" s="4" t="inlineStr">
         <is>
           <t>TC-10.6-044</t>
         </is>
       </c>
-      <c r="B141" s="5" t="inlineStr">
+      <c r="B181" s="5" t="inlineStr">
         <is>
           <t>[실험체] 샬럿 - 주는 보호막 효과 수치 확인</t>
         </is>
       </c>
-      <c r="C141" s="5" t="inlineStr">
+      <c r="C181" s="5" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 샬럿 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D141" s="5" t="inlineStr">
+      <c r="D181" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 샬럿 선택
@@ -5157,32 +6477,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E141" s="5" t="inlineStr">
+      <c r="E181" s="5" t="inlineStr">
         <is>
           <t>주는 보호막 효과: 70%
 (변경 전: 65%)</t>
         </is>
       </c>
-      <c r="F141" s="5" t="inlineStr"/>
-    </row>
-    <row r="142" ht="60" customHeight="1">
-      <c r="A142" s="4" t="inlineStr">
+      <c r="F181" s="5" t="inlineStr"/>
+    </row>
+    <row r="182" ht="60" customHeight="1">
+      <c r="A182" s="4" t="inlineStr">
         <is>
           <t>TC-10.6-045</t>
         </is>
       </c>
-      <c r="B142" s="5" t="inlineStr">
+      <c r="B182" s="5" t="inlineStr">
         <is>
           <t>[실험체] 슈린 - 레벨 당 공격력 수치 확인</t>
         </is>
       </c>
-      <c r="C142" s="5" t="inlineStr">
+      <c r="C182" s="5" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 슈린 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D142" s="5" t="inlineStr">
+      <c r="D182" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 슈린 선택
@@ -5190,32 +6510,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E142" s="5" t="inlineStr">
+      <c r="E182" s="5" t="inlineStr">
         <is>
           <t>레벨 당 공격력: 4.6
 (변경 전: 4.3)</t>
         </is>
       </c>
-      <c r="F142" s="5" t="inlineStr"/>
-    </row>
-    <row r="143" ht="60" customHeight="1">
-      <c r="A143" s="4" t="inlineStr">
+      <c r="F182" s="5" t="inlineStr"/>
+    </row>
+    <row r="183" ht="60" customHeight="1">
+      <c r="A183" s="4" t="inlineStr">
         <is>
           <t>TC-10.6-046</t>
         </is>
       </c>
-      <c r="B143" s="5" t="inlineStr">
+      <c r="B183" s="5" t="inlineStr">
         <is>
           <t>[실험체] 실비아 - 주는 회복 효과 수치 확인</t>
         </is>
       </c>
-      <c r="C143" s="5" t="inlineStr">
+      <c r="C183" s="5" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 실비아 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D143" s="5" t="inlineStr">
+      <c r="D183" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 실비아 선택
@@ -5223,32 +6543,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E143" s="5" t="inlineStr">
+      <c r="E183" s="5" t="inlineStr">
         <is>
           <t>주는 회복 효과: 70%
 (변경 전: 65%)</t>
         </is>
       </c>
-      <c r="F143" s="5" t="inlineStr"/>
-    </row>
-    <row r="144" ht="60" customHeight="1">
-      <c r="A144" s="4" t="inlineStr">
+      <c r="F183" s="5" t="inlineStr"/>
+    </row>
+    <row r="184" ht="60" customHeight="1">
+      <c r="A184" s="4" t="inlineStr">
         <is>
           <t>TC-10.6-047</t>
         </is>
       </c>
-      <c r="B144" s="5" t="inlineStr">
+      <c r="B184" s="5" t="inlineStr">
         <is>
           <t>[실험체] 아르다 - 주는 회복 효과 수치 확인</t>
         </is>
       </c>
-      <c r="C144" s="5" t="inlineStr">
+      <c r="C184" s="5" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 아르다 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D144" s="5" t="inlineStr">
+      <c r="D184" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 아르다 선택
@@ -5256,32 +6576,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E144" s="5" t="inlineStr">
+      <c r="E184" s="5" t="inlineStr">
         <is>
           <t>주는 회복 효과: 70%
 (변경 전: 65%)</t>
         </is>
       </c>
-      <c r="F144" s="5" t="inlineStr"/>
-    </row>
-    <row r="145" ht="60" customHeight="1">
-      <c r="A145" s="4" t="inlineStr">
+      <c r="F184" s="5" t="inlineStr"/>
+    </row>
+    <row r="185" ht="60" customHeight="1">
+      <c r="A185" s="4" t="inlineStr">
         <is>
           <t>TC-10.6-048</t>
         </is>
       </c>
-      <c r="B145" s="5" t="inlineStr">
+      <c r="B185" s="5" t="inlineStr">
         <is>
           <t>[실험체] 아이솔 - 권총 무기 숙련도 레벨 당 스킬 증폭 수치 확인</t>
         </is>
       </c>
-      <c r="C145" s="5" t="inlineStr">
+      <c r="C185" s="5" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 아이솔 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D145" s="5" t="inlineStr">
+      <c r="D185" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 아이솔 선택
@@ -5289,32 +6609,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E145" s="5" t="inlineStr">
+      <c r="E185" s="5" t="inlineStr">
         <is>
           <t>권총 무기 숙련도 레벨 당 스킬 증폭: 4.5%
 (변경 전: 4.4%)</t>
         </is>
       </c>
-      <c r="F145" s="5" t="inlineStr"/>
-    </row>
-    <row r="146" ht="60" customHeight="1">
-      <c r="A146" s="4" t="inlineStr">
+      <c r="F185" s="5" t="inlineStr"/>
+    </row>
+    <row r="186" ht="60" customHeight="1">
+      <c r="A186" s="4" t="inlineStr">
         <is>
           <t>TC-10.6-049</t>
         </is>
       </c>
-      <c r="B146" s="5" t="inlineStr">
+      <c r="B186" s="5" t="inlineStr">
         <is>
           <t>[실험체] 에키온 - 기본 공격력 수치 확인</t>
         </is>
       </c>
-      <c r="C146" s="5" t="inlineStr">
+      <c r="C186" s="5" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 에키온 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D146" s="5" t="inlineStr">
+      <c r="D186" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 에키온 선택
@@ -5322,32 +6642,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E146" s="5" t="inlineStr">
+      <c r="E186" s="5" t="inlineStr">
         <is>
           <t>기본 공격력: 35
 (변경 전: 39)</t>
         </is>
       </c>
-      <c r="F146" s="5" t="inlineStr"/>
-    </row>
-    <row r="147" ht="60" customHeight="1">
-      <c r="A147" s="4" t="inlineStr">
+      <c r="F186" s="5" t="inlineStr"/>
+    </row>
+    <row r="187" ht="60" customHeight="1">
+      <c r="A187" s="4" t="inlineStr">
         <is>
           <t>TC-10.6-050</t>
         </is>
       </c>
-      <c r="B147" s="5" t="inlineStr">
+      <c r="B187" s="5" t="inlineStr">
         <is>
           <t>[실험체] 이렘 - 투척 무기 숙련도 레벨 당 공격 속도 수치 확인</t>
         </is>
       </c>
-      <c r="C147" s="5" t="inlineStr">
+      <c r="C187" s="5" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 이렘 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D147" s="5" t="inlineStr">
+      <c r="D187" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 이렘 선택
@@ -5355,32 +6675,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E147" s="5" t="inlineStr">
+      <c r="E187" s="5" t="inlineStr">
         <is>
           <t>투척 무기 숙련도 레벨 당 공격 속도: 2.2%
 (변경 전: 1.6%)</t>
         </is>
       </c>
-      <c r="F147" s="5" t="inlineStr"/>
-    </row>
-    <row r="148" ht="60" customHeight="1">
-      <c r="A148" s="4" t="inlineStr">
+      <c r="F187" s="5" t="inlineStr"/>
+    </row>
+    <row r="188" ht="60" customHeight="1">
+      <c r="A188" s="4" t="inlineStr">
         <is>
           <t>TC-10.6-051</t>
         </is>
       </c>
-      <c r="B148" s="5" t="inlineStr">
+      <c r="B188" s="5" t="inlineStr">
         <is>
           <t>[실험체] 카밀로 - 레이피어 무기 숙련도 레벨 당 기본 공격 증폭 수치 확인</t>
         </is>
       </c>
-      <c r="C148" s="5" t="inlineStr">
+      <c r="C188" s="5" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 카밀로 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D148" s="5" t="inlineStr">
+      <c r="D188" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 카밀로 선택
@@ -5388,32 +6708,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E148" s="5" t="inlineStr">
+      <c r="E188" s="5" t="inlineStr">
         <is>
           <t>레이피어 무기 숙련도 레벨 당 기본 공격 증폭: 1.4%
 (변경 전: 1.5%)</t>
         </is>
       </c>
-      <c r="F148" s="5" t="inlineStr"/>
-    </row>
-    <row r="149" ht="60" customHeight="1">
-      <c r="A149" s="4" t="inlineStr">
+      <c r="F188" s="5" t="inlineStr"/>
+    </row>
+    <row r="189" ht="60" customHeight="1">
+      <c r="A189" s="4" t="inlineStr">
         <is>
           <t>TC-10.6-052</t>
         </is>
       </c>
-      <c r="B149" s="5" t="inlineStr">
+      <c r="B189" s="5" t="inlineStr">
         <is>
           <t>[실험체] 캐시 - 기본 체력 수치 확인</t>
         </is>
       </c>
-      <c r="C149" s="5" t="inlineStr">
+      <c r="C189" s="5" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 캐시 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D149" s="5" t="inlineStr">
+      <c r="D189" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 캐시 선택
@@ -5421,32 +6741,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E149" s="5" t="inlineStr">
+      <c r="E189" s="5" t="inlineStr">
         <is>
           <t>기본 체력: 970
 (변경 전: 940)</t>
         </is>
       </c>
-      <c r="F149" s="5" t="inlineStr"/>
-    </row>
-    <row r="150" ht="60" customHeight="1">
-      <c r="A150" s="4" t="inlineStr">
+      <c r="F189" s="5" t="inlineStr"/>
+    </row>
+    <row r="190" ht="60" customHeight="1">
+      <c r="A190" s="4" t="inlineStr">
         <is>
           <t>TC-10.6-053</t>
         </is>
       </c>
-      <c r="B150" s="5" t="inlineStr">
+      <c r="B190" s="5" t="inlineStr">
         <is>
           <t>[실험체] 펜리르 - 레벨 당 체력 수치 확인</t>
         </is>
       </c>
-      <c r="C150" s="5" t="inlineStr">
+      <c r="C190" s="5" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 펜리르 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D150" s="5" t="inlineStr">
+      <c r="D190" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 펜리르 선택
@@ -5454,32 +6774,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E150" s="5" t="inlineStr">
+      <c r="E190" s="5" t="inlineStr">
         <is>
           <t>레벨 당 체력: 94
 (변경 전: 92)</t>
         </is>
       </c>
-      <c r="F150" s="5" t="inlineStr"/>
-    </row>
-    <row r="151" ht="60" customHeight="1">
-      <c r="A151" s="4" t="inlineStr">
+      <c r="F190" s="5" t="inlineStr"/>
+    </row>
+    <row r="191" ht="60" customHeight="1">
+      <c r="A191" s="4" t="inlineStr">
         <is>
           <t>TC-10.6-054</t>
         </is>
       </c>
-      <c r="B151" s="5" t="inlineStr">
+      <c r="B191" s="5" t="inlineStr">
         <is>
           <t>[실험체] 피오라 - 레이피어 무기 숙련도 레벨 당 스킬 증폭 수치 확인</t>
         </is>
       </c>
-      <c r="C151" s="5" t="inlineStr">
+      <c r="C191" s="5" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 피오라 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D151" s="5" t="inlineStr">
+      <c r="D191" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 피오라 선택
@@ -5487,32 +6807,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E151" s="5" t="inlineStr">
+      <c r="E191" s="5" t="inlineStr">
         <is>
           <t>레이피어 무기 숙련도 레벨 당 스킬 증폭: 4.2%
 (변경 전: 4.3%)</t>
         </is>
       </c>
-      <c r="F151" s="5" t="inlineStr"/>
-    </row>
-    <row r="152" ht="60" customHeight="1">
-      <c r="A152" s="4" t="inlineStr">
+      <c r="F191" s="5" t="inlineStr"/>
+    </row>
+    <row r="192" ht="60" customHeight="1">
+      <c r="A192" s="4" t="inlineStr">
         <is>
           <t>TC-10.6-055</t>
         </is>
       </c>
-      <c r="B152" s="5" t="inlineStr">
+      <c r="B192" s="5" t="inlineStr">
         <is>
           <t>[실험체] 현우 - 톤파 무기 숙련도 레벨 당 스킬 증폭 수치 확인</t>
         </is>
       </c>
-      <c r="C152" s="5" t="inlineStr">
+      <c r="C192" s="5" t="inlineStr">
         <is>
           <t>· 10.6 패치 적용 완료
 · 현우 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D152" s="5" t="inlineStr">
+      <c r="D192" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 현우 선택
@@ -5520,32 +6840,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E152" s="5" t="inlineStr">
+      <c r="E192" s="5" t="inlineStr">
         <is>
           <t>톤파 무기 숙련도 레벨 당 스킬 증폭: 4.5%
 (변경 전: 4.3%)</t>
         </is>
       </c>
-      <c r="F152" s="5" t="inlineStr"/>
-    </row>
-    <row r="153" ht="60" customHeight="1">
-      <c r="A153" s="2" t="inlineStr">
+      <c r="F192" s="5" t="inlineStr"/>
+    </row>
+    <row r="193" ht="60" customHeight="1">
+      <c r="A193" s="2" t="inlineStr">
         <is>
           <t>TC-10.5a-001</t>
         </is>
       </c>
-      <c r="B153" s="3" t="inlineStr">
+      <c r="B193" s="3" t="inlineStr">
         <is>
           <t>[실험체] 코렐라인 - 단죄의 섬광(Q) 백경 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C153" s="3" t="inlineStr">
+      <c r="C193" s="3" t="inlineStr">
         <is>
           <t>· 10.5a 패치 적용 완료
 · 코렐라인 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D153" s="3" t="inlineStr">
+      <c r="D193" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 코렐라인 선택
@@ -5553,32 +6873,32 @@
 4. 백경 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E153" s="3" t="inlineStr">
+      <c r="E193" s="3" t="inlineStr">
         <is>
           <t>단죄의 섬광(Q) 백경 피해량: 60/105/150/195/240(+스킬 증폭의 80%)(+현재 체력의 4/6/8/10/12%)
 (변경 전: 60/105/150/195/240(+스킬 증폭의 85%)(+현재 체력의 4/6/8/10/12%))</t>
         </is>
       </c>
-      <c r="F153" s="3" t="inlineStr"/>
-    </row>
-    <row r="154" ht="60" customHeight="1">
-      <c r="A154" s="2" t="inlineStr">
+      <c r="F193" s="3" t="inlineStr"/>
+    </row>
+    <row r="194" ht="60" customHeight="1">
+      <c r="A194" s="2" t="inlineStr">
         <is>
           <t>TC-10.5a-002</t>
         </is>
       </c>
-      <c r="B154" s="3" t="inlineStr">
+      <c r="B194" s="3" t="inlineStr">
         <is>
           <t>[실험체] 코렐라인 - 단죄의 섬광(Q) 흑경 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C154" s="3" t="inlineStr">
+      <c r="C194" s="3" t="inlineStr">
         <is>
           <t>· 10.5a 패치 적용 완료
 · 코렐라인 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D154" s="3" t="inlineStr">
+      <c r="D194" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 코렐라인 선택
@@ -5586,32 +6906,32 @@
 4. 흑경 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E154" s="3" t="inlineStr">
+      <c r="E194" s="3" t="inlineStr">
         <is>
           <t>단죄의 섬광(Q) 흑경 피해량: 60/105/150/195/240(+스킬 증폭의 80%)(+잃은 체력의 3/6/9/12/15%)
 (변경 전: 60/105/150/195/240(+스킬 증폭의 85%)(+잃은 체력의 3/6/9/12/15%))</t>
         </is>
       </c>
-      <c r="F154" s="3" t="inlineStr"/>
-    </row>
-    <row r="155" ht="60" customHeight="1">
-      <c r="A155" s="4" t="inlineStr">
+      <c r="F194" s="3" t="inlineStr"/>
+    </row>
+    <row r="195" ht="60" customHeight="1">
+      <c r="A195" s="4" t="inlineStr">
         <is>
           <t>TC-10.5a-003</t>
         </is>
       </c>
-      <c r="B155" s="5" t="inlineStr">
+      <c r="B195" s="5" t="inlineStr">
         <is>
           <t>[실험체] 현우 - 최대 체력 수치 확인</t>
         </is>
       </c>
-      <c r="C155" s="5" t="inlineStr">
+      <c r="C195" s="5" t="inlineStr">
         <is>
           <t>· 10.5a 패치 적용 완료
 · 현우 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D155" s="5" t="inlineStr">
+      <c r="D195" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 현우 선택
@@ -5619,32 +6939,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E155" s="5" t="inlineStr">
+      <c r="E195" s="5" t="inlineStr">
         <is>
           <t>최대 체력: 960
 (변경 전: 1000)</t>
         </is>
       </c>
-      <c r="F155" s="5" t="inlineStr"/>
-    </row>
-    <row r="156" ht="60" customHeight="1">
-      <c r="A156" s="2" t="inlineStr">
+      <c r="F195" s="5" t="inlineStr"/>
+    </row>
+    <row r="196" ht="60" customHeight="1">
+      <c r="A196" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-001</t>
         </is>
       </c>
-      <c r="B156" s="3" t="inlineStr">
+      <c r="B196" s="3" t="inlineStr">
         <is>
           <t>[실험체] 나타폰 - 슬로우 셔터(P) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C156" s="3" t="inlineStr">
+      <c r="C196" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 나타폰 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D156" s="3" t="inlineStr">
+      <c r="D196" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 나타폰 선택
@@ -5652,32 +6972,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E156" s="3" t="inlineStr">
+      <c r="E196" s="3" t="inlineStr">
         <is>
           <t>슬로우 셔터(P) 피해량: 30/60/90(+공격 속도의 20%)(+스킬 증폭의 65%)
 (변경 전: 40/70/100(+공격 속도의 20%)(+스킬 증폭의 65%))</t>
         </is>
       </c>
-      <c r="F156" s="3" t="inlineStr"/>
-    </row>
-    <row r="157" ht="60" customHeight="1">
-      <c r="A157" s="2" t="inlineStr">
+      <c r="F196" s="3" t="inlineStr"/>
+    </row>
+    <row r="197" ht="60" customHeight="1">
+      <c r="A197" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-002</t>
         </is>
       </c>
-      <c r="B157" s="3" t="inlineStr">
+      <c r="B197" s="3" t="inlineStr">
         <is>
           <t>[실험체] 다르코 - 고리대금(Q) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C157" s="3" t="inlineStr">
+      <c r="C197" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 다르코 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D157" s="3" t="inlineStr">
+      <c r="D197" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 다르코 선택
@@ -5685,32 +7005,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E157" s="3" t="inlineStr">
+      <c r="E197" s="3" t="inlineStr">
         <is>
           <t>고리대금(Q) 피해량: 20/40/60/80/100(+공격력의 40%)(+대상 최대 체력의 2/3/4/5/6%)
 (변경 전: 20/40/60/80/100(+공격력의 40%)(+대상 최대 체력의 1/2/3/4/5%))</t>
         </is>
       </c>
-      <c r="F157" s="3" t="inlineStr"/>
-    </row>
-    <row r="158" ht="60" customHeight="1">
-      <c r="A158" s="2" t="inlineStr">
+      <c r="F197" s="3" t="inlineStr"/>
+    </row>
+    <row r="198" ht="60" customHeight="1">
+      <c r="A198" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-003</t>
         </is>
       </c>
-      <c r="B158" s="3" t="inlineStr">
+      <c r="B198" s="3" t="inlineStr">
         <is>
           <t>[실험체] 띠아 - 색칠놀이(E) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C158" s="3" t="inlineStr">
+      <c r="C198" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 띠아 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D158" s="3" t="inlineStr">
+      <c r="D198" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 띠아 선택
@@ -5718,32 +7038,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E158" s="3" t="inlineStr">
+      <c r="E198" s="3" t="inlineStr">
         <is>
           <t>색칠놀이(E) 피해량: 40/90/140/190/240(+스킬 증폭의 90%)
 (변경 전: 40/90/140/190/240(+스킬 증폭의 80%))</t>
         </is>
       </c>
-      <c r="F158" s="3" t="inlineStr"/>
-    </row>
-    <row r="159" ht="60" customHeight="1">
-      <c r="A159" s="2" t="inlineStr">
+      <c r="F198" s="3" t="inlineStr"/>
+    </row>
+    <row r="199" ht="60" customHeight="1">
+      <c r="A199" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-004</t>
         </is>
       </c>
-      <c r="B159" s="3" t="inlineStr">
+      <c r="B199" s="3" t="inlineStr">
         <is>
           <t>[실험체] 라우라 - 날카로운 꽃(Q) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C159" s="3" t="inlineStr">
+      <c r="C199" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 라우라 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D159" s="3" t="inlineStr">
+      <c r="D199" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 라우라 선택
@@ -5751,32 +7071,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E159" s="3" t="inlineStr">
+      <c r="E199" s="3" t="inlineStr">
         <is>
           <t>날카로운 꽃(Q) 피해량: 50/75/100/125/150(+스킬 증폭의 60%)
 (변경 전: 50/75/100/125/150(+스킬 증폭의 55%))</t>
         </is>
       </c>
-      <c r="F159" s="3" t="inlineStr"/>
-    </row>
-    <row r="160" ht="60" customHeight="1">
-      <c r="A160" s="2" t="inlineStr">
+      <c r="F199" s="3" t="inlineStr"/>
+    </row>
+    <row r="200" ht="60" customHeight="1">
+      <c r="A200" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-005</t>
         </is>
       </c>
-      <c r="B160" s="3" t="inlineStr">
+      <c r="B200" s="3" t="inlineStr">
         <is>
           <t>[실험체] 레녹스 - 위풍당당(P) 쿨다운 수치 확인</t>
         </is>
       </c>
-      <c r="C160" s="3" t="inlineStr">
+      <c r="C200" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 레녹스 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D160" s="3" t="inlineStr">
+      <c r="D200" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 레녹스 선택
@@ -5784,32 +7104,32 @@
 4. 쿨다운 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E160" s="3" t="inlineStr">
+      <c r="E200" s="3" t="inlineStr">
         <is>
           <t>위풍당당(P) 쿨다운: 15/13/11초
 (변경 전: 14/12/10초)</t>
         </is>
       </c>
-      <c r="F160" s="3" t="inlineStr"/>
-    </row>
-    <row r="161" ht="60" customHeight="1">
-      <c r="A161" s="2" t="inlineStr">
+      <c r="F200" s="3" t="inlineStr"/>
+    </row>
+    <row r="201" ht="60" customHeight="1">
+      <c r="A201" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-006</t>
         </is>
       </c>
-      <c r="B161" s="3" t="inlineStr">
+      <c r="B201" s="3" t="inlineStr">
         <is>
           <t>[실험체] 마르티나 - 되감기 - 방송 중(E) 체력 회복량 받은 피해의 수치 확인</t>
         </is>
       </c>
-      <c r="C161" s="3" t="inlineStr">
+      <c r="C201" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 마르티나 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D161" s="3" t="inlineStr">
+      <c r="D201" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 마르티나 선택
@@ -5817,32 +7137,32 @@
 4. 체력 회복량 받은 피해의 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E161" s="3" t="inlineStr">
+      <c r="E201" s="3" t="inlineStr">
         <is>
           <t>되감기 - 방송 중(E) 체력 회복량 받은 피해의: 40/45/50/55/60%
 (변경 전: 37/41/45/49/53%)</t>
         </is>
       </c>
-      <c r="F161" s="3" t="inlineStr"/>
-    </row>
-    <row r="162" ht="60" customHeight="1">
-      <c r="A162" s="2" t="inlineStr">
+      <c r="F201" s="3" t="inlineStr"/>
+    </row>
+    <row r="202" ht="60" customHeight="1">
+      <c r="A202" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-007</t>
         </is>
       </c>
-      <c r="B162" s="3" t="inlineStr">
+      <c r="B202" s="3" t="inlineStr">
         <is>
           <t>[실험체] 마이 - 캣 워크(E) 보호막 흡수량 수치 확인</t>
         </is>
       </c>
-      <c r="C162" s="3" t="inlineStr">
+      <c r="C202" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 마이 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D162" s="3" t="inlineStr">
+      <c r="D202" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 마이 선택
@@ -5850,32 +7170,32 @@
 4. 보호막 흡수량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E162" s="3" t="inlineStr">
+      <c r="E202" s="3" t="inlineStr">
         <is>
           <t>캣 워크(E) 보호막 흡수량: 60/90/120/150/180(+스킬 증폭의 40%)(+최대 체력의 7%)
 (변경 전: 60/90/120/150/180(+스킬 증폭의 40%)(+최대 체력의 6%))</t>
         </is>
       </c>
-      <c r="F162" s="3" t="inlineStr"/>
-    </row>
-    <row r="163" ht="60" customHeight="1">
-      <c r="A163" s="2" t="inlineStr">
+      <c r="F202" s="3" t="inlineStr"/>
+    </row>
+    <row r="203" ht="60" customHeight="1">
+      <c r="A203" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-008</t>
         </is>
       </c>
-      <c r="B163" s="3" t="inlineStr">
+      <c r="B203" s="3" t="inlineStr">
         <is>
           <t>[실험체] 비앙카 - 진조의 군림(R)  수치 확인</t>
         </is>
       </c>
-      <c r="C163" s="3" t="inlineStr">
+      <c r="C203" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 비앙카 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D163" s="3" t="inlineStr">
+      <c r="D203" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 비앙카 선택
@@ -5883,32 +7203,32 @@
 4.  수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E163" s="3" t="inlineStr">
+      <c r="E203" s="3" t="inlineStr">
         <is>
           <t>진조의 군림(R) : 50/100/150(+스킬 증폭의 40%)(+대상 최대 체력의 11%)
 (변경 전: 1타 피해량 50/100/150(+스킬 증폭의 50%)(+대상 최대 체력의 11%))</t>
         </is>
       </c>
-      <c r="F163" s="3" t="inlineStr"/>
-    </row>
-    <row r="164" ht="60" customHeight="1">
-      <c r="A164" s="2" t="inlineStr">
+      <c r="F203" s="3" t="inlineStr"/>
+    </row>
+    <row r="204" ht="60" customHeight="1">
+      <c r="A204" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-009</t>
         </is>
       </c>
-      <c r="B164" s="3" t="inlineStr">
+      <c r="B204" s="3" t="inlineStr">
         <is>
           <t>[실험체] 시셀라 - 모두 해방이에요.(R) 패시브 효과 증가 지속 시간 수치 확인</t>
         </is>
       </c>
-      <c r="C164" s="3" t="inlineStr">
+      <c r="C204" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 시셀라 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D164" s="3" t="inlineStr">
+      <c r="D204" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 시셀라 선택
@@ -5916,32 +7236,32 @@
 4. 패시브 효과 증가 지속 시간 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E164" s="3" t="inlineStr">
+      <c r="E204" s="3" t="inlineStr">
         <is>
           <t>모두 해방이에요.(R) 패시브 효과 증가 지속 시간: 7/8/9초
 (변경 전: 6/7/8초)</t>
         </is>
       </c>
-      <c r="F164" s="3" t="inlineStr"/>
-    </row>
-    <row r="165" ht="60" customHeight="1">
-      <c r="A165" s="2" t="inlineStr">
+      <c r="F204" s="3" t="inlineStr"/>
+    </row>
+    <row r="205" ht="60" customHeight="1">
+      <c r="A205" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-010</t>
         </is>
       </c>
-      <c r="B165" s="3" t="inlineStr">
+      <c r="B205" s="3" t="inlineStr">
         <is>
           <t>[실험체] 시셀라 - 어딨어 윌슨?(W) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C165" s="3" t="inlineStr">
+      <c r="C205" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 시셀라 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D165" s="3" t="inlineStr">
+      <c r="D205" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 시셀라 선택
@@ -5949,32 +7269,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E165" s="3" t="inlineStr">
+      <c r="E205" s="3" t="inlineStr">
         <is>
           <t>어딨어 윌슨?(W) 피해량: 100/135/170/205/240(+스킬 증폭의 80%)
 (변경 전: 100/135/170/205/240(+스킬 증폭의 70%))</t>
         </is>
       </c>
-      <c r="F165" s="3" t="inlineStr"/>
-    </row>
-    <row r="166" ht="60" customHeight="1">
-      <c r="A166" s="2" t="inlineStr">
+      <c r="F205" s="3" t="inlineStr"/>
+    </row>
+    <row r="206" ht="60" customHeight="1">
+      <c r="A206" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-011</t>
         </is>
       </c>
-      <c r="B166" s="3" t="inlineStr">
+      <c r="B206" s="3" t="inlineStr">
         <is>
           <t>[실험체] 아야 - 고정 사격(W) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C166" s="3" t="inlineStr">
+      <c r="C206" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 아야 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D166" s="3" t="inlineStr">
+      <c r="D206" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 아야 선택
@@ -5982,32 +7302,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E166" s="3" t="inlineStr">
+      <c r="E206" s="3" t="inlineStr">
         <is>
           <t>고정 사격(W) 피해량: 30/40/50/60/70(+공격력의 50%)(+스킬 증폭의 30/35/40/45/50%)
 (변경 전: 20/30/40/50/60(+공격력의 50%)(+스킬 증폭의 30/35/40/45/50%))</t>
         </is>
       </c>
-      <c r="F166" s="3" t="inlineStr"/>
-    </row>
-    <row r="167" ht="60" customHeight="1">
-      <c r="A167" s="2" t="inlineStr">
+      <c r="F206" s="3" t="inlineStr"/>
+    </row>
+    <row r="207" ht="60" customHeight="1">
+      <c r="A207" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-012</t>
         </is>
       </c>
-      <c r="B167" s="3" t="inlineStr">
+      <c r="B207" s="3" t="inlineStr">
         <is>
           <t>[실험체] 알론소 - 어트랙션 슬램!(E) 속박 지속 시간 수치 확인</t>
         </is>
       </c>
-      <c r="C167" s="3" t="inlineStr">
+      <c r="C207" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 알론소 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D167" s="3" t="inlineStr">
+      <c r="D207" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 알론소 선택
@@ -6015,32 +7335,32 @@
 4. 속박 지속 시간 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E167" s="3" t="inlineStr">
+      <c r="E207" s="3" t="inlineStr">
         <is>
           <t>어트랙션 슬램!(E) 속박 지속 시간: 0.8/0.9/1/1.1/1.2초
 (변경 전: 0.7/0.8/0.9/1/1.1초)</t>
         </is>
       </c>
-      <c r="F167" s="3" t="inlineStr"/>
-    </row>
-    <row r="168" ht="60" customHeight="1">
-      <c r="A168" s="2" t="inlineStr">
+      <c r="F207" s="3" t="inlineStr"/>
+    </row>
+    <row r="208" ht="60" customHeight="1">
+      <c r="A208" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-013</t>
         </is>
       </c>
-      <c r="B168" s="3" t="inlineStr">
+      <c r="B208" s="3" t="inlineStr">
         <is>
           <t>[실험체] 얀 - 니 스트라이크(Q) 리핑 니 스트라이크(Q2) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C168" s="3" t="inlineStr">
+      <c r="C208" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 얀 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D168" s="3" t="inlineStr">
+      <c r="D208" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 얀 선택
@@ -6048,32 +7368,32 @@
 4. 리핑 니 스트라이크(Q2) 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E168" s="3" t="inlineStr">
+      <c r="E208" s="3" t="inlineStr">
         <is>
           <t>니 스트라이크(Q) 리핑 니 스트라이크(Q2) 피해량: 65/90/115/140/165(+추가 공격력의 90%)(+스킬 증폭의 70%)(+적 최대 체력의 6%)
 (변경 전: 65/90/115/140/165(+추가 공격력의 90%)(+스킬 증폭의 60%)(+적 최대 체력의 6%))</t>
         </is>
       </c>
-      <c r="F168" s="3" t="inlineStr"/>
-    </row>
-    <row r="169" ht="60" customHeight="1">
-      <c r="A169" s="2" t="inlineStr">
+      <c r="F208" s="3" t="inlineStr"/>
+    </row>
+    <row r="209" ht="60" customHeight="1">
+      <c r="A209" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-014</t>
         </is>
       </c>
-      <c r="B169" s="3" t="inlineStr">
+      <c r="B209" s="3" t="inlineStr">
         <is>
           <t>[실험체] 에스텔 - 선제대응(W) 이동 속도 감소 수치 확인</t>
         </is>
       </c>
-      <c r="C169" s="3" t="inlineStr">
+      <c r="C209" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 에스텔 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D169" s="3" t="inlineStr">
+      <c r="D209" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 에스텔 선택
@@ -6081,32 +7401,32 @@
 4. 이동 속도 감소 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E169" s="3" t="inlineStr">
+      <c r="E209" s="3" t="inlineStr">
         <is>
           <t>선제대응(W) 이동 속도 감소: 30%
 (변경 전: 25%)</t>
         </is>
       </c>
-      <c r="F169" s="3" t="inlineStr"/>
-    </row>
-    <row r="170" ht="60" customHeight="1">
-      <c r="A170" s="2" t="inlineStr">
+      <c r="F209" s="3" t="inlineStr"/>
+    </row>
+    <row r="210" ht="60" customHeight="1">
+      <c r="A210" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-015</t>
         </is>
       </c>
-      <c r="B170" s="3" t="inlineStr">
+      <c r="B210" s="3" t="inlineStr">
         <is>
           <t>[실험체] 엘레나 - 겨울여왕의 영지(P) 빙결 지속 시간 수치 확인</t>
         </is>
       </c>
-      <c r="C170" s="3" t="inlineStr">
+      <c r="C210" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 엘레나 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D170" s="3" t="inlineStr">
+      <c r="D210" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 엘레나 선택
@@ -6114,32 +7434,32 @@
 4. 빙결 지속 시간 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E170" s="3" t="inlineStr">
+      <c r="E210" s="3" t="inlineStr">
         <is>
           <t>겨울여왕의 영지(P) 빙결 지속 시간: 1.1초
 (변경 전: 1초)</t>
         </is>
       </c>
-      <c r="F170" s="3" t="inlineStr"/>
-    </row>
-    <row r="171" ht="60" customHeight="1">
-      <c r="A171" s="2" t="inlineStr">
+      <c r="F210" s="3" t="inlineStr"/>
+    </row>
+    <row r="211" ht="60" customHeight="1">
+      <c r="A211" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-016</t>
         </is>
       </c>
-      <c r="B171" s="3" t="inlineStr">
+      <c r="B211" s="3" t="inlineStr">
         <is>
           <t>[실험체] 엘레나 - 더블 악셀(W) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C171" s="3" t="inlineStr">
+      <c r="C211" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 엘레나 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D171" s="3" t="inlineStr">
+      <c r="D211" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 엘레나 선택
@@ -6147,32 +7467,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E171" s="3" t="inlineStr">
+      <c r="E211" s="3" t="inlineStr">
         <is>
           <t>더블 악셀(W) 피해량: 50/70/90/110/130(+스킬 증폭의 50%)(+추가 체력의 10%)
 (변경 전: 50/70/90/110/130(+스킬 증폭의 50%)(+추가 체력의 8%))</t>
         </is>
       </c>
-      <c r="F171" s="3" t="inlineStr"/>
-    </row>
-    <row r="172" ht="60" customHeight="1">
-      <c r="A172" s="2" t="inlineStr">
+      <c r="F211" s="3" t="inlineStr"/>
+    </row>
+    <row r="212" ht="60" customHeight="1">
+      <c r="A212" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-017</t>
         </is>
       </c>
-      <c r="B172" s="3" t="inlineStr">
+      <c r="B212" s="3" t="inlineStr">
         <is>
           <t>[실험체] 유스티나 - 부스트 대쉬(E) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C172" s="3" t="inlineStr">
+      <c r="C212" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 유스티나 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D172" s="3" t="inlineStr">
+      <c r="D212" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 유스티나 선택
@@ -6180,32 +7500,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E172" s="3" t="inlineStr">
+      <c r="E212" s="3" t="inlineStr">
         <is>
           <t>부스트 대쉬(E) 피해량: 50/75/100/125/150(+스킬 증폭의 30%)
 (변경 전: 40/60/80/100/120(+스킬 증폭의 30%))</t>
         </is>
       </c>
-      <c r="F172" s="3" t="inlineStr"/>
-    </row>
-    <row r="173" ht="60" customHeight="1">
-      <c r="A173" s="2" t="inlineStr">
+      <c r="F212" s="3" t="inlineStr"/>
+    </row>
+    <row r="213" ht="60" customHeight="1">
+      <c r="A213" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-018</t>
         </is>
       </c>
-      <c r="B173" s="3" t="inlineStr">
+      <c r="B213" s="3" t="inlineStr">
         <is>
           <t>[실험체] 이바 - 위상의 소용돌이(W)  수치 확인</t>
         </is>
       </c>
-      <c r="C173" s="3" t="inlineStr">
+      <c r="C213" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 이바 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D173" s="3" t="inlineStr">
+      <c r="D213" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 이바 선택
@@ -6213,32 +7533,32 @@
 4.  수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E173" s="3" t="inlineStr">
+      <c r="E213" s="3" t="inlineStr">
         <is>
           <t>위상의 소용돌이(W) : 40/70/100/130/160(+스킬 증폭의 40%)
 (변경 전: 1타 피해량 40/70/100/130/160(+스킬 증폭의 45%))</t>
         </is>
       </c>
-      <c r="F173" s="3" t="inlineStr"/>
-    </row>
-    <row r="174" ht="60" customHeight="1">
-      <c r="A174" s="2" t="inlineStr">
+      <c r="F213" s="3" t="inlineStr"/>
+    </row>
+    <row r="214" ht="60" customHeight="1">
+      <c r="A214" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-019</t>
         </is>
       </c>
-      <c r="B174" s="3" t="inlineStr">
+      <c r="B214" s="3" t="inlineStr">
         <is>
           <t>[실험체] 일레븐 - 다 덤벼보라구!(R) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C174" s="3" t="inlineStr">
+      <c r="C214" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 일레븐 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D174" s="3" t="inlineStr">
+      <c r="D214" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 일레븐 선택
@@ -6246,32 +7566,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E174" s="3" t="inlineStr">
+      <c r="E214" s="3" t="inlineStr">
         <is>
           <t>다 덤벼보라구!(R) 피해량: 10/15/20(+공격력의 3%)(+추가 체력의 3%)
 (변경 전: 6/9/12(+공격력의 3%)(+추가 체력의 3%))</t>
         </is>
       </c>
-      <c r="F174" s="3" t="inlineStr"/>
-    </row>
-    <row r="175" ht="60" customHeight="1">
-      <c r="A175" s="2" t="inlineStr">
+      <c r="F214" s="3" t="inlineStr"/>
+    </row>
+    <row r="215" ht="60" customHeight="1">
+      <c r="A215" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-020</t>
         </is>
       </c>
-      <c r="B175" s="3" t="inlineStr">
+      <c r="B215" s="3" t="inlineStr">
         <is>
           <t>[실험체] 제니 - 레드 카펫(W) 쿨다운 수치 확인</t>
         </is>
       </c>
-      <c r="C175" s="3" t="inlineStr">
+      <c r="C215" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 제니 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D175" s="3" t="inlineStr">
+      <c r="D215" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 제니 선택
@@ -6279,32 +7599,32 @@
 4. 쿨다운 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E175" s="3" t="inlineStr">
+      <c r="E215" s="3" t="inlineStr">
         <is>
           <t>레드 카펫(W) 쿨다운: 15초
 (변경 전: 16초)</t>
         </is>
       </c>
-      <c r="F175" s="3" t="inlineStr"/>
-    </row>
-    <row r="176" ht="60" customHeight="1">
-      <c r="A176" s="2" t="inlineStr">
+      <c r="F215" s="3" t="inlineStr"/>
+    </row>
+    <row r="216" ht="60" customHeight="1">
+      <c r="A216" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-021</t>
         </is>
       </c>
-      <c r="B176" s="3" t="inlineStr">
+      <c r="B216" s="3" t="inlineStr">
         <is>
           <t>[실험체] 제니 - 시상식의 여왕(R) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C176" s="3" t="inlineStr">
+      <c r="C216" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 제니 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D176" s="3" t="inlineStr">
+      <c r="D216" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 제니 선택
@@ -6312,32 +7632,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E176" s="3" t="inlineStr">
+      <c r="E216" s="3" t="inlineStr">
         <is>
           <t>시상식의 여왕(R) 피해량: 150/240/330(+스킬 증폭의 70%)
 (변경 전: 100/200/300(+스킬 증폭의 70%))</t>
         </is>
       </c>
-      <c r="F176" s="3" t="inlineStr"/>
-    </row>
-    <row r="177" ht="60" customHeight="1">
-      <c r="A177" s="2" t="inlineStr">
+      <c r="F216" s="3" t="inlineStr"/>
+    </row>
+    <row r="217" ht="60" customHeight="1">
+      <c r="A217" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-022</t>
         </is>
       </c>
-      <c r="B177" s="3" t="inlineStr">
+      <c r="B217" s="3" t="inlineStr">
         <is>
           <t>[실험체] 캐시 - 수쳐(E) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C177" s="3" t="inlineStr">
+      <c r="C217" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 캐시 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D177" s="3" t="inlineStr">
+      <c r="D217" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 캐시 선택
@@ -6345,32 +7665,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E177" s="3" t="inlineStr">
+      <c r="E217" s="3" t="inlineStr">
         <is>
           <t>수쳐(E) 피해량: 50/60/70/80/90(+스킬 증폭의 45%)
 (변경 전: 50/60/70/80/90(+스킬 증폭의 40%))</t>
         </is>
       </c>
-      <c r="F177" s="3" t="inlineStr"/>
-    </row>
-    <row r="178" ht="60" customHeight="1">
-      <c r="A178" s="2" t="inlineStr">
+      <c r="F217" s="3" t="inlineStr"/>
+    </row>
+    <row r="218" ht="60" customHeight="1">
+      <c r="A218" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-023</t>
         </is>
       </c>
-      <c r="B178" s="3" t="inlineStr">
+      <c r="B218" s="3" t="inlineStr">
         <is>
           <t>[실험체] 케네스 - 업화(W) 받는 피해 감소 수치 확인</t>
         </is>
       </c>
-      <c r="C178" s="3" t="inlineStr">
+      <c r="C218" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 케네스 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D178" s="3" t="inlineStr">
+      <c r="D218" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 케네스 선택
@@ -6378,32 +7698,32 @@
 4. 받는 피해 감소 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E178" s="3" t="inlineStr">
+      <c r="E218" s="3" t="inlineStr">
         <is>
           <t>업화(W) 받는 피해 감소: 2(+공격력의 3/3.25/3.5/3.75/4%)%
 (변경 전: 4(+공격력의 3/3.25/3.5/3.75/4%)%)</t>
         </is>
       </c>
-      <c r="F178" s="3" t="inlineStr"/>
-    </row>
-    <row r="179" ht="60" customHeight="1">
-      <c r="A179" s="2" t="inlineStr">
+      <c r="F218" s="3" t="inlineStr"/>
+    </row>
+    <row r="219" ht="60" customHeight="1">
+      <c r="A219" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-024</t>
         </is>
       </c>
-      <c r="B179" s="3" t="inlineStr">
+      <c r="B219" s="3" t="inlineStr">
         <is>
           <t>[실험체] 타지아 - 스틸레토(Q) 스파다 폭발 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C179" s="3" t="inlineStr">
+      <c r="C219" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 타지아 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D179" s="3" t="inlineStr">
+      <c r="D219" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 타지아 선택
@@ -6411,32 +7731,32 @@
 4. 스파다 폭발 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E179" s="3" t="inlineStr">
+      <c r="E219" s="3" t="inlineStr">
         <is>
           <t>스틸레토(Q) 스파다 폭발 피해량: 40/70/100/130/160(+스킬 증폭의 55%)
 (변경 전: 40/70/100/130/160(+스킬 증폭의 50%))</t>
         </is>
       </c>
-      <c r="F179" s="3" t="inlineStr"/>
-    </row>
-    <row r="180" ht="60" customHeight="1">
-      <c r="A180" s="2" t="inlineStr">
+      <c r="F219" s="3" t="inlineStr"/>
+    </row>
+    <row r="220" ht="60" customHeight="1">
+      <c r="A220" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-025</t>
         </is>
       </c>
-      <c r="B180" s="3" t="inlineStr">
+      <c r="B220" s="3" t="inlineStr">
         <is>
           <t>[실험체] 프리야 - 개화의 선율(Q) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C180" s="3" t="inlineStr">
+      <c r="C220" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 프리야 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D180" s="3" t="inlineStr">
+      <c r="D220" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 프리야 선택
@@ -6444,32 +7764,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E180" s="3" t="inlineStr">
+      <c r="E220" s="3" t="inlineStr">
         <is>
           <t>개화의 선율(Q) 피해량: 60/90/120/150/180(+스킬 증폭의 70%)
 (변경 전: 80/110/140/170/200(+스킬 증폭의 70%))</t>
         </is>
       </c>
-      <c r="F180" s="3" t="inlineStr"/>
-    </row>
-    <row r="181" ht="60" customHeight="1">
-      <c r="A181" s="2" t="inlineStr">
+      <c r="F220" s="3" t="inlineStr"/>
+    </row>
+    <row r="221" ht="60" customHeight="1">
+      <c r="A221" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-026</t>
         </is>
       </c>
-      <c r="B181" s="3" t="inlineStr">
+      <c r="B221" s="3" t="inlineStr">
         <is>
           <t>[실험체] 프리야 - 대지의 메아리(R) 쿨다운 수치 확인</t>
         </is>
       </c>
-      <c r="C181" s="3" t="inlineStr">
+      <c r="C221" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 프리야 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D181" s="3" t="inlineStr">
+      <c r="D221" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 프리야 선택
@@ -6477,32 +7797,32 @@
 4. 쿨다운 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E181" s="3" t="inlineStr">
+      <c r="E221" s="3" t="inlineStr">
         <is>
           <t>대지의 메아리(R) 쿨다운: 80/75/70초
 (변경 전: 80/70/60초)</t>
         </is>
       </c>
-      <c r="F181" s="3" t="inlineStr"/>
-    </row>
-    <row r="182" ht="60" customHeight="1">
-      <c r="A182" s="2" t="inlineStr">
+      <c r="F221" s="3" t="inlineStr"/>
+    </row>
+    <row r="222" ht="60" customHeight="1">
+      <c r="A222" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-027</t>
         </is>
       </c>
-      <c r="B182" s="3" t="inlineStr">
+      <c r="B222" s="3" t="inlineStr">
         <is>
           <t>[실험체] 피올로 - 사슬 묶기(E) 최대 충전까지 걸리는 시간 수치 확인</t>
         </is>
       </c>
-      <c r="C182" s="3" t="inlineStr">
+      <c r="C222" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 피올로 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D182" s="3" t="inlineStr">
+      <c r="D222" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 피올로 선택
@@ -6510,32 +7830,32 @@
 4. 최대 충전까지 걸리는 시간 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E182" s="3" t="inlineStr">
+      <c r="E222" s="3" t="inlineStr">
         <is>
           <t>사슬 묶기(E) 최대 충전까지 걸리는 시간: 1.2초
 (변경 전: 1.5초)</t>
         </is>
       </c>
-      <c r="F182" s="3" t="inlineStr"/>
-    </row>
-    <row r="183" ht="60" customHeight="1">
-      <c r="A183" s="2" t="inlineStr">
+      <c r="F222" s="3" t="inlineStr"/>
+    </row>
+    <row r="223" ht="60" customHeight="1">
+      <c r="A223" s="2" t="inlineStr">
         <is>
           <t>TC-10.5-028</t>
         </is>
       </c>
-      <c r="B183" s="3" t="inlineStr">
+      <c r="B223" s="3" t="inlineStr">
         <is>
           <t>[실험체] 헤이즈 - 웨폰 케이스(P) 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C183" s="3" t="inlineStr">
+      <c r="C223" s="3" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 헤이즈 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D183" s="3" t="inlineStr">
+      <c r="D223" s="3" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 헤이즈 선택
@@ -6543,32 +7863,32 @@
 4. 피해량 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E183" s="3" t="inlineStr">
+      <c r="E223" s="3" t="inlineStr">
         <is>
           <t>웨폰 케이스(P) 피해량: 60/90/120(+스킬 증폭의 60%)
 (변경 전: 60/90/120(+스킬 증폭의 55%))</t>
         </is>
       </c>
-      <c r="F183" s="3" t="inlineStr"/>
-    </row>
-    <row r="184" ht="60" customHeight="1">
-      <c r="A184" s="4" t="inlineStr">
+      <c r="F223" s="3" t="inlineStr"/>
+    </row>
+    <row r="224" ht="60" customHeight="1">
+      <c r="A224" s="4" t="inlineStr">
         <is>
           <t>TC-10.5-029</t>
         </is>
       </c>
-      <c r="B184" s="5" t="inlineStr">
+      <c r="B224" s="5" t="inlineStr">
         <is>
           <t>[실험체] 가넷 - 기본 체력 수치 확인</t>
         </is>
       </c>
-      <c r="C184" s="5" t="inlineStr">
+      <c r="C224" s="5" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 가넷 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D184" s="5" t="inlineStr">
+      <c r="D224" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 가넷 선택
@@ -6576,32 +7896,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E184" s="5" t="inlineStr">
+      <c r="E224" s="5" t="inlineStr">
         <is>
           <t>기본 체력: 1000
 (변경 전: 950)</t>
         </is>
       </c>
-      <c r="F184" s="5" t="inlineStr"/>
-    </row>
-    <row r="185" ht="60" customHeight="1">
-      <c r="A185" s="4" t="inlineStr">
+      <c r="F224" s="5" t="inlineStr"/>
+    </row>
+    <row r="225" ht="60" customHeight="1">
+      <c r="A225" s="4" t="inlineStr">
         <is>
           <t>TC-10.5-030</t>
         </is>
       </c>
-      <c r="B185" s="5" t="inlineStr">
+      <c r="B225" s="5" t="inlineStr">
         <is>
           <t>[실험체] 로지 - 기본 방어력 수치 확인</t>
         </is>
       </c>
-      <c r="C185" s="5" t="inlineStr">
+      <c r="C225" s="5" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 로지 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D185" s="5" t="inlineStr">
+      <c r="D225" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 로지 선택
@@ -6609,32 +7929,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E185" s="5" t="inlineStr">
+      <c r="E225" s="5" t="inlineStr">
         <is>
           <t>기본 방어력: 50
 (변경 전: 53)</t>
         </is>
       </c>
-      <c r="F185" s="5" t="inlineStr"/>
-    </row>
-    <row r="186" ht="60" customHeight="1">
-      <c r="A186" s="4" t="inlineStr">
+      <c r="F225" s="5" t="inlineStr"/>
+    </row>
+    <row r="226" ht="60" customHeight="1">
+      <c r="A226" s="4" t="inlineStr">
         <is>
           <t>TC-10.5-031</t>
         </is>
       </c>
-      <c r="B186" s="5" t="inlineStr">
+      <c r="B226" s="5" t="inlineStr">
         <is>
           <t>[실험체] 마커스 - 도끼 무기 숙련도 레벨 당 기본 공격 증폭 수치 확인</t>
         </is>
       </c>
-      <c r="C186" s="5" t="inlineStr">
+      <c r="C226" s="5" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 마커스 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D186" s="5" t="inlineStr">
+      <c r="D226" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 마커스 선택
@@ -6642,32 +7962,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E186" s="5" t="inlineStr">
+      <c r="E226" s="5" t="inlineStr">
         <is>
           <t>도끼 무기 숙련도 레벨 당 기본 공격 증폭: 1.9%
 (변경 전: 1.8%)</t>
         </is>
       </c>
-      <c r="F186" s="5" t="inlineStr"/>
-    </row>
-    <row r="187" ht="60" customHeight="1">
-      <c r="A187" s="4" t="inlineStr">
+      <c r="F226" s="5" t="inlineStr"/>
+    </row>
+    <row r="227" ht="60" customHeight="1">
+      <c r="A227" s="4" t="inlineStr">
         <is>
           <t>TC-10.5-032</t>
         </is>
       </c>
-      <c r="B187" s="5" t="inlineStr">
+      <c r="B227" s="5" t="inlineStr">
         <is>
           <t>[실험체] 마커스 - 받는 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C187" s="5" t="inlineStr">
+      <c r="C227" s="5" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 마커스 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D187" s="5" t="inlineStr">
+      <c r="D227" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 마커스 선택
@@ -6675,32 +7995,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E187" s="5" t="inlineStr">
+      <c r="E227" s="5" t="inlineStr">
         <is>
           <t>받는 피해량: 100%
 (변경 전: 102%)</t>
         </is>
       </c>
-      <c r="F187" s="5" t="inlineStr"/>
-    </row>
-    <row r="188" ht="60" customHeight="1">
-      <c r="A188" s="4" t="inlineStr">
+      <c r="F227" s="5" t="inlineStr"/>
+    </row>
+    <row r="228" ht="60" customHeight="1">
+      <c r="A228" s="4" t="inlineStr">
         <is>
           <t>TC-10.5-033</t>
         </is>
       </c>
-      <c r="B188" s="5" t="inlineStr">
+      <c r="B228" s="5" t="inlineStr">
         <is>
           <t>[실험체] 매그너스 - 받는 피해량 수치 확인</t>
         </is>
       </c>
-      <c r="C188" s="5" t="inlineStr">
+      <c r="C228" s="5" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 매그너스 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D188" s="5" t="inlineStr">
+      <c r="D228" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 매그너스 선택
@@ -6708,32 +8028,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E188" s="5" t="inlineStr">
+      <c r="E228" s="5" t="inlineStr">
         <is>
           <t>받는 피해량: 100%
 (변경 전: 102%)</t>
         </is>
       </c>
-      <c r="F188" s="5" t="inlineStr"/>
-    </row>
-    <row r="189" ht="60" customHeight="1">
-      <c r="A189" s="4" t="inlineStr">
+      <c r="F228" s="5" t="inlineStr"/>
+    </row>
+    <row r="229" ht="60" customHeight="1">
+      <c r="A229" s="4" t="inlineStr">
         <is>
           <t>TC-10.5-034</t>
         </is>
       </c>
-      <c r="B189" s="5" t="inlineStr">
+      <c r="B229" s="5" t="inlineStr">
         <is>
           <t>[실험체] 아델라 - 레이피어 무기 숙련도 레벨 당 스킬 증폭 수치 확인</t>
         </is>
       </c>
-      <c r="C189" s="5" t="inlineStr">
+      <c r="C229" s="5" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 아델라 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D189" s="5" t="inlineStr">
+      <c r="D229" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 아델라 선택
@@ -6741,32 +8061,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E189" s="5" t="inlineStr">
+      <c r="E229" s="5" t="inlineStr">
         <is>
           <t>레이피어 무기 숙련도 레벨 당 스킬 증폭: 4.6%
 (변경 전: 4.7%)</t>
         </is>
       </c>
-      <c r="F189" s="5" t="inlineStr"/>
-    </row>
-    <row r="190" ht="60" customHeight="1">
-      <c r="A190" s="4" t="inlineStr">
+      <c r="F229" s="5" t="inlineStr"/>
+    </row>
+    <row r="230" ht="60" customHeight="1">
+      <c r="A230" s="4" t="inlineStr">
         <is>
           <t>TC-10.5-035</t>
         </is>
       </c>
-      <c r="B190" s="5" t="inlineStr">
+      <c r="B230" s="5" t="inlineStr">
         <is>
           <t>[실험체] 윌리엄 - 투척 무기 숙련도 레벨 당 기본 공격 증폭 수치 확인</t>
         </is>
       </c>
-      <c r="C190" s="5" t="inlineStr">
+      <c r="C230" s="5" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 윌리엄 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D190" s="5" t="inlineStr">
+      <c r="D230" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 윌리엄 선택
@@ -6774,32 +8094,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E190" s="5" t="inlineStr">
+      <c r="E230" s="5" t="inlineStr">
         <is>
           <t>투척 무기 숙련도 레벨 당 기본 공격 증폭: 1.4%
 (변경 전: 1.5%)</t>
         </is>
       </c>
-      <c r="F190" s="5" t="inlineStr"/>
-    </row>
-    <row r="191" ht="60" customHeight="1">
-      <c r="A191" s="4" t="inlineStr">
+      <c r="F230" s="5" t="inlineStr"/>
+    </row>
+    <row r="231" ht="60" customHeight="1">
+      <c r="A231" s="4" t="inlineStr">
         <is>
           <t>TC-10.5-036</t>
         </is>
       </c>
-      <c r="B191" s="5" t="inlineStr">
+      <c r="B231" s="5" t="inlineStr">
         <is>
           <t>[실험체] 이안 - 기본 공격력 수치 확인</t>
         </is>
       </c>
-      <c r="C191" s="5" t="inlineStr">
+      <c r="C231" s="5" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 이안 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D191" s="5" t="inlineStr">
+      <c r="D231" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 이안 선택
@@ -6807,32 +8127,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E191" s="5" t="inlineStr">
+      <c r="E231" s="5" t="inlineStr">
         <is>
           <t>기본 공격력: 38
 (변경 전: 40)</t>
         </is>
       </c>
-      <c r="F191" s="5" t="inlineStr"/>
-    </row>
-    <row r="192" ht="60" customHeight="1">
-      <c r="A192" s="4" t="inlineStr">
+      <c r="F231" s="5" t="inlineStr"/>
+    </row>
+    <row r="232" ht="60" customHeight="1">
+      <c r="A232" s="4" t="inlineStr">
         <is>
           <t>TC-10.5-037</t>
         </is>
       </c>
-      <c r="B192" s="5" t="inlineStr">
+      <c r="B232" s="5" t="inlineStr">
         <is>
           <t>[실험체] 일레븐 - 주는 회복 효과 수치 확인</t>
         </is>
       </c>
-      <c r="C192" s="5" t="inlineStr">
+      <c r="C232" s="5" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 일레븐 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D192" s="5" t="inlineStr">
+      <c r="D232" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 일레븐 선택
@@ -6840,32 +8160,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E192" s="5" t="inlineStr">
+      <c r="E232" s="5" t="inlineStr">
         <is>
           <t>주는 회복 효과: 100%
 (변경 전: 80%)</t>
         </is>
       </c>
-      <c r="F192" s="5" t="inlineStr"/>
-    </row>
-    <row r="193" ht="60" customHeight="1">
-      <c r="A193" s="4" t="inlineStr">
+      <c r="F232" s="5" t="inlineStr"/>
+    </row>
+    <row r="233" ht="60" customHeight="1">
+      <c r="A233" s="4" t="inlineStr">
         <is>
           <t>TC-10.5-038</t>
         </is>
       </c>
-      <c r="B193" s="5" t="inlineStr">
+      <c r="B233" s="5" t="inlineStr">
         <is>
           <t>[실험체] 카밀로 - 기본 공격력 수치 확인</t>
         </is>
       </c>
-      <c r="C193" s="5" t="inlineStr">
+      <c r="C233" s="5" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 카밀로 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D193" s="5" t="inlineStr">
+      <c r="D233" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 카밀로 선택
@@ -6873,32 +8193,32 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E193" s="5" t="inlineStr">
+      <c r="E233" s="5" t="inlineStr">
         <is>
           <t>기본 공격력: 31
 (변경 전: 34)</t>
         </is>
       </c>
-      <c r="F193" s="5" t="inlineStr"/>
-    </row>
-    <row r="194" ht="60" customHeight="1">
-      <c r="A194" s="4" t="inlineStr">
+      <c r="F233" s="5" t="inlineStr"/>
+    </row>
+    <row r="234" ht="60" customHeight="1">
+      <c r="A234" s="4" t="inlineStr">
         <is>
           <t>TC-10.5-039</t>
         </is>
       </c>
-      <c r="B194" s="5" t="inlineStr">
+      <c r="B234" s="5" t="inlineStr">
         <is>
           <t>[실험체] 피오라 - 레이피어 무기 숙련도 레벨 당 스킬 증폭 수치 확인</t>
         </is>
       </c>
-      <c r="C194" s="5" t="inlineStr">
+      <c r="C234" s="5" t="inlineStr">
         <is>
           <t>· 10.5 패치 적용 완료
 · 피오라 실험체 선택 가능 상태</t>
         </is>
       </c>
-      <c r="D194" s="5" t="inlineStr">
+      <c r="D234" s="5" t="inlineStr">
         <is>
           <t>1. 게임 클라이언트 실행 및 패치 버전 확인
 2. 훈련 모드 진입 후 피오라 선택
@@ -6906,13 +8226,13 @@
 4. 수치가 패치 내용과 일치하는지 검증</t>
         </is>
       </c>
-      <c r="E194" s="5" t="inlineStr">
+      <c r="E234" s="5" t="inlineStr">
         <is>
           <t>레이피어 무기 숙련도 레벨 당 스킬 증폭: 4.3%
 (변경 전: 4.5%)</t>
         </is>
       </c>
-      <c r="F194" s="5" t="inlineStr"/>
+      <c r="F234" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
